--- a/data/prod_parameters/PigHerd.xlsx
+++ b/data/prod_parameters/PigHerd.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\modelX\data\prod_parameters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\data\prod_parameters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="164">
   <si>
     <t>parameter</t>
   </si>
@@ -520,9 +520,6 @@
   </si>
   <si>
     <t>dif org/conv?</t>
-  </si>
-  <si>
-    <t>% of DM</t>
   </si>
   <si>
     <t>Fallback</t>
@@ -538,7 +535,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -648,6 +645,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -871,7 +875,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1124,6 +1128,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7457,7 +7463,16 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E48" s="13"/>
+      <c r="D48" s="100" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="101">
+        <v>0</v>
+      </c>
+      <c r="F48" s="100"/>
+      <c r="G48" s="100" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
@@ -7563,17 +7578,15 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D57" s="87" t="s">
+      <c r="D57" s="100" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="87">
+      <c r="E57" s="100">
         <v>0</v>
       </c>
-      <c r="F57" s="87" t="s">
+      <c r="F57" s="100"/>
+      <c r="G57" s="100" t="s">
         <v>163</v>
-      </c>
-      <c r="G57" s="87" t="s">
-        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/data/prod_parameters/PigHerd.xlsx
+++ b/data/prod_parameters/PigHerd.xlsx
@@ -13,10 +13,11 @@
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
-    <sheet name="Kontroll" sheetId="2" r:id="rId2"/>
-    <sheet name="Slaktstat" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId4"/>
-    <sheet name="Energi rek" sheetId="5" r:id="rId5"/>
+    <sheet name="feed rations" sheetId="8" r:id="rId2"/>
+    <sheet name="Kontroll" sheetId="2" r:id="rId3"/>
+    <sheet name="Slaktstat" sheetId="3" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
+    <sheet name="Energi rek" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913" iterate="1"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="253">
   <si>
     <t>parameter</t>
   </si>
@@ -121,18 +122,6 @@
   </si>
   <si>
     <t>Zira et al 2020</t>
-  </si>
-  <si>
-    <t>Zira et al 2027</t>
-  </si>
-  <si>
-    <t>Zira et al 2028</t>
-  </si>
-  <si>
-    <t>Zira et al 2029</t>
-  </si>
-  <si>
-    <t>Zira et al 2030</t>
   </si>
   <si>
     <t>nr</t>
@@ -507,9 +496,6 @@
     <t>gestation_period</t>
   </si>
   <si>
-    <t>RISE LCA</t>
-  </si>
-  <si>
     <t>Tabell 3: 420 MJ / (31.5kg@delivery - 10kg@weaning)</t>
   </si>
   <si>
@@ -523,6 +509,292 @@
   </si>
   <si>
     <t>Fallback</t>
+  </si>
+  <si>
+    <t>Landquist et al. 2020. Uppdaterad och utökad livscykelanalys av svensk grisproduktion</t>
+  </si>
+  <si>
+    <t>barley</t>
+  </si>
+  <si>
+    <t>oats</t>
+  </si>
+  <si>
+    <t>triticale</t>
+  </si>
+  <si>
+    <t>rapeseed</t>
+  </si>
+  <si>
+    <t>linseed</t>
+  </si>
+  <si>
+    <t>maize</t>
+  </si>
+  <si>
+    <t>Fodersammansättning till sugga, smågris och slaktgris</t>
+  </si>
+  <si>
+    <t>Råvara</t>
+  </si>
+  <si>
+    <t>Kg råvara per djurslag</t>
+  </si>
+  <si>
+    <t>Per årssugga inkl. rekrytering</t>
+  </si>
+  <si>
+    <t>Per smågris</t>
+  </si>
+  <si>
+    <t>Per slaktgris</t>
+  </si>
+  <si>
+    <t>Premix</t>
+  </si>
+  <si>
+    <t>Vete</t>
+  </si>
+  <si>
+    <t>Korn</t>
+  </si>
+  <si>
+    <t>Havre</t>
+  </si>
+  <si>
+    <t>Rågvete</t>
+  </si>
+  <si>
+    <t>Betmelass</t>
+  </si>
+  <si>
+    <t>Betfiber</t>
+  </si>
+  <si>
+    <t>Palmkärnexpeller</t>
+  </si>
+  <si>
+    <t>Rapsfrö</t>
+  </si>
+  <si>
+    <t>Linfrö</t>
+  </si>
+  <si>
+    <t>Majs</t>
+  </si>
+  <si>
+    <t>Vetekli</t>
+  </si>
+  <si>
+    <t>Vetefodermjöl</t>
+  </si>
+  <si>
+    <t>Havremjöl</t>
+  </si>
+  <si>
+    <t>Maltgroddar</t>
+  </si>
+  <si>
+    <t>Solrosmjöl</t>
+  </si>
+  <si>
+    <t>Ärtor</t>
+  </si>
+  <si>
+    <t>Åkerböna</t>
+  </si>
+  <si>
+    <t>Sojamjöl</t>
+  </si>
+  <si>
+    <t>Rapsmjöl</t>
+  </si>
+  <si>
+    <t>Drank, torr</t>
+  </si>
+  <si>
+    <t>Vasslepulver</t>
+  </si>
+  <si>
+    <t>Sojaprotein koncentrat</t>
+  </si>
+  <si>
+    <t>Potatisprotein</t>
+  </si>
+  <si>
+    <t>Fiskmjöl</t>
+  </si>
+  <si>
+    <t>Olja / Fett</t>
+  </si>
+  <si>
+    <t>Vatten</t>
+  </si>
+  <si>
+    <t>Drank, blöt</t>
+  </si>
+  <si>
+    <t>Vassle</t>
+  </si>
+  <si>
+    <t>Fodernjölk</t>
+  </si>
+  <si>
+    <t>Biprodukt etanolindustri</t>
+  </si>
+  <si>
+    <t>Biprodukt mejeriindustri</t>
+  </si>
+  <si>
+    <t>Biprodukt
+spannmålsförädling</t>
+  </si>
+  <si>
+    <t>Bioprodukt
+potatisindustri</t>
+  </si>
+  <si>
+    <t>Biprodukt
+bryggeriindustri</t>
+  </si>
+  <si>
+    <t>Biprodukt bageri- o
+pastaindustri</t>
+  </si>
+  <si>
+    <t>Summa kg blött foder</t>
+  </si>
+  <si>
+    <t>%DM</t>
+  </si>
+  <si>
+    <t>feed</t>
+  </si>
+  <si>
+    <t>sugar beet molasses</t>
+  </si>
+  <si>
+    <t>sugar beet pulp</t>
+  </si>
+  <si>
+    <t>palm kernel expeller</t>
+  </si>
+  <si>
+    <t>wheat bran</t>
+  </si>
+  <si>
+    <t>siktat vetekli</t>
+  </si>
+  <si>
+    <t>wheat bran, fine</t>
+  </si>
+  <si>
+    <t>antar havre</t>
+  </si>
+  <si>
+    <t>sunflower seed meal</t>
+  </si>
+  <si>
+    <t>peas</t>
+  </si>
+  <si>
+    <t>broad beans</t>
+  </si>
+  <si>
+    <t>soybean meal</t>
+  </si>
+  <si>
+    <t>rapeseed meal</t>
+  </si>
+  <si>
+    <t>soybean protein concentrate</t>
+  </si>
+  <si>
+    <t>potatoe protein</t>
+  </si>
+  <si>
+    <t>fish meal</t>
+  </si>
+  <si>
+    <t>wheat distillers grain, dry</t>
+  </si>
+  <si>
+    <t>wheat distillers grain, wet</t>
+  </si>
+  <si>
+    <t>whey</t>
+  </si>
+  <si>
+    <t>Summa exkl. vatten</t>
+  </si>
+  <si>
+    <t>vad är dessa?</t>
+  </si>
+  <si>
+    <t>barley brewers grain</t>
+  </si>
+  <si>
+    <t>potatoe pulp</t>
+  </si>
+  <si>
+    <t>Sojamjöl, 45% Rp i vara</t>
+  </si>
+  <si>
+    <t>Sojaprotein-Hamlet 310</t>
+  </si>
+  <si>
+    <t>http://www2.freefarm.se/fodertabell/fodtab.pl?djur=gris</t>
+  </si>
+  <si>
+    <t>Palmkärnkaka</t>
+  </si>
+  <si>
+    <t>Agrodrank10</t>
+  </si>
+  <si>
+    <t>Agrodrank90</t>
+  </si>
+  <si>
+    <t>NEv</t>
+  </si>
+  <si>
+    <t>NEs</t>
+  </si>
+  <si>
+    <t>Betfiber, omelasserad</t>
+  </si>
+  <si>
+    <t>Vasslepulver, söt vassle</t>
+  </si>
+  <si>
+    <t>Potatisproteinkoncentrat</t>
+  </si>
+  <si>
+    <t>Potato protein concentrate is a byproduct of potato starch production</t>
+  </si>
+  <si>
+    <t>sows, gilts</t>
+  </si>
+  <si>
+    <t>growing, finishing</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>whey powder</t>
+  </si>
+  <si>
+    <t>Sows, gilts and boars</t>
+  </si>
+  <si>
+    <t>Piglets</t>
+  </si>
+  <si>
+    <t>Grpwing and finishing pigs</t>
+  </si>
+  <si>
+    <t>see feed rations sheet</t>
   </si>
 </sst>
 </file>
@@ -535,7 +807,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,8 +928,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -679,6 +959,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -871,11 +1163,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1092,6 +1385,8 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1128,10 +1423,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -1178,6 +1480,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1307,6 +1610,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1340,6 +1644,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1393,6 +1698,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1522,6 +1828,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1555,6 +1862,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1608,6 +1916,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1830,6 +2139,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1863,6 +2173,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -1876,6 +2187,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1920,6 +2232,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -2142,6 +2455,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -2175,6 +2489,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -2188,6 +2503,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -2232,6 +2548,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -2361,6 +2678,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -2394,6 +2712,7 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -2432,6 +2751,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2828,6 +3148,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3194,6 +3515,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6694,11 +7016,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.7109375" customWidth="1"/>
     <col min="8" max="8" width="31.42578125" bestFit="1" customWidth="1"/>
@@ -6706,13 +7029,13 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B1" t="s">
         <v>21</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -6732,7 +7055,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -6754,10 +7077,10 @@
         <v>2.2340000000000004</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -6772,10 +7095,10 @@
         <v>2.0397391304347829</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -6790,10 +7113,10 @@
         <v>14.580000000000002</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6808,10 +7131,10 @@
         <v>12.383013698630139</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -6826,10 +7149,10 @@
         <v>1.26</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -6844,10 +7167,10 @@
         <v>1.0701369863013699</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -6855,13 +7178,13 @@
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E9" s="3">
         <v>354</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H9" t="s">
         <v>30</v>
@@ -6872,13 +7195,13 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E10" s="3">
         <v>367</v>
       </c>
       <c r="F10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H10" t="s">
         <v>30</v>
@@ -6889,7 +7212,7 @@
         <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E11">
         <v>50</v>
@@ -6909,7 +7232,7 @@
         <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E12">
         <v>40</v>
@@ -6926,24 +7249,24 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E13" s="13">
         <v>115</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E14">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
         <v>17</v>
@@ -6954,7 +7277,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -6966,48 +7289,48 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E17">
         <v>1.5</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D18" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E19">
         <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="H19" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -7015,17 +7338,17 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E20" s="13">
         <f>E45/0.75</f>
         <v>240.64979221760481</v>
       </c>
       <c r="F20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" t="s">
         <v>81</v>
-      </c>
-      <c r="G20" t="s">
-        <v>85</v>
       </c>
       <c r="H20" s="15"/>
     </row>
@@ -7034,39 +7357,39 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E21" s="13">
         <f t="shared" ref="E21:E22" si="0">E46/0.75</f>
         <v>205.63847429519072</v>
       </c>
       <c r="F21" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" t="s">
         <v>81</v>
-      </c>
-      <c r="G21" t="s">
-        <v>85</v>
       </c>
       <c r="H21" s="15"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E22" s="13">
         <f t="shared" si="0"/>
         <v>122.41258802745277</v>
       </c>
       <c r="F22" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" t="s">
         <v>81</v>
-      </c>
-      <c r="G22" t="s">
-        <v>85</v>
       </c>
       <c r="H22" s="15"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -7081,13 +7404,13 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E24">
         <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H24" t="s">
         <v>30</v>
@@ -7098,13 +7421,13 @@
         <v>28</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E25">
         <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H25" t="s">
         <v>30</v>
@@ -7115,13 +7438,13 @@
         <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E26">
         <v>42</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H26" t="s">
         <v>30</v>
@@ -7132,13 +7455,13 @@
         <v>28</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E27">
         <v>38.5</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H27" t="s">
         <v>30</v>
@@ -7149,13 +7472,13 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E28">
         <v>37</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H28" t="s">
         <v>30</v>
@@ -7166,13 +7489,13 @@
         <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E29">
         <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H29" t="s">
         <v>30</v>
@@ -7183,13 +7506,13 @@
         <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E30">
         <v>67</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H30" t="s">
         <v>30</v>
@@ -7200,13 +7523,13 @@
         <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E31">
         <v>68</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H31" t="s">
         <v>30</v>
@@ -7215,7 +7538,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -7240,7 +7563,7 @@
         <v>23</v>
       </c>
       <c r="H34" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N34" s="62"/>
     </row>
@@ -7259,7 +7582,7 @@
         <v>23</v>
       </c>
       <c r="H35" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -7277,7 +7600,7 @@
         <v>23</v>
       </c>
       <c r="H36" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M36" s="13"/>
     </row>
@@ -7296,7 +7619,7 @@
         <v>23</v>
       </c>
       <c r="H37" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -7336,7 +7659,7 @@
         <v>23</v>
       </c>
       <c r="H39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -7356,7 +7679,7 @@
         <v>23</v>
       </c>
       <c r="H40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -7376,7 +7699,7 @@
         <v>23</v>
       </c>
       <c r="H41" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -7396,12 +7719,12 @@
         <v>23</v>
       </c>
       <c r="H42" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -7416,16 +7739,16 @@
         <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E45" s="13">
         <v>180.4873441632036</v>
       </c>
       <c r="F45" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -7433,16 +7756,16 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E46" s="13">
         <v>154.22885572139305</v>
       </c>
       <c r="F46" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -7450,33 +7773,33 @@
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E47" s="13">
         <v>91.809441020589574</v>
       </c>
       <c r="F47" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D48" s="100" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="101">
+      <c r="D48" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="E48" s="89">
         <v>0</v>
       </c>
-      <c r="F48" s="100"/>
-      <c r="G48" s="100" t="s">
-        <v>163</v>
+      <c r="F48" s="88"/>
+      <c r="G48" s="88" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -7491,19 +7814,19 @@
         <v>15</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E50" s="3">
         <v>19.5</v>
       </c>
       <c r="F50" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G50" t="s">
+        <v>154</v>
+      </c>
+      <c r="H50" t="s">
         <v>159</v>
-      </c>
-      <c r="H50" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -7511,20 +7834,20 @@
         <v>24</v>
       </c>
       <c r="D51" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E51" s="3">
         <f>AVERAGE(26.4,25.7,25.4,25.8,25.3)</f>
         <v>25.72</v>
       </c>
       <c r="F51" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G51" s="87" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H51" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -7532,20 +7855,20 @@
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E52" s="3">
         <f>AVERAGE(26.4,25.7,25.4,25.8,25.3)</f>
         <v>25.72</v>
       </c>
       <c r="F52" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G52" s="87" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="H52" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -7553,40 +7876,1170 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
+      <c r="G54" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C55" t="s">
-        <v>74</v>
-      </c>
-      <c r="D55" t="s">
-        <v>75</v>
-      </c>
-      <c r="E55">
-        <v>100</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="D55" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="88">
+        <v>0</v>
+      </c>
+      <c r="F55" s="88"/>
+      <c r="G55" s="88" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="106" t="s">
+        <v>249</v>
+      </c>
+      <c r="B56" s="106"/>
+      <c r="C56" s="106"/>
+      <c r="D56" s="107"/>
+      <c r="E56" s="107"/>
+      <c r="F56" s="107"/>
+      <c r="G56" s="107"/>
+      <c r="H56" s="106"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C57" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57">
+        <v>40.178411304260166</v>
+      </c>
+      <c r="F57" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D57" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="E57" s="100">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C58" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58">
+        <v>33.789919707775212</v>
+      </c>
+      <c r="F58" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C59" t="s">
+        <v>161</v>
+      </c>
+      <c r="D59" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59">
+        <v>4.9058647496700978</v>
+      </c>
+      <c r="F59" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C60" t="s">
+        <v>162</v>
+      </c>
+      <c r="D60" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60">
+        <v>0.45022176500136973</v>
+      </c>
+      <c r="F60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C61" t="s">
+        <v>165</v>
+      </c>
+      <c r="D61" t="s">
+        <v>71</v>
+      </c>
+      <c r="E61">
+        <v>0.22511088250068487</v>
+      </c>
+      <c r="F61" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C62" t="s">
+        <v>219</v>
+      </c>
+      <c r="D62" t="s">
+        <v>71</v>
+      </c>
+      <c r="E62">
+        <v>0.79953175508863938</v>
+      </c>
+      <c r="F62" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C63" t="s">
+        <v>220</v>
+      </c>
+      <c r="D63" t="s">
+        <v>71</v>
+      </c>
+      <c r="E63">
+        <v>0.10091177491410011</v>
+      </c>
+      <c r="F63" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C64" t="s">
+        <v>163</v>
+      </c>
+      <c r="D64" t="s">
+        <v>71</v>
+      </c>
+      <c r="E64">
+        <v>0.35296815345727672</v>
+      </c>
+      <c r="F64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C65" t="s">
+        <v>164</v>
+      </c>
+      <c r="D65" t="s">
+        <v>71</v>
+      </c>
+      <c r="E65">
+        <v>0.12990941138366913</v>
+      </c>
+      <c r="F65" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C66" t="s">
+        <v>221</v>
+      </c>
+      <c r="D66" t="s">
+        <v>71</v>
+      </c>
+      <c r="E66">
+        <v>6.9565776007980151</v>
+      </c>
+      <c r="F66" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C67" t="s">
+        <v>222</v>
+      </c>
+      <c r="D67" t="s">
+        <v>71</v>
+      </c>
+      <c r="E67">
+        <v>3.2319427256529165</v>
+      </c>
+      <c r="F67" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C68" t="s">
+        <v>218</v>
+      </c>
+      <c r="D68" t="s">
+        <v>71</v>
+      </c>
+      <c r="E68">
+        <v>0.44165630930574318</v>
+      </c>
+      <c r="F68" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C69" t="s">
+        <v>213</v>
+      </c>
+      <c r="D69" t="s">
+        <v>71</v>
+      </c>
+      <c r="E69">
+        <v>0.12990941138366913</v>
+      </c>
+      <c r="F69" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C70" t="s">
+        <v>214</v>
+      </c>
+      <c r="D70" t="s">
+        <v>71</v>
+      </c>
+      <c r="E70">
+        <v>3.0972152454404571</v>
+      </c>
+      <c r="F70" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C71" t="s">
+        <v>216</v>
+      </c>
+      <c r="D71" t="s">
+        <v>71</v>
+      </c>
+      <c r="E71">
+        <v>2.331945313134324</v>
+      </c>
+      <c r="F71" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C72" t="s">
+        <v>226</v>
+      </c>
+      <c r="D72" t="s">
+        <v>71</v>
+      </c>
+      <c r="E72">
+        <v>0.13651195014904788</v>
+      </c>
+      <c r="F72" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C73" t="s">
+        <v>227</v>
+      </c>
+      <c r="D73" t="s">
+        <v>71</v>
+      </c>
+      <c r="E73">
+        <v>0.59280091293481973</v>
+      </c>
+      <c r="F73" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C74" t="s">
+        <v>211</v>
+      </c>
+      <c r="D74" t="s">
+        <v>71</v>
+      </c>
+      <c r="E74">
+        <v>0.35261125946995903</v>
+      </c>
+      <c r="F74" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C75" t="s">
+        <v>212</v>
+      </c>
+      <c r="D75" t="s">
+        <v>71</v>
+      </c>
+      <c r="E75">
+        <v>0.69085753595037758</v>
+      </c>
+      <c r="F75" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>228</v>
+      </c>
+      <c r="D76" t="s">
+        <v>71</v>
+      </c>
+      <c r="E76">
+        <v>0.92453387414668897</v>
+      </c>
+      <c r="F76" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C77" t="s">
+        <v>225</v>
+      </c>
+      <c r="D77" t="s">
+        <v>71</v>
+      </c>
+      <c r="E77">
+        <v>0.18058835758279279</v>
+      </c>
+      <c r="F77" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="106" t="s">
+        <v>250</v>
+      </c>
+      <c r="B78" s="106"/>
+      <c r="C78" s="106"/>
+      <c r="D78" s="107"/>
+      <c r="E78" s="107"/>
+      <c r="F78" s="107"/>
+      <c r="G78" s="107"/>
+      <c r="H78" s="106"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B79" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="E79" s="88">
         <v>0</v>
       </c>
-      <c r="F57" s="100"/>
-      <c r="G57" s="100" t="s">
-        <v>163</v>
+      <c r="F79" s="88"/>
+      <c r="G79" s="88" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" t="s">
+        <v>70</v>
+      </c>
+      <c r="D80" t="s">
+        <v>71</v>
+      </c>
+      <c r="E80">
+        <v>38.250221304219536</v>
+      </c>
+      <c r="F80" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" t="s">
+        <v>160</v>
+      </c>
+      <c r="D81" t="s">
+        <v>71</v>
+      </c>
+      <c r="E81">
+        <v>34.656240778990849</v>
+      </c>
+      <c r="F81" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" t="s">
+        <v>161</v>
+      </c>
+      <c r="D82" t="s">
+        <v>71</v>
+      </c>
+      <c r="E82">
+        <v>6.9312481557981709</v>
+      </c>
+      <c r="F82" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" t="s">
+        <v>165</v>
+      </c>
+      <c r="D83" t="s">
+        <v>71</v>
+      </c>
+      <c r="E83">
+        <v>1.7969902626143404</v>
+      </c>
+      <c r="F83" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" t="s">
+        <v>219</v>
+      </c>
+      <c r="D84" t="s">
+        <v>71</v>
+      </c>
+      <c r="E84">
+        <v>0.2567128946591915</v>
+      </c>
+      <c r="F84" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" t="s">
+        <v>220</v>
+      </c>
+      <c r="D85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E85">
+        <v>0.77013868397757457</v>
+      </c>
+      <c r="F85" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D86" t="s">
+        <v>71</v>
+      </c>
+      <c r="E86">
+        <v>7.270581292416642</v>
+      </c>
+      <c r="F86" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" t="s">
+        <v>223</v>
+      </c>
+      <c r="D87" t="s">
+        <v>71</v>
+      </c>
+      <c r="E87">
+        <v>2.3104160519327235</v>
+      </c>
+      <c r="F87" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" t="s">
+        <v>216</v>
+      </c>
+      <c r="D88" t="s">
+        <v>71</v>
+      </c>
+      <c r="E88">
+        <v>1.2983180879315432</v>
+      </c>
+      <c r="F88" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" t="s">
+        <v>228</v>
+      </c>
+      <c r="D89" t="s">
+        <v>71</v>
+      </c>
+      <c r="E89">
+        <v>1.557981705517852</v>
+      </c>
+      <c r="F89" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" t="s">
+        <v>248</v>
+      </c>
+      <c r="D90" t="s">
+        <v>71</v>
+      </c>
+      <c r="E90">
+        <v>0.28622012393036295</v>
+      </c>
+      <c r="F90" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" t="s">
+        <v>224</v>
+      </c>
+      <c r="D91" t="s">
+        <v>71</v>
+      </c>
+      <c r="E91">
+        <v>1.3573325464738861</v>
+      </c>
+      <c r="F91" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" t="s">
+        <v>225</v>
+      </c>
+      <c r="D92" t="s">
+        <v>71</v>
+      </c>
+      <c r="E92">
+        <v>3.2575981115373271</v>
+      </c>
+      <c r="F92" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="106" t="s">
+        <v>251</v>
+      </c>
+      <c r="B93" s="106"/>
+      <c r="C93" s="106"/>
+      <c r="D93" s="107"/>
+      <c r="E93" s="107"/>
+      <c r="F93" s="107"/>
+      <c r="G93" s="107"/>
+      <c r="H93" s="106"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B94" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="D94" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="E94" s="88">
+        <v>0</v>
+      </c>
+      <c r="F94" s="88"/>
+      <c r="G94" s="88" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" t="s">
+        <v>70</v>
+      </c>
+      <c r="D95" t="s">
+        <v>71</v>
+      </c>
+      <c r="E95">
+        <v>32.548570057825053</v>
+      </c>
+      <c r="F95" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" t="s">
+        <v>160</v>
+      </c>
+      <c r="D96" t="s">
+        <v>71</v>
+      </c>
+      <c r="E96">
+        <v>25.003402152928501</v>
+      </c>
+      <c r="F96" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" t="s">
+        <v>161</v>
+      </c>
+      <c r="D97" t="s">
+        <v>71</v>
+      </c>
+      <c r="E97">
+        <v>4.2140565426283985</v>
+      </c>
+      <c r="F97" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" t="s">
+        <v>162</v>
+      </c>
+      <c r="D98" t="s">
+        <v>71</v>
+      </c>
+      <c r="E98">
+        <v>3.9331194397865055</v>
+      </c>
+      <c r="F98" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" t="s">
+        <v>165</v>
+      </c>
+      <c r="D99" t="s">
+        <v>71</v>
+      </c>
+      <c r="E99">
+        <v>8.0267743669112365E-2</v>
+      </c>
+      <c r="F99" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" t="s">
+        <v>219</v>
+      </c>
+      <c r="D100" t="s">
+        <v>71</v>
+      </c>
+      <c r="E100">
+        <v>0.48160646201467416</v>
+      </c>
+      <c r="F100" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" t="s">
+        <v>220</v>
+      </c>
+      <c r="D101" t="s">
+        <v>71</v>
+      </c>
+      <c r="E101">
+        <v>8.1471759824149039</v>
+      </c>
+      <c r="F101" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" t="s">
+        <v>221</v>
+      </c>
+      <c r="D102" t="s">
+        <v>71</v>
+      </c>
+      <c r="E102">
+        <v>2.9228530108476773</v>
+      </c>
+      <c r="F102" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" t="s">
+        <v>222</v>
+      </c>
+      <c r="D103" t="s">
+        <v>71</v>
+      </c>
+      <c r="E103">
+        <v>3.5719145932754999</v>
+      </c>
+      <c r="F103" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" t="s">
+        <v>218</v>
+      </c>
+      <c r="D104" t="s">
+        <v>71</v>
+      </c>
+      <c r="E104">
+        <v>0.16607119379816351</v>
+      </c>
+      <c r="F104" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" t="s">
+        <v>214</v>
+      </c>
+      <c r="D105" t="s">
+        <v>71</v>
+      </c>
+      <c r="E105">
+        <v>8.5083808289259082</v>
+      </c>
+      <c r="F105" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" t="s">
+        <v>216</v>
+      </c>
+      <c r="D106" t="s">
+        <v>71</v>
+      </c>
+      <c r="E106">
+        <v>0.89309397553679037</v>
+      </c>
+      <c r="F106" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" t="s">
+        <v>226</v>
+      </c>
+      <c r="D107" t="s">
+        <v>71</v>
+      </c>
+      <c r="E107">
+        <v>0.16607119379816351</v>
+      </c>
+      <c r="F107" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s">
+        <v>227</v>
+      </c>
+      <c r="D108" t="s">
+        <v>71</v>
+      </c>
+      <c r="E108">
+        <v>6.0994259011092158</v>
+      </c>
+      <c r="F108" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" t="s">
+        <v>211</v>
+      </c>
+      <c r="D109" t="s">
+        <v>71</v>
+      </c>
+      <c r="E109">
+        <v>0.10517842273883686</v>
+      </c>
+      <c r="F109" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" t="s">
+        <v>228</v>
+      </c>
+      <c r="D110" t="s">
+        <v>71</v>
+      </c>
+      <c r="E110">
+        <v>3.1588124987025679</v>
+      </c>
+      <c r="F110" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B111" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="D111" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="E111" s="88">
+        <v>0</v>
+      </c>
+      <c r="F111" s="88"/>
+      <c r="G111" s="88" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>25</v>
+      </c>
+      <c r="C112" t="s">
+        <v>70</v>
+      </c>
+      <c r="D112" t="s">
+        <v>71</v>
+      </c>
+      <c r="E112">
+        <v>32.548570057825053</v>
+      </c>
+      <c r="F112" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>25</v>
+      </c>
+      <c r="C113" t="s">
+        <v>160</v>
+      </c>
+      <c r="D113" t="s">
+        <v>71</v>
+      </c>
+      <c r="E113">
+        <v>25.003402152928501</v>
+      </c>
+      <c r="F113" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>25</v>
+      </c>
+      <c r="C114" t="s">
+        <v>161</v>
+      </c>
+      <c r="D114" t="s">
+        <v>71</v>
+      </c>
+      <c r="E114">
+        <v>4.2140565426283985</v>
+      </c>
+      <c r="F114" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>25</v>
+      </c>
+      <c r="C115" t="s">
+        <v>162</v>
+      </c>
+      <c r="D115" t="s">
+        <v>71</v>
+      </c>
+      <c r="E115">
+        <v>3.9331194397865055</v>
+      </c>
+      <c r="F115" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" t="s">
+        <v>165</v>
+      </c>
+      <c r="D116" t="s">
+        <v>71</v>
+      </c>
+      <c r="E116">
+        <v>8.0267743669112365E-2</v>
+      </c>
+      <c r="F116" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C117" t="s">
+        <v>219</v>
+      </c>
+      <c r="D117" t="s">
+        <v>71</v>
+      </c>
+      <c r="E117">
+        <v>0.48160646201467416</v>
+      </c>
+      <c r="F117" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>25</v>
+      </c>
+      <c r="C118" t="s">
+        <v>220</v>
+      </c>
+      <c r="D118" t="s">
+        <v>71</v>
+      </c>
+      <c r="E118">
+        <v>8.1471759824149039</v>
+      </c>
+      <c r="F118" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>25</v>
+      </c>
+      <c r="C119" t="s">
+        <v>221</v>
+      </c>
+      <c r="D119" t="s">
+        <v>71</v>
+      </c>
+      <c r="E119">
+        <v>2.9228530108476773</v>
+      </c>
+      <c r="F119" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>25</v>
+      </c>
+      <c r="C120" t="s">
+        <v>222</v>
+      </c>
+      <c r="D120" t="s">
+        <v>71</v>
+      </c>
+      <c r="E120">
+        <v>3.5719145932754999</v>
+      </c>
+      <c r="F120" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>25</v>
+      </c>
+      <c r="C121" t="s">
+        <v>218</v>
+      </c>
+      <c r="D121" t="s">
+        <v>71</v>
+      </c>
+      <c r="E121">
+        <v>0.16607119379816351</v>
+      </c>
+      <c r="F121" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>25</v>
+      </c>
+      <c r="C122" t="s">
+        <v>214</v>
+      </c>
+      <c r="D122" t="s">
+        <v>71</v>
+      </c>
+      <c r="E122">
+        <v>8.5083808289259082</v>
+      </c>
+      <c r="F122" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>25</v>
+      </c>
+      <c r="C123" t="s">
+        <v>216</v>
+      </c>
+      <c r="D123" t="s">
+        <v>71</v>
+      </c>
+      <c r="E123">
+        <v>0.89309397553679037</v>
+      </c>
+      <c r="F123" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>25</v>
+      </c>
+      <c r="C124" t="s">
+        <v>226</v>
+      </c>
+      <c r="D124" t="s">
+        <v>71</v>
+      </c>
+      <c r="E124">
+        <v>0.16607119379816351</v>
+      </c>
+      <c r="F124" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>25</v>
+      </c>
+      <c r="C125" t="s">
+        <v>227</v>
+      </c>
+      <c r="D125" t="s">
+        <v>71</v>
+      </c>
+      <c r="E125">
+        <v>6.0994259011092158</v>
+      </c>
+      <c r="F125" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>25</v>
+      </c>
+      <c r="C126" t="s">
+        <v>211</v>
+      </c>
+      <c r="D126" t="s">
+        <v>71</v>
+      </c>
+      <c r="E126">
+        <v>0.10517842273883686</v>
+      </c>
+      <c r="F126" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>25</v>
+      </c>
+      <c r="C127" t="s">
+        <v>228</v>
+      </c>
+      <c r="D127" t="s">
+        <v>71</v>
+      </c>
+      <c r="E127">
+        <v>3.1588124987025679</v>
+      </c>
+      <c r="F127" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -7595,6 +9048,1889 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B5:Z45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" customWidth="1"/>
+    <col min="11" max="11" width="27.7109375" customWidth="1"/>
+    <col min="12" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="17" width="12.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="3:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="102" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C6" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="3:22" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="4"/>
+      <c r="D7" s="103" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103" t="s">
+        <v>170</v>
+      </c>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103" t="s">
+        <v>171</v>
+      </c>
+      <c r="I7" s="103"/>
+      <c r="K7" s="103" t="s">
+        <v>210</v>
+      </c>
+      <c r="L7" s="103" t="s">
+        <v>245</v>
+      </c>
+      <c r="M7" s="103" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="103" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="103" t="s">
+        <v>23</v>
+      </c>
+      <c r="P7" s="103" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q7" s="103" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" s="103" t="s">
+        <v>209</v>
+      </c>
+      <c r="S7" s="103" t="s">
+        <v>239</v>
+      </c>
+      <c r="T7" s="103" t="s">
+        <v>240</v>
+      </c>
+      <c r="U7" s="103"/>
+      <c r="V7" s="104" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C8" s="105" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8">
+        <v>517.6</v>
+      </c>
+      <c r="E8" s="5">
+        <f>D8/D$45</f>
+        <v>0.31776045183866414</v>
+      </c>
+      <c r="F8">
+        <v>14.9</v>
+      </c>
+      <c r="G8" s="5">
+        <f>F8/F$45</f>
+        <v>0.27090909090909093</v>
+      </c>
+      <c r="H8">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="I8" s="5">
+        <f>H8/H$45</f>
+        <v>0.15836750634641669</v>
+      </c>
+      <c r="K8" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" s="13">
+        <f>(D8)*($R8/100)</f>
+        <v>450.31200000000001</v>
+      </c>
+      <c r="M8" s="13">
+        <f>L8/L$32*100</f>
+        <v>40.178411304260166</v>
+      </c>
+      <c r="N8" s="13">
+        <f>(F8)*($R8/100)</f>
+        <v>12.963000000000001</v>
+      </c>
+      <c r="O8" s="13">
+        <f>N8/N$32*100</f>
+        <v>38.250221304219536</v>
+      </c>
+      <c r="P8" s="13">
+        <f>(H8)*($R8/100)</f>
+        <v>70.556999999999988</v>
+      </c>
+      <c r="Q8" s="13">
+        <f>P8/P$32*100</f>
+        <v>32.548570057825053</v>
+      </c>
+      <c r="R8">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C9" s="105" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9">
+        <v>435.3</v>
+      </c>
+      <c r="E9" s="5">
+        <f>D9/D$45</f>
+        <v>0.267235557738351</v>
+      </c>
+      <c r="F9">
+        <v>13.5</v>
+      </c>
+      <c r="G9" s="5">
+        <f>F9/F$45</f>
+        <v>0.24545454545454545</v>
+      </c>
+      <c r="H9">
+        <v>62.3</v>
+      </c>
+      <c r="I9" s="5">
+        <f>H9/H$45</f>
+        <v>0.12165592657684045</v>
+      </c>
+      <c r="K9" t="s">
+        <v>160</v>
+      </c>
+      <c r="L9" s="13">
+        <f>(D9)*($R9/100)</f>
+        <v>378.71100000000001</v>
+      </c>
+      <c r="M9" s="13">
+        <f t="shared" ref="M9:O31" si="0">L9/L$32*100</f>
+        <v>33.789919707775212</v>
+      </c>
+      <c r="N9" s="13">
+        <f>(F9)*($R9/100)</f>
+        <v>11.744999999999999</v>
+      </c>
+      <c r="O9" s="13">
+        <f t="shared" si="0"/>
+        <v>34.656240778990849</v>
+      </c>
+      <c r="P9" s="13">
+        <f>(H9)*($R9/100)</f>
+        <v>54.201000000000001</v>
+      </c>
+      <c r="Q9" s="13">
+        <f t="shared" ref="Q9" si="1">P9/P$32*100</f>
+        <v>25.003402152928501</v>
+      </c>
+      <c r="R9">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C10" s="105" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10">
+        <v>63.2</v>
+      </c>
+      <c r="E10" s="5">
+        <f>D10/D$45</f>
+        <v>3.8799189637178461E-2</v>
+      </c>
+      <c r="F10">
+        <v>2.7</v>
+      </c>
+      <c r="G10" s="5">
+        <f>F10/F$45</f>
+        <v>4.9090909090909095E-2</v>
+      </c>
+      <c r="H10">
+        <v>10.5</v>
+      </c>
+      <c r="I10" s="5">
+        <f>H10/H$45</f>
+        <v>2.0503807850029289E-2</v>
+      </c>
+      <c r="K10" t="s">
+        <v>161</v>
+      </c>
+      <c r="L10" s="13">
+        <f>(D10)*($R10/100)</f>
+        <v>54.984000000000002</v>
+      </c>
+      <c r="M10" s="3">
+        <f t="shared" si="0"/>
+        <v>4.9058647496700978</v>
+      </c>
+      <c r="N10" s="13">
+        <f>(F10)*($R10/100)</f>
+        <v>2.3490000000000002</v>
+      </c>
+      <c r="O10" s="3">
+        <f t="shared" si="0"/>
+        <v>6.9312481557981709</v>
+      </c>
+      <c r="P10" s="13">
+        <f>(H10)*($R10/100)</f>
+        <v>9.1349999999999998</v>
+      </c>
+      <c r="Q10" s="3">
+        <f t="shared" ref="Q10" si="2">P10/P$32*100</f>
+        <v>4.2140565426283985</v>
+      </c>
+      <c r="R10">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C11" s="105" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11">
+        <v>5.8</v>
+      </c>
+      <c r="E11" s="5">
+        <f>D11/D$45</f>
+        <v>3.5606851249309346E-3</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <f>F11/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I11" s="5">
+        <f>H11/H$45</f>
+        <v>1.9136887326694007E-2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>162</v>
+      </c>
+      <c r="L11" s="13">
+        <f>(D11)*($R11/100)</f>
+        <v>5.0460000000000003</v>
+      </c>
+      <c r="M11" s="3">
+        <f t="shared" si="0"/>
+        <v>0.45022176500136973</v>
+      </c>
+      <c r="N11" s="13">
+        <f>(F11)*($R11/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P11" s="13">
+        <f>(H11)*($R11/100)</f>
+        <v>8.5259999999999998</v>
+      </c>
+      <c r="Q11" s="3">
+        <f t="shared" ref="Q11" si="3">P11/P$32*100</f>
+        <v>3.9331194397865055</v>
+      </c>
+      <c r="R11">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C12" s="105" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12">
+        <v>2.9</v>
+      </c>
+      <c r="E12" s="5">
+        <f>D12/D$45</f>
+        <v>1.7803425624654673E-3</v>
+      </c>
+      <c r="F12">
+        <v>0.7</v>
+      </c>
+      <c r="G12" s="5">
+        <f>F12/F$45</f>
+        <v>1.2727272727272726E-2</v>
+      </c>
+      <c r="H12">
+        <v>0.2</v>
+      </c>
+      <c r="I12" s="5">
+        <f>H12/H$45</f>
+        <v>3.905487209529389E-4</v>
+      </c>
+      <c r="K12" t="s">
+        <v>165</v>
+      </c>
+      <c r="L12" s="13">
+        <f>(D12)*($R12/100)</f>
+        <v>2.5230000000000001</v>
+      </c>
+      <c r="M12" s="3">
+        <f t="shared" si="0"/>
+        <v>0.22511088250068487</v>
+      </c>
+      <c r="N12" s="13">
+        <f>(F12)*($R12/100)</f>
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="O12" s="3">
+        <f t="shared" si="0"/>
+        <v>1.7969902626143404</v>
+      </c>
+      <c r="P12" s="13">
+        <f>(H12)*($R12/100)</f>
+        <v>0.17400000000000002</v>
+      </c>
+      <c r="Q12" s="3">
+        <f t="shared" ref="Q12" si="4">P12/P$32*100</f>
+        <v>8.0267743669112365E-2</v>
+      </c>
+      <c r="R12">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C13" s="105" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13">
+        <v>10.3</v>
+      </c>
+      <c r="E13" s="5">
+        <f>D13/D$45</f>
+        <v>6.3232856528945914E-3</v>
+      </c>
+      <c r="F13">
+        <v>0.1</v>
+      </c>
+      <c r="G13" s="5">
+        <f>F13/F$45</f>
+        <v>1.8181818181818182E-3</v>
+      </c>
+      <c r="H13">
+        <v>1.2</v>
+      </c>
+      <c r="I13" s="5">
+        <f>H13/H$45</f>
+        <v>2.3432923257176333E-3</v>
+      </c>
+      <c r="K13" t="s">
+        <v>219</v>
+      </c>
+      <c r="L13" s="13">
+        <f>(D13)*($R13/100)</f>
+        <v>8.9610000000000003</v>
+      </c>
+      <c r="M13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.79953175508863938</v>
+      </c>
+      <c r="N13" s="13">
+        <f>(F13)*($R13/100)</f>
+        <v>8.7000000000000008E-2</v>
+      </c>
+      <c r="O13" s="3">
+        <f t="shared" si="0"/>
+        <v>0.2567128946591915</v>
+      </c>
+      <c r="P13" s="13">
+        <f>(H13)*($R13/100)</f>
+        <v>1.044</v>
+      </c>
+      <c r="Q13" s="3">
+        <f t="shared" ref="Q13" si="5">P13/P$32*100</f>
+        <v>0.48160646201467416</v>
+      </c>
+      <c r="R13">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C14" s="105" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14">
+        <v>1.3</v>
+      </c>
+      <c r="E14" s="5">
+        <f>D14/D$45</f>
+        <v>7.9808459696727846E-4</v>
+      </c>
+      <c r="F14">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="5">
+        <f>F14/F$45</f>
+        <v>5.4545454545454541E-3</v>
+      </c>
+      <c r="H14">
+        <v>20.3</v>
+      </c>
+      <c r="I14" s="5">
+        <f>H14/H$45</f>
+        <v>3.9640695176723299E-2</v>
+      </c>
+      <c r="K14" t="s">
+        <v>220</v>
+      </c>
+      <c r="L14" s="13">
+        <f>(D14)*($R14/100)</f>
+        <v>1.131</v>
+      </c>
+      <c r="M14" s="3">
+        <f t="shared" si="0"/>
+        <v>0.10091177491410011</v>
+      </c>
+      <c r="N14" s="13">
+        <f>(F14)*($R14/100)</f>
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="O14" s="3">
+        <f t="shared" si="0"/>
+        <v>0.77013868397757457</v>
+      </c>
+      <c r="P14" s="13">
+        <f>(H14)*($R14/100)</f>
+        <v>17.661000000000001</v>
+      </c>
+      <c r="Q14" s="3">
+        <f t="shared" ref="Q14" si="6">P14/P$32*100</f>
+        <v>8.1471759824149039</v>
+      </c>
+      <c r="R14">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C15" s="105" t="s">
+        <v>180</v>
+      </c>
+      <c r="D15">
+        <v>4.3</v>
+      </c>
+      <c r="E15" s="5">
+        <f>D15/D$45</f>
+        <v>2.6398182822763828E-3</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <f>F15/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <f>H15/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>163</v>
+      </c>
+      <c r="L15" s="13">
+        <f>(D15)*($R15/100)</f>
+        <v>3.956</v>
+      </c>
+      <c r="M15" s="3">
+        <f t="shared" si="0"/>
+        <v>0.35296815345727672</v>
+      </c>
+      <c r="N15" s="13">
+        <f>(F15)*($R15/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="13">
+        <f>(H15)*($R15/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <f t="shared" ref="Q15" si="7">P15/P$32*100</f>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C16" s="105" t="s">
+        <v>181</v>
+      </c>
+      <c r="D16">
+        <v>1.6</v>
+      </c>
+      <c r="E16" s="5">
+        <f>D16/D$45</f>
+        <v>9.8225796549818905E-4</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <f>F16/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <f>H16/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>164</v>
+      </c>
+      <c r="L16" s="13">
+        <f>(D16)*($R16/100)</f>
+        <v>1.4560000000000002</v>
+      </c>
+      <c r="M16" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12990941138366913</v>
+      </c>
+      <c r="N16" s="13">
+        <f>(F16)*($R16/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="13">
+        <f>(H16)*($R16/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3">
+        <f t="shared" ref="Q16" si="8">P16/P$32*100</f>
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C17" s="105" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17">
+        <v>88.6</v>
+      </c>
+      <c r="E17" s="5">
+        <f>D17/D$45</f>
+        <v>5.4392534839462207E-2</v>
+      </c>
+      <c r="F17">
+        <v>2.8</v>
+      </c>
+      <c r="G17" s="5">
+        <f>F17/F$45</f>
+        <v>5.0909090909090904E-2</v>
+      </c>
+      <c r="H17">
+        <v>7.2</v>
+      </c>
+      <c r="I17" s="5">
+        <f>H17/H$45</f>
+        <v>1.4059753954305799E-2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>221</v>
+      </c>
+      <c r="L17" s="13">
+        <f>(D17)*($R17/100)</f>
+        <v>77.967999999999989</v>
+      </c>
+      <c r="M17" s="3">
+        <f t="shared" si="0"/>
+        <v>6.9565776007980151</v>
+      </c>
+      <c r="N17" s="13">
+        <f>(F17)*($R17/100)</f>
+        <v>2.464</v>
+      </c>
+      <c r="O17" s="3">
+        <f t="shared" si="0"/>
+        <v>7.270581292416642</v>
+      </c>
+      <c r="P17" s="13">
+        <f>(H17)*($R17/100)</f>
+        <v>6.3360000000000003</v>
+      </c>
+      <c r="Q17" s="3">
+        <f t="shared" ref="Q17" si="9">P17/P$32*100</f>
+        <v>2.9228530108476773</v>
+      </c>
+      <c r="R17">
+        <v>88</v>
+      </c>
+      <c r="V17" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C18" s="105" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <f>D18/D$45</f>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0.9</v>
+      </c>
+      <c r="G18" s="5">
+        <f>F18/F$45</f>
+        <v>1.6363636363636365E-2</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <f>H18/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K18" t="s">
+        <v>223</v>
+      </c>
+      <c r="L18" s="13">
+        <f>(D18)*($R18/100)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="13">
+        <f>(F18)*($R18/100)</f>
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="O18" s="3">
+        <f t="shared" si="0"/>
+        <v>2.3104160519327235</v>
+      </c>
+      <c r="P18" s="13">
+        <f>(H18)*($R18/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
+        <f t="shared" ref="Q18" si="10">P18/P$32*100</f>
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>87</v>
+      </c>
+      <c r="V18" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C19" s="105" t="s">
+        <v>191</v>
+      </c>
+      <c r="D19">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="E19" s="5">
+        <f>D19/D$45</f>
+        <v>2.4986186997360181E-2</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5">
+        <f>F19/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I19" s="5">
+        <f>H19/H$45</f>
+        <v>1.698886936145284E-2</v>
+      </c>
+      <c r="K19" t="s">
+        <v>222</v>
+      </c>
+      <c r="L19" s="13">
+        <f>(D19)*($R19/100)</f>
+        <v>36.223000000000006</v>
+      </c>
+      <c r="M19" s="3">
+        <f t="shared" si="0"/>
+        <v>3.2319427256529165</v>
+      </c>
+      <c r="N19" s="13">
+        <f>(F19)*($R19/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="13">
+        <f>(H19)*($R19/100)</f>
+        <v>7.7429999999999994</v>
+      </c>
+      <c r="Q19" s="3">
+        <f t="shared" ref="Q19" si="11">P19/P$32*100</f>
+        <v>3.5719145932754999</v>
+      </c>
+      <c r="R19">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C20" s="105" t="s">
+        <v>187</v>
+      </c>
+      <c r="D20">
+        <v>5.5</v>
+      </c>
+      <c r="E20" s="5">
+        <f>D20/D$45</f>
+        <v>3.3765117564000242E-3</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5">
+        <f>F20/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0.4</v>
+      </c>
+      <c r="I20" s="5">
+        <f>H20/H$45</f>
+        <v>7.810974419058778E-4</v>
+      </c>
+      <c r="K20" t="s">
+        <v>218</v>
+      </c>
+      <c r="L20" s="13">
+        <f>(D20)*($R20/100)</f>
+        <v>4.95</v>
+      </c>
+      <c r="M20" s="3">
+        <f t="shared" si="0"/>
+        <v>0.44165630930574318</v>
+      </c>
+      <c r="N20" s="13">
+        <f>(F20)*($R20/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="13">
+        <f>(H20)*($R20/100)</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="Q20" s="3">
+        <f t="shared" ref="Q20" si="12">P20/P$32*100</f>
+        <v>0.16607119379816351</v>
+      </c>
+      <c r="R20">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C21" s="105" t="s">
+        <v>179</v>
+      </c>
+      <c r="D21">
+        <v>1.6</v>
+      </c>
+      <c r="E21" s="5">
+        <f>D21/D$45</f>
+        <v>9.8225796549818905E-4</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <f>F21/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <f>H21/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K21" t="s">
+        <v>213</v>
+      </c>
+      <c r="L21" s="13">
+        <f>(D21)*($R21/100)</f>
+        <v>1.4560000000000002</v>
+      </c>
+      <c r="M21" s="3">
+        <f t="shared" si="0"/>
+        <v>0.12990941138366913</v>
+      </c>
+      <c r="N21" s="13">
+        <f>(F21)*($R21/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="13">
+        <f>(H21)*($R21/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3">
+        <f t="shared" ref="Q21" si="13">P21/P$32*100</f>
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>91</v>
+      </c>
+      <c r="V21" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C22" s="105" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22">
+        <v>39.9</v>
+      </c>
+      <c r="E22" s="5">
+        <f>D22/D$45</f>
+        <v>2.4495058014611083E-2</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5">
+        <f>F22/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>3.3</v>
+      </c>
+      <c r="I22" s="5">
+        <f>H22/H$45</f>
+        <v>6.444053895723491E-3</v>
+      </c>
+      <c r="K22" t="s">
+        <v>214</v>
+      </c>
+      <c r="L22" s="13">
+        <f>(D22+D39)*($R22/100)</f>
+        <v>34.713000000000001</v>
+      </c>
+      <c r="M22" s="3">
+        <f t="shared" si="0"/>
+        <v>3.0972152454404571</v>
+      </c>
+      <c r="N22" s="13">
+        <f>(F22+F39)*($R22/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="13">
+        <f>(H22+H39)*($R22/100)</f>
+        <v>18.443999999999999</v>
+      </c>
+      <c r="Q22" s="3">
+        <f t="shared" ref="Q22" si="14">P22/P$32*100</f>
+        <v>8.5083808289259082</v>
+      </c>
+      <c r="R22">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>215</v>
+      </c>
+      <c r="C23" s="105" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23">
+        <v>29.7</v>
+      </c>
+      <c r="E23" s="5">
+        <f>D23/D$45</f>
+        <v>1.8233163484560132E-2</v>
+      </c>
+      <c r="F23">
+        <v>0.5</v>
+      </c>
+      <c r="G23" s="5">
+        <f>F23/F$45</f>
+        <v>9.0909090909090905E-3</v>
+      </c>
+      <c r="H23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I23" s="5">
+        <f>H23/H$45</f>
+        <v>4.2960359304823276E-3</v>
+      </c>
+      <c r="K23" t="s">
+        <v>216</v>
+      </c>
+      <c r="L23" s="13">
+        <f>(D23)*($R23/100)</f>
+        <v>26.135999999999999</v>
+      </c>
+      <c r="M23" s="3">
+        <f t="shared" si="0"/>
+        <v>2.331945313134324</v>
+      </c>
+      <c r="N23" s="13">
+        <f>(F23)*($R23/100)</f>
+        <v>0.44</v>
+      </c>
+      <c r="O23" s="3">
+        <f t="shared" si="0"/>
+        <v>1.2983180879315432</v>
+      </c>
+      <c r="P23" s="13">
+        <f>(H23)*($R23/100)</f>
+        <v>1.9360000000000002</v>
+      </c>
+      <c r="Q23" s="3">
+        <f t="shared" ref="Q23" si="15">P23/P$32*100</f>
+        <v>0.89309397553679037</v>
+      </c>
+      <c r="R23">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C24" s="105" t="s">
+        <v>192</v>
+      </c>
+      <c r="D24">
+        <v>1.7</v>
+      </c>
+      <c r="E24" s="5">
+        <f>D24/D$45</f>
+        <v>1.0436490883418256E-3</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5">
+        <f>F24/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0.4</v>
+      </c>
+      <c r="I24" s="5">
+        <f>H24/H$45</f>
+        <v>7.810974419058778E-4</v>
+      </c>
+      <c r="K24" t="s">
+        <v>226</v>
+      </c>
+      <c r="L24" s="13">
+        <f>(D24)*($R24/100)</f>
+        <v>1.53</v>
+      </c>
+      <c r="M24" s="3">
+        <f t="shared" si="0"/>
+        <v>0.13651195014904788</v>
+      </c>
+      <c r="N24" s="13">
+        <f>(F24)*($R24/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="13">
+        <f>(H24)*($R24/100)</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="Q24" s="3">
+        <f t="shared" ref="Q24" si="16">P24/P$32*100</f>
+        <v>0.16607119379816351</v>
+      </c>
+      <c r="R24">
+        <v>90</v>
+      </c>
+      <c r="V24" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C25" s="105" t="s">
+        <v>199</v>
+      </c>
+      <c r="D25">
+        <v>60.4</v>
+      </c>
+      <c r="E25" s="5">
+        <f>D25/D$45</f>
+        <v>3.7080238197556632E-2</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5">
+        <f>F25/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5">
+        <f>H25/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>227</v>
+      </c>
+      <c r="L25" s="13">
+        <f>(D25+D37)*($R25/100)</f>
+        <v>6.6440000000000001</v>
+      </c>
+      <c r="M25" s="3">
+        <f t="shared" si="0"/>
+        <v>0.59280091293481973</v>
+      </c>
+      <c r="N25" s="13">
+        <f>(F25+F37)*($R25/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="13">
+        <f>(H25+H37)*($R25/100)</f>
+        <v>13.222</v>
+      </c>
+      <c r="Q25" s="3">
+        <f t="shared" ref="Q25" si="17">P25/P$32*100</f>
+        <v>6.0994259011092158</v>
+      </c>
+      <c r="R25">
+        <v>11</v>
+      </c>
+      <c r="V25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C26" s="105" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26">
+        <v>5.2</v>
+      </c>
+      <c r="E26" s="5">
+        <f>D26/D$45</f>
+        <v>3.1923383878691139E-3</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5">
+        <f>F26/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0.3</v>
+      </c>
+      <c r="I26" s="5">
+        <f>H26/H$45</f>
+        <v>5.8582308142940832E-4</v>
+      </c>
+      <c r="K26" t="s">
+        <v>211</v>
+      </c>
+      <c r="L26" s="13">
+        <f>(D26)*($R26/100)</f>
+        <v>3.9520000000000004</v>
+      </c>
+      <c r="M26" s="3">
+        <f t="shared" si="0"/>
+        <v>0.35261125946995903</v>
+      </c>
+      <c r="N26" s="13">
+        <f>(F26)*($R26/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="13">
+        <f>(H26)*($R26/100)</f>
+        <v>0.22799999999999998</v>
+      </c>
+      <c r="Q26" s="3">
+        <f t="shared" ref="Q26" si="18">P26/P$32*100</f>
+        <v>0.10517842273883686</v>
+      </c>
+      <c r="R26">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C27" s="105" t="s">
+        <v>178</v>
+      </c>
+      <c r="D27">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E27" s="5">
+        <f>D27/D$45</f>
+        <v>5.3410276873964019E-3</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" s="5">
+        <f>F27/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5">
+        <f>H27/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>212</v>
+      </c>
+      <c r="L27" s="13">
+        <f>(D27)*($R27/100)</f>
+        <v>7.7429999999999994</v>
+      </c>
+      <c r="M27" s="3">
+        <f t="shared" si="0"/>
+        <v>0.69085753595037758</v>
+      </c>
+      <c r="N27" s="13">
+        <f>(F27)*($R27/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="13">
+        <f>(H27)*($R27/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
+        <f t="shared" ref="Q27" si="19">P27/P$32*100</f>
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>89</v>
+      </c>
+      <c r="V27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C28" s="105" t="s">
+        <v>200</v>
+      </c>
+      <c r="D28">
+        <v>188.4</v>
+      </c>
+      <c r="E28" s="5">
+        <f>D28/D$45</f>
+        <v>0.11566087543741174</v>
+      </c>
+      <c r="F28">
+        <v>9.6</v>
+      </c>
+      <c r="G28" s="5">
+        <f>F28/F$45</f>
+        <v>0.17454545454545453</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5">
+        <f>H28/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>228</v>
+      </c>
+      <c r="L28" s="13">
+        <f>(D28+D38)*($R28/100)</f>
+        <v>10.362</v>
+      </c>
+      <c r="M28" s="3">
+        <f t="shared" si="0"/>
+        <v>0.92453387414668897</v>
+      </c>
+      <c r="N28" s="13">
+        <f>(F28+F38)*($R28/100)</f>
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="O28" s="3">
+        <f t="shared" si="0"/>
+        <v>1.557981705517852</v>
+      </c>
+      <c r="P28" s="13">
+        <f>(H28+H38)*($R28/100)</f>
+        <v>6.8475000000000001</v>
+      </c>
+      <c r="Q28" s="3">
+        <f t="shared" ref="Q28" si="20">P28/P$32*100</f>
+        <v>3.1588124987025679</v>
+      </c>
+      <c r="R28">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C29" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5">
+        <f>D29/D$45</f>
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0.1</v>
+      </c>
+      <c r="G29" s="5">
+        <f>F29/F$45</f>
+        <v>1.8181818181818182E-3</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5">
+        <f>H29/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>248</v>
+      </c>
+      <c r="L29" s="13">
+        <f>(D29)*($R29/100)</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N29" s="13">
+        <f>(F29)*($R29/100)</f>
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="O29" s="3">
+        <f t="shared" si="0"/>
+        <v>0.28622012393036295</v>
+      </c>
+      <c r="P29" s="13">
+        <f>(H29)*($R29/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <f t="shared" ref="Q29" si="21">P29/P$32*100</f>
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>97</v>
+      </c>
+      <c r="V29" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C30" s="105" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" s="5">
+        <f>D30/D$45</f>
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0.5</v>
+      </c>
+      <c r="G30" s="5">
+        <f>F30/F$45</f>
+        <v>9.0909090909090905E-3</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5">
+        <f>H30/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>224</v>
+      </c>
+      <c r="L30" s="13">
+        <f>(D30)*($R30/100)</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="13">
+        <f>(F30)*($R30/100)</f>
+        <v>0.46</v>
+      </c>
+      <c r="O30" s="3">
+        <f t="shared" si="0"/>
+        <v>1.3573325464738861</v>
+      </c>
+      <c r="P30" s="13">
+        <f>(H30)*($R30/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <f t="shared" ref="Q30" si="22">P30/P$32*100</f>
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>92</v>
+      </c>
+      <c r="V30" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C31" s="105" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E31" s="5">
+        <f>D31/D$45</f>
+        <v>1.3506047025600098E-3</v>
+      </c>
+      <c r="F31">
+        <v>1.2</v>
+      </c>
+      <c r="G31" s="5">
+        <f>F31/F$45</f>
+        <v>2.1818181818181816E-2</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5">
+        <f>H31/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>225</v>
+      </c>
+      <c r="L31" s="13">
+        <f>(D31)*($R31/100)</f>
+        <v>2.0240000000000005</v>
+      </c>
+      <c r="M31" s="3">
+        <f t="shared" si="0"/>
+        <v>0.18058835758279279</v>
+      </c>
+      <c r="N31" s="13">
+        <f>(F31)*($R31/100)</f>
+        <v>1.1040000000000001</v>
+      </c>
+      <c r="O31" s="3">
+        <f t="shared" si="0"/>
+        <v>3.2575981115373271</v>
+      </c>
+      <c r="P31" s="13">
+        <f>(H31)*($R31/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <f t="shared" ref="Q31" si="23">P31/P$32*100</f>
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E32" s="5">
+        <f>D32/D$45</f>
+        <v>1.4119958254036463E-3</v>
+      </c>
+      <c r="F32">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="5">
+        <f>F32/F$45</f>
+        <v>9.0909090909090905E-3</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5">
+        <f>H32/H$45</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="L32" s="13">
+        <f>SUM(L8:L31)</f>
+        <v>1120.7809999999997</v>
+      </c>
+      <c r="M32" s="13">
+        <f>L32/L$32*100</f>
+        <v>100</v>
+      </c>
+      <c r="N32" s="13">
+        <f>SUM(N8:N31)</f>
+        <v>33.89</v>
+      </c>
+      <c r="O32" s="13">
+        <f>N32/N$32*100</f>
+        <v>100</v>
+      </c>
+      <c r="P32" s="13">
+        <f>SUM(P8:P31)</f>
+        <v>216.77450000000005</v>
+      </c>
+      <c r="Q32" s="13">
+        <f>P32/P$32*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33">
+        <v>62.6</v>
+      </c>
+      <c r="E33" s="5">
+        <f>D33/D$45</f>
+        <v>3.8430842900116641E-2</v>
+      </c>
+      <c r="F33">
+        <v>1.8</v>
+      </c>
+      <c r="G33" s="5">
+        <f>F33/F$45</f>
+        <v>3.272727272727273E-2</v>
+      </c>
+      <c r="H33">
+        <v>11</v>
+      </c>
+      <c r="I33" s="5">
+        <f>H33/H$45</f>
+        <v>2.1480179652411637E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34">
+        <v>5.8</v>
+      </c>
+      <c r="E34" s="5">
+        <f>D34/D$45</f>
+        <v>3.5606851249309346E-3</v>
+      </c>
+      <c r="F34">
+        <v>0.2</v>
+      </c>
+      <c r="G34" s="5">
+        <f>F34/F$45</f>
+        <v>3.6363636363636364E-3</v>
+      </c>
+      <c r="H34">
+        <v>1.4</v>
+      </c>
+      <c r="I34" s="5">
+        <f>H34/H$45</f>
+        <v>2.7338410466705718E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35">
+        <v>43.3</v>
+      </c>
+      <c r="E35" s="5">
+        <f>D35/D$45</f>
+        <v>2.6582356191294735E-2</v>
+      </c>
+      <c r="F35">
+        <v>4.5</v>
+      </c>
+      <c r="G35" s="5">
+        <f>F35/F$45</f>
+        <v>8.1818181818181818E-2</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" s="5">
+        <f>H35/H$45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>217</v>
+      </c>
+      <c r="C36" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5">
+        <f>D36/D$45</f>
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0.2</v>
+      </c>
+      <c r="G36" s="5">
+        <f>F36/F$45</f>
+        <v>3.6363636363636364E-3</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" s="5">
+        <f>H36/H$45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B37" s="87" t="s">
+        <v>230</v>
+      </c>
+      <c r="C37" s="105" t="s">
+        <v>202</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5">
+        <f>D37/D$45</f>
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5">
+        <f>F37/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>120.2</v>
+      </c>
+      <c r="I37" s="5">
+        <f>H37/H$45</f>
+        <v>0.23471978129271626</v>
+      </c>
+      <c r="K37" s="87" t="s">
+        <v>227</v>
+      </c>
+      <c r="L37" s="87"/>
+      <c r="M37" s="87"/>
+      <c r="N37" s="87"/>
+      <c r="O37" s="87"/>
+      <c r="P37" s="87"/>
+      <c r="Q37" s="87"/>
+    </row>
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C38" s="105" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38" s="5">
+        <f>D38/D$45</f>
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38" s="5">
+        <f>F38/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>124.5</v>
+      </c>
+      <c r="I38" s="5">
+        <f>H38/H$45</f>
+        <v>0.24311657879320445</v>
+      </c>
+      <c r="K38" s="87" t="s">
+        <v>228</v>
+      </c>
+      <c r="L38" s="87"/>
+      <c r="M38" s="87"/>
+      <c r="N38" s="87"/>
+      <c r="O38" s="87"/>
+      <c r="P38" s="87"/>
+      <c r="Q38" s="87"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C39" s="105" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5">
+        <f>D39/D$45</f>
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39" s="5">
+        <f>F39/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="I39" s="5">
+        <f>H39/H$45</f>
+        <v>3.4954110525288025E-2</v>
+      </c>
+      <c r="K39" s="87" t="s">
+        <v>214</v>
+      </c>
+      <c r="L39" s="87"/>
+      <c r="M39" s="87"/>
+      <c r="N39" s="87"/>
+      <c r="O39" s="87"/>
+      <c r="P39" s="87"/>
+      <c r="Q39" s="87"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>205</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40" s="5">
+        <f>D40/D$45</f>
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40" s="5">
+        <f>F40/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>15.7</v>
+      </c>
+      <c r="I40" s="5">
+        <f>H40/H$45</f>
+        <v>3.0658074594805698E-2</v>
+      </c>
+      <c r="K40" s="87" t="s">
+        <v>232</v>
+      </c>
+      <c r="L40" s="87"/>
+      <c r="M40" s="87"/>
+      <c r="N40" s="87"/>
+      <c r="O40" s="87"/>
+      <c r="P40" s="87"/>
+      <c r="Q40" s="87"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C41" t="s">
+        <v>206</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5">
+        <f>D41/D$45</f>
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41" s="5">
+        <f>F41/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I41" s="5">
+        <f>H41/H$45</f>
+        <v>1.718414372192931E-2</v>
+      </c>
+      <c r="K41" s="87" t="s">
+        <v>231</v>
+      </c>
+      <c r="L41" s="87"/>
+      <c r="M41" s="87"/>
+      <c r="N41" s="87"/>
+      <c r="O41" s="87"/>
+      <c r="P41" s="87"/>
+      <c r="Q41" s="87"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C42" t="s">
+        <v>207</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42" s="5">
+        <f>D42/D$45</f>
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42" s="5">
+        <f>F42/F$45</f>
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>4.7</v>
+      </c>
+      <c r="I42" s="5">
+        <f>H42/H$45</f>
+        <v>9.1778949423940628E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C43" t="s">
+        <v>198</v>
+      </c>
+      <c r="D43">
+        <v>2746.2</v>
+      </c>
+      <c r="F43">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="H43">
+        <v>330.2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C44" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D44" s="4">
+        <v>4375.1000000000004</v>
+      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4">
+        <v>134.9</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4">
+        <v>842.3</v>
+      </c>
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C45" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D45" s="4">
+        <f>SUM(D8:D42)</f>
+        <v>1628.9</v>
+      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4">
+        <f>SUM(F8:F42)</f>
+        <v>55</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4">
+        <f>SUM(H8:H42)</f>
+        <v>512.1</v>
+      </c>
+      <c r="I45" s="4"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="V7" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:K19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7633,12 +10969,12 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="K4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2">
         <v>33623.920935000002</v>
@@ -7651,7 +10987,7 @@
         <v>14.6</v>
       </c>
       <c r="K5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -7672,7 +11008,7 @@
         <v>1496.8</v>
       </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J6">
         <v>18</v>
@@ -7699,7 +11035,7 @@
         <v>374972.8</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J7">
         <f>J4*J5*(1-J6/100)</f>
@@ -7736,7 +11072,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -7759,7 +11095,7 @@
         <v>1.0402648044956555</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E13" s="3">
         <v>2514.0419999999999</v>
@@ -7790,7 +11126,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E15" s="3">
         <v>20.3</v>
@@ -7798,7 +11134,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D16" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E16" s="3">
         <v>5.68</v>
@@ -7813,7 +11149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:V25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7823,10 +11159,10 @@
   <sheetData>
     <row r="3" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -7834,7 +11170,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -7842,7 +11178,7 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
@@ -7910,7 +11246,7 @@
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -7963,7 +11299,7 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -8016,7 +11352,7 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2">
         <v>16.88</v>
@@ -8083,7 +11419,7 @@
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2">
         <v>11.26</v>
@@ -8150,7 +11486,7 @@
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2">
         <v>57.96</v>
@@ -8217,7 +11553,7 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -8270,7 +11606,7 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -8323,7 +11659,7 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -8376,7 +11712,7 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -8563,7 +11899,7 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C16" s="12">
         <v>1.93</v>
@@ -8630,7 +11966,7 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C17" s="12">
         <v>0.24</v>
@@ -8697,7 +12033,7 @@
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B18" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C18" s="9">
         <v>222</v>
@@ -8764,7 +12100,7 @@
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2">
         <v>0.95</v>
@@ -8831,7 +12167,7 @@
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C20" s="2">
         <v>4.09</v>
@@ -8898,7 +12234,7 @@
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>0.76</v>
@@ -8995,26 +12331,26 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="83" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B3" s="83"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="80" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B4" s="80">
         <v>0.99999493252819649</v>
@@ -9022,7 +12358,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="80" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B5" s="80">
         <v>0.99998986508207222</v>
@@ -9030,7 +12366,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="80" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B6" s="80">
         <v>0.85713127437951109</v>
@@ -9038,7 +12374,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="80" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B7" s="80">
         <v>0.25677629550654923</v>
@@ -9046,7 +12382,7 @@
     </row>
     <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="81" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B8" s="81">
         <v>9</v>
@@ -9054,30 +12390,30 @@
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="82"/>
       <c r="B11" s="82" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" s="82" t="s">
+        <v>131</v>
+      </c>
+      <c r="F11" s="82" t="s">
         <v>132</v>
-      </c>
-      <c r="C11" s="82" t="s">
-        <v>133</v>
-      </c>
-      <c r="D11" s="82" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="82" t="s">
-        <v>135</v>
-      </c>
-      <c r="F11" s="82" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="80" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B12" s="80">
         <v>2</v>
@@ -9097,7 +12433,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="80" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B13" s="80">
         <v>7</v>
@@ -9113,7 +12449,7 @@
     </row>
     <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="81" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B14" s="81">
         <v>9</v>
@@ -9129,33 +12465,33 @@
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="82"/>
       <c r="B16" s="82" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16" s="82" t="s">
+        <v>136</v>
+      </c>
+      <c r="G16" s="82" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="82" t="s">
-        <v>125</v>
-      </c>
-      <c r="D16" s="82" t="s">
+      <c r="H16" s="82" t="s">
         <v>138</v>
       </c>
-      <c r="E16" s="82" t="s">
+      <c r="I16" s="82" t="s">
         <v>139</v>
-      </c>
-      <c r="F16" s="82" t="s">
-        <v>140</v>
-      </c>
-      <c r="G16" s="82" t="s">
-        <v>141</v>
-      </c>
-      <c r="H16" s="82" t="s">
-        <v>142</v>
-      </c>
-      <c r="I16" s="82" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="80" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B17" s="80">
         <v>0</v>
@@ -9184,7 +12520,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="80" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B18" s="80">
         <v>5.4615384615384617</v>
@@ -9213,7 +12549,7 @@
     </row>
     <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="81" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B19" s="81">
         <v>5.7692307692307696E-2</v>
@@ -9242,31 +12578,31 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F23" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="82" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B25" s="82" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="82" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="82" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" s="82" t="s">
         <v>146</v>
       </c>
-      <c r="C25" s="82" t="s">
-        <v>147</v>
-      </c>
-      <c r="D25" s="82" t="s">
-        <v>148</v>
-      </c>
-      <c r="F25" s="82" t="s">
-        <v>150</v>
-      </c>
       <c r="G25" s="82" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -9458,7 +12794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:T60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9470,42 +12806,42 @@
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="25"/>
       <c r="E3" s="25"/>
       <c r="O3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="2:17" ht="30" x14ac:dyDescent="0.25">
       <c r="B4" s="16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E4" s="18"/>
       <c r="O4" s="77" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="P4" s="77" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="Q4" s="77" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
@@ -9708,22 +13044,22 @@
         <v>60</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E15" s="18"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C16" s="24"/>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
       <c r="O16" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="2:20" ht="15.75" x14ac:dyDescent="0.25">
@@ -9732,24 +13068,24 @@
       <c r="D17" s="23"/>
       <c r="E17" s="23"/>
       <c r="O17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="2:20" ht="30" x14ac:dyDescent="0.25">
       <c r="O18" s="79" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P18" s="79" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Q18" s="79" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="R18" s="79" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="S18" s="79" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.25">
@@ -9792,7 +13128,7 @@
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="O21">
         <v>10</v>
@@ -9814,7 +13150,7 @@
     </row>
     <row r="22" spans="2:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B22" s="39" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C22" s="39"/>
       <c r="D22" s="39"/>
@@ -9842,19 +13178,19 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="40"/>
-      <c r="C23" s="94" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" s="96" t="s">
-        <v>90</v>
-      </c>
-      <c r="E23" s="89" t="s">
-        <v>91</v>
-      </c>
-      <c r="F23" s="91" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="93"/>
+      <c r="C23" s="96" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="91" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="93" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="95"/>
       <c r="H23" s="31"/>
       <c r="O23">
         <v>11</v>
@@ -9876,11 +13212,11 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="41"/>
-      <c r="C24" s="95"/>
-      <c r="D24" s="97"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="93"/>
+      <c r="C24" s="97"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="95"/>
       <c r="H24" s="18"/>
       <c r="O24">
         <v>13</v>
@@ -9901,13 +13237,13 @@
       </c>
     </row>
     <row r="25" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="99" t="s">
+      <c r="B25" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
+      <c r="C25" s="101"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="101"/>
       <c r="G25" s="42"/>
       <c r="H25" s="18"/>
       <c r="O25">
@@ -9929,13 +13265,13 @@
       </c>
     </row>
     <row r="26" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="88" t="s">
-        <v>97</v>
-      </c>
-      <c r="C26" s="88"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
+      <c r="B26" s="90" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="90"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="90"/>
       <c r="G26" s="42"/>
       <c r="H26" s="18"/>
       <c r="O26">
@@ -10028,19 +13364,19 @@
       <c r="G29" s="43"/>
       <c r="H29" s="86"/>
       <c r="O29" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P29" s="84" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="Q29" s="84">
         <v>5.46</v>
       </c>
       <c r="R29" s="85" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="S29" s="84" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="T29">
         <v>5.8000000000000003E-2</v>
@@ -10065,7 +13401,7 @@
       <c r="G30" s="43"/>
       <c r="H30" s="86"/>
       <c r="O30" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.25">
@@ -10127,25 +13463,25 @@
       <c r="R33" s="3"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="98" t="s">
+      <c r="B34" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="98"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
       <c r="G34" s="42"/>
       <c r="H34" s="18"/>
       <c r="R34" s="13"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="88" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="88"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="88"/>
+      <c r="B35" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="90"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="90"/>
+      <c r="F35" s="90"/>
       <c r="G35" s="42"/>
       <c r="H35" s="18"/>
     </row>
@@ -10263,14 +13599,14 @@
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B42" s="35" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C42" s="36"/>
       <c r="D42" s="37" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F42" s="36"/>
       <c r="G42" s="43"/>
@@ -10278,7 +13614,7 @@
     </row>
     <row r="43" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="46" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C43" s="45"/>
       <c r="D43" s="45"/>
@@ -10291,17 +13627,17 @@
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="67" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C47" s="67"/>
       <c r="D47" s="67"/>
@@ -10309,13 +13645,13 @@
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B48" s="16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E48" s="18"/>
     </row>
@@ -10381,7 +13717,7 @@
     </row>
     <row r="54" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="75" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C54" s="75"/>
       <c r="D54" s="75"/>

--- a/data/prod_parameters/PigHerd.xlsx
+++ b/data/prod_parameters/PigHerd.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="251">
   <si>
     <t>parameter</t>
   </si>
@@ -689,9 +689,6 @@
     <t>wheat bran, fine</t>
   </si>
   <si>
-    <t>antar havre</t>
-  </si>
-  <si>
     <t>sunflower seed meal</t>
   </si>
   <si>
@@ -755,12 +752,6 @@
     <t>Agrodrank90</t>
   </si>
   <si>
-    <t>NEv</t>
-  </si>
-  <si>
-    <t>NEs</t>
-  </si>
-  <si>
     <t>Betfiber, omelasserad</t>
   </si>
   <si>
@@ -795,6 +786,9 @@
   </si>
   <si>
     <t>see feed rations sheet</t>
+  </si>
+  <si>
+    <t>vegetable oils</t>
   </si>
 </sst>
 </file>
@@ -1168,7 +1162,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1387,6 +1381,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1423,14 +1425,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1480,7 +1477,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1610,7 +1606,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1644,7 +1639,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1698,7 +1692,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -1828,7 +1821,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1862,7 +1854,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -1916,7 +1907,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -2139,7 +2129,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -2173,7 +2162,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -2187,7 +2175,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -2232,7 +2219,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -2455,7 +2441,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -2489,7 +2474,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="1"/>
@@ -2503,7 +2487,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -2548,7 +2531,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -2678,7 +2660,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -2712,7 +2693,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -2751,7 +2731,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3148,7 +3127,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3515,7 +3493,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7016,11 +6993,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N127"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.7109375" customWidth="1"/>
@@ -7884,7 +7861,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>159</v>
@@ -7903,16 +7880,16 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="106" t="s">
-        <v>249</v>
-      </c>
-      <c r="B56" s="106"/>
-      <c r="C56" s="106"/>
-      <c r="D56" s="107"/>
-      <c r="E56" s="107"/>
-      <c r="F56" s="107"/>
-      <c r="G56" s="107"/>
-      <c r="H56" s="106"/>
+      <c r="A56" s="94" t="s">
+        <v>246</v>
+      </c>
+      <c r="B56" s="94"/>
+      <c r="C56" s="94"/>
+      <c r="D56" s="95"/>
+      <c r="E56" s="95"/>
+      <c r="F56" s="95"/>
+      <c r="G56" s="95"/>
+      <c r="H56" s="94"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
@@ -7921,8 +7898,9 @@
       <c r="D57" t="s">
         <v>71</v>
       </c>
-      <c r="E57">
-        <v>40.178411304260166</v>
+      <c r="E57" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C57,'feed rations'!K$8:K$33,0))</f>
+        <v>40.096128418163971</v>
       </c>
       <c r="F57" t="s">
         <v>23</v>
@@ -7935,8 +7913,9 @@
       <c r="D58" t="s">
         <v>71</v>
       </c>
-      <c r="E58">
-        <v>33.789919707775212</v>
+      <c r="E58" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C58,'feed rations'!K$8:K$33,0))</f>
+        <v>33.720720054920363</v>
       </c>
       <c r="F58" t="s">
         <v>23</v>
@@ -7949,8 +7928,9 @@
       <c r="D59" t="s">
         <v>71</v>
       </c>
-      <c r="E59">
-        <v>4.9058647496700978</v>
+      <c r="E59" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C59,'feed rations'!K$8:K$33,0))</f>
+        <v>4.8958178439489242</v>
       </c>
       <c r="F59" t="s">
         <v>23</v>
@@ -7963,8 +7943,9 @@
       <c r="D60" t="s">
         <v>71</v>
       </c>
-      <c r="E60">
-        <v>0.45022176500136973</v>
+      <c r="E60" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C60,'feed rations'!K$8:K$33,0))</f>
+        <v>0.44929973884341395</v>
       </c>
       <c r="F60" t="s">
         <v>23</v>
@@ -7977,8 +7958,9 @@
       <c r="D61" t="s">
         <v>71</v>
       </c>
-      <c r="E61">
-        <v>0.22511088250068487</v>
+      <c r="E61" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C61,'feed rations'!K$8:K$33,0))</f>
+        <v>0.22464986942170698</v>
       </c>
       <c r="F61" t="s">
         <v>23</v>
@@ -7986,13 +7968,14 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D62" t="s">
         <v>71</v>
       </c>
-      <c r="E62">
-        <v>0.79953175508863938</v>
+      <c r="E62" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C62,'feed rations'!K$8:K$33,0))</f>
+        <v>0.79789436380813161</v>
       </c>
       <c r="F62" t="s">
         <v>23</v>
@@ -8000,13 +7983,14 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D63" t="s">
         <v>71</v>
       </c>
-      <c r="E63">
-        <v>0.10091177491410011</v>
+      <c r="E63" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C63,'feed rations'!K$8:K$33,0))</f>
+        <v>0.10070511387869623</v>
       </c>
       <c r="F63" t="s">
         <v>23</v>
@@ -8019,8 +8003,9 @@
       <c r="D64" t="s">
         <v>71</v>
       </c>
-      <c r="E64">
-        <v>0.35296815345727672</v>
+      <c r="E64" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C64,'feed rations'!K$8:K$33,0))</f>
+        <v>0.35224529664378623</v>
       </c>
       <c r="F64" t="s">
         <v>23</v>
@@ -8033,8 +8018,9 @@
       <c r="D65" t="s">
         <v>71</v>
       </c>
-      <c r="E65">
-        <v>0.12990941138366913</v>
+      <c r="E65" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C65,'feed rations'!K$8:K$33,0))</f>
+        <v>0.12964336499326412</v>
       </c>
       <c r="F65" t="s">
         <v>23</v>
@@ -8042,13 +8028,14 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
-        <v>221</v>
+        <v>250</v>
       </c>
       <c r="D66" t="s">
         <v>71</v>
       </c>
-      <c r="E66">
-        <v>6.9565776007980151</v>
+      <c r="E66" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C66,'feed rations'!K$8:K$33,0))</f>
+        <v>0.20479377711848037</v>
       </c>
       <c r="F66" t="s">
         <v>23</v>
@@ -8056,13 +8043,14 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D67" t="s">
         <v>71</v>
       </c>
-      <c r="E67">
-        <v>3.2319427256529165</v>
+      <c r="E67" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C67,'feed rations'!K$8:K$33,0))</f>
+        <v>6.9423309627711633</v>
       </c>
       <c r="F67" t="s">
         <v>23</v>
@@ -8070,13 +8058,14 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D68" t="s">
         <v>71</v>
       </c>
-      <c r="E68">
-        <v>0.44165630930574318</v>
+      <c r="E68" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C68,'feed rations'!K$8:K$33,0))</f>
+        <v>3.2253239080707465</v>
       </c>
       <c r="F68" t="s">
         <v>23</v>
@@ -8084,13 +8073,14 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D69" t="s">
         <v>71</v>
       </c>
-      <c r="E69">
-        <v>0.12990941138366913</v>
+      <c r="E69" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C69,'feed rations'!K$8:K$33,0))</f>
+        <v>0.44075182466803386</v>
       </c>
       <c r="F69" t="s">
         <v>23</v>
@@ -8098,13 +8088,14 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D70" t="s">
         <v>71</v>
       </c>
-      <c r="E70">
-        <v>3.0972152454404571</v>
+      <c r="E70" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C70,'feed rations'!K$8:K$33,0))</f>
+        <v>0.12964336499326412</v>
       </c>
       <c r="F70" t="s">
         <v>23</v>
@@ -8112,13 +8103,14 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D71" t="s">
         <v>71</v>
       </c>
-      <c r="E71">
-        <v>2.331945313134324</v>
+      <c r="E71" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C71,'feed rations'!K$8:K$33,0))</f>
+        <v>3.0908723413538302</v>
       </c>
       <c r="F71" t="s">
         <v>23</v>
@@ -8126,13 +8118,14 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C72" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D72" t="s">
         <v>71</v>
       </c>
-      <c r="E72">
-        <v>0.13651195014904788</v>
+      <c r="E72" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C72,'feed rations'!K$8:K$33,0))</f>
+        <v>2.3271696342472188</v>
       </c>
       <c r="F72" t="s">
         <v>23</v>
@@ -8140,13 +8133,14 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C73" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D73" t="s">
         <v>71</v>
       </c>
-      <c r="E73">
-        <v>0.59280091293481973</v>
+      <c r="E73" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C73,'feed rations'!K$8:K$33,0))</f>
+        <v>0.13623238217011954</v>
       </c>
       <c r="F73" t="s">
         <v>23</v>
@@ -8154,13 +8148,14 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C74" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="D74" t="s">
         <v>71</v>
       </c>
-      <c r="E74">
-        <v>0.35261125946995903</v>
+      <c r="E74" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C74,'feed rations'!K$8:K$33,0))</f>
+        <v>0.59158689355442773</v>
       </c>
       <c r="F74" t="s">
         <v>23</v>
@@ -8168,13 +8163,14 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C75" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D75" t="s">
         <v>71</v>
       </c>
-      <c r="E75">
-        <v>0.69085753595037758</v>
+      <c r="E75" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C75,'feed rations'!K$8:K$33,0))</f>
+        <v>0.35188913355314549</v>
       </c>
       <c r="F75" t="s">
         <v>23</v>
@@ -8182,13 +8178,14 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="D76" t="s">
         <v>71</v>
       </c>
-      <c r="E76">
-        <v>0.92453387414668897</v>
+      <c r="E76" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C76,'feed rations'!K$8:K$33,0))</f>
+        <v>0.68944270270799723</v>
       </c>
       <c r="F76" t="s">
         <v>23</v>
@@ -8196,60 +8193,59 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D77" t="s">
         <v>71</v>
       </c>
-      <c r="E77">
-        <v>0.18058835758279279</v>
+      <c r="E77" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C77,'feed rations'!K$8:K$33,0))</f>
+        <v>0.92264048630508433</v>
       </c>
       <c r="F77" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="106" t="s">
-        <v>250</v>
-      </c>
-      <c r="B78" s="106"/>
-      <c r="C78" s="106"/>
-      <c r="D78" s="107"/>
-      <c r="E78" s="107"/>
-      <c r="F78" s="107"/>
-      <c r="G78" s="107"/>
-      <c r="H78" s="106"/>
+      <c r="C78" t="s">
+        <v>224</v>
+      </c>
+      <c r="D78" t="s">
+        <v>71</v>
+      </c>
+      <c r="E78" s="62">
+        <f>INDEX('feed rations'!M$8:M$33,MATCH(C78,'feed rations'!K$8:K$33,0))</f>
+        <v>0.18021852386426279</v>
+      </c>
+      <c r="F78" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B79" s="88" t="s">
+      <c r="A79" s="94" t="s">
+        <v>247</v>
+      </c>
+      <c r="B79" s="94"/>
+      <c r="C79" s="94"/>
+      <c r="D79" s="95"/>
+      <c r="E79" s="109"/>
+      <c r="F79" s="95"/>
+      <c r="G79" s="95"/>
+      <c r="H79" s="94"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B80" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D79" s="88" t="s">
+      <c r="D80" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E79" s="88">
+      <c r="E80" s="110">
         <v>0</v>
       </c>
-      <c r="F79" s="88"/>
-      <c r="G79" s="88" t="s">
+      <c r="F80" s="88"/>
+      <c r="G80" s="88" t="s">
         <v>158</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>15</v>
-      </c>
-      <c r="C80" t="s">
-        <v>70</v>
-      </c>
-      <c r="D80" t="s">
-        <v>71</v>
-      </c>
-      <c r="E80">
-        <v>38.250221304219536</v>
-      </c>
-      <c r="F80" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -8257,13 +8253,14 @@
         <v>15</v>
       </c>
       <c r="C81" t="s">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="D81" t="s">
         <v>71</v>
       </c>
-      <c r="E81">
-        <v>34.656240778990849</v>
+      <c r="E81" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C81,'feed rations'!K$8:K$33,0))</f>
+        <v>37.694097121256185</v>
       </c>
       <c r="F81" t="s">
         <v>23</v>
@@ -8274,13 +8271,14 @@
         <v>15</v>
       </c>
       <c r="C82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D82" t="s">
         <v>71</v>
       </c>
-      <c r="E82">
-        <v>6.9312481557981709</v>
+      <c r="E82" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C82,'feed rations'!K$8:K$33,0))</f>
+        <v>34.152369874963654</v>
       </c>
       <c r="F82" t="s">
         <v>23</v>
@@ -8291,13 +8289,14 @@
         <v>15</v>
       </c>
       <c r="C83" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D83" t="s">
         <v>71</v>
       </c>
-      <c r="E83">
-        <v>1.7969902626143404</v>
+      <c r="E83" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C83,'feed rations'!K$8:K$33,0))</f>
+        <v>6.8304739749927315</v>
       </c>
       <c r="F83" t="s">
         <v>23</v>
@@ -8308,13 +8307,14 @@
         <v>15</v>
       </c>
       <c r="C84" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="D84" t="s">
         <v>71</v>
       </c>
-      <c r="E84">
-        <v>0.2567128946591915</v>
+      <c r="E84" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C84,'feed rations'!K$8:K$33,0))</f>
+        <v>1.7708636231462638</v>
       </c>
       <c r="F84" t="s">
         <v>23</v>
@@ -8325,13 +8325,14 @@
         <v>15</v>
       </c>
       <c r="C85" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D85" t="s">
         <v>71</v>
       </c>
-      <c r="E85">
-        <v>0.77013868397757457</v>
+      <c r="E85" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C85,'feed rations'!K$8:K$33,0))</f>
+        <v>0.25298051759232343</v>
       </c>
       <c r="F85" t="s">
         <v>23</v>
@@ -8342,13 +8343,14 @@
         <v>15</v>
       </c>
       <c r="C86" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D86" t="s">
         <v>71</v>
       </c>
-      <c r="E86">
-        <v>7.270581292416642</v>
+      <c r="E86" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C86,'feed rations'!K$8:K$33,0))</f>
+        <v>0.75894155277697029</v>
       </c>
       <c r="F86" t="s">
         <v>23</v>
@@ -8359,13 +8361,14 @@
         <v>15</v>
       </c>
       <c r="C87" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="D87" t="s">
         <v>71</v>
       </c>
-      <c r="E87">
-        <v>2.3104160519327235</v>
+      <c r="E87" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C87,'feed rations'!K$8:K$33,0))</f>
+        <v>1.4539110206455368</v>
       </c>
       <c r="F87" t="s">
         <v>23</v>
@@ -8376,13 +8379,14 @@
         <v>15</v>
       </c>
       <c r="C88" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D88" t="s">
         <v>71</v>
       </c>
-      <c r="E88">
-        <v>1.2983180879315432</v>
+      <c r="E88" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C88,'feed rations'!K$8:K$33,0))</f>
+        <v>7.1648735097412057</v>
       </c>
       <c r="F88" t="s">
         <v>23</v>
@@ -8393,13 +8397,14 @@
         <v>15</v>
       </c>
       <c r="C89" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D89" t="s">
         <v>71</v>
       </c>
-      <c r="E89">
-        <v>1.557981705517852</v>
+      <c r="E89" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C89,'feed rations'!K$8:K$33,0))</f>
+        <v>2.2768246583309106</v>
       </c>
       <c r="F89" t="s">
         <v>23</v>
@@ -8410,13 +8415,14 @@
         <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="D90" t="s">
         <v>71</v>
       </c>
-      <c r="E90">
-        <v>0.28622012393036295</v>
+      <c r="E90" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C90,'feed rations'!K$8:K$33,0))</f>
+        <v>1.2794416981680723</v>
       </c>
       <c r="F90" t="s">
         <v>23</v>
@@ -8427,13 +8433,14 @@
         <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D91" t="s">
         <v>71</v>
       </c>
-      <c r="E91">
-        <v>1.3573325464738861</v>
+      <c r="E91" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C91,'feed rations'!K$8:K$33,0))</f>
+        <v>1.535330037801687</v>
       </c>
       <c r="F91" t="s">
         <v>23</v>
@@ -8444,601 +8451,745 @@
         <v>15</v>
       </c>
       <c r="C92" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="D92" t="s">
         <v>71</v>
       </c>
-      <c r="E92">
-        <v>3.2575981115373271</v>
+      <c r="E92" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C92,'feed rations'!K$8:K$33,0))</f>
+        <v>0.28205873800523412</v>
       </c>
       <c r="F92" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="106" t="s">
-        <v>251</v>
-      </c>
-      <c r="B93" s="106"/>
-      <c r="C93" s="106"/>
-      <c r="D93" s="107"/>
-      <c r="E93" s="107"/>
-      <c r="F93" s="107"/>
-      <c r="G93" s="107"/>
-      <c r="H93" s="106"/>
+      <c r="B93" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" t="s">
+        <v>223</v>
+      </c>
+      <c r="D93" t="s">
+        <v>71</v>
+      </c>
+      <c r="E93" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C93,'feed rations'!K$8:K$33,0))</f>
+        <v>1.337598138993894</v>
+      </c>
+      <c r="F93" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B94" s="88" t="s">
+      <c r="B94" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" t="s">
+        <v>224</v>
+      </c>
+      <c r="D94" t="s">
+        <v>71</v>
+      </c>
+      <c r="E94" s="62">
+        <f>INDEX('feed rations'!O$8:O$33,MATCH(C94,'feed rations'!K$8:K$33,0))</f>
+        <v>3.2102355335853456</v>
+      </c>
+      <c r="F94" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="94" t="s">
+        <v>248</v>
+      </c>
+      <c r="B95" s="94"/>
+      <c r="C95" s="94"/>
+      <c r="D95" s="95"/>
+      <c r="E95" s="109"/>
+      <c r="F95" s="95"/>
+      <c r="G95" s="95"/>
+      <c r="H95" s="94"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B96" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="D94" s="88" t="s">
+      <c r="D96" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E94" s="88">
+      <c r="E96" s="110">
         <v>0</v>
       </c>
-      <c r="F94" s="88"/>
-      <c r="G94" s="88" t="s">
+      <c r="F96" s="88"/>
+      <c r="G96" s="88" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B95" t="s">
-        <v>24</v>
-      </c>
-      <c r="C95" t="s">
-        <v>70</v>
-      </c>
-      <c r="D95" t="s">
-        <v>71</v>
-      </c>
-      <c r="E95">
-        <v>32.548570057825053</v>
-      </c>
-      <c r="F95" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B96" t="s">
-        <v>24</v>
-      </c>
-      <c r="C96" t="s">
-        <v>160</v>
-      </c>
-      <c r="D96" t="s">
-        <v>71</v>
-      </c>
-      <c r="E96">
-        <v>25.003402152928501</v>
-      </c>
-      <c r="F96" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
         <v>24</v>
       </c>
       <c r="C97" t="s">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="D97" t="s">
         <v>71</v>
       </c>
-      <c r="E97">
-        <v>4.2140565426283985</v>
+      <c r="E97" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C97,'feed rations'!K$8:K$33,0))</f>
+        <v>29.396484021023365</v>
       </c>
       <c r="F97" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
         <v>24</v>
       </c>
       <c r="C98" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D98" t="s">
         <v>71</v>
       </c>
-      <c r="E98">
-        <v>3.9331194397865055</v>
+      <c r="E98" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C98,'feed rations'!K$8:K$33,0))</f>
+        <v>22.582009303449521</v>
       </c>
       <c r="F98" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>24</v>
       </c>
       <c r="C99" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D99" t="s">
         <v>71</v>
       </c>
-      <c r="E99">
-        <v>8.0267743669112365E-2</v>
+      <c r="E99" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C99,'feed rations'!K$8:K$33,0))</f>
+        <v>3.8059566241768858</v>
       </c>
       <c r="F99" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>24</v>
       </c>
       <c r="C100" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="D100" t="s">
         <v>71</v>
       </c>
-      <c r="E100">
-        <v>0.48160646201467416</v>
+      <c r="E100" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C100,'feed rations'!K$8:K$33,0))</f>
+        <v>3.5522261825650929</v>
       </c>
       <c r="F100" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>24</v>
       </c>
       <c r="C101" t="s">
-        <v>220</v>
+        <v>165</v>
       </c>
       <c r="D101" t="s">
         <v>71</v>
       </c>
-      <c r="E101">
-        <v>8.1471759824149039</v>
+      <c r="E101" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C101,'feed rations'!K$8:K$33,0))</f>
+        <v>7.2494411889083538E-2</v>
       </c>
       <c r="F101" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>24</v>
       </c>
       <c r="C102" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D102" t="s">
         <v>71</v>
       </c>
-      <c r="E102">
-        <v>2.9228530108476773</v>
+      <c r="E102" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C102,'feed rations'!K$8:K$33,0))</f>
+        <v>0.43496647133450123</v>
       </c>
       <c r="F102" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>24</v>
       </c>
       <c r="C103" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D103" t="s">
         <v>71</v>
       </c>
-      <c r="E103">
-        <v>3.5719145932754999</v>
+      <c r="E103" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C103,'feed rations'!K$8:K$33,0))</f>
+        <v>7.3581828067419792</v>
       </c>
       <c r="F103" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>24</v>
       </c>
       <c r="C104" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D104" t="s">
         <v>71</v>
       </c>
-      <c r="E104">
-        <v>0.16607119379816351</v>
+      <c r="E104" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C104,'feed rations'!K$8:K$33,0))</f>
+        <v>2.6397965156852488</v>
       </c>
       <c r="F104" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>24</v>
       </c>
       <c r="C105" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D105" t="s">
         <v>71</v>
       </c>
-      <c r="E105">
-        <v>8.5083808289259082</v>
+      <c r="E105" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C105,'feed rations'!K$8:K$33,0))</f>
+        <v>3.2260013290642173</v>
       </c>
       <c r="F105" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>24</v>
       </c>
       <c r="C106" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D106" t="s">
         <v>71</v>
       </c>
-      <c r="E106">
-        <v>0.89309397553679037</v>
+      <c r="E106" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C106,'feed rations'!K$8:K$33,0))</f>
+        <v>0.14998843839120732</v>
       </c>
       <c r="F106" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>24</v>
       </c>
       <c r="C107" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="D107" t="s">
         <v>71</v>
       </c>
-      <c r="E107">
-        <v>0.16607119379816351</v>
+      <c r="E107" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C107,'feed rations'!K$8:K$33,0))</f>
+        <v>7.6844076602428553</v>
       </c>
       <c r="F107" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>24</v>
       </c>
       <c r="C108" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D108" t="s">
         <v>71</v>
       </c>
-      <c r="E108">
-        <v>6.0994259011092158</v>
+      <c r="E108" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C108,'feed rations'!K$8:K$33,0))</f>
+        <v>0.80660449090382613</v>
       </c>
       <c r="F108" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>24</v>
       </c>
       <c r="C109" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="D109" t="s">
         <v>71</v>
       </c>
-      <c r="E109">
-        <v>0.10517842273883686</v>
+      <c r="E109" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C109,'feed rations'!K$8:K$33,0))</f>
+        <v>0.14998843839120732</v>
       </c>
       <c r="F109" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>24</v>
       </c>
       <c r="C110" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D110" t="s">
         <v>71</v>
       </c>
-      <c r="E110">
-        <v>3.1588124987025679</v>
+      <c r="E110" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C110,'feed rations'!K$8:K$33,0))</f>
+        <v>5.5087420344681757</v>
       </c>
       <c r="F110" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B111" s="88" t="s">
-        <v>25</v>
-      </c>
-      <c r="D111" s="88" t="s">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" t="s">
+        <v>230</v>
+      </c>
+      <c r="D111" t="s">
         <v>71</v>
       </c>
-      <c r="E111" s="88">
-        <v>0</v>
-      </c>
-      <c r="F111" s="88"/>
-      <c r="G111" s="88" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E111" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C111,'feed rations'!K$8:K$33,0))</f>
+        <v>3.6663840495628457</v>
+      </c>
+      <c r="F111" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C112" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="D112" t="s">
         <v>71</v>
       </c>
-      <c r="E112">
-        <v>32.548570057825053</v>
+      <c r="E112" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C112,'feed rations'!K$8:K$33,0))</f>
+        <v>9.4992677647764617E-2</v>
       </c>
       <c r="F112" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C113" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="D113" t="s">
         <v>71</v>
       </c>
-      <c r="E113">
-        <v>25.003402152928501</v>
+      <c r="E113" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C113,'feed rations'!K$8:K$33,0))</f>
+        <v>2.8529050885660894</v>
       </c>
       <c r="F113" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C114" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
       <c r="D114" t="s">
         <v>71</v>
       </c>
-      <c r="E114">
-        <v>4.2140565426283985</v>
+      <c r="E114" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C114,'feed rations'!K$8:K$33,0))</f>
+        <v>6.0178694558961068</v>
       </c>
       <c r="F114" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B115" t="s">
+    <row r="115" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E115" s="62"/>
+    </row>
+    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B116" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="C115" t="s">
-        <v>162</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="D116" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E115">
-        <v>3.9331194397865055</v>
-      </c>
-      <c r="F115" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B116" t="s">
-        <v>25</v>
-      </c>
-      <c r="C116" t="s">
-        <v>165</v>
-      </c>
-      <c r="D116" t="s">
-        <v>71</v>
-      </c>
-      <c r="E116">
-        <v>8.0267743669112365E-2</v>
-      </c>
-      <c r="F116" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E116" s="110">
+        <v>0</v>
+      </c>
+      <c r="F116" s="88"/>
+      <c r="G116" s="88" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>25</v>
       </c>
       <c r="C117" t="s">
-        <v>219</v>
+        <v>70</v>
       </c>
       <c r="D117" t="s">
         <v>71</v>
       </c>
-      <c r="E117">
-        <v>0.48160646201467416</v>
+      <c r="E117" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C117,'feed rations'!K$8:K$33,0))</f>
+        <v>29.396484021023365</v>
       </c>
       <c r="F117" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>25</v>
       </c>
       <c r="C118" t="s">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="D118" t="s">
         <v>71</v>
       </c>
-      <c r="E118">
-        <v>8.1471759824149039</v>
+      <c r="E118" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C118,'feed rations'!K$8:K$33,0))</f>
+        <v>22.582009303449521</v>
       </c>
       <c r="F118" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>25</v>
       </c>
       <c r="C119" t="s">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="D119" t="s">
         <v>71</v>
       </c>
-      <c r="E119">
-        <v>2.9228530108476773</v>
+      <c r="E119" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C119,'feed rations'!K$8:K$33,0))</f>
+        <v>3.8059566241768858</v>
       </c>
       <c r="F119" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>25</v>
       </c>
       <c r="C120" t="s">
-        <v>222</v>
+        <v>162</v>
       </c>
       <c r="D120" t="s">
         <v>71</v>
       </c>
-      <c r="E120">
-        <v>3.5719145932754999</v>
+      <c r="E120" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C120,'feed rations'!K$8:K$33,0))</f>
+        <v>3.5522261825650929</v>
       </c>
       <c r="F120" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>25</v>
       </c>
       <c r="C121" t="s">
-        <v>218</v>
+        <v>165</v>
       </c>
       <c r="D121" t="s">
         <v>71</v>
       </c>
-      <c r="E121">
-        <v>0.16607119379816351</v>
+      <c r="E121" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C121,'feed rations'!K$8:K$33,0))</f>
+        <v>7.2494411889083538E-2</v>
       </c>
       <c r="F121" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D122" t="s">
         <v>71</v>
       </c>
-      <c r="E122">
-        <v>8.5083808289259082</v>
+      <c r="E122" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C122,'feed rations'!K$8:K$33,0))</f>
+        <v>0.43496647133450123</v>
       </c>
       <c r="F122" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>25</v>
       </c>
       <c r="C123" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D123" t="s">
         <v>71</v>
       </c>
-      <c r="E123">
-        <v>0.89309397553679037</v>
+      <c r="E123" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C123,'feed rations'!K$8:K$33,0))</f>
+        <v>7.3581828067419792</v>
       </c>
       <c r="F123" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>25</v>
       </c>
       <c r="C124" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D124" t="s">
         <v>71</v>
       </c>
-      <c r="E124">
-        <v>0.16607119379816351</v>
+      <c r="E124" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C124,'feed rations'!K$8:K$33,0))</f>
+        <v>2.6397965156852488</v>
       </c>
       <c r="F124" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>25</v>
       </c>
       <c r="C125" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D125" t="s">
         <v>71</v>
       </c>
-      <c r="E125">
-        <v>6.0994259011092158</v>
+      <c r="E125" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C125,'feed rations'!K$8:K$33,0))</f>
+        <v>3.2260013290642173</v>
       </c>
       <c r="F125" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>25</v>
       </c>
       <c r="C126" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D126" t="s">
         <v>71</v>
       </c>
-      <c r="E126">
-        <v>0.10517842273883686</v>
+      <c r="E126" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C126,'feed rations'!K$8:K$33,0))</f>
+        <v>0.14998843839120732</v>
       </c>
       <c r="F126" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>25</v>
       </c>
       <c r="C127" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="D127" t="s">
         <v>71</v>
       </c>
-      <c r="E127">
-        <v>3.1588124987025679</v>
+      <c r="E127" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C127,'feed rations'!K$8:K$33,0))</f>
+        <v>7.6844076602428553</v>
       </c>
       <c r="F127" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>25</v>
+      </c>
+      <c r="C128" t="s">
+        <v>216</v>
+      </c>
+      <c r="D128" t="s">
+        <v>71</v>
+      </c>
+      <c r="E128" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C128,'feed rations'!K$8:K$33,0))</f>
+        <v>0.80660449090382613</v>
+      </c>
+      <c r="F128" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="129" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>25</v>
+      </c>
+      <c r="C129" t="s">
+        <v>225</v>
+      </c>
+      <c r="D129" t="s">
+        <v>71</v>
+      </c>
+      <c r="E129" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C129,'feed rations'!K$8:K$33,0))</f>
+        <v>0.14998843839120732</v>
+      </c>
+      <c r="F129" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>25</v>
+      </c>
+      <c r="C130" t="s">
+        <v>226</v>
+      </c>
+      <c r="D130" t="s">
+        <v>71</v>
+      </c>
+      <c r="E130" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C130,'feed rations'!K$8:K$33,0))</f>
+        <v>5.5087420344681757</v>
+      </c>
+      <c r="F130" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>25</v>
+      </c>
+      <c r="C131" t="s">
+        <v>230</v>
+      </c>
+      <c r="D131" t="s">
+        <v>71</v>
+      </c>
+      <c r="E131" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C131,'feed rations'!K$8:K$33,0))</f>
+        <v>3.6663840495628457</v>
+      </c>
+      <c r="F131" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>25</v>
+      </c>
+      <c r="C132" t="s">
+        <v>211</v>
+      </c>
+      <c r="D132" t="s">
+        <v>71</v>
+      </c>
+      <c r="E132" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C132,'feed rations'!K$8:K$33,0))</f>
+        <v>9.4992677647764617E-2</v>
+      </c>
+      <c r="F132" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>25</v>
+      </c>
+      <c r="C133" t="s">
+        <v>227</v>
+      </c>
+      <c r="D133" t="s">
+        <v>71</v>
+      </c>
+      <c r="E133" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C133,'feed rations'!K$8:K$33,0))</f>
+        <v>2.8529050885660894</v>
+      </c>
+      <c r="F133" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="134" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>25</v>
+      </c>
+      <c r="C134" t="s">
+        <v>223</v>
+      </c>
+      <c r="D134" t="s">
+        <v>71</v>
+      </c>
+      <c r="E134" s="62">
+        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C134,'feed rations'!K$8:K$33,0))</f>
+        <v>6.0178694558961068</v>
+      </c>
+      <c r="F134" t="s">
         <v>23</v>
       </c>
     </row>
@@ -9066,7 +9217,7 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="102" t="s">
+      <c r="C5" s="90" t="s">
         <v>166</v>
       </c>
     </row>
@@ -9085,1617 +9236,1670 @@
     </row>
     <row r="7" spans="3:22" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="4"/>
-      <c r="D7" s="103" t="s">
+      <c r="D7" s="91" t="s">
         <v>169</v>
       </c>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103" t="s">
+      <c r="E7" s="91"/>
+      <c r="F7" s="91" t="s">
         <v>170</v>
       </c>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103" t="s">
+      <c r="G7" s="91"/>
+      <c r="H7" s="91" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="103"/>
-      <c r="K7" s="103" t="s">
+      <c r="I7" s="91"/>
+      <c r="K7" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="L7" s="103" t="s">
-        <v>245</v>
-      </c>
-      <c r="M7" s="103" t="s">
+      <c r="L7" s="91" t="s">
+        <v>242</v>
+      </c>
+      <c r="M7" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="N7" s="103" t="s">
+      <c r="N7" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="103" t="s">
+      <c r="O7" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="P7" s="103" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q7" s="103" t="s">
+      <c r="P7" s="91" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q7" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="R7" s="103" t="s">
+      <c r="R7" s="91" t="s">
         <v>209</v>
       </c>
-      <c r="S7" s="103" t="s">
-        <v>239</v>
-      </c>
-      <c r="T7" s="103" t="s">
-        <v>240</v>
-      </c>
-      <c r="U7" s="103"/>
-      <c r="V7" s="104" t="s">
-        <v>235</v>
+      <c r="S7" s="91"/>
+      <c r="T7" s="91"/>
+      <c r="U7" s="91"/>
+      <c r="V7" s="92" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C8" s="105" t="s">
+      <c r="C8" s="93" t="s">
         <v>173</v>
       </c>
       <c r="D8">
         <v>517.6</v>
       </c>
       <c r="E8" s="5">
-        <f>D8/D$45</f>
+        <f t="shared" ref="E8:E42" si="0">D8/D$45</f>
         <v>0.31776045183866414</v>
       </c>
       <c r="F8">
         <v>14.9</v>
       </c>
       <c r="G8" s="5">
-        <f>F8/F$45</f>
+        <f t="shared" ref="G8:G42" si="1">F8/F$45</f>
         <v>0.27090909090909093</v>
       </c>
       <c r="H8">
         <v>81.099999999999994</v>
       </c>
       <c r="I8" s="5">
-        <f>H8/H$45</f>
+        <f t="shared" ref="I8:I42" si="2">H8/H$45</f>
         <v>0.15836750634641669</v>
       </c>
       <c r="K8" t="s">
         <v>70</v>
       </c>
-      <c r="L8" s="13">
-        <f>(D8)*($R8/100)</f>
+      <c r="L8" s="3">
+        <f t="shared" ref="L8:L21" si="3">(D8)*($R8/100)</f>
         <v>450.31200000000001</v>
       </c>
-      <c r="M8" s="13">
-        <f>L8/L$32*100</f>
-        <v>40.178411304260166</v>
-      </c>
-      <c r="N8" s="13">
-        <f>(F8)*($R8/100)</f>
+      <c r="M8" s="62">
+        <f>L8/L$34*100</f>
+        <v>40.096128418163971</v>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" ref="N8:N21" si="4">(F8)*($R8/100)</f>
         <v>12.963000000000001</v>
       </c>
-      <c r="O8" s="13">
-        <f>N8/N$32*100</f>
-        <v>38.250221304219536</v>
-      </c>
-      <c r="P8" s="13">
-        <f>(H8)*($R8/100)</f>
+      <c r="O8" s="62">
+        <f>N8/N$34*100</f>
+        <v>37.694097121256185</v>
+      </c>
+      <c r="P8" s="3">
+        <f t="shared" ref="P8:P21" si="5">(H8)*($R8/100)</f>
         <v>70.556999999999988</v>
       </c>
-      <c r="Q8" s="13">
-        <f>P8/P$32*100</f>
-        <v>32.548570057825053</v>
+      <c r="Q8" s="62">
+        <f>P8/P$34*100</f>
+        <v>29.396484021023365</v>
       </c>
       <c r="R8">
         <v>87</v>
       </c>
     </row>
     <row r="9" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C9" s="105" t="s">
+      <c r="C9" s="93" t="s">
         <v>174</v>
       </c>
       <c r="D9">
         <v>435.3</v>
       </c>
       <c r="E9" s="5">
-        <f>D9/D$45</f>
+        <f t="shared" si="0"/>
         <v>0.267235557738351</v>
       </c>
       <c r="F9">
         <v>13.5</v>
       </c>
       <c r="G9" s="5">
-        <f>F9/F$45</f>
+        <f t="shared" si="1"/>
         <v>0.24545454545454545</v>
       </c>
       <c r="H9">
         <v>62.3</v>
       </c>
       <c r="I9" s="5">
-        <f>H9/H$45</f>
+        <f t="shared" si="2"/>
         <v>0.12165592657684045</v>
       </c>
       <c r="K9" t="s">
         <v>160</v>
       </c>
-      <c r="L9" s="13">
-        <f>(D9)*($R9/100)</f>
+      <c r="L9" s="3">
+        <f t="shared" si="3"/>
         <v>378.71100000000001</v>
       </c>
-      <c r="M9" s="13">
-        <f t="shared" ref="M9:O31" si="0">L9/L$32*100</f>
-        <v>33.789919707775212</v>
-      </c>
-      <c r="N9" s="13">
-        <f>(F9)*($R9/100)</f>
+      <c r="M9" s="62">
+        <f>L9/L$34*100</f>
+        <v>33.720720054920363</v>
+      </c>
+      <c r="N9" s="3">
+        <f t="shared" si="4"/>
         <v>11.744999999999999</v>
       </c>
-      <c r="O9" s="13">
-        <f t="shared" si="0"/>
-        <v>34.656240778990849</v>
-      </c>
-      <c r="P9" s="13">
-        <f>(H9)*($R9/100)</f>
+      <c r="O9" s="62">
+        <f>N9/N$34*100</f>
+        <v>34.152369874963654</v>
+      </c>
+      <c r="P9" s="3">
+        <f t="shared" si="5"/>
         <v>54.201000000000001</v>
       </c>
-      <c r="Q9" s="13">
-        <f t="shared" ref="Q9" si="1">P9/P$32*100</f>
-        <v>25.003402152928501</v>
+      <c r="Q9" s="62">
+        <f>P9/P$34*100</f>
+        <v>22.582009303449521</v>
       </c>
       <c r="R9">
         <v>87</v>
       </c>
     </row>
     <row r="10" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C10" s="105" t="s">
+      <c r="C10" s="93" t="s">
         <v>175</v>
       </c>
       <c r="D10">
         <v>63.2</v>
       </c>
       <c r="E10" s="5">
-        <f>D10/D$45</f>
+        <f t="shared" si="0"/>
         <v>3.8799189637178461E-2</v>
       </c>
       <c r="F10">
         <v>2.7</v>
       </c>
       <c r="G10" s="5">
-        <f>F10/F$45</f>
+        <f t="shared" si="1"/>
         <v>4.9090909090909095E-2</v>
       </c>
       <c r="H10">
         <v>10.5</v>
       </c>
       <c r="I10" s="5">
-        <f>H10/H$45</f>
+        <f t="shared" si="2"/>
         <v>2.0503807850029289E-2</v>
       </c>
       <c r="K10" t="s">
         <v>161</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="3">
         <f>(D10)*($R10/100)</f>
         <v>54.984000000000002</v>
       </c>
-      <c r="M10" s="3">
-        <f t="shared" si="0"/>
-        <v>4.9058647496700978</v>
-      </c>
-      <c r="N10" s="13">
-        <f>(F10)*($R10/100)</f>
+      <c r="M10" s="62">
+        <f>L10/L$34*100</f>
+        <v>4.8958178439489242</v>
+      </c>
+      <c r="N10" s="3">
+        <f t="shared" si="4"/>
         <v>2.3490000000000002</v>
       </c>
-      <c r="O10" s="3">
-        <f t="shared" si="0"/>
-        <v>6.9312481557981709</v>
-      </c>
-      <c r="P10" s="13">
-        <f>(H10)*($R10/100)</f>
+      <c r="O10" s="62">
+        <f>N10/N$34*100</f>
+        <v>6.8304739749927315</v>
+      </c>
+      <c r="P10" s="3">
+        <f t="shared" si="5"/>
         <v>9.1349999999999998</v>
       </c>
-      <c r="Q10" s="3">
-        <f t="shared" ref="Q10" si="2">P10/P$32*100</f>
-        <v>4.2140565426283985</v>
+      <c r="Q10" s="62">
+        <f>P10/P$34*100</f>
+        <v>3.8059566241768858</v>
       </c>
       <c r="R10">
         <v>87</v>
       </c>
     </row>
     <row r="11" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C11" s="105" t="s">
+      <c r="C11" s="93" t="s">
         <v>176</v>
       </c>
       <c r="D11">
         <v>5.8</v>
       </c>
       <c r="E11" s="5">
-        <f>D11/D$45</f>
+        <f t="shared" si="0"/>
         <v>3.5606851249309346E-3</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <f>F11/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H11">
         <v>9.8000000000000007</v>
       </c>
       <c r="I11" s="5">
-        <f>H11/H$45</f>
+        <f t="shared" si="2"/>
         <v>1.9136887326694007E-2</v>
       </c>
       <c r="K11" t="s">
         <v>162</v>
       </c>
-      <c r="L11" s="13">
-        <f>(D11)*($R11/100)</f>
+      <c r="L11" s="3">
+        <f t="shared" si="3"/>
         <v>5.0460000000000003</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="62">
+        <f>L11/L$34*100</f>
+        <v>0.44929973884341395</v>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="62">
+        <f>N11/N$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="P11" s="3">
+        <f t="shared" si="5"/>
+        <v>8.5259999999999998</v>
+      </c>
+      <c r="Q11" s="62">
+        <f>P11/P$34*100</f>
+        <v>3.5522261825650929</v>
+      </c>
+      <c r="R11">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C12" s="93" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12">
+        <v>2.9</v>
+      </c>
+      <c r="E12" s="5">
         <f t="shared" si="0"/>
-        <v>0.45022176500136973</v>
-      </c>
-      <c r="N11" s="13">
-        <f>(F11)*($R11/100)</f>
+        <v>1.7803425624654673E-3</v>
+      </c>
+      <c r="F12">
+        <v>0.7</v>
+      </c>
+      <c r="G12" s="5">
+        <f t="shared" si="1"/>
+        <v>1.2727272727272726E-2</v>
+      </c>
+      <c r="H12">
+        <v>0.2</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="2"/>
+        <v>3.905487209529389E-4</v>
+      </c>
+      <c r="K12" t="s">
+        <v>165</v>
+      </c>
+      <c r="L12" s="3">
+        <f t="shared" si="3"/>
+        <v>2.5230000000000001</v>
+      </c>
+      <c r="M12" s="62">
+        <f>L12/L$34*100</f>
+        <v>0.22464986942170698</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="4"/>
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="O12" s="62">
+        <f>N12/N$34*100</f>
+        <v>1.7708636231462638</v>
+      </c>
+      <c r="P12" s="3">
+        <f t="shared" si="5"/>
+        <v>0.17400000000000002</v>
+      </c>
+      <c r="Q12" s="62">
+        <f>P12/P$34*100</f>
+        <v>7.2494411889083538E-2</v>
+      </c>
+      <c r="R12">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C13" s="93" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13">
+        <v>10.3</v>
+      </c>
+      <c r="E13" s="5">
+        <f t="shared" si="0"/>
+        <v>6.3232856528945914E-3</v>
+      </c>
+      <c r="F13">
+        <v>0.1</v>
+      </c>
+      <c r="G13" s="5">
+        <f t="shared" si="1"/>
+        <v>1.8181818181818182E-3</v>
+      </c>
+      <c r="H13">
+        <v>1.2</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="2"/>
+        <v>2.3432923257176333E-3</v>
+      </c>
+      <c r="K13" t="s">
+        <v>218</v>
+      </c>
+      <c r="L13" s="3">
+        <f t="shared" si="3"/>
+        <v>8.9610000000000003</v>
+      </c>
+      <c r="M13" s="62">
+        <f>L13/L$34*100</f>
+        <v>0.79789436380813161</v>
+      </c>
+      <c r="N13" s="3">
+        <f t="shared" si="4"/>
+        <v>8.7000000000000008E-2</v>
+      </c>
+      <c r="O13" s="62">
+        <f>N13/N$34*100</f>
+        <v>0.25298051759232343</v>
+      </c>
+      <c r="P13" s="3">
+        <f t="shared" si="5"/>
+        <v>1.044</v>
+      </c>
+      <c r="Q13" s="62">
+        <f>P13/P$34*100</f>
+        <v>0.43496647133450123</v>
+      </c>
+      <c r="R13">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C14" s="93" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14">
+        <v>1.3</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="0"/>
+        <v>7.9808459696727846E-4</v>
+      </c>
+      <c r="F14">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="1"/>
+        <v>5.4545454545454541E-3</v>
+      </c>
+      <c r="H14">
+        <v>20.3</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="2"/>
+        <v>3.9640695176723299E-2</v>
+      </c>
+      <c r="K14" t="s">
+        <v>219</v>
+      </c>
+      <c r="L14" s="3">
+        <f t="shared" si="3"/>
+        <v>1.131</v>
+      </c>
+      <c r="M14" s="62">
+        <f>L14/L$34*100</f>
+        <v>0.10070511387869623</v>
+      </c>
+      <c r="N14" s="3">
+        <f t="shared" si="4"/>
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="O14" s="62">
+        <f>N14/N$34*100</f>
+        <v>0.75894155277697029</v>
+      </c>
+      <c r="P14" s="3">
+        <f t="shared" si="5"/>
+        <v>17.661000000000001</v>
+      </c>
+      <c r="Q14" s="62">
+        <f>P14/P$34*100</f>
+        <v>7.3581828067419792</v>
+      </c>
+      <c r="R14">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C15" s="93" t="s">
+        <v>180</v>
+      </c>
+      <c r="D15">
+        <v>4.3</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="0"/>
+        <v>2.6398182822763828E-3</v>
+      </c>
+      <c r="F15">
         <v>0</v>
       </c>
-      <c r="O11" s="3">
+      <c r="G15" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>163</v>
+      </c>
+      <c r="L15" s="3">
+        <f t="shared" si="3"/>
+        <v>3.956</v>
+      </c>
+      <c r="M15" s="62">
+        <f>L15/L$34*100</f>
+        <v>0.35224529664378623</v>
+      </c>
+      <c r="N15" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="62">
+        <f>N15/N$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="62">
+        <f>P15/P$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="3:22" x14ac:dyDescent="0.25">
+      <c r="C16" s="93" t="s">
+        <v>181</v>
+      </c>
+      <c r="D16">
+        <v>1.6</v>
+      </c>
+      <c r="E16" s="5">
+        <f t="shared" si="0"/>
+        <v>9.8225796549818905E-4</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>164</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" si="3"/>
+        <v>1.4560000000000002</v>
+      </c>
+      <c r="M16" s="62">
+        <f>L16/L$34*100</f>
+        <v>0.12964336499326412</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="62">
+        <f>N16/N$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="P16" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="62">
+        <f>P16/P$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C17" s="93" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17">
+        <v>88.6</v>
+      </c>
+      <c r="E17" s="5">
+        <f t="shared" si="0"/>
+        <v>5.4392534839462207E-2</v>
+      </c>
+      <c r="F17">
+        <v>2.8</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" si="1"/>
+        <v>5.0909090909090904E-2</v>
+      </c>
+      <c r="H17">
+        <v>7.2</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="2"/>
+        <v>1.4059753954305799E-2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>250</v>
+      </c>
+      <c r="L17" s="3">
+        <f>(D32)*($R17/100)</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M17" s="62">
+        <f>L17/L$34*100</f>
+        <v>0.20479377711848037</v>
+      </c>
+      <c r="N17" s="3">
+        <f>(F32)*($R17/100)</f>
+        <v>0.5</v>
+      </c>
+      <c r="O17" s="62">
+        <f>N17/N$34*100</f>
+        <v>1.4539110206455368</v>
+      </c>
+      <c r="P17" s="3">
+        <f>(H32)*($R17/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="62">
+        <f>P17/P$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C18" s="93" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P11" s="13">
-        <f>(H11)*($R11/100)</f>
-        <v>8.5259999999999998</v>
-      </c>
-      <c r="Q11" s="3">
-        <f t="shared" ref="Q11" si="3">P11/P$32*100</f>
-        <v>3.9331194397865055</v>
-      </c>
-      <c r="R11">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C12" s="105" t="s">
-        <v>182</v>
-      </c>
-      <c r="D12">
-        <v>2.9</v>
-      </c>
-      <c r="E12" s="5">
-        <f>D12/D$45</f>
-        <v>1.7803425624654673E-3</v>
-      </c>
-      <c r="F12">
-        <v>0.7</v>
-      </c>
-      <c r="G12" s="5">
-        <f>F12/F$45</f>
-        <v>1.2727272727272726E-2</v>
-      </c>
-      <c r="H12">
-        <v>0.2</v>
-      </c>
-      <c r="I12" s="5">
-        <f>H12/H$45</f>
-        <v>3.905487209529389E-4</v>
-      </c>
-      <c r="K12" t="s">
-        <v>165</v>
-      </c>
-      <c r="L12" s="13">
-        <f>(D12)*($R12/100)</f>
-        <v>2.5230000000000001</v>
-      </c>
-      <c r="M12" s="3">
-        <f t="shared" si="0"/>
-        <v>0.22511088250068487</v>
-      </c>
-      <c r="N12" s="13">
-        <f>(F12)*($R12/100)</f>
-        <v>0.60899999999999999</v>
-      </c>
-      <c r="O12" s="3">
-        <f t="shared" si="0"/>
-        <v>1.7969902626143404</v>
-      </c>
-      <c r="P12" s="13">
-        <f>(H12)*($R12/100)</f>
-        <v>0.17400000000000002</v>
-      </c>
-      <c r="Q12" s="3">
-        <f t="shared" ref="Q12" si="4">P12/P$32*100</f>
-        <v>8.0267743669112365E-2</v>
-      </c>
-      <c r="R12">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C13" s="105" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13">
-        <v>10.3</v>
-      </c>
-      <c r="E13" s="5">
-        <f>D13/D$45</f>
-        <v>6.3232856528945914E-3</v>
-      </c>
-      <c r="F13">
-        <v>0.1</v>
-      </c>
-      <c r="G13" s="5">
-        <f>F13/F$45</f>
-        <v>1.8181818181818182E-3</v>
-      </c>
-      <c r="H13">
-        <v>1.2</v>
-      </c>
-      <c r="I13" s="5">
-        <f>H13/H$45</f>
-        <v>2.3432923257176333E-3</v>
-      </c>
-      <c r="K13" t="s">
-        <v>219</v>
-      </c>
-      <c r="L13" s="13">
-        <f>(D13)*($R13/100)</f>
-        <v>8.9610000000000003</v>
-      </c>
-      <c r="M13" s="3">
-        <f t="shared" si="0"/>
-        <v>0.79953175508863938</v>
-      </c>
-      <c r="N13" s="13">
-        <f>(F13)*($R13/100)</f>
-        <v>8.7000000000000008E-2</v>
-      </c>
-      <c r="O13" s="3">
-        <f t="shared" si="0"/>
-        <v>0.2567128946591915</v>
-      </c>
-      <c r="P13" s="13">
-        <f>(H13)*($R13/100)</f>
-        <v>1.044</v>
-      </c>
-      <c r="Q13" s="3">
-        <f t="shared" ref="Q13" si="5">P13/P$32*100</f>
-        <v>0.48160646201467416</v>
-      </c>
-      <c r="R13">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C14" s="105" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14">
-        <v>1.3</v>
-      </c>
-      <c r="E14" s="5">
-        <f>D14/D$45</f>
-        <v>7.9808459696727846E-4</v>
-      </c>
-      <c r="F14">
-        <v>0.3</v>
-      </c>
-      <c r="G14" s="5">
-        <f>F14/F$45</f>
-        <v>5.4545454545454541E-3</v>
-      </c>
-      <c r="H14">
-        <v>20.3</v>
-      </c>
-      <c r="I14" s="5">
-        <f>H14/H$45</f>
-        <v>3.9640695176723299E-2</v>
-      </c>
-      <c r="K14" t="s">
-        <v>220</v>
-      </c>
-      <c r="L14" s="13">
-        <f>(D14)*($R14/100)</f>
-        <v>1.131</v>
-      </c>
-      <c r="M14" s="3">
-        <f t="shared" si="0"/>
-        <v>0.10091177491410011</v>
-      </c>
-      <c r="N14" s="13">
-        <f>(F14)*($R14/100)</f>
-        <v>0.26100000000000001</v>
-      </c>
-      <c r="O14" s="3">
-        <f t="shared" si="0"/>
-        <v>0.77013868397757457</v>
-      </c>
-      <c r="P14" s="13">
-        <f>(H14)*($R14/100)</f>
-        <v>17.661000000000001</v>
-      </c>
-      <c r="Q14" s="3">
-        <f t="shared" ref="Q14" si="6">P14/P$32*100</f>
-        <v>8.1471759824149039</v>
-      </c>
-      <c r="R14">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C15" s="105" t="s">
-        <v>180</v>
-      </c>
-      <c r="D15">
-        <v>4.3</v>
-      </c>
-      <c r="E15" s="5">
-        <f>D15/D$45</f>
-        <v>2.6398182822763828E-3</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
-        <f>F15/F$45</f>
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5">
-        <f>H15/H$45</f>
-        <v>0</v>
-      </c>
-      <c r="K15" t="s">
-        <v>163</v>
-      </c>
-      <c r="L15" s="13">
-        <f>(D15)*($R15/100)</f>
-        <v>3.956</v>
-      </c>
-      <c r="M15" s="3">
-        <f t="shared" si="0"/>
-        <v>0.35296815345727672</v>
-      </c>
-      <c r="N15" s="13">
-        <f>(F15)*($R15/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="13">
-        <f>(H15)*($R15/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <f t="shared" ref="Q15" si="7">P15/P$32*100</f>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C16" s="105" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16">
-        <v>1.6</v>
-      </c>
-      <c r="E16" s="5">
-        <f>D16/D$45</f>
-        <v>9.8225796549818905E-4</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5">
-        <f>F16/F$45</f>
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5">
-        <f>H16/H$45</f>
-        <v>0</v>
-      </c>
-      <c r="K16" t="s">
-        <v>164</v>
-      </c>
-      <c r="L16" s="13">
-        <f>(D16)*($R16/100)</f>
-        <v>1.4560000000000002</v>
-      </c>
-      <c r="M16" s="3">
-        <f t="shared" si="0"/>
-        <v>0.12990941138366913</v>
-      </c>
-      <c r="N16" s="13">
-        <f>(F16)*($R16/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O16" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="13">
-        <f>(H16)*($R16/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="3">
-        <f t="shared" ref="Q16" si="8">P16/P$32*100</f>
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C17" s="105" t="s">
-        <v>190</v>
-      </c>
-      <c r="D17">
-        <v>88.6</v>
-      </c>
-      <c r="E17" s="5">
-        <f>D17/D$45</f>
-        <v>5.4392534839462207E-2</v>
-      </c>
-      <c r="F17">
-        <v>2.8</v>
-      </c>
-      <c r="G17" s="5">
-        <f>F17/F$45</f>
-        <v>5.0909090909090904E-2</v>
-      </c>
-      <c r="H17">
-        <v>7.2</v>
-      </c>
-      <c r="I17" s="5">
-        <f>H17/H$45</f>
-        <v>1.4059753954305799E-2</v>
-      </c>
-      <c r="K17" t="s">
-        <v>221</v>
-      </c>
-      <c r="L17" s="13">
-        <f>(D17)*($R17/100)</f>
-        <v>77.967999999999989</v>
-      </c>
-      <c r="M17" s="3">
-        <f t="shared" si="0"/>
-        <v>6.9565776007980151</v>
-      </c>
-      <c r="N17" s="13">
-        <f>(F17)*($R17/100)</f>
-        <v>2.464</v>
-      </c>
-      <c r="O17" s="3">
-        <f t="shared" si="0"/>
-        <v>7.270581292416642</v>
-      </c>
-      <c r="P17" s="13">
-        <f>(H17)*($R17/100)</f>
-        <v>6.3360000000000003</v>
-      </c>
-      <c r="Q17" s="3">
-        <f t="shared" ref="Q17" si="9">P17/P$32*100</f>
-        <v>2.9228530108476773</v>
-      </c>
-      <c r="R17">
-        <v>88</v>
-      </c>
-      <c r="V17" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C18" s="105" t="s">
-        <v>194</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18" s="5">
-        <f>D18/D$45</f>
-        <v>0</v>
-      </c>
       <c r="F18">
         <v>0.9</v>
       </c>
       <c r="G18" s="5">
-        <f>F18/F$45</f>
+        <f t="shared" si="1"/>
         <v>1.6363636363636365E-2</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18" s="5">
-        <f>H18/H$45</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>223</v>
-      </c>
-      <c r="L18" s="13">
-        <f>(D18)*($R18/100)</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="13">
-        <f>(F18)*($R18/100)</f>
-        <v>0.78300000000000003</v>
-      </c>
-      <c r="O18" s="3">
-        <f t="shared" si="0"/>
-        <v>2.3104160519327235</v>
-      </c>
-      <c r="P18" s="13">
-        <f>(H18)*($R18/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="3">
-        <f t="shared" ref="Q18" si="10">P18/P$32*100</f>
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="L18" s="3">
+        <f>(D17)*($R18/100)</f>
+        <v>77.967999999999989</v>
+      </c>
+      <c r="M18" s="62">
+        <f>L18/L$34*100</f>
+        <v>6.9423309627711633</v>
+      </c>
+      <c r="N18" s="3">
+        <f>(F17)*($R18/100)</f>
+        <v>2.464</v>
+      </c>
+      <c r="O18" s="62">
+        <f>N18/N$34*100</f>
+        <v>7.1648735097412057</v>
+      </c>
+      <c r="P18" s="3">
+        <f>(H17)*($R18/100)</f>
+        <v>6.3360000000000003</v>
+      </c>
+      <c r="Q18" s="62">
+        <f>P18/P$34*100</f>
+        <v>2.6397965156852488</v>
       </c>
       <c r="R18">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="V18" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C19" s="105" t="s">
+      <c r="C19" s="93" t="s">
         <v>191</v>
       </c>
       <c r="D19">
         <v>40.700000000000003</v>
       </c>
       <c r="E19" s="5">
-        <f>D19/D$45</f>
+        <f t="shared" si="0"/>
         <v>2.4986186997360181E-2</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
       <c r="G19" s="5">
-        <f>F19/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H19">
         <v>8.6999999999999993</v>
       </c>
       <c r="I19" s="5">
-        <f>H19/H$45</f>
+        <f t="shared" si="2"/>
         <v>1.698886936145284E-2</v>
       </c>
       <c r="K19" t="s">
         <v>222</v>
       </c>
-      <c r="L19" s="13">
-        <f>(D19)*($R19/100)</f>
-        <v>36.223000000000006</v>
-      </c>
-      <c r="M19" s="3">
-        <f t="shared" si="0"/>
-        <v>3.2319427256529165</v>
-      </c>
-      <c r="N19" s="13">
-        <f>(F19)*($R19/100)</f>
+      <c r="L19" s="3">
+        <f>(D18)*($R19/100)</f>
         <v>0</v>
       </c>
-      <c r="O19" s="3">
-        <f t="shared" si="0"/>
+      <c r="M19" s="62">
+        <f>L19/L$34*100</f>
         <v>0</v>
       </c>
-      <c r="P19" s="13">
-        <f>(H19)*($R19/100)</f>
-        <v>7.7429999999999994</v>
-      </c>
-      <c r="Q19" s="3">
-        <f t="shared" ref="Q19" si="11">P19/P$32*100</f>
-        <v>3.5719145932754999</v>
+      <c r="N19" s="3">
+        <f>(F18)*($R19/100)</f>
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="O19" s="62">
+        <f>N19/N$34*100</f>
+        <v>2.2768246583309106</v>
+      </c>
+      <c r="P19" s="3">
+        <f>(H18)*($R19/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="62">
+        <f>P19/P$34*100</f>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>89</v>
+        <v>87</v>
+      </c>
+      <c r="V19" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C20" s="105" t="s">
+      <c r="C20" s="93" t="s">
         <v>187</v>
       </c>
       <c r="D20">
         <v>5.5</v>
       </c>
       <c r="E20" s="5">
-        <f>D20/D$45</f>
+        <f t="shared" si="0"/>
         <v>3.3765117564000242E-3</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20" s="5">
-        <f>F20/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H20">
         <v>0.4</v>
       </c>
       <c r="I20" s="5">
-        <f>H20/H$45</f>
+        <f t="shared" si="2"/>
         <v>7.810974419058778E-4</v>
       </c>
       <c r="K20" t="s">
-        <v>218</v>
-      </c>
-      <c r="L20" s="13">
-        <f>(D20)*($R20/100)</f>
-        <v>4.95</v>
-      </c>
-      <c r="M20" s="3">
-        <f t="shared" si="0"/>
-        <v>0.44165630930574318</v>
-      </c>
-      <c r="N20" s="13">
-        <f>(F20)*($R20/100)</f>
+        <v>221</v>
+      </c>
+      <c r="L20" s="3">
+        <f>(D19)*($R20/100)</f>
+        <v>36.223000000000006</v>
+      </c>
+      <c r="M20" s="62">
+        <f>L20/L$34*100</f>
+        <v>3.2253239080707465</v>
+      </c>
+      <c r="N20" s="3">
+        <f>(F19)*($R20/100)</f>
         <v>0</v>
       </c>
-      <c r="O20" s="3">
-        <f t="shared" si="0"/>
+      <c r="O20" s="62">
+        <f>N20/N$34*100</f>
         <v>0</v>
       </c>
-      <c r="P20" s="13">
-        <f>(H20)*($R20/100)</f>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="Q20" s="3">
-        <f t="shared" ref="Q20" si="12">P20/P$32*100</f>
-        <v>0.16607119379816351</v>
+      <c r="P20" s="3">
+        <f>(H19)*($R20/100)</f>
+        <v>7.7429999999999994</v>
+      </c>
+      <c r="Q20" s="62">
+        <f>P20/P$34*100</f>
+        <v>3.2260013290642173</v>
       </c>
       <c r="R20">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C21" s="105" t="s">
+      <c r="C21" s="93" t="s">
         <v>179</v>
       </c>
       <c r="D21">
         <v>1.6</v>
       </c>
       <c r="E21" s="5">
-        <f>D21/D$45</f>
+        <f t="shared" si="0"/>
         <v>9.8225796549818905E-4</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <f>F21/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21" s="5">
-        <f>H21/H$45</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>213</v>
-      </c>
-      <c r="L21" s="13">
-        <f>(D21)*($R21/100)</f>
-        <v>1.4560000000000002</v>
-      </c>
-      <c r="M21" s="3">
-        <f t="shared" si="0"/>
-        <v>0.12990941138366913</v>
-      </c>
-      <c r="N21" s="13">
-        <f>(F21)*($R21/100)</f>
+        <v>217</v>
+      </c>
+      <c r="L21" s="3">
+        <f>(D20)*($R21/100)</f>
+        <v>4.95</v>
+      </c>
+      <c r="M21" s="62">
+        <f>L21/L$34*100</f>
+        <v>0.44075182466803386</v>
+      </c>
+      <c r="N21" s="3">
+        <f>(F20)*($R21/100)</f>
         <v>0</v>
       </c>
-      <c r="O21" s="3">
-        <f t="shared" si="0"/>
+      <c r="O21" s="62">
+        <f>N21/N$34*100</f>
         <v>0</v>
       </c>
-      <c r="P21" s="13">
-        <f>(H21)*($R21/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3">
-        <f t="shared" ref="Q21" si="13">P21/P$32*100</f>
-        <v>0</v>
+      <c r="P21" s="3">
+        <f>(H20)*($R21/100)</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="Q21" s="62">
+        <f>P21/P$34*100</f>
+        <v>0.14998843839120732</v>
       </c>
       <c r="R21">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C22" s="105" t="s">
+      <c r="C22" s="93" t="s">
         <v>183</v>
       </c>
       <c r="D22">
         <v>39.9</v>
       </c>
       <c r="E22" s="5">
-        <f>D22/D$45</f>
+        <f t="shared" si="0"/>
         <v>2.4495058014611083E-2</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
       <c r="G22" s="5">
-        <f>F22/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H22">
         <v>3.3</v>
       </c>
       <c r="I22" s="5">
-        <f>H22/H$45</f>
+        <f t="shared" si="2"/>
         <v>6.444053895723491E-3</v>
       </c>
       <c r="K22" t="s">
-        <v>214</v>
-      </c>
-      <c r="L22" s="13">
-        <f>(D22+D39)*($R22/100)</f>
-        <v>34.713000000000001</v>
-      </c>
-      <c r="M22" s="3">
-        <f t="shared" si="0"/>
-        <v>3.0972152454404571</v>
-      </c>
-      <c r="N22" s="13">
-        <f>(F22+F39)*($R22/100)</f>
+        <v>213</v>
+      </c>
+      <c r="L22" s="3">
+        <f>(D21)*($R22/100)</f>
+        <v>1.4560000000000002</v>
+      </c>
+      <c r="M22" s="62">
+        <f>L22/L$34*100</f>
+        <v>0.12964336499326412</v>
+      </c>
+      <c r="N22" s="3">
+        <f>(F21)*($R22/100)</f>
         <v>0</v>
       </c>
-      <c r="O22" s="3">
-        <f t="shared" si="0"/>
+      <c r="O22" s="62">
+        <f>N22/N$34*100</f>
         <v>0</v>
       </c>
-      <c r="P22" s="13">
-        <f>(H22+H39)*($R22/100)</f>
-        <v>18.443999999999999</v>
-      </c>
-      <c r="Q22" s="3">
-        <f t="shared" ref="Q22" si="14">P22/P$32*100</f>
-        <v>8.5083808289259082</v>
+      <c r="P22" s="3">
+        <f>(H21)*($R22/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="62">
+        <f>P22/P$34*100</f>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>215</v>
       </c>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="93" t="s">
         <v>184</v>
       </c>
       <c r="D23">
         <v>29.7</v>
       </c>
       <c r="E23" s="5">
-        <f>D23/D$45</f>
+        <f t="shared" si="0"/>
         <v>1.8233163484560132E-2</v>
       </c>
       <c r="F23">
         <v>0.5</v>
       </c>
       <c r="G23" s="5">
-        <f>F23/F$45</f>
+        <f t="shared" si="1"/>
         <v>9.0909090909090905E-3</v>
       </c>
       <c r="H23">
         <v>2.2000000000000002</v>
       </c>
       <c r="I23" s="5">
-        <f>H23/H$45</f>
+        <f t="shared" si="2"/>
         <v>4.2960359304823276E-3</v>
       </c>
       <c r="K23" t="s">
-        <v>216</v>
-      </c>
-      <c r="L23" s="13">
-        <f>(D23)*($R23/100)</f>
-        <v>26.135999999999999</v>
-      </c>
-      <c r="M23" s="3">
-        <f t="shared" si="0"/>
-        <v>2.331945313134324</v>
-      </c>
-      <c r="N23" s="13">
-        <f>(F23)*($R23/100)</f>
-        <v>0.44</v>
-      </c>
-      <c r="O23" s="3">
-        <f t="shared" si="0"/>
-        <v>1.2983180879315432</v>
-      </c>
-      <c r="P23" s="13">
-        <f>(H23)*($R23/100)</f>
-        <v>1.9360000000000002</v>
-      </c>
-      <c r="Q23" s="3">
-        <f t="shared" ref="Q23" si="15">P23/P$32*100</f>
-        <v>0.89309397553679037</v>
+        <v>214</v>
+      </c>
+      <c r="L23" s="3">
+        <f>(D22+D39)*($R23/100)</f>
+        <v>34.713000000000001</v>
+      </c>
+      <c r="M23" s="62">
+        <f>L23/L$34*100</f>
+        <v>3.0908723413538302</v>
+      </c>
+      <c r="N23" s="3">
+        <f>(F22+F39)*($R23/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="62">
+        <f>N23/N$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <f>(H22+H39)*($R23/100)</f>
+        <v>18.443999999999999</v>
+      </c>
+      <c r="Q23" s="62">
+        <f>P23/P$34*100</f>
+        <v>7.6844076602428553</v>
       </c>
       <c r="R23">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C24" s="105" t="s">
+      <c r="C24" s="93" t="s">
         <v>192</v>
       </c>
       <c r="D24">
         <v>1.7</v>
       </c>
       <c r="E24" s="5">
-        <f>D24/D$45</f>
+        <f t="shared" si="0"/>
         <v>1.0436490883418256E-3</v>
       </c>
       <c r="F24">
         <v>0</v>
       </c>
       <c r="G24" s="5">
-        <f>F24/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H24">
         <v>0.4</v>
       </c>
       <c r="I24" s="5">
-        <f>H24/H$45</f>
+        <f t="shared" si="2"/>
         <v>7.810974419058778E-4</v>
       </c>
       <c r="K24" t="s">
+        <v>216</v>
+      </c>
+      <c r="L24" s="3">
+        <f>(D23)*($R24/100)</f>
+        <v>26.135999999999999</v>
+      </c>
+      <c r="M24" s="62">
+        <f>L24/L$34*100</f>
+        <v>2.3271696342472188</v>
+      </c>
+      <c r="N24" s="3">
+        <f>(F23)*($R24/100)</f>
+        <v>0.44</v>
+      </c>
+      <c r="O24" s="62">
+        <f>N24/N$34*100</f>
+        <v>1.2794416981680723</v>
+      </c>
+      <c r="P24" s="3">
+        <f>(H23)*($R24/100)</f>
+        <v>1.9360000000000002</v>
+      </c>
+      <c r="Q24" s="62">
+        <f>P24/P$34*100</f>
+        <v>0.80660449090382613</v>
+      </c>
+      <c r="R24">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C25" s="93" t="s">
+        <v>199</v>
+      </c>
+      <c r="D25">
+        <v>60.4</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" si="0"/>
+        <v>3.7080238197556632E-2</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>225</v>
+      </c>
+      <c r="L25" s="3">
+        <f>(D24)*($R25/100)</f>
+        <v>1.53</v>
+      </c>
+      <c r="M25" s="62">
+        <f>L25/L$34*100</f>
+        <v>0.13623238217011954</v>
+      </c>
+      <c r="N25" s="3">
+        <f>(F24)*($R25/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="62">
+        <f>N25/N$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <f>(H24)*($R25/100)</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="Q25" s="62">
+        <f>P25/P$34*100</f>
+        <v>0.14998843839120732</v>
+      </c>
+      <c r="R25">
+        <v>90</v>
+      </c>
+      <c r="V25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C26" s="93" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26">
+        <v>5.2</v>
+      </c>
+      <c r="E26" s="5">
+        <f t="shared" si="0"/>
+        <v>3.1923383878691139E-3</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0.3</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="2"/>
+        <v>5.8582308142940832E-4</v>
+      </c>
+      <c r="K26" t="s">
         <v>226</v>
       </c>
-      <c r="L24" s="13">
-        <f>(D24)*($R24/100)</f>
-        <v>1.53</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="L26" s="3">
+        <f>(D25+D37)*($R26/100)</f>
+        <v>6.6440000000000001</v>
+      </c>
+      <c r="M26" s="62">
+        <f>L26/L$34*100</f>
+        <v>0.59158689355442773</v>
+      </c>
+      <c r="N26" s="3">
+        <f>(F25+F37)*($R26/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="62">
+        <f>N26/N$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <f>(H25+H37)*($R26/100)</f>
+        <v>13.222</v>
+      </c>
+      <c r="Q26" s="62">
+        <f>P26/P$34*100</f>
+        <v>5.5087420344681757</v>
+      </c>
+      <c r="R26">
+        <v>11</v>
+      </c>
+      <c r="V26" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C27" s="93" t="s">
+        <v>178</v>
+      </c>
+      <c r="D27">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E27" s="5">
         <f t="shared" si="0"/>
-        <v>0.13651195014904788</v>
-      </c>
-      <c r="N24" s="13">
-        <f>(F24)*($R24/100)</f>
+        <v>5.3410276873964019E-3</v>
+      </c>
+      <c r="F27">
         <v>0</v>
       </c>
-      <c r="O24" s="3">
+      <c r="G27" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>230</v>
+      </c>
+      <c r="L27">
+        <f>D41</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="62">
+        <f>L27/L$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <f>F41</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="62">
+        <f>N27/N$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <f>H41</f>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="Q27" s="62">
+        <f>P27/P$34*100</f>
+        <v>3.6663840495628457</v>
+      </c>
+      <c r="R27">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C28" s="93" t="s">
+        <v>200</v>
+      </c>
+      <c r="D28">
+        <v>188.4</v>
+      </c>
+      <c r="E28" s="5">
+        <f t="shared" si="0"/>
+        <v>0.11566087543741174</v>
+      </c>
+      <c r="F28">
+        <v>9.6</v>
+      </c>
+      <c r="G28" s="5">
+        <f t="shared" si="1"/>
+        <v>0.17454545454545453</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>211</v>
+      </c>
+      <c r="L28" s="3">
+        <f>(D26)*($R28/100)</f>
+        <v>3.9520000000000004</v>
+      </c>
+      <c r="M28" s="62">
+        <f>L28/L$34*100</f>
+        <v>0.35188913355314549</v>
+      </c>
+      <c r="N28" s="3">
+        <f>(F26)*($R28/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O28" s="62">
+        <f>N28/N$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <f>(H26)*($R28/100)</f>
+        <v>0.22799999999999998</v>
+      </c>
+      <c r="Q28" s="62">
+        <f>P28/P$34*100</f>
+        <v>9.4992677647764617E-2</v>
+      </c>
+      <c r="R28">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C29" s="93" t="s">
+        <v>193</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P24" s="13">
-        <f>(H24)*($R24/100)</f>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="Q24" s="3">
-        <f t="shared" ref="Q24" si="16">P24/P$32*100</f>
-        <v>0.16607119379816351</v>
-      </c>
-      <c r="R24">
-        <v>90</v>
-      </c>
-      <c r="V24" t="s">
+      <c r="F29">
+        <v>0.1</v>
+      </c>
+      <c r="G29" s="5">
+        <f t="shared" si="1"/>
+        <v>1.8181818181818182E-3</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>212</v>
+      </c>
+      <c r="L29" s="3">
+        <f>(D27)*($R29/100)</f>
+        <v>7.7429999999999994</v>
+      </c>
+      <c r="M29" s="62">
+        <f>L29/L$34*100</f>
+        <v>0.68944270270799723</v>
+      </c>
+      <c r="N29" s="3">
+        <f>(F27)*($R29/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="62">
+        <f>N29/N$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <f>(H27)*($R29/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="62">
+        <f>P29/P$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>89</v>
+      </c>
+      <c r="V29" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="25" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C25" s="105" t="s">
-        <v>199</v>
-      </c>
-      <c r="D25">
-        <v>60.4</v>
-      </c>
-      <c r="E25" s="5">
-        <f>D25/D$45</f>
-        <v>3.7080238197556632E-2</v>
-      </c>
-      <c r="F25">
+    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C30" s="93" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30">
         <v>0</v>
       </c>
-      <c r="G25" s="5">
-        <f>F25/F$45</f>
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25" s="5">
-        <f>H25/H$45</f>
-        <v>0</v>
-      </c>
-      <c r="K25" t="s">
-        <v>227</v>
-      </c>
-      <c r="L25" s="13">
-        <f>(D25+D37)*($R25/100)</f>
-        <v>6.6440000000000001</v>
-      </c>
-      <c r="M25" s="3">
-        <f t="shared" si="0"/>
-        <v>0.59280091293481973</v>
-      </c>
-      <c r="N25" s="13">
-        <f>(F25+F37)*($R25/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="3">
+      <c r="E30" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P25" s="13">
-        <f>(H25+H37)*($R25/100)</f>
-        <v>13.222</v>
-      </c>
-      <c r="Q25" s="3">
-        <f t="shared" ref="Q25" si="17">P25/P$32*100</f>
-        <v>6.0994259011092158</v>
-      </c>
-      <c r="R25">
+      <c r="F30">
+        <v>0.5</v>
+      </c>
+      <c r="G30" s="5">
+        <f t="shared" si="1"/>
+        <v>9.0909090909090905E-3</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>227</v>
+      </c>
+      <c r="L30" s="3">
+        <f>(D28+D38)*($R30/100)</f>
+        <v>10.362</v>
+      </c>
+      <c r="M30" s="62">
+        <f>L30/L$34*100</f>
+        <v>0.92264048630508433</v>
+      </c>
+      <c r="N30" s="3">
+        <f>(F28+F38)*($R30/100)</f>
+        <v>0.52800000000000002</v>
+      </c>
+      <c r="O30" s="62">
+        <f>N30/N$34*100</f>
+        <v>1.535330037801687</v>
+      </c>
+      <c r="P30" s="3">
+        <f>(H28+H38)*($R30/100)</f>
+        <v>6.8475000000000001</v>
+      </c>
+      <c r="Q30" s="62">
+        <f>P30/P$34*100</f>
+        <v>2.8529050885660894</v>
+      </c>
+      <c r="R30">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C31" s="93" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E31" s="5">
+        <f t="shared" si="0"/>
+        <v>1.3506047025600098E-3</v>
+      </c>
+      <c r="F31">
+        <v>1.2</v>
+      </c>
+      <c r="G31" s="5">
+        <f t="shared" si="1"/>
+        <v>2.1818181818181816E-2</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>245</v>
+      </c>
+      <c r="L31" s="3">
+        <f>(D29)*($R31/100)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="62">
+        <f>L31/L$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <f>(F29)*($R31/100)</f>
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="O31" s="62">
+        <f>N31/N$34*100</f>
+        <v>0.28205873800523412</v>
+      </c>
+      <c r="P31" s="3">
+        <f>(H29)*($R31/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="62">
+        <f>P31/P$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>97</v>
+      </c>
+      <c r="V31" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="C32" s="93" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E32" s="5">
+        <f t="shared" si="0"/>
+        <v>1.4119958254036463E-3</v>
+      </c>
+      <c r="F32">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="5">
+        <f t="shared" si="1"/>
+        <v>9.0909090909090905E-3</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="3">
+        <f>(D30+D40)*($R32/100)</f>
+        <v>0</v>
+      </c>
+      <c r="M32" s="62">
+        <f>L32/L$34*100</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <f>(F30+F40)*($R32/100)</f>
+        <v>0.46</v>
+      </c>
+      <c r="O32" s="62">
+        <f>N32/N$34*100</f>
+        <v>1.337598138993894</v>
+      </c>
+      <c r="P32" s="3">
+        <f>(H30+H40)*($R32/100)</f>
+        <v>14.444000000000001</v>
+      </c>
+      <c r="Q32" s="62">
+        <f>P32/P$34*100</f>
+        <v>6.0178694558961068</v>
+      </c>
+      <c r="R32">
+        <v>92</v>
+      </c>
+      <c r="V32" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33">
+        <v>62.6</v>
+      </c>
+      <c r="E33" s="5">
+        <f t="shared" si="0"/>
+        <v>3.8430842900116641E-2</v>
+      </c>
+      <c r="F33">
+        <v>1.8</v>
+      </c>
+      <c r="G33" s="5">
+        <f t="shared" si="1"/>
+        <v>3.272727272727273E-2</v>
+      </c>
+      <c r="H33">
         <v>11</v>
       </c>
-      <c r="V25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C26" s="105" t="s">
-        <v>177</v>
-      </c>
-      <c r="D26">
-        <v>5.2</v>
-      </c>
-      <c r="E26" s="5">
-        <f>D26/D$45</f>
-        <v>3.1923383878691139E-3</v>
-      </c>
-      <c r="F26">
+      <c r="I33" s="5">
+        <f t="shared" si="2"/>
+        <v>2.1480179652411637E-2</v>
+      </c>
+      <c r="K33" t="s">
+        <v>224</v>
+      </c>
+      <c r="L33" s="3">
+        <f>(D31)*($R33/100)</f>
+        <v>2.0240000000000005</v>
+      </c>
+      <c r="M33" s="62">
+        <f>L33/L$34*100</f>
+        <v>0.18021852386426279</v>
+      </c>
+      <c r="N33" s="3">
+        <f>(F31)*($R33/100)</f>
+        <v>1.1040000000000001</v>
+      </c>
+      <c r="O33" s="62">
+        <f>N33/N$34*100</f>
+        <v>3.2102355335853456</v>
+      </c>
+      <c r="P33" s="3">
+        <f>(H31)*($R33/100)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="5">
-        <f>F26/F$45</f>
+      <c r="Q33" s="62">
+        <f>P33/P$34*100</f>
         <v>0</v>
       </c>
-      <c r="H26">
-        <v>0.3</v>
-      </c>
-      <c r="I26" s="5">
-        <f>H26/H$45</f>
-        <v>5.8582308142940832E-4</v>
-      </c>
-      <c r="K26" t="s">
-        <v>211</v>
-      </c>
-      <c r="L26" s="13">
-        <f>(D26)*($R26/100)</f>
-        <v>3.9520000000000004</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="R33">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34">
+        <v>5.8</v>
+      </c>
+      <c r="E34" s="5">
         <f t="shared" si="0"/>
-        <v>0.35261125946995903</v>
-      </c>
-      <c r="N26" s="13">
-        <f>(F26)*($R26/100)</f>
+        <v>3.5606851249309346E-3</v>
+      </c>
+      <c r="F34">
+        <v>0.2</v>
+      </c>
+      <c r="G34" s="5">
+        <f t="shared" si="1"/>
+        <v>3.6363636363636364E-3</v>
+      </c>
+      <c r="H34">
+        <v>1.4</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="2"/>
+        <v>2.7338410466705718E-3</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="L34" s="108">
+        <f>SUM(L8:L33)</f>
+        <v>1123.0809999999997</v>
+      </c>
+      <c r="M34" s="108">
+        <f>L34/L$34*100</f>
+        <v>100</v>
+      </c>
+      <c r="N34" s="108">
+        <f>SUM(N8:N33)</f>
+        <v>34.389999999999993</v>
+      </c>
+      <c r="O34" s="108">
+        <f>N34/N$34*100</f>
+        <v>100</v>
+      </c>
+      <c r="P34" s="108">
+        <f>SUM(P8:P33)</f>
+        <v>240.01850000000005</v>
+      </c>
+      <c r="Q34" s="108">
+        <f>P34/P$34*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35">
+        <v>43.3</v>
+      </c>
+      <c r="E35" s="5">
+        <f t="shared" si="0"/>
+        <v>2.6582356191294735E-2</v>
+      </c>
+      <c r="F35">
+        <v>4.5</v>
+      </c>
+      <c r="G35" s="5">
+        <f t="shared" si="1"/>
+        <v>8.1818181818181818E-2</v>
+      </c>
+      <c r="H35">
         <v>0</v>
       </c>
-      <c r="O26" s="3">
+      <c r="I35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P26" s="13">
-        <f>(H26)*($R26/100)</f>
-        <v>0.22799999999999998</v>
-      </c>
-      <c r="Q26" s="3">
-        <f t="shared" ref="Q26" si="18">P26/P$32*100</f>
-        <v>0.10517842273883686</v>
-      </c>
-      <c r="R26">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C27" s="105" t="s">
-        <v>178</v>
-      </c>
-      <c r="D27">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="E27" s="5">
-        <f>D27/D$45</f>
-        <v>5.3410276873964019E-3</v>
-      </c>
-      <c r="F27">
+      <c r="F36">
+        <v>0.2</v>
+      </c>
+      <c r="G36" s="5">
+        <f t="shared" si="1"/>
+        <v>3.6363636363636364E-3</v>
+      </c>
+      <c r="H36">
         <v>0</v>
       </c>
-      <c r="G27" s="5">
-        <f>F27/F$45</f>
+      <c r="I36" s="5">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H27">
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B37" s="87" t="s">
+        <v>229</v>
+      </c>
+      <c r="C37" s="93" t="s">
+        <v>202</v>
+      </c>
+      <c r="D37">
         <v>0</v>
       </c>
-      <c r="I27" s="5">
-        <f>H27/H$45</f>
-        <v>0</v>
-      </c>
-      <c r="K27" t="s">
-        <v>212</v>
-      </c>
-      <c r="L27" s="13">
-        <f>(D27)*($R27/100)</f>
-        <v>7.7429999999999994</v>
-      </c>
-      <c r="M27" s="3">
-        <f t="shared" si="0"/>
-        <v>0.69085753595037758</v>
-      </c>
-      <c r="N27" s="13">
-        <f>(F27)*($R27/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="E37" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P27" s="13">
-        <f>(H27)*($R27/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
-        <f t="shared" ref="Q27" si="19">P27/P$32*100</f>
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>89</v>
-      </c>
-      <c r="V27" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C28" s="105" t="s">
-        <v>200</v>
-      </c>
-      <c r="D28">
-        <v>188.4</v>
-      </c>
-      <c r="E28" s="5">
-        <f>D28/D$45</f>
-        <v>0.11566087543741174</v>
-      </c>
-      <c r="F28">
-        <v>9.6</v>
-      </c>
-      <c r="G28" s="5">
-        <f>F28/F$45</f>
-        <v>0.17454545454545453</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28" s="5">
-        <f>H28/H$45</f>
-        <v>0</v>
-      </c>
-      <c r="K28" t="s">
-        <v>228</v>
-      </c>
-      <c r="L28" s="13">
-        <f>(D28+D38)*($R28/100)</f>
-        <v>10.362</v>
-      </c>
-      <c r="M28" s="3">
-        <f t="shared" si="0"/>
-        <v>0.92453387414668897</v>
-      </c>
-      <c r="N28" s="13">
-        <f>(F28+F38)*($R28/100)</f>
-        <v>0.52800000000000002</v>
-      </c>
-      <c r="O28" s="3">
-        <f t="shared" si="0"/>
-        <v>1.557981705517852</v>
-      </c>
-      <c r="P28" s="13">
-        <f>(H28+H38)*($R28/100)</f>
-        <v>6.8475000000000001</v>
-      </c>
-      <c r="Q28" s="3">
-        <f t="shared" ref="Q28" si="20">P28/P$32*100</f>
-        <v>3.1588124987025679</v>
-      </c>
-      <c r="R28">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C29" s="105" t="s">
-        <v>193</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5">
-        <f>D29/D$45</f>
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0.1</v>
-      </c>
-      <c r="G29" s="5">
-        <f>F29/F$45</f>
-        <v>1.8181818181818182E-3</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29" s="5">
-        <f>H29/H$45</f>
-        <v>0</v>
-      </c>
-      <c r="K29" t="s">
-        <v>248</v>
-      </c>
-      <c r="L29" s="13">
-        <f>(D29)*($R29/100)</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="13">
-        <f>(F29)*($R29/100)</f>
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="O29" s="3">
-        <f t="shared" si="0"/>
-        <v>0.28622012393036295</v>
-      </c>
-      <c r="P29" s="13">
-        <f>(H29)*($R29/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <f t="shared" ref="Q29" si="21">P29/P$32*100</f>
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>97</v>
-      </c>
-      <c r="V29" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C30" s="105" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" s="5">
-        <f>D30/D$45</f>
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0.5</v>
-      </c>
-      <c r="G30" s="5">
-        <f>F30/F$45</f>
-        <v>9.0909090909090905E-3</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5">
-        <f>H30/H$45</f>
-        <v>0</v>
-      </c>
-      <c r="K30" t="s">
-        <v>224</v>
-      </c>
-      <c r="L30" s="13">
-        <f>(D30)*($R30/100)</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N30" s="13">
-        <f>(F30)*($R30/100)</f>
-        <v>0.46</v>
-      </c>
-      <c r="O30" s="3">
-        <f t="shared" si="0"/>
-        <v>1.3573325464738861</v>
-      </c>
-      <c r="P30" s="13">
-        <f>(H30)*($R30/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="3">
-        <f t="shared" ref="Q30" si="22">P30/P$32*100</f>
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>92</v>
-      </c>
-      <c r="V30" t="s">
-        <v>243</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C31" s="105" t="s">
-        <v>196</v>
-      </c>
-      <c r="D31">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E31" s="5">
-        <f>D31/D$45</f>
-        <v>1.3506047025600098E-3</v>
-      </c>
-      <c r="F31">
-        <v>1.2</v>
-      </c>
-      <c r="G31" s="5">
-        <f>F31/F$45</f>
-        <v>2.1818181818181816E-2</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31" s="5">
-        <f>H31/H$45</f>
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
-        <v>225</v>
-      </c>
-      <c r="L31" s="13">
-        <f>(D31)*($R31/100)</f>
-        <v>2.0240000000000005</v>
-      </c>
-      <c r="M31" s="3">
-        <f t="shared" si="0"/>
-        <v>0.18058835758279279</v>
-      </c>
-      <c r="N31" s="13">
-        <f>(F31)*($R31/100)</f>
-        <v>1.1040000000000001</v>
-      </c>
-      <c r="O31" s="3">
-        <f t="shared" si="0"/>
-        <v>3.2575981115373271</v>
-      </c>
-      <c r="P31" s="13">
-        <f>(H31)*($R31/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="3">
-        <f t="shared" ref="Q31" si="23">P31/P$32*100</f>
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C32" t="s">
-        <v>197</v>
-      </c>
-      <c r="D32">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E32" s="5">
-        <f>D32/D$45</f>
-        <v>1.4119958254036463E-3</v>
-      </c>
-      <c r="F32">
-        <v>0.5</v>
-      </c>
-      <c r="G32" s="5">
-        <f>F32/F$45</f>
-        <v>9.0909090909090905E-3</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5">
-        <f>H32/H$45</f>
-        <v>0</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="L32" s="13">
-        <f>SUM(L8:L31)</f>
-        <v>1120.7809999999997</v>
-      </c>
-      <c r="M32" s="13">
-        <f>L32/L$32*100</f>
-        <v>100</v>
-      </c>
-      <c r="N32" s="13">
-        <f>SUM(N8:N31)</f>
-        <v>33.89</v>
-      </c>
-      <c r="O32" s="13">
-        <f>N32/N$32*100</f>
-        <v>100</v>
-      </c>
-      <c r="P32" s="13">
-        <f>SUM(P8:P31)</f>
-        <v>216.77450000000005</v>
-      </c>
-      <c r="Q32" s="13">
-        <f>P32/P$32*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D33">
-        <v>62.6</v>
-      </c>
-      <c r="E33" s="5">
-        <f>D33/D$45</f>
-        <v>3.8430842900116641E-2</v>
-      </c>
-      <c r="F33">
-        <v>1.8</v>
-      </c>
-      <c r="G33" s="5">
-        <f>F33/F$45</f>
-        <v>3.272727272727273E-2</v>
-      </c>
-      <c r="H33">
-        <v>11</v>
-      </c>
-      <c r="I33" s="5">
-        <f>H33/H$45</f>
-        <v>2.1480179652411637E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
-        <v>186</v>
-      </c>
-      <c r="D34">
-        <v>5.8</v>
-      </c>
-      <c r="E34" s="5">
-        <f>D34/D$45</f>
-        <v>3.5606851249309346E-3</v>
-      </c>
-      <c r="F34">
-        <v>0.2</v>
-      </c>
-      <c r="G34" s="5">
-        <f>F34/F$45</f>
-        <v>3.6363636363636364E-3</v>
-      </c>
-      <c r="H34">
-        <v>1.4</v>
-      </c>
-      <c r="I34" s="5">
-        <f>H34/H$45</f>
-        <v>2.7338410466705718E-3</v>
-      </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C35" t="s">
-        <v>201</v>
-      </c>
-      <c r="D35">
-        <v>43.3</v>
-      </c>
-      <c r="E35" s="5">
-        <f>D35/D$45</f>
-        <v>2.6582356191294735E-2</v>
-      </c>
-      <c r="F35">
-        <v>4.5</v>
-      </c>
-      <c r="G35" s="5">
-        <f>F35/F$45</f>
-        <v>8.1818181818181818E-2</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5">
-        <f>H35/H$45</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" t="s">
-        <v>185</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36" s="5">
-        <f>D36/D$45</f>
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>0.2</v>
-      </c>
-      <c r="G36" s="5">
-        <f>F36/F$45</f>
-        <v>3.6363636363636364E-3</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5">
-        <f>H36/H$45</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B37" s="87" t="s">
-        <v>230</v>
-      </c>
-      <c r="C37" s="105" t="s">
-        <v>202</v>
-      </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37" s="5">
-        <f>D37/D$45</f>
-        <v>0</v>
-      </c>
       <c r="F37">
         <v>0</v>
       </c>
       <c r="G37" s="5">
-        <f>F37/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H37">
         <v>120.2</v>
       </c>
       <c r="I37" s="5">
-        <f>H37/H$45</f>
+        <f t="shared" si="2"/>
         <v>0.23471978129271626</v>
       </c>
       <c r="K37" s="87" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L37" s="87"/>
       <c r="M37" s="87"/>
@@ -10704,33 +10908,33 @@
       <c r="P37" s="87"/>
       <c r="Q37" s="87"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C38" s="105" t="s">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C38" s="93" t="s">
         <v>203</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38" s="5">
-        <f>D38/D$45</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F38">
         <v>0</v>
       </c>
       <c r="G38" s="5">
-        <f>F38/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H38">
         <v>124.5</v>
       </c>
       <c r="I38" s="5">
-        <f>H38/H$45</f>
+        <f t="shared" si="2"/>
         <v>0.24311657879320445</v>
       </c>
       <c r="K38" s="87" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L38" s="87"/>
       <c r="M38" s="87"/>
@@ -10739,29 +10943,29 @@
       <c r="P38" s="87"/>
       <c r="Q38" s="87"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C39" s="105" t="s">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C39" s="93" t="s">
         <v>204</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39" s="5">
-        <f>D39/D$45</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <f>F39/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H39">
         <v>17.899999999999999</v>
       </c>
       <c r="I39" s="5">
-        <f>H39/H$45</f>
+        <f t="shared" si="2"/>
         <v>3.4954110525288025E-2</v>
       </c>
       <c r="K39" s="87" t="s">
@@ -10774,33 +10978,33 @@
       <c r="P39" s="87"/>
       <c r="Q39" s="87"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C40" t="s">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C40" s="93" t="s">
         <v>205</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40" s="5">
-        <f>D40/D$45</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40" s="5">
-        <f>F40/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H40">
         <v>15.7</v>
       </c>
       <c r="I40" s="5">
-        <f>H40/H$45</f>
+        <f t="shared" si="2"/>
         <v>3.0658074594805698E-2</v>
       </c>
       <c r="K40" s="87" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L40" s="87"/>
       <c r="M40" s="87"/>
@@ -10809,33 +11013,33 @@
       <c r="P40" s="87"/>
       <c r="Q40" s="87"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="C41" t="s">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="C41" s="93" t="s">
         <v>206</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41" s="5">
-        <f>D41/D$45</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F41">
         <v>0</v>
       </c>
       <c r="G41" s="5">
-        <f>F41/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H41">
         <v>8.8000000000000007</v>
       </c>
       <c r="I41" s="5">
-        <f>H41/H$45</f>
+        <f t="shared" si="2"/>
         <v>1.718414372192931E-2</v>
       </c>
       <c r="K41" s="87" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L41" s="87"/>
       <c r="M41" s="87"/>
@@ -10844,7 +11048,7 @@
       <c r="P41" s="87"/>
       <c r="Q41" s="87"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>207</v>
       </c>
@@ -10852,25 +11056,25 @@
         <v>0</v>
       </c>
       <c r="E42" s="5">
-        <f>D42/D$45</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F42">
         <v>0</v>
       </c>
       <c r="G42" s="5">
-        <f>F42/F$45</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H42">
         <v>4.7</v>
       </c>
       <c r="I42" s="5">
-        <f>H42/H$45</f>
+        <f t="shared" si="2"/>
         <v>9.1778949423940628E-3</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>198</v>
       </c>
@@ -10884,7 +11088,7 @@
         <v>330.2</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C44" s="4" t="s">
         <v>208</v>
       </c>
@@ -10901,9 +11105,9 @@
       </c>
       <c r="I44" s="4"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C45" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D45" s="4">
         <f>SUM(D8:D42)</f>
@@ -13178,19 +13382,19 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="40"/>
-      <c r="C23" s="96" t="s">
+      <c r="C23" s="102" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="98" t="s">
+      <c r="D23" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="91" t="s">
+      <c r="E23" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="93" t="s">
+      <c r="F23" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="95"/>
+      <c r="G23" s="101"/>
       <c r="H23" s="31"/>
       <c r="O23">
         <v>11</v>
@@ -13212,11 +13416,11 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="41"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="95"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="101"/>
       <c r="H24" s="18"/>
       <c r="O24">
         <v>13</v>
@@ -13237,13 +13441,13 @@
       </c>
     </row>
     <row r="25" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="101" t="s">
+      <c r="B25" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="101"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="107"/>
       <c r="G25" s="42"/>
       <c r="H25" s="18"/>
       <c r="O25">
@@ -13265,13 +13469,13 @@
       </c>
     </row>
     <row r="26" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="90" t="s">
+      <c r="B26" s="96" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+      <c r="E26" s="96"/>
+      <c r="F26" s="96"/>
       <c r="G26" s="42"/>
       <c r="H26" s="18"/>
       <c r="O26">
@@ -13463,25 +13667,25 @@
       <c r="R33" s="3"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="100" t="s">
+      <c r="B34" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="100"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
+      <c r="C34" s="106"/>
+      <c r="D34" s="106"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="106"/>
       <c r="G34" s="42"/>
       <c r="H34" s="18"/>
       <c r="R34" s="13"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="90" t="s">
+      <c r="B35" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="90"/>
-      <c r="D35" s="90"/>
-      <c r="E35" s="90"/>
-      <c r="F35" s="90"/>
+      <c r="C35" s="96"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="96"/>
       <c r="G35" s="42"/>
       <c r="H35" s="18"/>
     </row>

--- a/data/prod_parameters/PigHerd.xlsx
+++ b/data/prod_parameters/PigHerd.xlsx
@@ -1389,6 +1389,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1425,9 +1428,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -8228,7 +8228,7 @@
       <c r="B79" s="94"/>
       <c r="C79" s="94"/>
       <c r="D79" s="95"/>
-      <c r="E79" s="109"/>
+      <c r="E79" s="97"/>
       <c r="F79" s="95"/>
       <c r="G79" s="95"/>
       <c r="H79" s="94"/>
@@ -8240,7 +8240,7 @@
       <c r="D80" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E80" s="110">
+      <c r="E80" s="98">
         <v>0</v>
       </c>
       <c r="F80" s="88"/>
@@ -8507,7 +8507,7 @@
       <c r="B95" s="94"/>
       <c r="C95" s="94"/>
       <c r="D95" s="95"/>
-      <c r="E95" s="109"/>
+      <c r="E95" s="97"/>
       <c r="F95" s="95"/>
       <c r="G95" s="95"/>
       <c r="H95" s="94"/>
@@ -8519,7 +8519,7 @@
       <c r="D96" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E96" s="110">
+      <c r="E96" s="98">
         <v>0</v>
       </c>
       <c r="F96" s="88"/>
@@ -8861,7 +8861,7 @@
       <c r="D116" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E116" s="110">
+      <c r="E116" s="98">
         <v>0</v>
       </c>
       <c r="F116" s="88"/>
@@ -9308,27 +9308,27 @@
         <v>70</v>
       </c>
       <c r="L8" s="3">
-        <f t="shared" ref="L8:L21" si="3">(D8)*($R8/100)</f>
+        <f t="shared" ref="L8:L16" si="3">(D8)*($R8/100)</f>
         <v>450.31200000000001</v>
       </c>
       <c r="M8" s="62">
-        <f>L8/L$34*100</f>
+        <f t="shared" ref="M8:M34" si="4">L8/L$34*100</f>
         <v>40.096128418163971</v>
       </c>
       <c r="N8" s="3">
-        <f t="shared" ref="N8:N21" si="4">(F8)*($R8/100)</f>
+        <f t="shared" ref="N8:N16" si="5">(F8)*($R8/100)</f>
         <v>12.963000000000001</v>
       </c>
       <c r="O8" s="62">
-        <f>N8/N$34*100</f>
+        <f t="shared" ref="O8:O34" si="6">N8/N$34*100</f>
         <v>37.694097121256185</v>
       </c>
       <c r="P8" s="3">
-        <f t="shared" ref="P8:P21" si="5">(H8)*($R8/100)</f>
+        <f t="shared" ref="P8:P16" si="7">(H8)*($R8/100)</f>
         <v>70.556999999999988</v>
       </c>
       <c r="Q8" s="62">
-        <f>P8/P$34*100</f>
+        <f t="shared" ref="Q8:Q34" si="8">P8/P$34*100</f>
         <v>29.396484021023365</v>
       </c>
       <c r="R8">
@@ -9368,23 +9368,23 @@
         <v>378.71100000000001</v>
       </c>
       <c r="M9" s="62">
-        <f>L9/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>33.720720054920363</v>
       </c>
       <c r="N9" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.744999999999999</v>
       </c>
       <c r="O9" s="62">
-        <f>N9/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>34.152369874963654</v>
       </c>
       <c r="P9" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>54.201000000000001</v>
       </c>
       <c r="Q9" s="62">
-        <f>P9/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>22.582009303449521</v>
       </c>
       <c r="R9">
@@ -9424,23 +9424,23 @@
         <v>54.984000000000002</v>
       </c>
       <c r="M10" s="62">
-        <f>L10/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>4.8958178439489242</v>
       </c>
       <c r="N10" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.3490000000000002</v>
       </c>
       <c r="O10" s="62">
-        <f>N10/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>6.8304739749927315</v>
       </c>
       <c r="P10" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9.1349999999999998</v>
       </c>
       <c r="Q10" s="62">
-        <f>P10/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>3.8059566241768858</v>
       </c>
       <c r="R10">
@@ -9480,23 +9480,23 @@
         <v>5.0460000000000003</v>
       </c>
       <c r="M11" s="62">
-        <f>L11/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.44929973884341395</v>
       </c>
       <c r="N11" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O11" s="62">
-        <f>N11/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P11" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>8.5259999999999998</v>
       </c>
       <c r="Q11" s="62">
-        <f>P11/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>3.5522261825650929</v>
       </c>
       <c r="R11">
@@ -9536,23 +9536,23 @@
         <v>2.5230000000000001</v>
       </c>
       <c r="M12" s="62">
-        <f>L12/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.22464986942170698</v>
       </c>
       <c r="N12" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.60899999999999999</v>
       </c>
       <c r="O12" s="62">
-        <f>N12/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>1.7708636231462638</v>
       </c>
       <c r="P12" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.17400000000000002</v>
       </c>
       <c r="Q12" s="62">
-        <f>P12/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>7.2494411889083538E-2</v>
       </c>
       <c r="R12">
@@ -9592,23 +9592,23 @@
         <v>8.9610000000000003</v>
       </c>
       <c r="M13" s="62">
-        <f>L13/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.79789436380813161</v>
       </c>
       <c r="N13" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.7000000000000008E-2</v>
       </c>
       <c r="O13" s="62">
-        <f>N13/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0.25298051759232343</v>
       </c>
       <c r="P13" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1.044</v>
       </c>
       <c r="Q13" s="62">
-        <f>P13/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0.43496647133450123</v>
       </c>
       <c r="R13">
@@ -9648,23 +9648,23 @@
         <v>1.131</v>
       </c>
       <c r="M14" s="62">
-        <f>L14/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.10070511387869623</v>
       </c>
       <c r="N14" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.26100000000000001</v>
       </c>
       <c r="O14" s="62">
-        <f>N14/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0.75894155277697029</v>
       </c>
       <c r="P14" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>17.661000000000001</v>
       </c>
       <c r="Q14" s="62">
-        <f>P14/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>7.3581828067419792</v>
       </c>
       <c r="R14">
@@ -9704,23 +9704,23 @@
         <v>3.956</v>
       </c>
       <c r="M15" s="62">
-        <f>L15/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.35224529664378623</v>
       </c>
       <c r="N15" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="62">
-        <f>N15/N$34*100</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="O15" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="Q15" s="62">
-        <f>P15/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R15">
@@ -9760,23 +9760,23 @@
         <v>1.4560000000000002</v>
       </c>
       <c r="M16" s="62">
-        <f>L16/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.12964336499326412</v>
       </c>
       <c r="N16" s="3">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="62">
-        <f>N16/N$34*100</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="O16" s="62">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="Q16" s="62">
-        <f>P16/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R16">
@@ -9816,7 +9816,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="M17" s="62">
-        <f>L17/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.20479377711848037</v>
       </c>
       <c r="N17" s="3">
@@ -9824,7 +9824,7 @@
         <v>0.5</v>
       </c>
       <c r="O17" s="62">
-        <f>N17/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>1.4539110206455368</v>
       </c>
       <c r="P17" s="3">
@@ -9832,7 +9832,7 @@
         <v>0</v>
       </c>
       <c r="Q17" s="62">
-        <f>P17/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R17">
@@ -9872,7 +9872,7 @@
         <v>77.967999999999989</v>
       </c>
       <c r="M18" s="62">
-        <f>L18/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>6.9423309627711633</v>
       </c>
       <c r="N18" s="3">
@@ -9880,7 +9880,7 @@
         <v>2.464</v>
       </c>
       <c r="O18" s="62">
-        <f>N18/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>7.1648735097412057</v>
       </c>
       <c r="P18" s="3">
@@ -9888,7 +9888,7 @@
         <v>6.3360000000000003</v>
       </c>
       <c r="Q18" s="62">
-        <f>P18/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>2.6397965156852488</v>
       </c>
       <c r="R18">
@@ -9931,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="62">
-        <f>L19/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N19" s="3">
@@ -9939,7 +9939,7 @@
         <v>0.78300000000000003</v>
       </c>
       <c r="O19" s="62">
-        <f>N19/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>2.2768246583309106</v>
       </c>
       <c r="P19" s="3">
@@ -9947,7 +9947,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="62">
-        <f>P19/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R19">
@@ -9990,7 +9990,7 @@
         <v>36.223000000000006</v>
       </c>
       <c r="M20" s="62">
-        <f>L20/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>3.2253239080707465</v>
       </c>
       <c r="N20" s="3">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="62">
-        <f>N20/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P20" s="3">
@@ -10006,7 +10006,7 @@
         <v>7.7429999999999994</v>
       </c>
       <c r="Q20" s="62">
-        <f>P20/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>3.2260013290642173</v>
       </c>
       <c r="R20">
@@ -10046,7 +10046,7 @@
         <v>4.95</v>
       </c>
       <c r="M21" s="62">
-        <f>L21/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.44075182466803386</v>
       </c>
       <c r="N21" s="3">
@@ -10054,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="62">
-        <f>N21/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P21" s="3">
@@ -10062,7 +10062,7 @@
         <v>0.36000000000000004</v>
       </c>
       <c r="Q21" s="62">
-        <f>P21/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0.14998843839120732</v>
       </c>
       <c r="R21">
@@ -10105,7 +10105,7 @@
         <v>1.4560000000000002</v>
       </c>
       <c r="M22" s="62">
-        <f>L22/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.12964336499326412</v>
       </c>
       <c r="N22" s="3">
@@ -10113,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="62">
-        <f>N22/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P22" s="3">
@@ -10121,7 +10121,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="62">
-        <f>P22/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R22">
@@ -10164,7 +10164,7 @@
         <v>34.713000000000001</v>
       </c>
       <c r="M23" s="62">
-        <f>L23/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>3.0908723413538302</v>
       </c>
       <c r="N23" s="3">
@@ -10172,7 +10172,7 @@
         <v>0</v>
       </c>
       <c r="O23" s="62">
-        <f>N23/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P23" s="3">
@@ -10180,7 +10180,7 @@
         <v>18.443999999999999</v>
       </c>
       <c r="Q23" s="62">
-        <f>P23/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>7.6844076602428553</v>
       </c>
       <c r="R23">
@@ -10220,7 +10220,7 @@
         <v>26.135999999999999</v>
       </c>
       <c r="M24" s="62">
-        <f>L24/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>2.3271696342472188</v>
       </c>
       <c r="N24" s="3">
@@ -10228,7 +10228,7 @@
         <v>0.44</v>
       </c>
       <c r="O24" s="62">
-        <f>N24/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>1.2794416981680723</v>
       </c>
       <c r="P24" s="3">
@@ -10236,7 +10236,7 @@
         <v>1.9360000000000002</v>
       </c>
       <c r="Q24" s="62">
-        <f>P24/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0.80660449090382613</v>
       </c>
       <c r="R24">
@@ -10276,7 +10276,7 @@
         <v>1.53</v>
       </c>
       <c r="M25" s="62">
-        <f>L25/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.13623238217011954</v>
       </c>
       <c r="N25" s="3">
@@ -10284,7 +10284,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="62">
-        <f>N25/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P25" s="3">
@@ -10292,7 +10292,7 @@
         <v>0.36000000000000004</v>
       </c>
       <c r="Q25" s="62">
-        <f>P25/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0.14998843839120732</v>
       </c>
       <c r="R25">
@@ -10335,7 +10335,7 @@
         <v>6.6440000000000001</v>
       </c>
       <c r="M26" s="62">
-        <f>L26/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.59158689355442773</v>
       </c>
       <c r="N26" s="3">
@@ -10343,7 +10343,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="62">
-        <f>N26/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P26" s="3">
@@ -10351,7 +10351,7 @@
         <v>13.222</v>
       </c>
       <c r="Q26" s="62">
-        <f>P26/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>5.5087420344681757</v>
       </c>
       <c r="R26">
@@ -10394,7 +10394,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="62">
-        <f>L27/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N27">
@@ -10402,7 +10402,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="62">
-        <f>N27/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P27">
@@ -10410,7 +10410,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="Q27" s="62">
-        <f>P27/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>3.6663840495628457</v>
       </c>
       <c r="R27">
@@ -10450,7 +10450,7 @@
         <v>3.9520000000000004</v>
       </c>
       <c r="M28" s="62">
-        <f>L28/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.35188913355314549</v>
       </c>
       <c r="N28" s="3">
@@ -10458,7 +10458,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="62">
-        <f>N28/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P28" s="3">
@@ -10466,7 +10466,7 @@
         <v>0.22799999999999998</v>
       </c>
       <c r="Q28" s="62">
-        <f>P28/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>9.4992677647764617E-2</v>
       </c>
       <c r="R28">
@@ -10506,7 +10506,7 @@
         <v>7.7429999999999994</v>
       </c>
       <c r="M29" s="62">
-        <f>L29/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.68944270270799723</v>
       </c>
       <c r="N29" s="3">
@@ -10514,7 +10514,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="62">
-        <f>N29/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P29" s="3">
@@ -10522,7 +10522,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="62">
-        <f>P29/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R29">
@@ -10565,7 +10565,7 @@
         <v>10.362</v>
       </c>
       <c r="M30" s="62">
-        <f>L30/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.92264048630508433</v>
       </c>
       <c r="N30" s="3">
@@ -10573,7 +10573,7 @@
         <v>0.52800000000000002</v>
       </c>
       <c r="O30" s="62">
-        <f>N30/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>1.535330037801687</v>
       </c>
       <c r="P30" s="3">
@@ -10581,7 +10581,7 @@
         <v>6.8475000000000001</v>
       </c>
       <c r="Q30" s="62">
-        <f>P30/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>2.8529050885660894</v>
       </c>
       <c r="R30">
@@ -10621,7 +10621,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="62">
-        <f>L31/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N31" s="3">
@@ -10629,7 +10629,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="O31" s="62">
-        <f>N31/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>0.28205873800523412</v>
       </c>
       <c r="P31" s="3">
@@ -10637,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="62">
-        <f>P31/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R31">
@@ -10680,7 +10680,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="62">
-        <f>L32/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="N32" s="3">
@@ -10688,7 +10688,7 @@
         <v>0.46</v>
       </c>
       <c r="O32" s="62">
-        <f>N32/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>1.337598138993894</v>
       </c>
       <c r="P32" s="3">
@@ -10696,7 +10696,7 @@
         <v>14.444000000000001</v>
       </c>
       <c r="Q32" s="62">
-        <f>P32/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>6.0178694558961068</v>
       </c>
       <c r="R32">
@@ -10742,7 +10742,7 @@
         <v>2.0240000000000005</v>
       </c>
       <c r="M33" s="62">
-        <f>L33/L$34*100</f>
+        <f t="shared" si="4"/>
         <v>0.18021852386426279</v>
       </c>
       <c r="N33" s="3">
@@ -10750,7 +10750,7 @@
         <v>1.1040000000000001</v>
       </c>
       <c r="O33" s="62">
-        <f>N33/N$34*100</f>
+        <f t="shared" si="6"/>
         <v>3.2102355335853456</v>
       </c>
       <c r="P33" s="3">
@@ -10758,7 +10758,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="62">
-        <f>P33/P$34*100</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R33">
@@ -10793,28 +10793,28 @@
       <c r="K34" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="L34" s="108">
+      <c r="L34" s="96">
         <f>SUM(L8:L33)</f>
         <v>1123.0809999999997</v>
       </c>
-      <c r="M34" s="108">
-        <f>L34/L$34*100</f>
+      <c r="M34" s="96">
+        <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="N34" s="108">
+      <c r="N34" s="96">
         <f>SUM(N8:N33)</f>
         <v>34.389999999999993</v>
       </c>
-      <c r="O34" s="108">
-        <f>N34/N$34*100</f>
+      <c r="O34" s="96">
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="P34" s="108">
+      <c r="P34" s="96">
         <f>SUM(P8:P33)</f>
         <v>240.01850000000005</v>
       </c>
-      <c r="Q34" s="108">
-        <f>P34/P$34*100</f>
+      <c r="Q34" s="96">
+        <f t="shared" si="8"/>
         <v>100</v>
       </c>
     </row>
@@ -13382,19 +13382,19 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="40"/>
-      <c r="C23" s="102" t="s">
+      <c r="C23" s="105" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="104" t="s">
+      <c r="D23" s="107" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="97" t="s">
+      <c r="E23" s="100" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="99" t="s">
+      <c r="F23" s="102" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="101"/>
+      <c r="G23" s="104"/>
       <c r="H23" s="31"/>
       <c r="O23">
         <v>11</v>
@@ -13416,11 +13416,11 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="41"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="105"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="101"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="108"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="104"/>
       <c r="H24" s="18"/>
       <c r="O24">
         <v>13</v>
@@ -13441,13 +13441,13 @@
       </c>
     </row>
     <row r="25" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="107" t="s">
+      <c r="B25" s="110" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="107"/>
-      <c r="D25" s="107"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="107"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
       <c r="G25" s="42"/>
       <c r="H25" s="18"/>
       <c r="O25">
@@ -13469,13 +13469,13 @@
       </c>
     </row>
     <row r="26" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="96" t="s">
+      <c r="B26" s="99" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-      <c r="E26" s="96"/>
-      <c r="F26" s="96"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
       <c r="G26" s="42"/>
       <c r="H26" s="18"/>
       <c r="O26">
@@ -13667,25 +13667,25 @@
       <c r="R33" s="3"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="106" t="s">
+      <c r="B34" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="106"/>
-      <c r="D34" s="106"/>
-      <c r="E34" s="106"/>
-      <c r="F34" s="106"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="109"/>
+      <c r="E34" s="109"/>
+      <c r="F34" s="109"/>
       <c r="G34" s="42"/>
       <c r="H34" s="18"/>
       <c r="R34" s="13"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="96" t="s">
+      <c r="B35" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
+      <c r="C35" s="99"/>
+      <c r="D35" s="99"/>
+      <c r="E35" s="99"/>
+      <c r="F35" s="99"/>
       <c r="G35" s="42"/>
       <c r="H35" s="18"/>
     </row>

--- a/data/prod_parameters/PigHerd.xlsx
+++ b/data/prod_parameters/PigHerd.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\data\prod_parameters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\CIBUSmod\data\prod_parameters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="9000"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="254">
   <si>
     <t>parameter</t>
   </si>
@@ -725,15 +725,9 @@
     <t>Summa exkl. vatten</t>
   </si>
   <si>
-    <t>vad är dessa?</t>
-  </si>
-  <si>
     <t>barley brewers grain</t>
   </si>
   <si>
-    <t>potatoe pulp</t>
-  </si>
-  <si>
     <t>Sojamjöl, 45% Rp i vara</t>
   </si>
   <si>
@@ -767,12 +761,6 @@
     <t>sows, gilts</t>
   </si>
   <si>
-    <t>growing, finishing</t>
-  </si>
-  <si>
-    <t>total</t>
-  </si>
-  <si>
     <t>whey powder</t>
   </si>
   <si>
@@ -789,6 +777,27 @@
   </si>
   <si>
     <t>vegetable oils</t>
+  </si>
+  <si>
+    <t>total, kg DM</t>
+  </si>
+  <si>
+    <t>Feed rations, kg dry matter</t>
+  </si>
+  <si>
+    <t>Feed rations, % of DM</t>
+  </si>
+  <si>
+    <t>growing/ finishing pigs</t>
+  </si>
+  <si>
+    <t>Source: Birgit Landquist (2023) Komplettering till RISE Rapport 2020:59:</t>
+  </si>
+  <si>
+    <t>Uppdaterad och utökad livscykelanalys av svensk grisproduktion. RISE</t>
+  </si>
+  <si>
+    <t>excluded</t>
   </si>
 </sst>
 </file>
@@ -801,7 +810,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -930,6 +939,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -969,7 +994,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1156,13 +1181,110 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1386,10 +1508,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1428,6 +1548,67 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -7861,7 +8042,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>159</v>
@@ -7880,87 +8061,78 @@
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="94" t="s">
-        <v>246</v>
-      </c>
-      <c r="B56" s="94"/>
-      <c r="C56" s="94"/>
-      <c r="D56" s="95"/>
-      <c r="E56" s="95"/>
-      <c r="F56" s="95"/>
-      <c r="G56" s="95"/>
-      <c r="H56" s="94"/>
+      <c r="B56" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="88" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="96">
+        <v>0</v>
+      </c>
+      <c r="F56" s="88"/>
+      <c r="G56" s="88" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C57" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="B57" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E57" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C57,'feed rations'!K$8:K$33,0))</f>
-        <v>40.096128418163971</v>
-      </c>
-      <c r="F57" t="s">
-        <v>23</v>
+      <c r="E57" s="96">
+        <v>0</v>
+      </c>
+      <c r="F57" s="88"/>
+      <c r="G57" s="88" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C58" t="s">
-        <v>160</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="B58" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="D58" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C58,'feed rations'!K$8:K$33,0))</f>
-        <v>33.720720054920363</v>
-      </c>
-      <c r="F58" t="s">
-        <v>23</v>
+      <c r="E58" s="96">
+        <v>0</v>
+      </c>
+      <c r="F58" s="88"/>
+      <c r="G58" s="88" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C59" t="s">
-        <v>161</v>
-      </c>
-      <c r="D59" t="s">
-        <v>71</v>
-      </c>
-      <c r="E59" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C59,'feed rations'!K$8:K$33,0))</f>
-        <v>4.8958178439489242</v>
-      </c>
-      <c r="F59" t="s">
-        <v>23</v>
-      </c>
+      <c r="D59" s="88"/>
+      <c r="E59" s="88"/>
+      <c r="F59" s="88"/>
+      <c r="G59" s="88"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C60" t="s">
-        <v>162</v>
-      </c>
-      <c r="D60" t="s">
-        <v>71</v>
-      </c>
-      <c r="E60" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C60,'feed rations'!K$8:K$33,0))</f>
-        <v>0.44929973884341395</v>
-      </c>
-      <c r="F60" t="s">
-        <v>23</v>
-      </c>
+      <c r="A60" s="93" t="s">
+        <v>242</v>
+      </c>
+      <c r="B60" s="93"/>
+      <c r="C60" s="93"/>
+      <c r="D60" s="94"/>
+      <c r="E60" s="94"/>
+      <c r="F60" s="94"/>
+      <c r="G60" s="94"/>
+      <c r="H60" s="93"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D61" t="s">
         <v>71</v>
       </c>
       <c r="E61" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C61,'feed rations'!K$8:K$33,0))</f>
-        <v>0.22464986942170698</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C61,'feed rations'!$K$8:$K$43,0),MATCH(B61,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>39.939446969082496</v>
       </c>
       <c r="F61" t="s">
         <v>23</v>
@@ -7968,14 +8140,14 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
-        <v>218</v>
+        <v>160</v>
       </c>
       <c r="D62" t="s">
         <v>71</v>
       </c>
       <c r="E62" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C62,'feed rations'!K$8:K$33,0))</f>
-        <v>0.79789436380813161</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C62,'feed rations'!$K$8:$K$43,0),MATCH(B62,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>33.588951440574981</v>
       </c>
       <c r="F62" t="s">
         <v>23</v>
@@ -7983,14 +8155,14 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="D63" t="s">
         <v>71</v>
       </c>
       <c r="E63" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C63,'feed rations'!K$8:K$33,0))</f>
-        <v>0.10070511387869623</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C63,'feed rations'!$K$8:$K$43,0),MATCH(B63,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>4.876686724200181</v>
       </c>
       <c r="F63" t="s">
         <v>23</v>
@@ -7998,323 +8170,314 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D64" t="s">
         <v>71</v>
       </c>
       <c r="E64" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C64,'feed rations'!K$8:K$33,0))</f>
-        <v>0.35224529664378623</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C64,'feed rations'!$K$8:$K$43,0),MATCH(B64,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.44754403481583932</v>
       </c>
       <c r="F64" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D65" t="s">
         <v>71</v>
       </c>
       <c r="E65" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C65,'feed rations'!K$8:K$33,0))</f>
-        <v>0.12964336499326412</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C65,'feed rations'!$K$8:$K$43,0),MATCH(B65,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.22377201740791966</v>
       </c>
       <c r="F65" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="D66" t="s">
         <v>71</v>
       </c>
       <c r="E66" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C66,'feed rations'!K$8:K$33,0))</f>
-        <v>0.20479377711848037</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C66,'feed rations'!$K$8:$K$43,0),MATCH(B66,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.78553488869540378</v>
       </c>
       <c r="F66" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D67" t="s">
         <v>71</v>
       </c>
       <c r="E67" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C67,'feed rations'!K$8:K$33,0))</f>
-        <v>6.9423309627711633</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C67,'feed rations'!$K$8:$K$43,0),MATCH(B67,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>9.9145180126604351E-2</v>
       </c>
       <c r="F67" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
-        <v>221</v>
+        <v>163</v>
       </c>
       <c r="D68" t="s">
         <v>71</v>
       </c>
       <c r="E68" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C68,'feed rations'!K$8:K$33,0))</f>
-        <v>3.2253239080707465</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C68,'feed rations'!$K$8:$K$43,0),MATCH(B68,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.35109057903656365</v>
       </c>
       <c r="F68" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="D69" t="s">
         <v>71</v>
       </c>
       <c r="E69" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C69,'feed rations'!K$8:K$33,0))</f>
-        <v>0.44075182466803386</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C69,'feed rations'!$K$8:$K$43,0),MATCH(B69,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.13063835499034929</v>
       </c>
       <c r="F69" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="D70" t="s">
         <v>71</v>
       </c>
       <c r="E70" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C70,'feed rations'!K$8:K$33,0))</f>
-        <v>0.12964336499326412</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C70,'feed rations'!$K$8:$K$43,0),MATCH(B70,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.20636553329519458</v>
       </c>
       <c r="F70" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="D71" t="s">
         <v>71</v>
       </c>
       <c r="E71" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C71,'feed rations'!K$8:K$33,0))</f>
-        <v>3.0908723413538302</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C71,'feed rations'!$K$8:$K$43,0),MATCH(B71,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>6.9956121304172738</v>
       </c>
       <c r="F71" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C72" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="D72" t="s">
         <v>71</v>
       </c>
       <c r="E72" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C72,'feed rations'!K$8:K$33,0))</f>
-        <v>2.3271696342472188</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C72,'feed rations'!$K$8:$K$43,0),MATCH(B72,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>3.2865954280882512</v>
       </c>
       <c r="F72" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C73" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D73" t="s">
         <v>71</v>
       </c>
       <c r="E73" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C73,'feed rations'!K$8:K$33,0))</f>
-        <v>0.13623238217011954</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C73,'feed rations'!$K$8:$K$43,0),MATCH(B73,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.44906934527932563</v>
       </c>
       <c r="F73" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C74" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="D74" t="s">
         <v>71</v>
       </c>
       <c r="E74" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C74,'feed rations'!K$8:K$33,0))</f>
-        <v>0.59158689355442773</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C74,'feed rations'!$K$8:$K$43,0),MATCH(B74,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.13063835499034929</v>
       </c>
       <c r="F74" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C75" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D75" t="s">
         <v>71</v>
       </c>
       <c r="E75" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C75,'feed rations'!K$8:K$33,0))</f>
-        <v>0.35188913355314549</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C75,'feed rations'!$K$8:$K$43,0),MATCH(B75,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>3.1145942422939523</v>
       </c>
       <c r="F75" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D76" t="s">
         <v>71</v>
       </c>
       <c r="E76" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C76,'feed rations'!K$8:K$33,0))</f>
-        <v>0.68944270270799723</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C76,'feed rations'!$K$8:$K$43,0),MATCH(B76,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.3450302513926982</v>
       </c>
       <c r="F76" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D77" t="s">
         <v>71</v>
       </c>
       <c r="E77" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C77,'feed rations'!K$8:K$33,0))</f>
-        <v>0.92264048630508433</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C77,'feed rations'!$K$8:$K$43,0),MATCH(B77,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.13727794171375987</v>
       </c>
       <c r="F77" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D78" t="s">
         <v>71</v>
       </c>
       <c r="E78" s="62">
-        <f>INDEX('feed rations'!M$8:M$33,MATCH(C78,'feed rations'!K$8:K$33,0))</f>
-        <v>0.18021852386426279</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C78,'feed rations'!$K$8:$K$43,0),MATCH(B78,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.59612721878837949</v>
       </c>
       <c r="F78" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="94" t="s">
-        <v>247</v>
-      </c>
-      <c r="B79" s="94"/>
-      <c r="C79" s="94"/>
-      <c r="D79" s="95"/>
-      <c r="E79" s="97"/>
-      <c r="F79" s="95"/>
-      <c r="G79" s="95"/>
-      <c r="H79" s="94"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B80" s="88" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="88" t="s">
+    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C79" t="s">
+        <v>211</v>
+      </c>
+      <c r="D79" t="s">
         <v>71</v>
       </c>
-      <c r="E80" s="98">
-        <v>0</v>
-      </c>
-      <c r="F80" s="88"/>
-      <c r="G80" s="88" t="s">
-        <v>158</v>
+      <c r="E79" s="62">
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C79,'feed rations'!$K$8:$K$43,0),MATCH(B79,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.35458982068809092</v>
+      </c>
+      <c r="F79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C80" t="s">
+        <v>212</v>
+      </c>
+      <c r="D80" t="s">
+        <v>71</v>
+      </c>
+      <c r="E80" s="62">
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C80,'feed rations'!$K$8:$K$43,0),MATCH(B80,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.69473405404551813</v>
+      </c>
+      <c r="F80" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
-        <v>15</v>
-      </c>
       <c r="C81" t="s">
-        <v>70</v>
+        <v>227</v>
       </c>
       <c r="D81" t="s">
         <v>71</v>
       </c>
       <c r="E81" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C81,'feed rations'!K$8:K$33,0))</f>
-        <v>37.694097121256185</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C81,'feed rations'!$K$8:$K$43,0),MATCH(B81,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>1.0649538207770974</v>
       </c>
       <c r="F81" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B82" t="s">
-        <v>15</v>
-      </c>
       <c r="C82" t="s">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="D82" t="s">
         <v>71</v>
       </c>
       <c r="E82" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C82,'feed rations'!K$8:K$33,0))</f>
-        <v>34.152369874963654</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C82,'feed rations'!$K$8:$K$43,0),MATCH(B82,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.18160166929977128</v>
       </c>
       <c r="F82" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B83" t="s">
-        <v>15</v>
-      </c>
-      <c r="C83" t="s">
-        <v>161</v>
-      </c>
-      <c r="D83" t="s">
-        <v>71</v>
-      </c>
-      <c r="E83" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C83,'feed rations'!K$8:K$33,0))</f>
-        <v>6.8304739749927315</v>
-      </c>
-      <c r="F83" t="s">
-        <v>23</v>
-      </c>
+      <c r="A83" s="93" t="s">
+        <v>243</v>
+      </c>
+      <c r="B83" s="93"/>
+      <c r="C83" s="93"/>
+      <c r="D83" s="94"/>
+      <c r="E83" s="95"/>
+      <c r="F83" s="94"/>
+      <c r="G83" s="94"/>
+      <c r="H83" s="93"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
         <v>15</v>
       </c>
       <c r="C84" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D84" t="s">
         <v>71</v>
       </c>
       <c r="E84" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C84,'feed rations'!K$8:K$33,0))</f>
-        <v>1.7708636231462638</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C84,'feed rations'!$K$8:$K$43,0),MATCH(B84,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>37.344664381805039</v>
       </c>
       <c r="F84" t="s">
         <v>23</v>
@@ -8325,14 +8488,14 @@
         <v>15</v>
       </c>
       <c r="C85" t="s">
-        <v>218</v>
+        <v>160</v>
       </c>
       <c r="D85" t="s">
         <v>71</v>
       </c>
       <c r="E85" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C85,'feed rations'!K$8:K$33,0))</f>
-        <v>0.25298051759232343</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C85,'feed rations'!$K$8:$K$43,0),MATCH(B85,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>33.835769741903896</v>
       </c>
       <c r="F85" t="s">
         <v>23</v>
@@ -8343,14 +8506,14 @@
         <v>15</v>
       </c>
       <c r="C86" t="s">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="D86" t="s">
         <v>71</v>
       </c>
       <c r="E86" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C86,'feed rations'!K$8:K$33,0))</f>
-        <v>0.75894155277697029</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C86,'feed rations'!$K$8:$K$43,0),MATCH(B86,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>7.2684246112238</v>
       </c>
       <c r="F86" t="s">
         <v>23</v>
@@ -8361,14 +8524,14 @@
         <v>15</v>
       </c>
       <c r="C87" t="s">
-        <v>250</v>
+        <v>165</v>
       </c>
       <c r="D87" t="s">
         <v>71</v>
       </c>
       <c r="E87" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C87,'feed rations'!K$8:K$33,0))</f>
-        <v>1.4539110206455368</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C87,'feed rations'!$K$8:$K$43,0),MATCH(B87,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>1.7544473199505721</v>
       </c>
       <c r="F87" t="s">
         <v>23</v>
@@ -8379,14 +8542,14 @@
         <v>15</v>
       </c>
       <c r="C88" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D88" t="s">
         <v>71</v>
       </c>
       <c r="E88" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C88,'feed rations'!K$8:K$33,0))</f>
-        <v>7.1648735097412057</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C88,'feed rations'!$K$8:$K$43,0),MATCH(B88,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.24772096710265556</v>
       </c>
       <c r="F88" t="s">
         <v>23</v>
@@ -8397,14 +8560,14 @@
         <v>15</v>
       </c>
       <c r="C89" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D89" t="s">
         <v>71</v>
       </c>
       <c r="E89" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C89,'feed rations'!K$8:K$33,0))</f>
-        <v>2.2768246583309106</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C89,'feed rations'!$K$8:$K$43,0),MATCH(B89,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.74316290130796658</v>
       </c>
       <c r="F89" t="s">
         <v>23</v>
@@ -8415,14 +8578,14 @@
         <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="D90" t="s">
         <v>71</v>
       </c>
       <c r="E90" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C90,'feed rations'!K$8:K$33,0))</f>
-        <v>1.2794416981680723</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C90,'feed rations'!$K$8:$K$43,0),MATCH(B90,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>1.4571821594273857</v>
       </c>
       <c r="F90" t="s">
         <v>23</v>
@@ -8433,14 +8596,14 @@
         <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D91" t="s">
         <v>71</v>
       </c>
       <c r="E91" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C91,'feed rations'!K$8:K$33,0))</f>
-        <v>1.535330037801687</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C91,'feed rations'!$K$8:$K$43,0),MATCH(B91,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>7.1809936816581557</v>
       </c>
       <c r="F91" t="s">
         <v>23</v>
@@ -8451,14 +8614,14 @@
         <v>15</v>
       </c>
       <c r="C92" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="D92" t="s">
         <v>71</v>
       </c>
       <c r="E92" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C92,'feed rations'!K$8:K$33,0))</f>
-        <v>0.28205873800523412</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C92,'feed rations'!$K$8:$K$43,0),MATCH(B92,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.2819472616632859</v>
       </c>
       <c r="F92" t="s">
         <v>23</v>
@@ -8469,14 +8632,14 @@
         <v>15</v>
       </c>
       <c r="C93" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D93" t="s">
         <v>71</v>
       </c>
       <c r="E93" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C93,'feed rations'!K$8:K$33,0))</f>
-        <v>1.337598138993894</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C93,'feed rations'!$K$8:$K$43,0),MATCH(B93,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>1.2823203002960992</v>
       </c>
       <c r="F93" t="s">
         <v>23</v>
@@ -8487,389 +8650,410 @@
         <v>15</v>
       </c>
       <c r="C94" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D94" t="s">
         <v>71</v>
       </c>
       <c r="E94" s="62">
-        <f>INDEX('feed rations'!O$8:O$33,MATCH(C94,'feed rations'!K$8:K$33,0))</f>
-        <v>3.2102355335853456</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C94,'feed rations'!$K$8:$K$43,0),MATCH(B94,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>1.7626075400433656</v>
       </c>
       <c r="F94" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="94" t="s">
-        <v>248</v>
-      </c>
-      <c r="B95" s="94"/>
-      <c r="C95" s="94"/>
-      <c r="D95" s="95"/>
-      <c r="E95" s="97"/>
-      <c r="F95" s="95"/>
-      <c r="G95" s="95"/>
-      <c r="H95" s="94"/>
+      <c r="B95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" t="s">
+        <v>241</v>
+      </c>
+      <c r="D95" t="s">
+        <v>71</v>
+      </c>
+      <c r="E95" s="62">
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C95,'feed rations'!$K$8:$K$43,0),MATCH(B95,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.2826933389289128</v>
+      </c>
+      <c r="F95" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B96" s="88" t="s">
-        <v>24</v>
-      </c>
-      <c r="D96" s="88" t="s">
+      <c r="B96" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" t="s">
+        <v>223</v>
+      </c>
+      <c r="D96" t="s">
         <v>71</v>
       </c>
-      <c r="E96" s="98">
-        <v>0</v>
-      </c>
-      <c r="F96" s="88"/>
-      <c r="G96" s="88" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E96" s="62">
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C96,'feed rations'!$K$8:$K$43,0),MATCH(B96,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>1.3406075866731948</v>
+      </c>
+      <c r="F96" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C97" t="s">
-        <v>70</v>
+        <v>224</v>
       </c>
       <c r="D97" t="s">
         <v>71</v>
       </c>
       <c r="E97" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C97,'feed rations'!K$8:K$33,0))</f>
-        <v>29.396484021023365</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C97,'feed rations'!$K$8:$K$43,0),MATCH(B97,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>3.2174582080156675</v>
       </c>
       <c r="F97" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B98" t="s">
-        <v>24</v>
-      </c>
-      <c r="C98" t="s">
-        <v>160</v>
-      </c>
-      <c r="D98" t="s">
-        <v>71</v>
-      </c>
-      <c r="E98" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C98,'feed rations'!K$8:K$33,0))</f>
-        <v>22.582009303449521</v>
-      </c>
-      <c r="F98" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="93" t="s">
+        <v>244</v>
+      </c>
+      <c r="B98" s="93"/>
+      <c r="C98" s="93"/>
+      <c r="D98" s="94"/>
+      <c r="E98" s="95"/>
+      <c r="F98" s="94"/>
+      <c r="G98" s="94"/>
+      <c r="H98" s="93"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
         <v>24</v>
       </c>
       <c r="C99" t="s">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="D99" t="s">
         <v>71</v>
       </c>
       <c r="E99" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C99,'feed rations'!K$8:K$33,0))</f>
-        <v>3.8059566241768858</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C99,'feed rations'!$K$8:$K$43,0),MATCH(B99,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>21.826284108458598</v>
       </c>
       <c r="F99" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>24</v>
       </c>
       <c r="C100" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D100" t="s">
         <v>71</v>
       </c>
       <c r="E100" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C100,'feed rations'!K$8:K$33,0))</f>
-        <v>3.5522261825650929</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C100,'feed rations'!$K$8:$K$43,0),MATCH(B100,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>16.76667694151628</v>
       </c>
       <c r="F100" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
         <v>24</v>
       </c>
       <c r="C101" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D101" t="s">
         <v>71</v>
       </c>
       <c r="E101" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C101,'feed rations'!K$8:K$33,0))</f>
-        <v>7.2494411889083538E-2</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C101,'feed rations'!$K$8:$K$43,0),MATCH(B101,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.8258444283454405</v>
       </c>
       <c r="F101" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>24</v>
       </c>
       <c r="C102" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="D102" t="s">
         <v>71</v>
       </c>
       <c r="E102" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C102,'feed rations'!K$8:K$33,0))</f>
-        <v>0.43496647133450123</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C102,'feed rations'!$K$8:$K$43,0),MATCH(B102,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.6374547997890785</v>
       </c>
       <c r="F102" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
         <v>24</v>
       </c>
       <c r="C103" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="D103" t="s">
         <v>71</v>
       </c>
       <c r="E103" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C103,'feed rations'!K$8:K$33,0))</f>
-        <v>7.3581828067419792</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C103,'feed rations'!$K$8:$K$43,0),MATCH(B103,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>5.3825608158960786E-2</v>
       </c>
       <c r="F103" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
         <v>24</v>
       </c>
       <c r="C104" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D104" t="s">
         <v>71</v>
       </c>
       <c r="E104" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C104,'feed rations'!K$8:K$33,0))</f>
-        <v>2.6397965156852488</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C104,'feed rations'!$K$8:$K$43,0),MATCH(B104,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.31919837396593026</v>
       </c>
       <c r="F104" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
         <v>24</v>
       </c>
       <c r="C105" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D105" t="s">
         <v>71</v>
       </c>
       <c r="E105" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C105,'feed rations'!K$8:K$33,0))</f>
-        <v>3.2260013290642173</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C105,'feed rations'!$K$8:$K$43,0),MATCH(B105,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>5.3997724929236526</v>
       </c>
       <c r="F105" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
         <v>24</v>
       </c>
       <c r="C106" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D106" t="s">
         <v>71</v>
       </c>
       <c r="E106" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C106,'feed rations'!K$8:K$33,0))</f>
-        <v>0.14998843839120732</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C106,'feed rations'!$K$8:$K$43,0),MATCH(B106,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>1.9827851935766017</v>
       </c>
       <c r="F106" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
         <v>24</v>
       </c>
       <c r="C107" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D107" t="s">
         <v>71</v>
       </c>
       <c r="E107" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C107,'feed rations'!K$8:K$33,0))</f>
-        <v>7.6844076602428553</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C107,'feed rations'!$K$8:$K$43,0),MATCH(B107,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.4503169295619931</v>
       </c>
       <c r="F107" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
         <v>24</v>
       </c>
       <c r="C108" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D108" t="s">
         <v>71</v>
       </c>
       <c r="E108" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C108,'feed rations'!K$8:K$33,0))</f>
-        <v>0.80660449090382613</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C108,'feed rations'!$K$8:$K$43,0),MATCH(B108,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.11391000796431236</v>
       </c>
       <c r="F108" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
         <v>24</v>
       </c>
       <c r="C109" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D109" t="s">
         <v>71</v>
       </c>
       <c r="E109" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C109,'feed rations'!K$8:K$33,0))</f>
-        <v>0.14998843839120732</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C109,'feed rations'!$K$8:$K$43,0),MATCH(B109,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>5.7718576563015853</v>
       </c>
       <c r="F109" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
         <v>24</v>
       </c>
       <c r="C110" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="D110" t="s">
         <v>71</v>
       </c>
       <c r="E110" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C110,'feed rations'!K$8:K$33,0))</f>
-        <v>5.5087420344681757</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C110,'feed rations'!$K$8:$K$43,0),MATCH(B110,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.60585103137062835</v>
       </c>
       <c r="F110" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
         <v>24</v>
       </c>
       <c r="C111" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D111" t="s">
         <v>71</v>
       </c>
       <c r="E111" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C111,'feed rations'!K$8:K$33,0))</f>
-        <v>3.6663840495628457</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C111,'feed rations'!$K$8:$K$43,0),MATCH(B111,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>33.966462264962807</v>
       </c>
       <c r="F111" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>24</v>
       </c>
       <c r="C112" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="D112" t="s">
         <v>71</v>
       </c>
       <c r="E112" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C112,'feed rations'!K$8:K$33,0))</f>
-        <v>9.4992677647764617E-2</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C112,'feed rations'!$K$8:$K$43,0),MATCH(B112,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0</v>
       </c>
       <c r="F112" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
         <v>24</v>
       </c>
       <c r="C113" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D113" t="s">
         <v>71</v>
       </c>
       <c r="E113" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C113,'feed rations'!K$8:K$33,0))</f>
-        <v>2.8529050885660894</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C113,'feed rations'!$K$8:$K$43,0),MATCH(B113,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.7538683244119473</v>
       </c>
       <c r="F113" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>24</v>
       </c>
       <c r="C114" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="D114" t="s">
         <v>71</v>
       </c>
       <c r="E114" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C114,'feed rations'!K$8:K$33,0))</f>
-        <v>6.0178694558961068</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C114,'feed rations'!$K$8:$K$43,0),MATCH(B114,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>7.1350224768854983E-2</v>
       </c>
       <c r="F114" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E115" s="62"/>
-    </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B116" s="88" t="s">
-        <v>25</v>
-      </c>
-      <c r="D116" s="88" t="s">
+    <row r="115" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" t="s">
+        <v>227</v>
+      </c>
+      <c r="D115" t="s">
         <v>71</v>
       </c>
-      <c r="E116" s="98">
-        <v>0</v>
-      </c>
-      <c r="F116" s="88"/>
-      <c r="G116" s="88" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E115" s="62">
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C115,'feed rations'!$K$8:$K$43,0),MATCH(B115,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.4545416139233072</v>
+      </c>
+      <c r="F115" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" t="s">
+        <v>223</v>
+      </c>
+      <c r="D116" t="s">
+        <v>71</v>
+      </c>
+      <c r="E116" s="62">
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C116,'feed rations'!$K$8:$K$43,0),MATCH(B116,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0</v>
+      </c>
+      <c r="F116" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
         <v>25</v>
       </c>
@@ -8880,14 +9064,14 @@
         <v>71</v>
       </c>
       <c r="E117" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C117,'feed rations'!K$8:K$33,0))</f>
-        <v>29.396484021023365</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C117,'feed rations'!$K$8:$K$43,0),MATCH(B117,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>21.826284108458598</v>
       </c>
       <c r="F117" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>25</v>
       </c>
@@ -8898,14 +9082,14 @@
         <v>71</v>
       </c>
       <c r="E118" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C118,'feed rations'!K$8:K$33,0))</f>
-        <v>22.582009303449521</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C118,'feed rations'!$K$8:$K$43,0),MATCH(B118,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>16.76667694151628</v>
       </c>
       <c r="F118" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>25</v>
       </c>
@@ -8916,14 +9100,14 @@
         <v>71</v>
       </c>
       <c r="E119" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C119,'feed rations'!K$8:K$33,0))</f>
-        <v>3.8059566241768858</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C119,'feed rations'!$K$8:$K$43,0),MATCH(B119,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.8258444283454405</v>
       </c>
       <c r="F119" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>25</v>
       </c>
@@ -8934,14 +9118,14 @@
         <v>71</v>
       </c>
       <c r="E120" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C120,'feed rations'!K$8:K$33,0))</f>
-        <v>3.5522261825650929</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C120,'feed rations'!$K$8:$K$43,0),MATCH(B120,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.6374547997890785</v>
       </c>
       <c r="F120" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>25</v>
       </c>
@@ -8952,14 +9136,14 @@
         <v>71</v>
       </c>
       <c r="E121" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C121,'feed rations'!K$8:K$33,0))</f>
-        <v>7.2494411889083538E-2</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C121,'feed rations'!$K$8:$K$43,0),MATCH(B121,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>5.3825608158960786E-2</v>
       </c>
       <c r="F121" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>25</v>
       </c>
@@ -8970,14 +9154,14 @@
         <v>71</v>
       </c>
       <c r="E122" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C122,'feed rations'!K$8:K$33,0))</f>
-        <v>0.43496647133450123</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C122,'feed rations'!$K$8:$K$43,0),MATCH(B122,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.31919837396593026</v>
       </c>
       <c r="F122" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>25</v>
       </c>
@@ -8988,14 +9172,14 @@
         <v>71</v>
       </c>
       <c r="E123" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C123,'feed rations'!K$8:K$33,0))</f>
-        <v>7.3581828067419792</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C123,'feed rations'!$K$8:$K$43,0),MATCH(B123,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>5.3997724929236526</v>
       </c>
       <c r="F123" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>25</v>
       </c>
@@ -9006,14 +9190,14 @@
         <v>71</v>
       </c>
       <c r="E124" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C124,'feed rations'!K$8:K$33,0))</f>
-        <v>2.6397965156852488</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C124,'feed rations'!$K$8:$K$43,0),MATCH(B124,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>1.9827851935766017</v>
       </c>
       <c r="F124" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="125" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>25</v>
       </c>
@@ -9024,14 +9208,14 @@
         <v>71</v>
       </c>
       <c r="E125" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C125,'feed rations'!K$8:K$33,0))</f>
-        <v>3.2260013290642173</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C125,'feed rations'!$K$8:$K$43,0),MATCH(B125,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.4503169295619931</v>
       </c>
       <c r="F125" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>25</v>
       </c>
@@ -9042,14 +9226,14 @@
         <v>71</v>
       </c>
       <c r="E126" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C126,'feed rations'!K$8:K$33,0))</f>
-        <v>0.14998843839120732</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C126,'feed rations'!$K$8:$K$43,0),MATCH(B126,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.11391000796431236</v>
       </c>
       <c r="F126" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>25</v>
       </c>
@@ -9060,14 +9244,14 @@
         <v>71</v>
       </c>
       <c r="E127" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C127,'feed rations'!K$8:K$33,0))</f>
-        <v>7.6844076602428553</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C127,'feed rations'!$K$8:$K$43,0),MATCH(B127,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>5.7718576563015853</v>
       </c>
       <c r="F127" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>25</v>
       </c>
@@ -9078,8 +9262,8 @@
         <v>71</v>
       </c>
       <c r="E128" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C128,'feed rations'!K$8:K$33,0))</f>
-        <v>0.80660449090382613</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C128,'feed rations'!$K$8:$K$43,0),MATCH(B128,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.60585103137062835</v>
       </c>
       <c r="F128" t="s">
         <v>23</v>
@@ -9096,8 +9280,8 @@
         <v>71</v>
       </c>
       <c r="E129" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C129,'feed rations'!K$8:K$33,0))</f>
-        <v>0.14998843839120732</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C129,'feed rations'!$K$8:$K$43,0),MATCH(B129,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>33.966462264962807</v>
       </c>
       <c r="F129" t="s">
         <v>23</v>
@@ -9114,8 +9298,8 @@
         <v>71</v>
       </c>
       <c r="E130" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C130,'feed rations'!K$8:K$33,0))</f>
-        <v>5.5087420344681757</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C130,'feed rations'!$K$8:$K$43,0),MATCH(B130,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0</v>
       </c>
       <c r="F130" t="s">
         <v>23</v>
@@ -9126,14 +9310,14 @@
         <v>25</v>
       </c>
       <c r="C131" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D131" t="s">
         <v>71</v>
       </c>
       <c r="E131" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C131,'feed rations'!K$8:K$33,0))</f>
-        <v>3.6663840495628457</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C131,'feed rations'!$K$8:$K$43,0),MATCH(B131,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.7538683244119473</v>
       </c>
       <c r="F131" t="s">
         <v>23</v>
@@ -9150,8 +9334,8 @@
         <v>71</v>
       </c>
       <c r="E132" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C132,'feed rations'!K$8:K$33,0))</f>
-        <v>9.4992677647764617E-2</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C132,'feed rations'!$K$8:$K$43,0),MATCH(B132,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>7.1350224768854983E-2</v>
       </c>
       <c r="F132" t="s">
         <v>23</v>
@@ -9168,8 +9352,8 @@
         <v>71</v>
       </c>
       <c r="E133" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C133,'feed rations'!K$8:K$33,0))</f>
-        <v>2.8529050885660894</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C133,'feed rations'!$K$8:$K$43,0),MATCH(B133,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.4545416139233072</v>
       </c>
       <c r="F133" t="s">
         <v>23</v>
@@ -9186,8 +9370,8 @@
         <v>71</v>
       </c>
       <c r="E134" s="62">
-        <f>INDEX('feed rations'!Q$8:Q$33,MATCH(C134,'feed rations'!K$8:K$33,0))</f>
-        <v>6.0178694558961068</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C134,'feed rations'!$K$8:$K$43,0),MATCH(B134,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0</v>
       </c>
       <c r="F134" t="s">
         <v>23</v>
@@ -9200,7 +9384,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B5:Z45"/>
+  <dimension ref="A5:Z50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9212,1918 +9396,2259 @@
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="5.42578125" customWidth="1"/>
     <col min="11" max="11" width="27.7109375" customWidth="1"/>
-    <col min="12" max="13" width="13.28515625" customWidth="1"/>
-    <col min="14" max="17" width="12.140625" customWidth="1"/>
+    <col min="12" max="14" width="13.28515625" customWidth="1"/>
+    <col min="17" max="20" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="90" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C6" s="4" t="s">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="C6" s="116" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="117" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="3:22" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C7" s="4"/>
-      <c r="D7" s="91" t="s">
+      <c r="E6" s="117"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="118"/>
+      <c r="L6" s="90" t="s">
+        <v>248</v>
+      </c>
+      <c r="O6" s="78"/>
+      <c r="Q6" s="90" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C7" s="127"/>
+      <c r="D7" s="143" t="s">
         <v>169</v>
       </c>
-      <c r="E7" s="91"/>
-      <c r="F7" s="91" t="s">
+      <c r="E7" s="143" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="143" t="s">
         <v>170</v>
       </c>
-      <c r="G7" s="91"/>
-      <c r="H7" s="91" t="s">
+      <c r="G7" s="143" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="143" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="91"/>
+      <c r="I7" s="144" t="s">
+        <v>23</v>
+      </c>
       <c r="K7" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="L7" s="91" t="s">
-        <v>242</v>
-      </c>
-      <c r="M7" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="91" t="s">
+      <c r="L7" s="141" t="s">
+        <v>240</v>
+      </c>
+      <c r="M7" s="147" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="P7" s="91" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q7" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="R7" s="91" t="s">
+      <c r="N7" s="142" t="s">
+        <v>250</v>
+      </c>
+      <c r="O7" s="151" t="s">
         <v>209</v>
       </c>
-      <c r="S7" s="91"/>
-      <c r="T7" s="91"/>
-      <c r="U7" s="91"/>
+      <c r="P7" s="91"/>
+      <c r="Q7" s="141">
+        <v>0</v>
+      </c>
+      <c r="R7" s="147" t="s">
+        <v>15</v>
+      </c>
+      <c r="S7" s="147" t="s">
+        <v>24</v>
+      </c>
+      <c r="T7" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="U7" s="120"/>
       <c r="V7" s="92" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C8" s="93" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="121" t="s">
         <v>173</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="78">
         <v>517.6</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="122">
         <f t="shared" ref="E8:E42" si="0">D8/D$45</f>
         <v>0.31776045183866414</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="78">
         <v>14.9</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="122">
         <f t="shared" ref="G8:G42" si="1">F8/F$45</f>
         <v>0.27090909090909093</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="78">
         <v>81.099999999999994</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="123">
         <f t="shared" ref="I8:I42" si="2">H8/H$45</f>
         <v>0.15836750634641669</v>
       </c>
       <c r="K8" t="s">
         <v>70</v>
       </c>
-      <c r="L8" s="3">
-        <f t="shared" ref="L8:L16" si="3">(D8)*($R8/100)</f>
-        <v>450.31200000000001</v>
-      </c>
-      <c r="M8" s="62">
-        <f t="shared" ref="M8:M34" si="4">L8/L$34*100</f>
-        <v>40.096128418163971</v>
-      </c>
-      <c r="N8" s="3">
-        <f t="shared" ref="N8:N16" si="5">(F8)*($R8/100)</f>
-        <v>12.963000000000001</v>
-      </c>
-      <c r="O8" s="62">
-        <f t="shared" ref="O8:O34" si="6">N8/N$34*100</f>
-        <v>37.694097121256185</v>
-      </c>
-      <c r="P8" s="3">
-        <f t="shared" ref="P8:P16" si="7">(H8)*($R8/100)</f>
-        <v>70.556999999999988</v>
-      </c>
-      <c r="Q8" s="62">
-        <f t="shared" ref="Q8:Q34" si="8">P8/P$34*100</f>
-        <v>29.396484021023365</v>
-      </c>
-      <c r="R8">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C9" s="93" t="s">
+      <c r="L8" s="109">
+        <f>(D8)*($O8/100)</f>
+        <v>445.13600000000002</v>
+      </c>
+      <c r="M8" s="111">
+        <f>(F8)*($O8/100)</f>
+        <v>12.814</v>
+      </c>
+      <c r="N8" s="146">
+        <f>(H8)*($O8/100)</f>
+        <v>69.745999999999995</v>
+      </c>
+      <c r="O8" s="152">
+        <v>86</v>
+      </c>
+      <c r="Q8" s="148">
+        <f>L8/L$44*100</f>
+        <v>39.939446969082496</v>
+      </c>
+      <c r="R8" s="110">
+        <f>M8/M$44*100</f>
+        <v>37.344664381805039</v>
+      </c>
+      <c r="S8" s="150">
+        <f>N8/N$44*100</f>
+        <v>21.826284108458598</v>
+      </c>
+      <c r="T8" s="114">
+        <f>N8/N$44*100</f>
+        <v>21.826284108458598</v>
+      </c>
+      <c r="U8" s="110"/>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C9" s="121" t="s">
         <v>174</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="78">
         <v>435.3</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="122">
         <f t="shared" si="0"/>
         <v>0.267235557738351</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="78">
         <v>13.5</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="122">
         <f t="shared" si="1"/>
         <v>0.24545454545454545</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="78">
         <v>62.3</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="123">
         <f t="shared" si="2"/>
         <v>0.12165592657684045</v>
       </c>
       <c r="K9" t="s">
         <v>160</v>
       </c>
-      <c r="L9" s="3">
-        <f t="shared" si="3"/>
-        <v>378.71100000000001</v>
-      </c>
-      <c r="M9" s="62">
-        <f t="shared" si="4"/>
-        <v>33.720720054920363</v>
-      </c>
-      <c r="N9" s="3">
-        <f t="shared" si="5"/>
-        <v>11.744999999999999</v>
-      </c>
-      <c r="O9" s="62">
-        <f t="shared" si="6"/>
-        <v>34.152369874963654</v>
-      </c>
-      <c r="P9" s="3">
-        <f t="shared" si="7"/>
-        <v>54.201000000000001</v>
-      </c>
-      <c r="Q9" s="62">
-        <f t="shared" si="8"/>
-        <v>22.582009303449521</v>
-      </c>
-      <c r="R9">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C10" s="93" t="s">
+      <c r="L9" s="109">
+        <f>(D9)*($O9/100)</f>
+        <v>374.358</v>
+      </c>
+      <c r="M9" s="111">
+        <f>(F9)*($O9/100)</f>
+        <v>11.61</v>
+      </c>
+      <c r="N9" s="146">
+        <f>(H9)*($O9/100)</f>
+        <v>53.577999999999996</v>
+      </c>
+      <c r="O9" s="152">
+        <v>86</v>
+      </c>
+      <c r="Q9" s="148">
+        <f>L9/L$44*100</f>
+        <v>33.588951440574981</v>
+      </c>
+      <c r="R9" s="110">
+        <f>M9/M$44*100</f>
+        <v>33.835769741903896</v>
+      </c>
+      <c r="S9" s="110">
+        <f>N9/N$44*100</f>
+        <v>16.76667694151628</v>
+      </c>
+      <c r="T9" s="114">
+        <f t="shared" ref="T9:T33" si="3">N9/N$44*100</f>
+        <v>16.76667694151628</v>
+      </c>
+      <c r="U9" s="110"/>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="121" t="s">
         <v>175</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="78">
         <v>63.2</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="122">
         <f t="shared" si="0"/>
         <v>3.8799189637178461E-2</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="78">
         <v>2.7</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="122">
         <f t="shared" si="1"/>
         <v>4.9090909090909095E-2</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="78">
         <v>10.5</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="123">
         <f t="shared" si="2"/>
         <v>2.0503807850029289E-2</v>
       </c>
       <c r="K10" t="s">
         <v>161</v>
       </c>
-      <c r="L10" s="3">
-        <f>(D10)*($R10/100)</f>
-        <v>54.984000000000002</v>
-      </c>
-      <c r="M10" s="62">
-        <f t="shared" si="4"/>
-        <v>4.8958178439489242</v>
-      </c>
-      <c r="N10" s="3">
-        <f t="shared" si="5"/>
-        <v>2.3490000000000002</v>
-      </c>
-      <c r="O10" s="62">
-        <f t="shared" si="6"/>
-        <v>6.8304739749927315</v>
-      </c>
-      <c r="P10" s="3">
-        <f t="shared" si="7"/>
-        <v>9.1349999999999998</v>
-      </c>
-      <c r="Q10" s="62">
-        <f t="shared" si="8"/>
-        <v>3.8059566241768858</v>
-      </c>
-      <c r="R10">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C11" s="93" t="s">
+      <c r="L10" s="109">
+        <f>(D10+D36)*($O10/100)</f>
+        <v>54.352000000000004</v>
+      </c>
+      <c r="M10" s="111">
+        <f>(F10+F36)*($O10/100)</f>
+        <v>2.4940000000000002</v>
+      </c>
+      <c r="N10" s="146">
+        <f>(H10+H36)*($O10/100)</f>
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="O10" s="152">
+        <v>86</v>
+      </c>
+      <c r="Q10" s="148">
+        <f>L10/L$44*100</f>
+        <v>4.876686724200181</v>
+      </c>
+      <c r="R10" s="110">
+        <f>M10/M$44*100</f>
+        <v>7.2684246112238</v>
+      </c>
+      <c r="S10" s="110">
+        <f>N10/N$44*100</f>
+        <v>2.8258444283454405</v>
+      </c>
+      <c r="T10" s="114">
+        <f t="shared" si="3"/>
+        <v>2.8258444283454405</v>
+      </c>
+      <c r="U10" s="110"/>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="121" t="s">
         <v>176</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="78">
         <v>5.8</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="122">
         <f t="shared" si="0"/>
         <v>3.5606851249309346E-3</v>
       </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
+      <c r="F11" s="78">
+        <v>0</v>
+      </c>
+      <c r="G11" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="78">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="123">
         <f t="shared" si="2"/>
         <v>1.9136887326694007E-2</v>
       </c>
       <c r="K11" t="s">
         <v>162</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="109">
+        <f>(D11)*($O11/100)</f>
+        <v>4.9879999999999995</v>
+      </c>
+      <c r="M11" s="111">
+        <f>(F11)*($O11/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="146">
+        <f>(H11)*($O11/100)</f>
+        <v>8.4280000000000008</v>
+      </c>
+      <c r="O11" s="152">
+        <v>86</v>
+      </c>
+      <c r="Q11" s="148">
+        <f>L11/L$44*100</f>
+        <v>0.44754403481583932</v>
+      </c>
+      <c r="R11" s="110">
+        <f>M11/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="110">
+        <f>N11/N$44*100</f>
+        <v>2.6374547997890785</v>
+      </c>
+      <c r="T11" s="114">
         <f t="shared" si="3"/>
-        <v>5.0460000000000003</v>
-      </c>
-      <c r="M11" s="62">
-        <f t="shared" si="4"/>
-        <v>0.44929973884341395</v>
-      </c>
-      <c r="N11" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="3">
-        <f t="shared" si="7"/>
-        <v>8.5259999999999998</v>
-      </c>
-      <c r="Q11" s="62">
-        <f t="shared" si="8"/>
-        <v>3.5522261825650929</v>
-      </c>
-      <c r="R11">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C12" s="93" t="s">
+        <v>2.6374547997890785</v>
+      </c>
+      <c r="U11" s="110"/>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="121" t="s">
         <v>182</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="78">
         <v>2.9</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="122">
         <f t="shared" si="0"/>
         <v>1.7803425624654673E-3</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="78">
         <v>0.7</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="122">
         <f t="shared" si="1"/>
         <v>1.2727272727272726E-2</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="78">
         <v>0.2</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="123">
         <f t="shared" si="2"/>
         <v>3.905487209529389E-4</v>
       </c>
       <c r="K12" t="s">
         <v>165</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="109">
+        <f>(D12)*($O12/100)</f>
+        <v>2.4939999999999998</v>
+      </c>
+      <c r="M12" s="111">
+        <f>(F12)*($O12/100)</f>
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="N12" s="146">
+        <f>(H12)*($O12/100)</f>
+        <v>0.17200000000000001</v>
+      </c>
+      <c r="O12" s="152">
+        <v>86</v>
+      </c>
+      <c r="Q12" s="148">
+        <f>L12/L$44*100</f>
+        <v>0.22377201740791966</v>
+      </c>
+      <c r="R12" s="110">
+        <f>M12/M$44*100</f>
+        <v>1.7544473199505721</v>
+      </c>
+      <c r="S12" s="110">
+        <f>N12/N$44*100</f>
+        <v>5.3825608158960786E-2</v>
+      </c>
+      <c r="T12" s="114">
         <f t="shared" si="3"/>
-        <v>2.5230000000000001</v>
-      </c>
-      <c r="M12" s="62">
-        <f t="shared" si="4"/>
-        <v>0.22464986942170698</v>
-      </c>
-      <c r="N12" s="3">
-        <f t="shared" si="5"/>
-        <v>0.60899999999999999</v>
-      </c>
-      <c r="O12" s="62">
-        <f t="shared" si="6"/>
-        <v>1.7708636231462638</v>
-      </c>
-      <c r="P12" s="3">
-        <f t="shared" si="7"/>
-        <v>0.17400000000000002</v>
-      </c>
-      <c r="Q12" s="62">
-        <f t="shared" si="8"/>
-        <v>7.2494411889083538E-2</v>
-      </c>
-      <c r="R12">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C13" s="93" t="s">
+        <v>5.3825608158960786E-2</v>
+      </c>
+      <c r="U12" s="110"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="121" t="s">
         <v>188</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="78">
         <v>10.3</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="122">
         <f t="shared" si="0"/>
         <v>6.3232856528945914E-3</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="78">
         <v>0.1</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="122">
         <f t="shared" si="1"/>
         <v>1.8181818181818182E-3</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="78">
         <v>1.2</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="123">
         <f t="shared" si="2"/>
         <v>2.3432923257176333E-3</v>
       </c>
       <c r="K13" t="s">
         <v>218</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="109">
+        <f>(D13)*($O13/100)</f>
+        <v>8.7550000000000008</v>
+      </c>
+      <c r="M13" s="111">
+        <f>(F13)*($O13/100)</f>
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="N13" s="146">
+        <f>(H13)*($O13/100)</f>
+        <v>1.02</v>
+      </c>
+      <c r="O13" s="152">
+        <v>85</v>
+      </c>
+      <c r="Q13" s="148">
+        <f>L13/L$44*100</f>
+        <v>0.78553488869540378</v>
+      </c>
+      <c r="R13" s="110">
+        <f>M13/M$44*100</f>
+        <v>0.24772096710265556</v>
+      </c>
+      <c r="S13" s="110">
+        <f>N13/N$44*100</f>
+        <v>0.31919837396593026</v>
+      </c>
+      <c r="T13" s="114">
         <f t="shared" si="3"/>
-        <v>8.9610000000000003</v>
-      </c>
-      <c r="M13" s="62">
-        <f t="shared" si="4"/>
-        <v>0.79789436380813161</v>
-      </c>
-      <c r="N13" s="3">
-        <f t="shared" si="5"/>
-        <v>8.7000000000000008E-2</v>
-      </c>
-      <c r="O13" s="62">
-        <f t="shared" si="6"/>
-        <v>0.25298051759232343</v>
-      </c>
-      <c r="P13" s="3">
-        <f t="shared" si="7"/>
-        <v>1.044</v>
-      </c>
-      <c r="Q13" s="62">
-        <f t="shared" si="8"/>
-        <v>0.43496647133450123</v>
-      </c>
-      <c r="R13">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C14" s="93" t="s">
+        <v>0.31919837396593026</v>
+      </c>
+      <c r="U13" s="110"/>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C14" s="121" t="s">
         <v>189</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="78">
         <v>1.3</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="122">
         <f t="shared" si="0"/>
         <v>7.9808459696727846E-4</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="78">
         <v>0.3</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="122">
         <f t="shared" si="1"/>
         <v>5.4545454545454541E-3</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="78">
         <v>20.3</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="123">
         <f t="shared" si="2"/>
         <v>3.9640695176723299E-2</v>
       </c>
       <c r="K14" t="s">
         <v>219</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="109">
+        <f>(D14)*($O14/100)</f>
+        <v>1.105</v>
+      </c>
+      <c r="M14" s="111">
+        <f>(F14)*($O14/100)</f>
+        <v>0.255</v>
+      </c>
+      <c r="N14" s="146">
+        <f>(H14)*($O14/100)</f>
+        <v>17.254999999999999</v>
+      </c>
+      <c r="O14" s="152">
+        <v>85</v>
+      </c>
+      <c r="Q14" s="148">
+        <f>L14/L$44*100</f>
+        <v>9.9145180126604351E-2</v>
+      </c>
+      <c r="R14" s="110">
+        <f>M14/M$44*100</f>
+        <v>0.74316290130796658</v>
+      </c>
+      <c r="S14" s="110">
+        <f>N14/N$44*100</f>
+        <v>5.3997724929236526</v>
+      </c>
+      <c r="T14" s="114">
         <f t="shared" si="3"/>
-        <v>1.131</v>
-      </c>
-      <c r="M14" s="62">
-        <f t="shared" si="4"/>
-        <v>0.10070511387869623</v>
-      </c>
-      <c r="N14" s="3">
-        <f t="shared" si="5"/>
-        <v>0.26100000000000001</v>
-      </c>
-      <c r="O14" s="62">
-        <f t="shared" si="6"/>
-        <v>0.75894155277697029</v>
-      </c>
-      <c r="P14" s="3">
-        <f t="shared" si="7"/>
-        <v>17.661000000000001</v>
-      </c>
-      <c r="Q14" s="62">
-        <f t="shared" si="8"/>
-        <v>7.3581828067419792</v>
-      </c>
-      <c r="R14">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C15" s="93" t="s">
+        <v>5.3997724929236526</v>
+      </c>
+      <c r="U14" s="110"/>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C15" s="121" t="s">
         <v>180</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="78">
         <v>4.3</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="122">
         <f t="shared" si="0"/>
         <v>2.6398182822763828E-3</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5">
+      <c r="F15" s="78">
+        <v>0</v>
+      </c>
+      <c r="G15" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5">
+      <c r="H15" s="78">
+        <v>0</v>
+      </c>
+      <c r="I15" s="123">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" t="s">
         <v>163</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="109">
+        <f>(D15)*($O15/100)</f>
+        <v>3.9129999999999998</v>
+      </c>
+      <c r="M15" s="111">
+        <f>(F15)*($O15/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="146">
+        <f>(H15)*($O15/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="152">
+        <v>91</v>
+      </c>
+      <c r="Q15" s="148">
+        <f>L15/L$44*100</f>
+        <v>0.35109057903656365</v>
+      </c>
+      <c r="R15" s="110">
+        <f>M15/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="110">
+        <f>N15/N$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="114">
         <f t="shared" si="3"/>
-        <v>3.956</v>
-      </c>
-      <c r="M15" s="62">
-        <f t="shared" si="4"/>
-        <v>0.35224529664378623</v>
-      </c>
-      <c r="N15" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="62">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="3:22" x14ac:dyDescent="0.25">
-      <c r="C16" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="U15" s="110"/>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" s="121" t="s">
         <v>181</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="78">
         <v>1.6</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="122">
         <f t="shared" si="0"/>
         <v>9.8225796549818905E-4</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5">
+      <c r="F16" s="78">
+        <v>0</v>
+      </c>
+      <c r="G16" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5">
+      <c r="H16" s="78">
+        <v>0</v>
+      </c>
+      <c r="I16" s="123">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K16" t="s">
         <v>164</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="109">
+        <f>(D16)*($O16/100)</f>
+        <v>1.4560000000000002</v>
+      </c>
+      <c r="M16" s="111">
+        <f>(F16)*($O16/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="146">
+        <f>(H16)*($O16/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="152">
+        <v>91</v>
+      </c>
+      <c r="Q16" s="148">
+        <f>L16/L$44*100</f>
+        <v>0.13063835499034929</v>
+      </c>
+      <c r="R16" s="110">
+        <f>M16/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="110">
+        <f>N16/N$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="T16" s="114">
         <f t="shared" si="3"/>
-        <v>1.4560000000000002</v>
-      </c>
-      <c r="M16" s="62">
-        <f t="shared" si="4"/>
-        <v>0.12964336499326412</v>
-      </c>
-      <c r="N16" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="62">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C17" s="93" t="s">
+        <v>0</v>
+      </c>
+      <c r="U16" s="110"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" s="121" t="s">
         <v>190</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="78">
         <v>88.6</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="122">
         <f t="shared" si="0"/>
         <v>5.4392534839462207E-2</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="78">
         <v>2.8</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="122">
         <f t="shared" si="1"/>
         <v>5.0909090909090904E-2</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="78">
         <v>7.2</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="123">
         <f t="shared" si="2"/>
         <v>1.4059753954305799E-2</v>
       </c>
       <c r="K17" t="s">
-        <v>250</v>
-      </c>
-      <c r="L17" s="3">
-        <f>(D32)*($R17/100)</f>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="M17" s="62">
-        <f t="shared" si="4"/>
-        <v>0.20479377711848037</v>
-      </c>
-      <c r="N17" s="3">
-        <f>(F32)*($R17/100)</f>
-        <v>0.5</v>
-      </c>
-      <c r="O17" s="62">
-        <f t="shared" si="6"/>
-        <v>1.4539110206455368</v>
-      </c>
-      <c r="P17" s="3">
-        <f>(H32)*($R17/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="62">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C18" s="93" t="s">
+        <v>220</v>
+      </c>
+      <c r="L17" s="109">
+        <f>(D17)*($O17/100)</f>
+        <v>77.967999999999989</v>
+      </c>
+      <c r="M17" s="111">
+        <f>(F17)*($O17/100)</f>
+        <v>2.464</v>
+      </c>
+      <c r="N17" s="146">
+        <f>(H17)*($O17/100)</f>
+        <v>6.3360000000000003</v>
+      </c>
+      <c r="O17" s="152">
+        <v>88</v>
+      </c>
+      <c r="Q17" s="148">
+        <f>L17/L$44*100</f>
+        <v>6.9956121304172738</v>
+      </c>
+      <c r="R17" s="110">
+        <f>M17/M$44*100</f>
+        <v>7.1809936816581557</v>
+      </c>
+      <c r="S17" s="110">
+        <f>N17/N$44*100</f>
+        <v>1.9827851935766017</v>
+      </c>
+      <c r="T17" s="114">
+        <f t="shared" si="3"/>
+        <v>1.9827851935766017</v>
+      </c>
+      <c r="U17" s="110"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="121" t="s">
         <v>194</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="D18" s="78">
+        <v>0</v>
+      </c>
+      <c r="E18" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="78">
         <v>0.9</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="122">
         <f t="shared" si="1"/>
         <v>1.6363636363636365E-2</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5">
+      <c r="H18" s="78">
+        <v>0</v>
+      </c>
+      <c r="I18" s="123">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>220</v>
-      </c>
-      <c r="L18" s="3">
-        <f>(D17)*($R18/100)</f>
-        <v>77.967999999999989</v>
-      </c>
-      <c r="M18" s="62">
-        <f t="shared" si="4"/>
-        <v>6.9423309627711633</v>
-      </c>
-      <c r="N18" s="3">
-        <f>(F17)*($R18/100)</f>
-        <v>2.464</v>
-      </c>
-      <c r="O18" s="62">
-        <f t="shared" si="6"/>
-        <v>7.1648735097412057</v>
-      </c>
-      <c r="P18" s="3">
-        <f>(H17)*($R18/100)</f>
-        <v>6.3360000000000003</v>
-      </c>
-      <c r="Q18" s="62">
-        <f t="shared" si="8"/>
-        <v>2.6397965156852488</v>
-      </c>
-      <c r="R18">
-        <v>88</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="L18" s="109">
+        <f>(D18)*($O18/100)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="111">
+        <f>(F18)*($O18/100)</f>
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="N18" s="146">
+        <f>(H18)*($O18/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O18" s="152">
+        <v>87</v>
+      </c>
+      <c r="Q18" s="148">
+        <f>L18/L$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="110">
+        <f>M18/M$44*100</f>
+        <v>2.2819472616632859</v>
+      </c>
+      <c r="S18" s="110">
+        <f>N18/N$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="110"/>
       <c r="V18" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C19" s="93" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>221</v>
+      </c>
+      <c r="C19" s="121" t="s">
         <v>191</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="78">
         <v>40.700000000000003</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="122">
         <f t="shared" si="0"/>
         <v>2.4986186997360181E-2</v>
       </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19" s="5">
+      <c r="F19" s="78">
+        <v>0</v>
+      </c>
+      <c r="G19" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="78">
         <v>8.6999999999999993</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="123">
         <f t="shared" si="2"/>
         <v>1.698886936145284E-2</v>
       </c>
       <c r="K19" t="s">
-        <v>222</v>
-      </c>
-      <c r="L19" s="3">
-        <f>(D18)*($R19/100)</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="62">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="3">
-        <f>(F18)*($R19/100)</f>
-        <v>0.78300000000000003</v>
-      </c>
-      <c r="O19" s="62">
-        <f t="shared" si="6"/>
-        <v>2.2768246583309106</v>
-      </c>
-      <c r="P19" s="3">
-        <f>(H18)*($R19/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="62">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>87</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="L19" s="109">
+        <f>(D19)*($O19/100)</f>
+        <v>36.630000000000003</v>
+      </c>
+      <c r="M19" s="111">
+        <f>(F19)*($O19/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="146">
+        <f>(H19)*($O19/100)</f>
+        <v>7.8299999999999992</v>
+      </c>
+      <c r="O19" s="152">
+        <v>90</v>
+      </c>
+      <c r="Q19" s="148">
+        <f>L19/L$44*100</f>
+        <v>3.2865954280882512</v>
+      </c>
+      <c r="R19" s="110">
+        <f>M19/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="110">
+        <f>N19/N$44*100</f>
+        <v>2.4503169295619931</v>
+      </c>
+      <c r="T19" s="114">
+        <f t="shared" si="3"/>
+        <v>2.4503169295619931</v>
+      </c>
+      <c r="U19" s="110"/>
       <c r="V19" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C20" s="93" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>217</v>
+      </c>
+      <c r="C20" s="121" t="s">
         <v>187</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="78">
         <v>5.5</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="122">
         <f t="shared" si="0"/>
         <v>3.3765117564000242E-3</v>
       </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" s="5">
+      <c r="F20" s="78">
+        <v>0</v>
+      </c>
+      <c r="G20" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="78">
         <v>0.4</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="123">
         <f t="shared" si="2"/>
         <v>7.810974419058778E-4</v>
       </c>
       <c r="K20" t="s">
-        <v>221</v>
-      </c>
-      <c r="L20" s="3">
-        <f>(D19)*($R20/100)</f>
-        <v>36.223000000000006</v>
-      </c>
-      <c r="M20" s="62">
-        <f t="shared" si="4"/>
-        <v>3.2253239080707465</v>
-      </c>
-      <c r="N20" s="3">
-        <f>(F19)*($R20/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O20" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <f>(H19)*($R20/100)</f>
-        <v>7.7429999999999994</v>
-      </c>
-      <c r="Q20" s="62">
-        <f t="shared" si="8"/>
-        <v>3.2260013290642173</v>
-      </c>
-      <c r="R20">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C21" s="93" t="s">
+        <v>217</v>
+      </c>
+      <c r="L20" s="109">
+        <f>(D20)*($O20/100)</f>
+        <v>5.0049999999999999</v>
+      </c>
+      <c r="M20" s="111">
+        <f>(F20)*($O20/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="146">
+        <f>(H20)*($O20/100)</f>
+        <v>0.36400000000000005</v>
+      </c>
+      <c r="O20" s="152">
+        <v>91</v>
+      </c>
+      <c r="Q20" s="148">
+        <f>L20/L$44*100</f>
+        <v>0.44906934527932563</v>
+      </c>
+      <c r="R20" s="110">
+        <f>M20/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S20" s="110">
+        <f>N20/N$44*100</f>
+        <v>0.11391000796431236</v>
+      </c>
+      <c r="T20" s="114">
+        <f t="shared" si="3"/>
+        <v>0.11391000796431236</v>
+      </c>
+      <c r="U20" s="110"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C21" s="121" t="s">
         <v>179</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="78">
         <v>1.6</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="122">
         <f t="shared" si="0"/>
         <v>9.8225796549818905E-4</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21" s="5">
+      <c r="F21" s="78">
+        <v>0</v>
+      </c>
+      <c r="G21" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21" s="5">
+      <c r="H21" s="78">
+        <v>0</v>
+      </c>
+      <c r="I21" s="123">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>217</v>
-      </c>
-      <c r="L21" s="3">
-        <f>(D20)*($R21/100)</f>
-        <v>4.95</v>
-      </c>
-      <c r="M21" s="62">
-        <f t="shared" si="4"/>
-        <v>0.44075182466803386</v>
-      </c>
-      <c r="N21" s="3">
-        <f>(F20)*($R21/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="3">
-        <f>(H20)*($R21/100)</f>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="Q21" s="62">
-        <f t="shared" si="8"/>
-        <v>0.14998843839120732</v>
-      </c>
-      <c r="R21">
-        <v>90</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="L21" s="109">
+        <f>(D21)*($O21/100)</f>
+        <v>1.4560000000000002</v>
+      </c>
+      <c r="M21" s="111">
+        <f>(F21)*($O21/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="146">
+        <f>(H21)*($O21/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="152">
+        <v>91</v>
+      </c>
+      <c r="Q21" s="148">
+        <f>L21/L$44*100</f>
+        <v>0.13063835499034929</v>
+      </c>
+      <c r="R21" s="110">
+        <f>M21/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S21" s="110">
+        <f>N21/N$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="T21" s="114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="110"/>
       <c r="V21" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C22" s="93" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="78">
         <v>39.9</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="122">
         <f t="shared" si="0"/>
         <v>2.4495058014611083E-2</v>
       </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22" s="5">
+      <c r="F22" s="78">
+        <v>0</v>
+      </c>
+      <c r="G22" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="78">
         <v>3.3</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="123">
         <f t="shared" si="2"/>
         <v>6.444053895723491E-3</v>
       </c>
       <c r="K22" t="s">
-        <v>213</v>
-      </c>
-      <c r="L22" s="3">
-        <f>(D21)*($R22/100)</f>
-        <v>1.4560000000000002</v>
-      </c>
-      <c r="M22" s="62">
-        <f t="shared" si="4"/>
-        <v>0.12964336499326412</v>
-      </c>
-      <c r="N22" s="3">
-        <f>(F21)*($R22/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O22" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <f>(H21)*($R22/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="62">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="L22" s="109">
+        <f>(D22+D39)*($O22/100)</f>
+        <v>34.713000000000001</v>
+      </c>
+      <c r="M22" s="111">
+        <f>(F22+F39)*($O22/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="146">
+        <f>(H22+H39)*($O22/100)</f>
+        <v>18.443999999999999</v>
+      </c>
+      <c r="O22" s="152">
+        <v>87</v>
+      </c>
+      <c r="Q22" s="148">
+        <f>L22/L$44*100</f>
+        <v>3.1145942422939523</v>
+      </c>
+      <c r="R22" s="110">
+        <f>M22/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="110">
+        <f>N22/N$44*100</f>
+        <v>5.7718576563015853</v>
+      </c>
+      <c r="T22" s="114">
+        <f t="shared" si="3"/>
+        <v>5.7718576563015853</v>
+      </c>
+      <c r="U22" s="110"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23" s="87" t="s">
+        <v>215</v>
+      </c>
       <c r="B23" t="s">
-        <v>215</v>
-      </c>
-      <c r="C23" s="93" t="s">
+        <v>216</v>
+      </c>
+      <c r="C23" s="121" t="s">
         <v>184</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="78">
         <v>29.7</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="122">
         <f t="shared" si="0"/>
         <v>1.8233163484560132E-2</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="78">
         <v>0.5</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="122">
         <f t="shared" si="1"/>
         <v>9.0909090909090905E-3</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="78">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="123">
         <f t="shared" si="2"/>
         <v>4.2960359304823276E-3</v>
       </c>
       <c r="K23" t="s">
-        <v>214</v>
-      </c>
-      <c r="L23" s="3">
-        <f>(D22+D39)*($R23/100)</f>
-        <v>34.713000000000001</v>
-      </c>
-      <c r="M23" s="62">
-        <f t="shared" si="4"/>
-        <v>3.0908723413538302</v>
-      </c>
-      <c r="N23" s="3">
-        <f>(F22+F39)*($R23/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O23" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
-        <f>(H22+H39)*($R23/100)</f>
-        <v>18.443999999999999</v>
-      </c>
-      <c r="Q23" s="62">
-        <f t="shared" si="8"/>
-        <v>7.6844076602428553</v>
-      </c>
-      <c r="R23">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C24" s="93" t="s">
+        <v>216</v>
+      </c>
+      <c r="L23" s="109">
+        <f>(D23)*($O23/100)</f>
+        <v>26.135999999999999</v>
+      </c>
+      <c r="M23" s="111">
+        <f>(F23)*($O23/100)</f>
+        <v>0.44</v>
+      </c>
+      <c r="N23" s="146">
+        <f>(H23)*($O23/100)</f>
+        <v>1.9360000000000002</v>
+      </c>
+      <c r="O23" s="152">
+        <v>88</v>
+      </c>
+      <c r="Q23" s="148">
+        <f>L23/L$44*100</f>
+        <v>2.3450302513926982</v>
+      </c>
+      <c r="R23" s="110">
+        <f>M23/M$44*100</f>
+        <v>1.2823203002960992</v>
+      </c>
+      <c r="S23" s="110">
+        <f>N23/N$44*100</f>
+        <v>0.60585103137062835</v>
+      </c>
+      <c r="T23" s="114">
+        <f t="shared" si="3"/>
+        <v>0.60585103137062835</v>
+      </c>
+      <c r="U23" s="110"/>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24" s="121" t="s">
         <v>192</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="78">
         <v>1.7</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="122">
         <f t="shared" si="0"/>
         <v>1.0436490883418256E-3</v>
       </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5">
+      <c r="F24" s="78">
+        <v>0</v>
+      </c>
+      <c r="G24" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="78">
         <v>0.4</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="123">
         <f t="shared" si="2"/>
         <v>7.810974419058778E-4</v>
       </c>
       <c r="K24" t="s">
-        <v>216</v>
-      </c>
-      <c r="L24" s="3">
-        <f>(D23)*($R24/100)</f>
-        <v>26.135999999999999</v>
-      </c>
-      <c r="M24" s="62">
-        <f t="shared" si="4"/>
-        <v>2.3271696342472188</v>
-      </c>
-      <c r="N24" s="3">
-        <f>(F23)*($R24/100)</f>
-        <v>0.44</v>
-      </c>
-      <c r="O24" s="62">
-        <f t="shared" si="6"/>
-        <v>1.2794416981680723</v>
-      </c>
-      <c r="P24" s="3">
-        <f>(H23)*($R24/100)</f>
-        <v>1.9360000000000002</v>
-      </c>
-      <c r="Q24" s="62">
-        <f t="shared" si="8"/>
-        <v>0.80660449090382613</v>
-      </c>
-      <c r="R24">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C25" s="93" t="s">
+        <v>225</v>
+      </c>
+      <c r="L24" s="109">
+        <f>(D24+D37)*($O24/100)</f>
+        <v>1.53</v>
+      </c>
+      <c r="M24" s="111">
+        <f>(F24+F37)*($O24/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="146">
+        <f>(H24+H37)*($O24/100)</f>
+        <v>108.54</v>
+      </c>
+      <c r="O24" s="152">
+        <v>90</v>
+      </c>
+      <c r="Q24" s="148">
+        <f>L24/L$44*100</f>
+        <v>0.13727794171375987</v>
+      </c>
+      <c r="R24" s="110">
+        <f>M24/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="110">
+        <f>N24/N$44*100</f>
+        <v>33.966462264962807</v>
+      </c>
+      <c r="T24" s="114">
+        <f t="shared" si="3"/>
+        <v>33.966462264962807</v>
+      </c>
+      <c r="U24" s="110"/>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>226</v>
+      </c>
+      <c r="C25" s="121" t="s">
         <v>199</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="78">
         <v>60.4</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="122">
         <f t="shared" si="0"/>
         <v>3.7080238197556632E-2</v>
       </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5">
+      <c r="F25" s="78">
+        <v>0</v>
+      </c>
+      <c r="G25" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25" s="5">
+      <c r="H25" s="78">
+        <v>0</v>
+      </c>
+      <c r="I25" s="123">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>225</v>
-      </c>
-      <c r="L25" s="3">
-        <f>(D24)*($R25/100)</f>
-        <v>1.53</v>
-      </c>
-      <c r="M25" s="62">
-        <f t="shared" si="4"/>
-        <v>0.13623238217011954</v>
-      </c>
-      <c r="N25" s="3">
-        <f>(F24)*($R25/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="3">
-        <f>(H24)*($R25/100)</f>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="Q25" s="62">
-        <f t="shared" si="8"/>
-        <v>0.14998843839120732</v>
-      </c>
-      <c r="R25">
-        <v>90</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="L25" s="109">
+        <f>(D25)*($O25/100)</f>
+        <v>6.6440000000000001</v>
+      </c>
+      <c r="M25" s="111">
+        <f>(F25)*($O25/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="146">
+        <f>(H25)*($O25/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="152">
+        <v>11</v>
+      </c>
+      <c r="Q25" s="148">
+        <f>L25/L$44*100</f>
+        <v>0.59612721878837949</v>
+      </c>
+      <c r="R25" s="110">
+        <f>M25/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S25" s="110">
+        <f>N25/N$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="T25" s="114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="110"/>
       <c r="V25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C26" s="93" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>211</v>
+      </c>
+      <c r="C26" s="121" t="s">
         <v>177</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="78">
         <v>5.2</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="122">
         <f t="shared" si="0"/>
         <v>3.1923383878691139E-3</v>
       </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5">
+      <c r="F26" s="78">
+        <v>0</v>
+      </c>
+      <c r="G26" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="78">
         <v>0.3</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="123">
         <f t="shared" si="2"/>
         <v>5.8582308142940832E-4</v>
       </c>
       <c r="K26" t="s">
-        <v>226</v>
-      </c>
-      <c r="L26" s="3">
-        <f>(D25+D37)*($R26/100)</f>
-        <v>6.6440000000000001</v>
-      </c>
-      <c r="M26" s="62">
-        <f t="shared" si="4"/>
-        <v>0.59158689355442773</v>
-      </c>
-      <c r="N26" s="3">
-        <f>(F25+F37)*($R26/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O26" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="3">
-        <f>(H25+H37)*($R26/100)</f>
-        <v>13.222</v>
-      </c>
-      <c r="Q26" s="62">
-        <f t="shared" si="8"/>
-        <v>5.5087420344681757</v>
-      </c>
-      <c r="R26">
-        <v>11</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="L26" s="109">
+        <f>(D26)*($O26/100)</f>
+        <v>3.9520000000000004</v>
+      </c>
+      <c r="M26" s="111">
+        <f>(F26)*($O26/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="146">
+        <f>(H26)*($O26/100)</f>
+        <v>0.22799999999999998</v>
+      </c>
+      <c r="O26" s="152">
+        <v>76</v>
+      </c>
+      <c r="Q26" s="148">
+        <f>L26/L$44*100</f>
+        <v>0.35458982068809092</v>
+      </c>
+      <c r="R26" s="110">
+        <f>M26/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="110">
+        <f>N26/N$44*100</f>
+        <v>7.1350224768854983E-2</v>
+      </c>
+      <c r="T26" s="114">
+        <f t="shared" si="3"/>
+        <v>7.1350224768854983E-2</v>
+      </c>
+      <c r="U26" s="110"/>
       <c r="V26" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C27" s="93" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" s="121" t="s">
         <v>178</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="78">
         <v>8.6999999999999993</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="122">
         <f t="shared" si="0"/>
         <v>5.3410276873964019E-3</v>
       </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27" s="5">
+      <c r="F27" s="78">
+        <v>0</v>
+      </c>
+      <c r="G27" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5">
+      <c r="H27" s="78">
+        <v>0</v>
+      </c>
+      <c r="I27" s="123">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>230</v>
-      </c>
-      <c r="L27">
+        <v>212</v>
+      </c>
+      <c r="L27" s="109">
+        <f>(D27)*($O27/100)</f>
+        <v>7.7429999999999994</v>
+      </c>
+      <c r="M27" s="111">
+        <f>(F27)*($O27/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="146">
+        <f>(H27)*($O27/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="152">
+        <v>89</v>
+      </c>
+      <c r="Q27" s="148">
+        <f>L27/L$44*100</f>
+        <v>0.69473405404551813</v>
+      </c>
+      <c r="R27" s="110">
+        <f>M27/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S27" s="110">
+        <f>N27/N$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="T27" s="114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="110"/>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>227</v>
+      </c>
+      <c r="C28" s="121" t="s">
+        <v>200</v>
+      </c>
+      <c r="D28" s="78">
+        <v>188.4</v>
+      </c>
+      <c r="E28" s="122">
+        <f t="shared" si="0"/>
+        <v>0.11566087543741174</v>
+      </c>
+      <c r="F28" s="78">
+        <v>9.6</v>
+      </c>
+      <c r="G28" s="122">
+        <f t="shared" si="1"/>
+        <v>0.17454545454545453</v>
+      </c>
+      <c r="H28" s="78">
+        <v>0</v>
+      </c>
+      <c r="I28" s="123">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>227</v>
+      </c>
+      <c r="L28" s="109">
+        <f>(D28+D38)*($O28/100)</f>
+        <v>11.869200000000001</v>
+      </c>
+      <c r="M28" s="111">
+        <f>(F28+F38)*($O28/100)</f>
+        <v>0.6048</v>
+      </c>
+      <c r="N28" s="146">
+        <f>(H28+H38)*($O28/100)</f>
+        <v>7.8434999999999997</v>
+      </c>
+      <c r="O28" s="152">
+        <v>6.3</v>
+      </c>
+      <c r="Q28" s="148">
+        <f>L28/L$44*100</f>
+        <v>1.0649538207770974</v>
+      </c>
+      <c r="R28" s="110">
+        <f>M28/M$44*100</f>
+        <v>1.7626075400433656</v>
+      </c>
+      <c r="S28" s="110">
+        <f>N28/N$44*100</f>
+        <v>2.4545416139233072</v>
+      </c>
+      <c r="T28" s="114">
+        <f t="shared" si="3"/>
+        <v>2.4545416139233072</v>
+      </c>
+      <c r="U28" s="110"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>241</v>
+      </c>
+      <c r="C29" s="121" t="s">
+        <v>193</v>
+      </c>
+      <c r="D29" s="78">
+        <v>0</v>
+      </c>
+      <c r="E29" s="122">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="78">
+        <v>0.1</v>
+      </c>
+      <c r="G29" s="122">
+        <f t="shared" si="1"/>
+        <v>1.8181818181818182E-3</v>
+      </c>
+      <c r="H29" s="78">
+        <v>0</v>
+      </c>
+      <c r="I29" s="123">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>241</v>
+      </c>
+      <c r="L29" s="109">
+        <f>(D29)*($O29/100)</f>
+        <v>0</v>
+      </c>
+      <c r="M29" s="111">
+        <f>(F29)*($O29/100)</f>
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="N29" s="146">
+        <f>(H29)*($O29/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O29" s="152">
+        <v>97</v>
+      </c>
+      <c r="Q29" s="148">
+        <f>L29/L$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="R29" s="110">
+        <f>M29/M$44*100</f>
+        <v>0.2826933389289128</v>
+      </c>
+      <c r="S29" s="110">
+        <f>N29/N$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="T29" s="114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="110"/>
+      <c r="V29" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30" s="121" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="78">
+        <v>0</v>
+      </c>
+      <c r="E30" s="122">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="G30" s="122">
+        <f t="shared" si="1"/>
+        <v>9.0909090909090905E-3</v>
+      </c>
+      <c r="H30" s="78">
+        <v>0</v>
+      </c>
+      <c r="I30" s="123">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>223</v>
+      </c>
+      <c r="L30" s="109">
+        <f>(D30)*($O30/100)</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="111">
+        <f>(F30)*($O30/100)</f>
+        <v>0.46</v>
+      </c>
+      <c r="N30" s="146">
+        <f>(H30)*($O30/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O30" s="152">
+        <v>92</v>
+      </c>
+      <c r="Q30" s="148">
+        <f>L30/L$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="R30" s="110">
+        <f>M30/M$44*100</f>
+        <v>1.3406075866731948</v>
+      </c>
+      <c r="S30" s="110">
+        <f>N30/N$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="T30" s="114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="110"/>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" s="121" t="s">
+        <v>196</v>
+      </c>
+      <c r="D31" s="78">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E31" s="122">
+        <f t="shared" si="0"/>
+        <v>1.3506047025600098E-3</v>
+      </c>
+      <c r="F31" s="78">
+        <v>1.2</v>
+      </c>
+      <c r="G31" s="122">
+        <f t="shared" si="1"/>
+        <v>2.1818181818181816E-2</v>
+      </c>
+      <c r="H31" s="78">
+        <v>0</v>
+      </c>
+      <c r="I31" s="123">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>224</v>
+      </c>
+      <c r="L31" s="109">
+        <f>(D31)*($O31/100)</f>
+        <v>2.0240000000000005</v>
+      </c>
+      <c r="M31" s="111">
+        <f>(F31)*($O31/100)</f>
+        <v>1.1040000000000001</v>
+      </c>
+      <c r="N31" s="146">
+        <f>(H31)*($O31/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O31" s="152">
+        <v>92</v>
+      </c>
+      <c r="Q31" s="148">
+        <f>L31/L$44*100</f>
+        <v>0.18160166929977128</v>
+      </c>
+      <c r="R31" s="110">
+        <f>M31/M$44*100</f>
+        <v>3.2174582080156675</v>
+      </c>
+      <c r="S31" s="110">
+        <f>N31/N$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="T31" s="114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="110"/>
+      <c r="V31" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>246</v>
+      </c>
+      <c r="C32" s="121" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32" s="78">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E32" s="122">
+        <f t="shared" si="0"/>
+        <v>1.4119958254036463E-3</v>
+      </c>
+      <c r="F32" s="78">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="122">
+        <f t="shared" si="1"/>
+        <v>9.0909090909090905E-3</v>
+      </c>
+      <c r="H32" s="78">
+        <v>0</v>
+      </c>
+      <c r="I32" s="123">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>246</v>
+      </c>
+      <c r="L32" s="109">
+        <f>(D32)*($O32/100)</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="M32" s="111">
+        <f>(F32)*($O32/100)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N32" s="146">
+        <f>(H32)*($O32/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O32" s="152">
+        <v>100</v>
+      </c>
+      <c r="Q32" s="148">
+        <f>L32/L$44*100</f>
+        <v>0.20636553329519458</v>
+      </c>
+      <c r="R32" s="110">
+        <f>M32/M$44*100</f>
+        <v>1.4571821594273857</v>
+      </c>
+      <c r="S32" s="110">
+        <f>N32/N$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="T32" s="114">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="110"/>
+      <c r="V32" t="s">
+        <v>238</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B33" s="87" t="s">
+        <v>253</v>
+      </c>
+      <c r="C33" s="113" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33" s="78">
+        <v>62.6</v>
+      </c>
+      <c r="E33" s="122">
+        <f t="shared" si="0"/>
+        <v>3.8430842900116641E-2</v>
+      </c>
+      <c r="F33" s="78">
+        <v>1.8</v>
+      </c>
+      <c r="G33" s="122">
+        <f t="shared" si="1"/>
+        <v>3.272727272727273E-2</v>
+      </c>
+      <c r="H33" s="78">
+        <v>11</v>
+      </c>
+      <c r="I33" s="123">
+        <f t="shared" si="2"/>
+        <v>2.1480179652411637E-2</v>
+      </c>
+      <c r="K33" t="s">
+        <v>229</v>
+      </c>
+      <c r="L33" s="113">
         <f>D41</f>
         <v>0</v>
       </c>
-      <c r="M27" s="62">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N27">
+      <c r="M33" s="78">
         <f>F41</f>
         <v>0</v>
       </c>
-      <c r="O27" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P27">
+      <c r="N33" s="112">
         <f>H41</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="Q27" s="62">
-        <f t="shared" si="8"/>
-        <v>3.6663840495628457</v>
-      </c>
-      <c r="R27">
+      <c r="O33" s="152">
         <v>91</v>
       </c>
-    </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C28" s="93" t="s">
-        <v>200</v>
-      </c>
-      <c r="D28">
-        <v>188.4</v>
-      </c>
-      <c r="E28" s="5">
-        <f t="shared" si="0"/>
-        <v>0.11566087543741174</v>
-      </c>
-      <c r="F28">
-        <v>9.6</v>
-      </c>
-      <c r="G28" s="5">
-        <f t="shared" si="1"/>
-        <v>0.17454545454545453</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K28" t="s">
-        <v>211</v>
-      </c>
-      <c r="L28" s="3">
-        <f>(D26)*($R28/100)</f>
-        <v>3.9520000000000004</v>
-      </c>
-      <c r="M28" s="62">
-        <f t="shared" si="4"/>
-        <v>0.35188913355314549</v>
-      </c>
-      <c r="N28" s="3">
-        <f>(F26)*($R28/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P28" s="3">
-        <f>(H26)*($R28/100)</f>
-        <v>0.22799999999999998</v>
-      </c>
-      <c r="Q28" s="62">
-        <f t="shared" si="8"/>
-        <v>9.4992677647764617E-2</v>
-      </c>
-      <c r="R28">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C29" s="93" t="s">
-        <v>193</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>0.1</v>
-      </c>
-      <c r="G29" s="5">
-        <f t="shared" si="1"/>
-        <v>1.8181818181818182E-3</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K29" t="s">
-        <v>212</v>
-      </c>
-      <c r="L29" s="3">
-        <f>(D27)*($R29/100)</f>
-        <v>7.7429999999999994</v>
-      </c>
-      <c r="M29" s="62">
-        <f t="shared" si="4"/>
-        <v>0.68944270270799723</v>
-      </c>
-      <c r="N29" s="3">
-        <f>(F27)*($R29/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O29" s="62">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <f>(H27)*($R29/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="62">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>89</v>
-      </c>
-      <c r="V29" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C30" s="93" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30">
-        <v>0</v>
-      </c>
-      <c r="E30" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>0.5</v>
-      </c>
-      <c r="G30" s="5">
-        <f t="shared" si="1"/>
-        <v>9.0909090909090905E-3</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K30" t="s">
-        <v>227</v>
-      </c>
-      <c r="L30" s="3">
-        <f>(D28+D38)*($R30/100)</f>
-        <v>10.362</v>
-      </c>
-      <c r="M30" s="62">
-        <f t="shared" si="4"/>
-        <v>0.92264048630508433</v>
-      </c>
-      <c r="N30" s="3">
-        <f>(F28+F38)*($R30/100)</f>
-        <v>0.52800000000000002</v>
-      </c>
-      <c r="O30" s="62">
-        <f t="shared" si="6"/>
-        <v>1.535330037801687</v>
-      </c>
-      <c r="P30" s="3">
-        <f>(H28+H38)*($R30/100)</f>
-        <v>6.8475000000000001</v>
-      </c>
-      <c r="Q30" s="62">
-        <f t="shared" si="8"/>
-        <v>2.8529050885660894</v>
-      </c>
-      <c r="R30">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C31" s="93" t="s">
-        <v>196</v>
-      </c>
-      <c r="D31">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E31" s="5">
-        <f t="shared" si="0"/>
-        <v>1.3506047025600098E-3</v>
-      </c>
-      <c r="F31">
-        <v>1.2</v>
-      </c>
-      <c r="G31" s="5">
-        <f t="shared" si="1"/>
-        <v>2.1818181818181816E-2</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
-        <v>245</v>
-      </c>
-      <c r="L31" s="3">
-        <f>(D29)*($R31/100)</f>
-        <v>0</v>
-      </c>
-      <c r="M31" s="62">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N31" s="3">
-        <f>(F29)*($R31/100)</f>
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="O31" s="62">
-        <f t="shared" si="6"/>
-        <v>0.28205873800523412</v>
-      </c>
-      <c r="P31" s="3">
-        <f>(H29)*($R31/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="62">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>97</v>
-      </c>
-      <c r="V31" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="C32" s="93" t="s">
-        <v>197</v>
-      </c>
-      <c r="D32">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E32" s="5">
-        <f t="shared" si="0"/>
-        <v>1.4119958254036463E-3</v>
-      </c>
-      <c r="F32">
-        <v>0.5</v>
-      </c>
-      <c r="G32" s="5">
-        <f t="shared" si="1"/>
-        <v>9.0909090909090905E-3</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K32" t="s">
-        <v>223</v>
-      </c>
-      <c r="L32" s="3">
-        <f>(D30+D40)*($R32/100)</f>
-        <v>0</v>
-      </c>
-      <c r="M32" s="62">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <f>(F30+F40)*($R32/100)</f>
-        <v>0.46</v>
-      </c>
-      <c r="O32" s="62">
-        <f t="shared" si="6"/>
-        <v>1.337598138993894</v>
-      </c>
-      <c r="P32" s="3">
-        <f>(H30+H40)*($R32/100)</f>
-        <v>14.444000000000001</v>
-      </c>
-      <c r="Q32" s="62">
-        <f t="shared" si="8"/>
-        <v>6.0178694558961068</v>
-      </c>
-      <c r="R32">
-        <v>92</v>
-      </c>
-      <c r="V32" t="s">
-        <v>240</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C33" t="s">
-        <v>172</v>
-      </c>
-      <c r="D33">
-        <v>62.6</v>
-      </c>
-      <c r="E33" s="5">
-        <f t="shared" si="0"/>
-        <v>3.8430842900116641E-2</v>
-      </c>
-      <c r="F33">
-        <v>1.8</v>
-      </c>
-      <c r="G33" s="5">
-        <f t="shared" si="1"/>
-        <v>3.272727272727273E-2</v>
-      </c>
-      <c r="H33">
-        <v>11</v>
-      </c>
-      <c r="I33" s="5">
-        <f t="shared" si="2"/>
-        <v>2.1480179652411637E-2</v>
-      </c>
-      <c r="K33" t="s">
-        <v>224</v>
-      </c>
-      <c r="L33" s="3">
-        <f>(D31)*($R33/100)</f>
-        <v>2.0240000000000005</v>
-      </c>
-      <c r="M33" s="62">
-        <f t="shared" si="4"/>
-        <v>0.18021852386426279</v>
-      </c>
-      <c r="N33" s="3">
-        <f>(F31)*($R33/100)</f>
-        <v>1.1040000000000001</v>
-      </c>
-      <c r="O33" s="62">
-        <f t="shared" si="6"/>
-        <v>3.2102355335853456</v>
-      </c>
-      <c r="P33" s="3">
-        <f>(H31)*($R33/100)</f>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="62">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R33">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C34" t="s">
+      <c r="Q33" s="148">
+        <f>L33/L$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="R33" s="110">
+        <f>M33/M$44*100</f>
+        <v>0</v>
+      </c>
+      <c r="S33" s="110">
+        <f>N33/N$44*100</f>
+        <v>2.7538683244119473</v>
+      </c>
+      <c r="T33" s="114">
+        <f t="shared" si="3"/>
+        <v>2.7538683244119473</v>
+      </c>
+      <c r="U33" s="110"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B34" s="87" t="s">
+        <v>253</v>
+      </c>
+      <c r="C34" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="78">
         <v>5.8</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="122">
         <f t="shared" si="0"/>
         <v>3.5606851249309346E-3</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="78">
         <v>0.2</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="122">
         <f t="shared" si="1"/>
         <v>3.6363636363636364E-3</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="78">
         <v>1.4</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="123">
         <f t="shared" si="2"/>
         <v>2.7338410466705718E-3</v>
       </c>
-      <c r="K34" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="L34" s="96">
-        <f>SUM(L8:L33)</f>
-        <v>1123.0809999999997</v>
-      </c>
-      <c r="M34" s="96">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="N34" s="96">
-        <f>SUM(N8:N33)</f>
-        <v>34.389999999999993</v>
-      </c>
-      <c r="O34" s="96">
-        <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="P34" s="96">
-        <f>SUM(P8:P33)</f>
-        <v>240.01850000000005</v>
-      </c>
-      <c r="Q34" s="96">
-        <f t="shared" si="8"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C35" t="s">
+      <c r="L34" s="113"/>
+      <c r="M34" s="78"/>
+      <c r="N34" s="112"/>
+      <c r="O34" s="152"/>
+      <c r="Q34" s="113"/>
+      <c r="R34" s="78"/>
+      <c r="S34" s="78"/>
+      <c r="T34" s="112"/>
+      <c r="U34" s="78"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B35" s="87" t="s">
+        <v>253</v>
+      </c>
+      <c r="C35" s="113" t="s">
         <v>201</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="78">
         <v>43.3</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="122">
         <f t="shared" si="0"/>
         <v>2.6582356191294735E-2</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="78">
         <v>4.5</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="122">
         <f t="shared" si="1"/>
         <v>8.1818181818181818E-2</v>
       </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35" s="5">
+      <c r="H35" s="78">
+        <v>0</v>
+      </c>
+      <c r="I35" s="123">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C36" t="s">
+      <c r="L35" s="113"/>
+      <c r="M35" s="78"/>
+      <c r="N35" s="112"/>
+      <c r="O35" s="152"/>
+      <c r="Q35" s="113"/>
+      <c r="R35" s="78"/>
+      <c r="S35" s="78"/>
+      <c r="T35" s="112"/>
+      <c r="U35" s="78"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" s="121" t="s">
         <v>185</v>
       </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36" s="5">
+      <c r="D36" s="78">
+        <v>0</v>
+      </c>
+      <c r="E36" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="78">
         <v>0.2</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="122">
         <f t="shared" si="1"/>
         <v>3.6363636363636364E-3</v>
       </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36" s="5">
+      <c r="H36" s="78">
+        <v>0</v>
+      </c>
+      <c r="I36" s="123">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B37" s="87" t="s">
-        <v>229</v>
-      </c>
-      <c r="C37" s="93" t="s">
+      <c r="L36" s="113"/>
+      <c r="M36" s="78"/>
+      <c r="N36" s="112"/>
+      <c r="O36" s="152"/>
+      <c r="Q36" s="113"/>
+      <c r="R36" s="78"/>
+      <c r="S36" s="78"/>
+      <c r="T36" s="112"/>
+      <c r="U36" s="78"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="87"/>
+      <c r="B37" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="130" t="s">
         <v>202</v>
       </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37" s="5">
+      <c r="D37" s="131">
+        <v>0</v>
+      </c>
+      <c r="E37" s="132">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F37">
-        <v>0</v>
-      </c>
-      <c r="G37" s="5">
+      <c r="F37" s="131">
+        <v>0</v>
+      </c>
+      <c r="G37" s="132">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="131">
         <v>120.2</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="133">
         <f t="shared" si="2"/>
         <v>0.23471978129271626</v>
       </c>
-      <c r="K37" s="87" t="s">
-        <v>226</v>
-      </c>
-      <c r="L37" s="87"/>
-      <c r="M37" s="87"/>
-      <c r="N37" s="87"/>
-      <c r="O37" s="87"/>
-      <c r="P37" s="87"/>
-      <c r="Q37" s="87"/>
-    </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C38" s="93" t="s">
+      <c r="L37" s="113"/>
+      <c r="M37" s="78"/>
+      <c r="N37" s="112"/>
+      <c r="O37" s="152"/>
+      <c r="Q37" s="113"/>
+      <c r="R37" s="78"/>
+      <c r="S37" s="78"/>
+      <c r="T37" s="112"/>
+      <c r="U37" s="78"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>227</v>
+      </c>
+      <c r="C38" s="121" t="s">
         <v>203</v>
       </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
-      <c r="E38" s="5">
+      <c r="D38" s="78">
+        <v>0</v>
+      </c>
+      <c r="E38" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F38">
-        <v>0</v>
-      </c>
-      <c r="G38" s="5">
+      <c r="F38" s="78">
+        <v>0</v>
+      </c>
+      <c r="G38" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="78">
         <v>124.5</v>
       </c>
-      <c r="I38" s="5">
+      <c r="I38" s="123">
         <f t="shared" si="2"/>
         <v>0.24311657879320445</v>
       </c>
-      <c r="K38" s="87" t="s">
-        <v>227</v>
-      </c>
-      <c r="L38" s="87"/>
-      <c r="M38" s="87"/>
-      <c r="N38" s="87"/>
-      <c r="O38" s="87"/>
-      <c r="P38" s="87"/>
-      <c r="Q38" s="87"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C39" s="93" t="s">
+      <c r="L38" s="113"/>
+      <c r="M38" s="78"/>
+      <c r="N38" s="112"/>
+      <c r="O38" s="152"/>
+      <c r="Q38" s="113"/>
+      <c r="R38" s="78"/>
+      <c r="S38" s="78"/>
+      <c r="T38" s="112"/>
+      <c r="U38" s="78"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>214</v>
+      </c>
+      <c r="C39" s="121" t="s">
         <v>204</v>
       </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5">
+      <c r="D39" s="78">
+        <v>0</v>
+      </c>
+      <c r="E39" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39" s="5">
+      <c r="F39" s="78">
+        <v>0</v>
+      </c>
+      <c r="G39" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="78">
         <v>17.899999999999999</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="123">
         <f t="shared" si="2"/>
         <v>3.4954110525288025E-2</v>
       </c>
-      <c r="K39" s="87" t="s">
-        <v>214</v>
-      </c>
-      <c r="L39" s="87"/>
-      <c r="M39" s="87"/>
-      <c r="N39" s="87"/>
-      <c r="O39" s="87"/>
-      <c r="P39" s="87"/>
-      <c r="Q39" s="87"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C40" s="93" t="s">
+      <c r="L39" s="113"/>
+      <c r="M39" s="78"/>
+      <c r="N39" s="112"/>
+      <c r="O39" s="152"/>
+      <c r="Q39" s="113"/>
+      <c r="R39" s="78"/>
+      <c r="S39" s="78"/>
+      <c r="T39" s="112"/>
+      <c r="U39" s="78"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B40" s="87" t="s">
+        <v>253</v>
+      </c>
+      <c r="C40" s="124" t="s">
         <v>205</v>
       </c>
-      <c r="D40">
-        <v>0</v>
-      </c>
-      <c r="E40" s="5">
+      <c r="D40" s="78">
+        <v>0</v>
+      </c>
+      <c r="E40" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F40">
-        <v>0</v>
-      </c>
-      <c r="G40" s="5">
+      <c r="F40" s="78">
+        <v>0</v>
+      </c>
+      <c r="G40" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="78">
         <v>15.7</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="123">
         <f t="shared" si="2"/>
         <v>3.0658074594805698E-2</v>
       </c>
-      <c r="K40" s="87" t="s">
-        <v>231</v>
-      </c>
-      <c r="L40" s="87"/>
-      <c r="M40" s="87"/>
-      <c r="N40" s="87"/>
-      <c r="O40" s="87"/>
-      <c r="P40" s="87"/>
-      <c r="Q40" s="87"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C41" s="93" t="s">
+      <c r="L40" s="113"/>
+      <c r="M40" s="78"/>
+      <c r="N40" s="112"/>
+      <c r="O40" s="152"/>
+      <c r="Q40" s="113"/>
+      <c r="R40" s="78"/>
+      <c r="S40" s="78"/>
+      <c r="T40" s="112"/>
+      <c r="U40" s="78"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>229</v>
+      </c>
+      <c r="C41" s="121" t="s">
         <v>206</v>
       </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41" s="5">
+      <c r="D41" s="78">
+        <v>0</v>
+      </c>
+      <c r="E41" s="122">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41" s="5">
+      <c r="F41" s="78">
+        <v>0</v>
+      </c>
+      <c r="G41" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="78">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="123">
         <f t="shared" si="2"/>
         <v>1.718414372192931E-2</v>
       </c>
-      <c r="K41" s="87" t="s">
-        <v>230</v>
-      </c>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
-      <c r="N41" s="87"/>
-      <c r="O41" s="87"/>
-      <c r="P41" s="87"/>
-      <c r="Q41" s="87"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C42" t="s">
+      <c r="L41" s="113"/>
+      <c r="M41" s="78"/>
+      <c r="N41" s="112"/>
+      <c r="O41" s="152"/>
+      <c r="Q41" s="113"/>
+      <c r="R41" s="78"/>
+      <c r="S41" s="78"/>
+      <c r="T41" s="112"/>
+      <c r="U41" s="78"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B42" s="87" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" s="134" t="s">
         <v>207</v>
       </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42" s="5">
+      <c r="D42" s="76">
+        <v>0</v>
+      </c>
+      <c r="E42" s="135">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F42">
-        <v>0</v>
-      </c>
-      <c r="G42" s="5">
+      <c r="F42" s="76">
+        <v>0</v>
+      </c>
+      <c r="G42" s="135">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="76">
         <v>4.7</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="136">
         <f t="shared" si="2"/>
         <v>9.1778949423940628E-3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C43" t="s">
+      <c r="L42" s="113"/>
+      <c r="M42" s="78"/>
+      <c r="N42" s="112"/>
+      <c r="O42" s="152"/>
+      <c r="Q42" s="113"/>
+      <c r="R42" s="78"/>
+      <c r="S42" s="78"/>
+      <c r="T42" s="112"/>
+      <c r="U42" s="78"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C43" s="137" t="s">
         <v>198</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="77">
         <v>2746.2</v>
       </c>
-      <c r="F43">
+      <c r="E43" s="77"/>
+      <c r="F43" s="77">
         <v>79.900000000000006</v>
       </c>
-      <c r="H43">
+      <c r="G43" s="77"/>
+      <c r="H43" s="77">
         <v>330.2</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C44" s="4" t="s">
+      <c r="I43" s="138"/>
+      <c r="L43" s="113"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="112"/>
+      <c r="O43" s="152"/>
+      <c r="Q43" s="113"/>
+      <c r="R43" s="78"/>
+      <c r="S43" s="78"/>
+      <c r="T43" s="112"/>
+      <c r="U43" s="78"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C44" s="119" t="s">
         <v>208</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="125">
         <v>4375.1000000000004</v>
       </c>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4">
+      <c r="E44" s="125"/>
+      <c r="F44" s="125">
         <v>134.9</v>
       </c>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4">
+      <c r="G44" s="125"/>
+      <c r="H44" s="125">
         <v>842.3</v>
       </c>
-      <c r="I44" s="4"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="C45" s="4" t="s">
+      <c r="I44" s="126"/>
+      <c r="K44" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="L44" s="139">
+        <f>SUM(L8:L43)</f>
+        <v>1114.5272</v>
+      </c>
+      <c r="M44" s="149">
+        <f>SUM(M8:M43)</f>
+        <v>34.312800000000003</v>
+      </c>
+      <c r="N44" s="140">
+        <f>SUM(N8:N43)</f>
+        <v>319.55050000000006</v>
+      </c>
+      <c r="O44" s="152"/>
+      <c r="Q44" s="139">
+        <f>SUM(Q8:Q43)</f>
+        <v>100</v>
+      </c>
+      <c r="R44" s="149">
+        <f t="shared" ref="R44:T44" si="4">SUM(R8:R43)</f>
+        <v>100</v>
+      </c>
+      <c r="S44" s="149">
+        <f t="shared" si="4"/>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="T44" s="140">
+        <f t="shared" si="4"/>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="U44" s="145"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C45" s="127" t="s">
         <v>228</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="128">
         <f>SUM(D8:D42)</f>
         <v>1628.9</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4">
+      <c r="E45" s="128"/>
+      <c r="F45" s="128">
         <f>SUM(F8:F42)</f>
         <v>55</v>
       </c>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4">
+      <c r="G45" s="128"/>
+      <c r="H45" s="128">
         <f>SUM(H8:H42)</f>
         <v>512.1</v>
       </c>
-      <c r="I45" s="4"/>
+      <c r="I45" s="129"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="K46" s="115"/>
+      <c r="L46" s="87"/>
+      <c r="M46" s="87"/>
+      <c r="N46" s="87"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C47" s="153" t="s">
+        <v>251</v>
+      </c>
+      <c r="K47" s="115"/>
+      <c r="L47" s="87"/>
+      <c r="M47" s="87"/>
+      <c r="N47" s="87"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C48" s="153" t="s">
+        <v>252</v>
+      </c>
+      <c r="K48" s="115"/>
+      <c r="L48" s="87"/>
+      <c r="M48" s="87"/>
+      <c r="N48" s="87"/>
+    </row>
+    <row r="49" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K49" s="87"/>
+      <c r="L49" s="87"/>
+      <c r="M49" s="87"/>
+      <c r="N49" s="87"/>
+    </row>
+    <row r="50" spans="11:14" x14ac:dyDescent="0.25">
+      <c r="K50" s="115"/>
+      <c r="L50" s="87"/>
+      <c r="M50" s="87"/>
+      <c r="N50" s="87"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13382,19 +13907,19 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="40"/>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="103" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="107" t="s">
+      <c r="D23" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="100" t="s">
+      <c r="E23" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="102" t="s">
+      <c r="F23" s="100" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="104"/>
+      <c r="G23" s="102"/>
       <c r="H23" s="31"/>
       <c r="O23">
         <v>11</v>
@@ -13416,11 +13941,11 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="41"/>
-      <c r="C24" s="106"/>
-      <c r="D24" s="108"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="104"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="106"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="101"/>
+      <c r="G24" s="102"/>
       <c r="H24" s="18"/>
       <c r="O24">
         <v>13</v>
@@ -13441,13 +13966,13 @@
       </c>
     </row>
     <row r="25" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="110" t="s">
+      <c r="B25" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="108"/>
+      <c r="E25" s="108"/>
+      <c r="F25" s="108"/>
       <c r="G25" s="42"/>
       <c r="H25" s="18"/>
       <c r="O25">
@@ -13469,13 +13994,13 @@
       </c>
     </row>
     <row r="26" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="99" t="s">
+      <c r="B26" s="97" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="99"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="99"/>
+      <c r="C26" s="97"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="97"/>
+      <c r="F26" s="97"/>
       <c r="G26" s="42"/>
       <c r="H26" s="18"/>
       <c r="O26">
@@ -13667,25 +14192,25 @@
       <c r="R33" s="3"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="109" t="s">
+      <c r="B34" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="109"/>
-      <c r="D34" s="109"/>
-      <c r="E34" s="109"/>
-      <c r="F34" s="109"/>
+      <c r="C34" s="107"/>
+      <c r="D34" s="107"/>
+      <c r="E34" s="107"/>
+      <c r="F34" s="107"/>
       <c r="G34" s="42"/>
       <c r="H34" s="18"/>
       <c r="R34" s="13"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="99" t="s">
+      <c r="B35" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="99"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="99"/>
-      <c r="F35" s="99"/>
+      <c r="C35" s="97"/>
+      <c r="D35" s="97"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="97"/>
       <c r="G35" s="42"/>
       <c r="H35" s="18"/>
     </row>

--- a/data/prod_parameters/PigHerd.xlsx
+++ b/data/prod_parameters/PigHerd.xlsx
@@ -19,7 +19,7 @@
     <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
     <sheet name="Energi rek" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913" iterate="1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1512,42 +1512,6 @@
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1609,6 +1573,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -7174,7 +7174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N134"/>
+  <dimension ref="A1:P134"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -7185,7 +7185,7 @@
     <col min="8" max="8" width="31.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>49</v>
       </c>
@@ -7211,7 +7211,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>73</v>
       </c>
@@ -7223,7 +7223,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -7241,7 +7241,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -7259,7 +7259,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -7277,7 +7277,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -7313,7 +7313,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -7331,7 +7331,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -7348,7 +7348,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -7365,7 +7365,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -7404,8 +7404,12 @@
       <c r="H12" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="P12" s="13">
+        <f>E3*E5</f>
+        <v>32.571720000000013</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
         <v>153</v>
       </c>
@@ -7415,8 +7419,12 @@
       <c r="F13" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="P13" s="13">
+        <f>P12*(1-E34/100)*(1-E36/100)</f>
+        <v>26.392688828712011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
         <v>48</v>
       </c>
@@ -7433,7 +7441,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>80</v>
       </c>
@@ -9406,17 +9414,17 @@
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="C6" s="116" t="s">
+      <c r="C6" s="104" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="105" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="118"/>
+      <c r="E6" s="105"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="106"/>
       <c r="L6" s="90" t="s">
         <v>248</v>
       </c>
@@ -9429,54 +9437,54 @@
       <c r="B7" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="127"/>
-      <c r="D7" s="143" t="s">
+      <c r="C7" s="115"/>
+      <c r="D7" s="131" t="s">
         <v>169</v>
       </c>
-      <c r="E7" s="143" t="s">
+      <c r="E7" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="143" t="s">
+      <c r="F7" s="131" t="s">
         <v>170</v>
       </c>
-      <c r="G7" s="143" t="s">
+      <c r="G7" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="143" t="s">
+      <c r="H7" s="131" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="144" t="s">
+      <c r="I7" s="132" t="s">
         <v>23</v>
       </c>
       <c r="K7" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="L7" s="141" t="s">
+      <c r="L7" s="129" t="s">
         <v>240</v>
       </c>
-      <c r="M7" s="147" t="s">
+      <c r="M7" s="135" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="142" t="s">
+      <c r="N7" s="130" t="s">
         <v>250</v>
       </c>
-      <c r="O7" s="151" t="s">
+      <c r="O7" s="139" t="s">
         <v>209</v>
       </c>
       <c r="P7" s="91"/>
-      <c r="Q7" s="141">
-        <v>0</v>
-      </c>
-      <c r="R7" s="147" t="s">
+      <c r="Q7" s="129">
+        <v>0</v>
+      </c>
+      <c r="R7" s="135" t="s">
         <v>15</v>
       </c>
-      <c r="S7" s="147" t="s">
+      <c r="S7" s="135" t="s">
         <v>24</v>
       </c>
-      <c r="T7" s="142" t="s">
+      <c r="T7" s="130" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="120"/>
+      <c r="U7" s="108"/>
       <c r="V7" s="92" t="s">
         <v>232</v>
       </c>
@@ -9485,705 +9493,705 @@
       <c r="B8" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="121" t="s">
+      <c r="C8" s="109" t="s">
         <v>173</v>
       </c>
       <c r="D8" s="78">
         <v>517.6</v>
       </c>
-      <c r="E8" s="122">
+      <c r="E8" s="110">
         <f t="shared" ref="E8:E42" si="0">D8/D$45</f>
         <v>0.31776045183866414</v>
       </c>
       <c r="F8" s="78">
         <v>14.9</v>
       </c>
-      <c r="G8" s="122">
+      <c r="G8" s="110">
         <f t="shared" ref="G8:G42" si="1">F8/F$45</f>
         <v>0.27090909090909093</v>
       </c>
       <c r="H8" s="78">
         <v>81.099999999999994</v>
       </c>
-      <c r="I8" s="123">
+      <c r="I8" s="111">
         <f t="shared" ref="I8:I42" si="2">H8/H$45</f>
         <v>0.15836750634641669</v>
       </c>
       <c r="K8" t="s">
         <v>70</v>
       </c>
-      <c r="L8" s="109">
+      <c r="L8" s="97">
         <f>(D8)*($O8/100)</f>
         <v>445.13600000000002</v>
       </c>
-      <c r="M8" s="111">
+      <c r="M8" s="99">
         <f>(F8)*($O8/100)</f>
         <v>12.814</v>
       </c>
-      <c r="N8" s="146">
+      <c r="N8" s="134">
         <f>(H8)*($O8/100)</f>
         <v>69.745999999999995</v>
       </c>
-      <c r="O8" s="152">
+      <c r="O8" s="140">
         <v>86</v>
       </c>
-      <c r="Q8" s="148">
-        <f>L8/L$44*100</f>
+      <c r="Q8" s="136">
+        <f t="shared" ref="Q8:Q33" si="3">L8/L$44*100</f>
         <v>39.939446969082496</v>
       </c>
-      <c r="R8" s="110">
-        <f>M8/M$44*100</f>
+      <c r="R8" s="98">
+        <f t="shared" ref="R8:R33" si="4">M8/M$44*100</f>
         <v>37.344664381805039</v>
       </c>
-      <c r="S8" s="150">
+      <c r="S8" s="138">
+        <f t="shared" ref="S8:S33" si="5">N8/N$44*100</f>
+        <v>21.826284108458598</v>
+      </c>
+      <c r="T8" s="102">
         <f>N8/N$44*100</f>
         <v>21.826284108458598</v>
       </c>
-      <c r="T8" s="114">
-        <f>N8/N$44*100</f>
-        <v>21.826284108458598</v>
-      </c>
-      <c r="U8" s="110"/>
+      <c r="U8" s="98"/>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="121" t="s">
+      <c r="C9" s="109" t="s">
         <v>174</v>
       </c>
       <c r="D9" s="78">
         <v>435.3</v>
       </c>
-      <c r="E9" s="122">
+      <c r="E9" s="110">
         <f t="shared" si="0"/>
         <v>0.267235557738351</v>
       </c>
       <c r="F9" s="78">
         <v>13.5</v>
       </c>
-      <c r="G9" s="122">
+      <c r="G9" s="110">
         <f t="shared" si="1"/>
         <v>0.24545454545454545</v>
       </c>
       <c r="H9" s="78">
         <v>62.3</v>
       </c>
-      <c r="I9" s="123">
+      <c r="I9" s="111">
         <f t="shared" si="2"/>
         <v>0.12165592657684045</v>
       </c>
       <c r="K9" t="s">
         <v>160</v>
       </c>
-      <c r="L9" s="109">
+      <c r="L9" s="97">
         <f>(D9)*($O9/100)</f>
         <v>374.358</v>
       </c>
-      <c r="M9" s="111">
+      <c r="M9" s="99">
         <f>(F9)*($O9/100)</f>
         <v>11.61</v>
       </c>
-      <c r="N9" s="146">
+      <c r="N9" s="134">
         <f>(H9)*($O9/100)</f>
         <v>53.577999999999996</v>
       </c>
-      <c r="O9" s="152">
+      <c r="O9" s="140">
         <v>86</v>
       </c>
-      <c r="Q9" s="148">
-        <f>L9/L$44*100</f>
+      <c r="Q9" s="136">
+        <f t="shared" si="3"/>
         <v>33.588951440574981</v>
       </c>
-      <c r="R9" s="110">
-        <f>M9/M$44*100</f>
+      <c r="R9" s="98">
+        <f t="shared" si="4"/>
         <v>33.835769741903896</v>
       </c>
-      <c r="S9" s="110">
-        <f>N9/N$44*100</f>
+      <c r="S9" s="98">
+        <f t="shared" si="5"/>
         <v>16.76667694151628</v>
       </c>
-      <c r="T9" s="114">
-        <f t="shared" ref="T9:T33" si="3">N9/N$44*100</f>
+      <c r="T9" s="102">
+        <f t="shared" ref="T9:T33" si="6">N9/N$44*100</f>
         <v>16.76667694151628</v>
       </c>
-      <c r="U9" s="110"/>
+      <c r="U9" s="98"/>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="109" t="s">
         <v>175</v>
       </c>
       <c r="D10" s="78">
         <v>63.2</v>
       </c>
-      <c r="E10" s="122">
+      <c r="E10" s="110">
         <f t="shared" si="0"/>
         <v>3.8799189637178461E-2</v>
       </c>
       <c r="F10" s="78">
         <v>2.7</v>
       </c>
-      <c r="G10" s="122">
+      <c r="G10" s="110">
         <f t="shared" si="1"/>
         <v>4.9090909090909095E-2</v>
       </c>
       <c r="H10" s="78">
         <v>10.5</v>
       </c>
-      <c r="I10" s="123">
+      <c r="I10" s="111">
         <f t="shared" si="2"/>
         <v>2.0503807850029289E-2</v>
       </c>
       <c r="K10" t="s">
         <v>161</v>
       </c>
-      <c r="L10" s="109">
+      <c r="L10" s="97">
         <f>(D10+D36)*($O10/100)</f>
         <v>54.352000000000004</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="99">
         <f>(F10+F36)*($O10/100)</f>
         <v>2.4940000000000002</v>
       </c>
-      <c r="N10" s="146">
+      <c r="N10" s="134">
         <f>(H10+H36)*($O10/100)</f>
         <v>9.0299999999999994</v>
       </c>
-      <c r="O10" s="152">
+      <c r="O10" s="140">
         <v>86</v>
       </c>
-      <c r="Q10" s="148">
-        <f>L10/L$44*100</f>
+      <c r="Q10" s="136">
+        <f t="shared" si="3"/>
         <v>4.876686724200181</v>
       </c>
-      <c r="R10" s="110">
-        <f>M10/M$44*100</f>
+      <c r="R10" s="98">
+        <f t="shared" si="4"/>
         <v>7.2684246112238</v>
       </c>
-      <c r="S10" s="110">
-        <f>N10/N$44*100</f>
+      <c r="S10" s="98">
+        <f t="shared" si="5"/>
         <v>2.8258444283454405</v>
       </c>
-      <c r="T10" s="114">
-        <f t="shared" si="3"/>
+      <c r="T10" s="102">
+        <f t="shared" si="6"/>
         <v>2.8258444283454405</v>
       </c>
-      <c r="U10" s="110"/>
+      <c r="U10" s="98"/>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>162</v>
       </c>
-      <c r="C11" s="121" t="s">
+      <c r="C11" s="109" t="s">
         <v>176</v>
       </c>
       <c r="D11" s="78">
         <v>5.8</v>
       </c>
-      <c r="E11" s="122">
+      <c r="E11" s="110">
         <f t="shared" si="0"/>
         <v>3.5606851249309346E-3</v>
       </c>
       <c r="F11" s="78">
         <v>0</v>
       </c>
-      <c r="G11" s="122">
+      <c r="G11" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H11" s="78">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I11" s="123">
+      <c r="I11" s="111">
         <f t="shared" si="2"/>
         <v>1.9136887326694007E-2</v>
       </c>
       <c r="K11" t="s">
         <v>162</v>
       </c>
-      <c r="L11" s="109">
-        <f>(D11)*($O11/100)</f>
+      <c r="L11" s="97">
+        <f t="shared" ref="L11:L21" si="7">(D11)*($O11/100)</f>
         <v>4.9879999999999995</v>
       </c>
-      <c r="M11" s="111">
-        <f>(F11)*($O11/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="146">
-        <f>(H11)*($O11/100)</f>
+      <c r="M11" s="99">
+        <f t="shared" ref="M11:M21" si="8">(F11)*($O11/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="134">
+        <f t="shared" ref="N11:N21" si="9">(H11)*($O11/100)</f>
         <v>8.4280000000000008</v>
       </c>
-      <c r="O11" s="152">
+      <c r="O11" s="140">
         <v>86</v>
       </c>
-      <c r="Q11" s="148">
-        <f>L11/L$44*100</f>
+      <c r="Q11" s="136">
+        <f t="shared" si="3"/>
         <v>0.44754403481583932</v>
       </c>
-      <c r="R11" s="110">
-        <f>M11/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S11" s="110">
-        <f>N11/N$44*100</f>
+      <c r="R11" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="98">
+        <f t="shared" si="5"/>
         <v>2.6374547997890785</v>
       </c>
-      <c r="T11" s="114">
-        <f t="shared" si="3"/>
+      <c r="T11" s="102">
+        <f t="shared" si="6"/>
         <v>2.6374547997890785</v>
       </c>
-      <c r="U11" s="110"/>
+      <c r="U11" s="98"/>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>165</v>
       </c>
-      <c r="C12" s="121" t="s">
+      <c r="C12" s="109" t="s">
         <v>182</v>
       </c>
       <c r="D12" s="78">
         <v>2.9</v>
       </c>
-      <c r="E12" s="122">
+      <c r="E12" s="110">
         <f t="shared" si="0"/>
         <v>1.7803425624654673E-3</v>
       </c>
       <c r="F12" s="78">
         <v>0.7</v>
       </c>
-      <c r="G12" s="122">
+      <c r="G12" s="110">
         <f t="shared" si="1"/>
         <v>1.2727272727272726E-2</v>
       </c>
       <c r="H12" s="78">
         <v>0.2</v>
       </c>
-      <c r="I12" s="123">
+      <c r="I12" s="111">
         <f t="shared" si="2"/>
         <v>3.905487209529389E-4</v>
       </c>
       <c r="K12" t="s">
         <v>165</v>
       </c>
-      <c r="L12" s="109">
-        <f>(D12)*($O12/100)</f>
+      <c r="L12" s="97">
+        <f t="shared" si="7"/>
         <v>2.4939999999999998</v>
       </c>
-      <c r="M12" s="111">
-        <f>(F12)*($O12/100)</f>
+      <c r="M12" s="99">
+        <f t="shared" si="8"/>
         <v>0.60199999999999998</v>
       </c>
-      <c r="N12" s="146">
-        <f>(H12)*($O12/100)</f>
+      <c r="N12" s="134">
+        <f t="shared" si="9"/>
         <v>0.17200000000000001</v>
       </c>
-      <c r="O12" s="152">
+      <c r="O12" s="140">
         <v>86</v>
       </c>
-      <c r="Q12" s="148">
-        <f>L12/L$44*100</f>
+      <c r="Q12" s="136">
+        <f t="shared" si="3"/>
         <v>0.22377201740791966</v>
       </c>
-      <c r="R12" s="110">
-        <f>M12/M$44*100</f>
+      <c r="R12" s="98">
+        <f t="shared" si="4"/>
         <v>1.7544473199505721</v>
       </c>
-      <c r="S12" s="110">
-        <f>N12/N$44*100</f>
+      <c r="S12" s="98">
+        <f t="shared" si="5"/>
         <v>5.3825608158960786E-2</v>
       </c>
-      <c r="T12" s="114">
-        <f t="shared" si="3"/>
+      <c r="T12" s="102">
+        <f t="shared" si="6"/>
         <v>5.3825608158960786E-2</v>
       </c>
-      <c r="U12" s="110"/>
+      <c r="U12" s="98"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>218</v>
       </c>
-      <c r="C13" s="121" t="s">
+      <c r="C13" s="109" t="s">
         <v>188</v>
       </c>
       <c r="D13" s="78">
         <v>10.3</v>
       </c>
-      <c r="E13" s="122">
+      <c r="E13" s="110">
         <f t="shared" si="0"/>
         <v>6.3232856528945914E-3</v>
       </c>
       <c r="F13" s="78">
         <v>0.1</v>
       </c>
-      <c r="G13" s="122">
+      <c r="G13" s="110">
         <f t="shared" si="1"/>
         <v>1.8181818181818182E-3</v>
       </c>
       <c r="H13" s="78">
         <v>1.2</v>
       </c>
-      <c r="I13" s="123">
+      <c r="I13" s="111">
         <f t="shared" si="2"/>
         <v>2.3432923257176333E-3</v>
       </c>
       <c r="K13" t="s">
         <v>218</v>
       </c>
-      <c r="L13" s="109">
-        <f>(D13)*($O13/100)</f>
+      <c r="L13" s="97">
+        <f t="shared" si="7"/>
         <v>8.7550000000000008</v>
       </c>
-      <c r="M13" s="111">
-        <f>(F13)*($O13/100)</f>
+      <c r="M13" s="99">
+        <f t="shared" si="8"/>
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="N13" s="146">
-        <f>(H13)*($O13/100)</f>
+      <c r="N13" s="134">
+        <f t="shared" si="9"/>
         <v>1.02</v>
       </c>
-      <c r="O13" s="152">
+      <c r="O13" s="140">
         <v>85</v>
       </c>
-      <c r="Q13" s="148">
-        <f>L13/L$44*100</f>
+      <c r="Q13" s="136">
+        <f t="shared" si="3"/>
         <v>0.78553488869540378</v>
       </c>
-      <c r="R13" s="110">
-        <f>M13/M$44*100</f>
+      <c r="R13" s="98">
+        <f t="shared" si="4"/>
         <v>0.24772096710265556</v>
       </c>
-      <c r="S13" s="110">
-        <f>N13/N$44*100</f>
+      <c r="S13" s="98">
+        <f t="shared" si="5"/>
         <v>0.31919837396593026</v>
       </c>
-      <c r="T13" s="114">
-        <f t="shared" si="3"/>
+      <c r="T13" s="102">
+        <f t="shared" si="6"/>
         <v>0.31919837396593026</v>
       </c>
-      <c r="U13" s="110"/>
+      <c r="U13" s="98"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>219</v>
       </c>
-      <c r="C14" s="121" t="s">
+      <c r="C14" s="109" t="s">
         <v>189</v>
       </c>
       <c r="D14" s="78">
         <v>1.3</v>
       </c>
-      <c r="E14" s="122">
+      <c r="E14" s="110">
         <f t="shared" si="0"/>
         <v>7.9808459696727846E-4</v>
       </c>
       <c r="F14" s="78">
         <v>0.3</v>
       </c>
-      <c r="G14" s="122">
+      <c r="G14" s="110">
         <f t="shared" si="1"/>
         <v>5.4545454545454541E-3</v>
       </c>
       <c r="H14" s="78">
         <v>20.3</v>
       </c>
-      <c r="I14" s="123">
+      <c r="I14" s="111">
         <f t="shared" si="2"/>
         <v>3.9640695176723299E-2</v>
       </c>
       <c r="K14" t="s">
         <v>219</v>
       </c>
-      <c r="L14" s="109">
-        <f>(D14)*($O14/100)</f>
+      <c r="L14" s="97">
+        <f t="shared" si="7"/>
         <v>1.105</v>
       </c>
-      <c r="M14" s="111">
-        <f>(F14)*($O14/100)</f>
+      <c r="M14" s="99">
+        <f t="shared" si="8"/>
         <v>0.255</v>
       </c>
-      <c r="N14" s="146">
-        <f>(H14)*($O14/100)</f>
+      <c r="N14" s="134">
+        <f t="shared" si="9"/>
         <v>17.254999999999999</v>
       </c>
-      <c r="O14" s="152">
+      <c r="O14" s="140">
         <v>85</v>
       </c>
-      <c r="Q14" s="148">
-        <f>L14/L$44*100</f>
+      <c r="Q14" s="136">
+        <f t="shared" si="3"/>
         <v>9.9145180126604351E-2</v>
       </c>
-      <c r="R14" s="110">
-        <f>M14/M$44*100</f>
+      <c r="R14" s="98">
+        <f t="shared" si="4"/>
         <v>0.74316290130796658</v>
       </c>
-      <c r="S14" s="110">
-        <f>N14/N$44*100</f>
+      <c r="S14" s="98">
+        <f t="shared" si="5"/>
         <v>5.3997724929236526</v>
       </c>
-      <c r="T14" s="114">
-        <f t="shared" si="3"/>
+      <c r="T14" s="102">
+        <f t="shared" si="6"/>
         <v>5.3997724929236526</v>
       </c>
-      <c r="U14" s="110"/>
+      <c r="U14" s="98"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>163</v>
       </c>
-      <c r="C15" s="121" t="s">
+      <c r="C15" s="109" t="s">
         <v>180</v>
       </c>
       <c r="D15" s="78">
         <v>4.3</v>
       </c>
-      <c r="E15" s="122">
+      <c r="E15" s="110">
         <f t="shared" si="0"/>
         <v>2.6398182822763828E-3</v>
       </c>
       <c r="F15" s="78">
         <v>0</v>
       </c>
-      <c r="G15" s="122">
+      <c r="G15" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H15" s="78">
         <v>0</v>
       </c>
-      <c r="I15" s="123">
+      <c r="I15" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" t="s">
         <v>163</v>
       </c>
-      <c r="L15" s="109">
-        <f>(D15)*($O15/100)</f>
+      <c r="L15" s="97">
+        <f t="shared" si="7"/>
         <v>3.9129999999999998</v>
       </c>
-      <c r="M15" s="111">
-        <f>(F15)*($O15/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="146">
-        <f>(H15)*($O15/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O15" s="152">
+      <c r="M15" s="99">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="134">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O15" s="140">
         <v>91</v>
       </c>
-      <c r="Q15" s="148">
-        <f>L15/L$44*100</f>
+      <c r="Q15" s="136">
+        <f t="shared" si="3"/>
         <v>0.35109057903656365</v>
       </c>
-      <c r="R15" s="110">
-        <f>M15/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S15" s="110">
-        <f>N15/N$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="T15" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="110"/>
+      <c r="R15" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="98"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="121" t="s">
+      <c r="C16" s="109" t="s">
         <v>181</v>
       </c>
       <c r="D16" s="78">
         <v>1.6</v>
       </c>
-      <c r="E16" s="122">
+      <c r="E16" s="110">
         <f t="shared" si="0"/>
         <v>9.8225796549818905E-4</v>
       </c>
       <c r="F16" s="78">
         <v>0</v>
       </c>
-      <c r="G16" s="122">
+      <c r="G16" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H16" s="78">
         <v>0</v>
       </c>
-      <c r="I16" s="123">
+      <c r="I16" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K16" t="s">
         <v>164</v>
       </c>
-      <c r="L16" s="109">
-        <f>(D16)*($O16/100)</f>
+      <c r="L16" s="97">
+        <f t="shared" si="7"/>
         <v>1.4560000000000002</v>
       </c>
-      <c r="M16" s="111">
-        <f>(F16)*($O16/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="146">
-        <f>(H16)*($O16/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O16" s="152">
+      <c r="M16" s="99">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="134">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="140">
         <v>91</v>
       </c>
-      <c r="Q16" s="148">
-        <f>L16/L$44*100</f>
+      <c r="Q16" s="136">
+        <f t="shared" si="3"/>
         <v>0.13063835499034929</v>
       </c>
-      <c r="R16" s="110">
-        <f>M16/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S16" s="110">
-        <f>N16/N$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U16" s="110"/>
+      <c r="R16" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="98"/>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>220</v>
       </c>
-      <c r="C17" s="121" t="s">
+      <c r="C17" s="109" t="s">
         <v>190</v>
       </c>
       <c r="D17" s="78">
         <v>88.6</v>
       </c>
-      <c r="E17" s="122">
+      <c r="E17" s="110">
         <f t="shared" si="0"/>
         <v>5.4392534839462207E-2</v>
       </c>
       <c r="F17" s="78">
         <v>2.8</v>
       </c>
-      <c r="G17" s="122">
+      <c r="G17" s="110">
         <f t="shared" si="1"/>
         <v>5.0909090909090904E-2</v>
       </c>
       <c r="H17" s="78">
         <v>7.2</v>
       </c>
-      <c r="I17" s="123">
+      <c r="I17" s="111">
         <f t="shared" si="2"/>
         <v>1.4059753954305799E-2</v>
       </c>
       <c r="K17" t="s">
         <v>220</v>
       </c>
-      <c r="L17" s="109">
-        <f>(D17)*($O17/100)</f>
+      <c r="L17" s="97">
+        <f t="shared" si="7"/>
         <v>77.967999999999989</v>
       </c>
-      <c r="M17" s="111">
-        <f>(F17)*($O17/100)</f>
+      <c r="M17" s="99">
+        <f t="shared" si="8"/>
         <v>2.464</v>
       </c>
-      <c r="N17" s="146">
-        <f>(H17)*($O17/100)</f>
+      <c r="N17" s="134">
+        <f t="shared" si="9"/>
         <v>6.3360000000000003</v>
       </c>
-      <c r="O17" s="152">
+      <c r="O17" s="140">
         <v>88</v>
       </c>
-      <c r="Q17" s="148">
-        <f>L17/L$44*100</f>
+      <c r="Q17" s="136">
+        <f t="shared" si="3"/>
         <v>6.9956121304172738</v>
       </c>
-      <c r="R17" s="110">
-        <f>M17/M$44*100</f>
+      <c r="R17" s="98">
+        <f t="shared" si="4"/>
         <v>7.1809936816581557</v>
       </c>
-      <c r="S17" s="110">
-        <f>N17/N$44*100</f>
+      <c r="S17" s="98">
+        <f t="shared" si="5"/>
         <v>1.9827851935766017</v>
       </c>
-      <c r="T17" s="114">
-        <f t="shared" si="3"/>
+      <c r="T17" s="102">
+        <f t="shared" si="6"/>
         <v>1.9827851935766017</v>
       </c>
-      <c r="U17" s="110"/>
+      <c r="U17" s="98"/>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>222</v>
       </c>
-      <c r="C18" s="121" t="s">
+      <c r="C18" s="109" t="s">
         <v>194</v>
       </c>
       <c r="D18" s="78">
         <v>0</v>
       </c>
-      <c r="E18" s="122">
+      <c r="E18" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F18" s="78">
         <v>0.9</v>
       </c>
-      <c r="G18" s="122">
+      <c r="G18" s="110">
         <f t="shared" si="1"/>
         <v>1.6363636363636365E-2</v>
       </c>
       <c r="H18" s="78">
         <v>0</v>
       </c>
-      <c r="I18" s="123">
+      <c r="I18" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K18" t="s">
         <v>222</v>
       </c>
-      <c r="L18" s="109">
-        <f>(D18)*($O18/100)</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="111">
-        <f>(F18)*($O18/100)</f>
+      <c r="L18" s="97">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="99">
+        <f t="shared" si="8"/>
         <v>0.78300000000000003</v>
       </c>
-      <c r="N18" s="146">
-        <f>(H18)*($O18/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O18" s="152">
+      <c r="N18" s="134">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="140">
         <v>87</v>
       </c>
-      <c r="Q18" s="148">
-        <f>L18/L$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="110">
-        <f>M18/M$44*100</f>
+      <c r="Q18" s="136">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R18" s="98">
+        <f t="shared" si="4"/>
         <v>2.2819472616632859</v>
       </c>
-      <c r="S18" s="110">
-        <f>N18/N$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="T18" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U18" s="110"/>
+      <c r="S18" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="98"/>
       <c r="V18" t="s">
         <v>230</v>
       </c>
@@ -10192,65 +10200,65 @@
       <c r="B19" t="s">
         <v>221</v>
       </c>
-      <c r="C19" s="121" t="s">
+      <c r="C19" s="109" t="s">
         <v>191</v>
       </c>
       <c r="D19" s="78">
         <v>40.700000000000003</v>
       </c>
-      <c r="E19" s="122">
+      <c r="E19" s="110">
         <f t="shared" si="0"/>
         <v>2.4986186997360181E-2</v>
       </c>
       <c r="F19" s="78">
         <v>0</v>
       </c>
-      <c r="G19" s="122">
+      <c r="G19" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H19" s="78">
         <v>8.6999999999999993</v>
       </c>
-      <c r="I19" s="123">
+      <c r="I19" s="111">
         <f t="shared" si="2"/>
         <v>1.698886936145284E-2</v>
       </c>
       <c r="K19" t="s">
         <v>221</v>
       </c>
-      <c r="L19" s="109">
-        <f>(D19)*($O19/100)</f>
+      <c r="L19" s="97">
+        <f t="shared" si="7"/>
         <v>36.630000000000003</v>
       </c>
-      <c r="M19" s="111">
-        <f>(F19)*($O19/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N19" s="146">
-        <f>(H19)*($O19/100)</f>
+      <c r="M19" s="99">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="134">
+        <f t="shared" si="9"/>
         <v>7.8299999999999992</v>
       </c>
-      <c r="O19" s="152">
+      <c r="O19" s="140">
         <v>90</v>
       </c>
-      <c r="Q19" s="148">
-        <f>L19/L$44*100</f>
+      <c r="Q19" s="136">
+        <f t="shared" si="3"/>
         <v>3.2865954280882512</v>
       </c>
-      <c r="R19" s="110">
-        <f>M19/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="110">
-        <f>N19/N$44*100</f>
+      <c r="R19" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="98">
+        <f t="shared" si="5"/>
         <v>2.4503169295619931</v>
       </c>
-      <c r="T19" s="114">
-        <f t="shared" si="3"/>
+      <c r="T19" s="102">
+        <f t="shared" si="6"/>
         <v>2.4503169295619931</v>
       </c>
-      <c r="U19" s="110"/>
+      <c r="U19" s="98"/>
       <c r="V19" t="s">
         <v>231</v>
       </c>
@@ -10259,129 +10267,129 @@
       <c r="B20" t="s">
         <v>217</v>
       </c>
-      <c r="C20" s="121" t="s">
+      <c r="C20" s="109" t="s">
         <v>187</v>
       </c>
       <c r="D20" s="78">
         <v>5.5</v>
       </c>
-      <c r="E20" s="122">
+      <c r="E20" s="110">
         <f t="shared" si="0"/>
         <v>3.3765117564000242E-3</v>
       </c>
       <c r="F20" s="78">
         <v>0</v>
       </c>
-      <c r="G20" s="122">
+      <c r="G20" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H20" s="78">
         <v>0.4</v>
       </c>
-      <c r="I20" s="123">
+      <c r="I20" s="111">
         <f t="shared" si="2"/>
         <v>7.810974419058778E-4</v>
       </c>
       <c r="K20" t="s">
         <v>217</v>
       </c>
-      <c r="L20" s="109">
-        <f>(D20)*($O20/100)</f>
+      <c r="L20" s="97">
+        <f t="shared" si="7"/>
         <v>5.0049999999999999</v>
       </c>
-      <c r="M20" s="111">
-        <f>(F20)*($O20/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N20" s="146">
-        <f>(H20)*($O20/100)</f>
+      <c r="M20" s="99">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="134">
+        <f t="shared" si="9"/>
         <v>0.36400000000000005</v>
       </c>
-      <c r="O20" s="152">
+      <c r="O20" s="140">
         <v>91</v>
       </c>
-      <c r="Q20" s="148">
-        <f>L20/L$44*100</f>
+      <c r="Q20" s="136">
+        <f t="shared" si="3"/>
         <v>0.44906934527932563</v>
       </c>
-      <c r="R20" s="110">
-        <f>M20/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S20" s="110">
-        <f>N20/N$44*100</f>
+      <c r="R20" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="98">
+        <f t="shared" si="5"/>
         <v>0.11391000796431236</v>
       </c>
-      <c r="T20" s="114">
-        <f t="shared" si="3"/>
+      <c r="T20" s="102">
+        <f t="shared" si="6"/>
         <v>0.11391000796431236</v>
       </c>
-      <c r="U20" s="110"/>
+      <c r="U20" s="98"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>213</v>
       </c>
-      <c r="C21" s="121" t="s">
+      <c r="C21" s="109" t="s">
         <v>179</v>
       </c>
       <c r="D21" s="78">
         <v>1.6</v>
       </c>
-      <c r="E21" s="122">
+      <c r="E21" s="110">
         <f t="shared" si="0"/>
         <v>9.8225796549818905E-4</v>
       </c>
       <c r="F21" s="78">
         <v>0</v>
       </c>
-      <c r="G21" s="122">
+      <c r="G21" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H21" s="78">
         <v>0</v>
       </c>
-      <c r="I21" s="123">
+      <c r="I21" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K21" t="s">
         <v>213</v>
       </c>
-      <c r="L21" s="109">
-        <f>(D21)*($O21/100)</f>
+      <c r="L21" s="97">
+        <f t="shared" si="7"/>
         <v>1.4560000000000002</v>
       </c>
-      <c r="M21" s="111">
-        <f>(F21)*($O21/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N21" s="146">
-        <f>(H21)*($O21/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O21" s="152">
+      <c r="M21" s="99">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="134">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="140">
         <v>91</v>
       </c>
-      <c r="Q21" s="148">
-        <f>L21/L$44*100</f>
+      <c r="Q21" s="136">
+        <f t="shared" si="3"/>
         <v>0.13063835499034929</v>
       </c>
-      <c r="R21" s="110">
-        <f>M21/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S21" s="110">
-        <f>N21/N$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="T21" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U21" s="110"/>
+      <c r="R21" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="98"/>
       <c r="V21" t="s">
         <v>233</v>
       </c>
@@ -10390,65 +10398,65 @@
       <c r="B22" t="s">
         <v>214</v>
       </c>
-      <c r="C22" s="121" t="s">
+      <c r="C22" s="109" t="s">
         <v>183</v>
       </c>
       <c r="D22" s="78">
         <v>39.9</v>
       </c>
-      <c r="E22" s="122">
+      <c r="E22" s="110">
         <f t="shared" si="0"/>
         <v>2.4495058014611083E-2</v>
       </c>
       <c r="F22" s="78">
         <v>0</v>
       </c>
-      <c r="G22" s="122">
+      <c r="G22" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H22" s="78">
         <v>3.3</v>
       </c>
-      <c r="I22" s="123">
+      <c r="I22" s="111">
         <f t="shared" si="2"/>
         <v>6.444053895723491E-3</v>
       </c>
       <c r="K22" t="s">
         <v>214</v>
       </c>
-      <c r="L22" s="109">
+      <c r="L22" s="97">
         <f>(D22+D39)*($O22/100)</f>
         <v>34.713000000000001</v>
       </c>
-      <c r="M22" s="111">
+      <c r="M22" s="99">
         <f>(F22+F39)*($O22/100)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="146">
+      <c r="N22" s="134">
         <f>(H22+H39)*($O22/100)</f>
         <v>18.443999999999999</v>
       </c>
-      <c r="O22" s="152">
+      <c r="O22" s="140">
         <v>87</v>
       </c>
-      <c r="Q22" s="148">
-        <f>L22/L$44*100</f>
+      <c r="Q22" s="136">
+        <f t="shared" si="3"/>
         <v>3.1145942422939523</v>
       </c>
-      <c r="R22" s="110">
-        <f>M22/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S22" s="110">
-        <f>N22/N$44*100</f>
+      <c r="R22" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="98">
+        <f t="shared" si="5"/>
         <v>5.7718576563015853</v>
       </c>
-      <c r="T22" s="114">
-        <f t="shared" si="3"/>
+      <c r="T22" s="102">
+        <f t="shared" si="6"/>
         <v>5.7718576563015853</v>
       </c>
-      <c r="U22" s="110"/>
+      <c r="U22" s="98"/>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="87" t="s">
@@ -10457,193 +10465,193 @@
       <c r="B23" t="s">
         <v>216</v>
       </c>
-      <c r="C23" s="121" t="s">
+      <c r="C23" s="109" t="s">
         <v>184</v>
       </c>
       <c r="D23" s="78">
         <v>29.7</v>
       </c>
-      <c r="E23" s="122">
+      <c r="E23" s="110">
         <f t="shared" si="0"/>
         <v>1.8233163484560132E-2</v>
       </c>
       <c r="F23" s="78">
         <v>0.5</v>
       </c>
-      <c r="G23" s="122">
+      <c r="G23" s="110">
         <f t="shared" si="1"/>
         <v>9.0909090909090905E-3</v>
       </c>
       <c r="H23" s="78">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I23" s="123">
+      <c r="I23" s="111">
         <f t="shared" si="2"/>
         <v>4.2960359304823276E-3</v>
       </c>
       <c r="K23" t="s">
         <v>216</v>
       </c>
-      <c r="L23" s="109">
+      <c r="L23" s="97">
         <f>(D23)*($O23/100)</f>
         <v>26.135999999999999</v>
       </c>
-      <c r="M23" s="111">
+      <c r="M23" s="99">
         <f>(F23)*($O23/100)</f>
         <v>0.44</v>
       </c>
-      <c r="N23" s="146">
+      <c r="N23" s="134">
         <f>(H23)*($O23/100)</f>
         <v>1.9360000000000002</v>
       </c>
-      <c r="O23" s="152">
+      <c r="O23" s="140">
         <v>88</v>
       </c>
-      <c r="Q23" s="148">
-        <f>L23/L$44*100</f>
+      <c r="Q23" s="136">
+        <f t="shared" si="3"/>
         <v>2.3450302513926982</v>
       </c>
-      <c r="R23" s="110">
-        <f>M23/M$44*100</f>
+      <c r="R23" s="98">
+        <f t="shared" si="4"/>
         <v>1.2823203002960992</v>
       </c>
-      <c r="S23" s="110">
-        <f>N23/N$44*100</f>
+      <c r="S23" s="98">
+        <f t="shared" si="5"/>
         <v>0.60585103137062835</v>
       </c>
-      <c r="T23" s="114">
-        <f t="shared" si="3"/>
+      <c r="T23" s="102">
+        <f t="shared" si="6"/>
         <v>0.60585103137062835</v>
       </c>
-      <c r="U23" s="110"/>
+      <c r="U23" s="98"/>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>225</v>
       </c>
-      <c r="C24" s="121" t="s">
+      <c r="C24" s="109" t="s">
         <v>192</v>
       </c>
       <c r="D24" s="78">
         <v>1.7</v>
       </c>
-      <c r="E24" s="122">
+      <c r="E24" s="110">
         <f t="shared" si="0"/>
         <v>1.0436490883418256E-3</v>
       </c>
       <c r="F24" s="78">
         <v>0</v>
       </c>
-      <c r="G24" s="122">
+      <c r="G24" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H24" s="78">
         <v>0.4</v>
       </c>
-      <c r="I24" s="123">
+      <c r="I24" s="111">
         <f t="shared" si="2"/>
         <v>7.810974419058778E-4</v>
       </c>
       <c r="K24" t="s">
         <v>225</v>
       </c>
-      <c r="L24" s="109">
+      <c r="L24" s="97">
         <f>(D24+D37)*($O24/100)</f>
         <v>1.53</v>
       </c>
-      <c r="M24" s="111">
+      <c r="M24" s="99">
         <f>(F24+F37)*($O24/100)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="146">
+      <c r="N24" s="134">
         <f>(H24+H37)*($O24/100)</f>
         <v>108.54</v>
       </c>
-      <c r="O24" s="152">
+      <c r="O24" s="140">
         <v>90</v>
       </c>
-      <c r="Q24" s="148">
-        <f>L24/L$44*100</f>
+      <c r="Q24" s="136">
+        <f t="shared" si="3"/>
         <v>0.13727794171375987</v>
       </c>
-      <c r="R24" s="110">
-        <f>M24/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S24" s="110">
-        <f>N24/N$44*100</f>
+      <c r="R24" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="98">
+        <f t="shared" si="5"/>
         <v>33.966462264962807</v>
       </c>
-      <c r="T24" s="114">
-        <f t="shared" si="3"/>
+      <c r="T24" s="102">
+        <f t="shared" si="6"/>
         <v>33.966462264962807</v>
       </c>
-      <c r="U24" s="110"/>
+      <c r="U24" s="98"/>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>226</v>
       </c>
-      <c r="C25" s="121" t="s">
+      <c r="C25" s="109" t="s">
         <v>199</v>
       </c>
       <c r="D25" s="78">
         <v>60.4</v>
       </c>
-      <c r="E25" s="122">
+      <c r="E25" s="110">
         <f t="shared" si="0"/>
         <v>3.7080238197556632E-2</v>
       </c>
       <c r="F25" s="78">
         <v>0</v>
       </c>
-      <c r="G25" s="122">
+      <c r="G25" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H25" s="78">
         <v>0</v>
       </c>
-      <c r="I25" s="123">
+      <c r="I25" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K25" t="s">
         <v>226</v>
       </c>
-      <c r="L25" s="109">
+      <c r="L25" s="97">
         <f>(D25)*($O25/100)</f>
         <v>6.6440000000000001</v>
       </c>
-      <c r="M25" s="111">
+      <c r="M25" s="99">
         <f>(F25)*($O25/100)</f>
         <v>0</v>
       </c>
-      <c r="N25" s="146">
+      <c r="N25" s="134">
         <f>(H25)*($O25/100)</f>
         <v>0</v>
       </c>
-      <c r="O25" s="152">
+      <c r="O25" s="140">
         <v>11</v>
       </c>
-      <c r="Q25" s="148">
-        <f>L25/L$44*100</f>
+      <c r="Q25" s="136">
+        <f t="shared" si="3"/>
         <v>0.59612721878837949</v>
       </c>
-      <c r="R25" s="110">
-        <f>M25/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S25" s="110">
-        <f>N25/N$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="T25" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U25" s="110"/>
+      <c r="R25" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="98"/>
       <c r="V25" t="s">
         <v>235</v>
       </c>
@@ -10652,65 +10660,65 @@
       <c r="B26" t="s">
         <v>211</v>
       </c>
-      <c r="C26" s="121" t="s">
+      <c r="C26" s="109" t="s">
         <v>177</v>
       </c>
       <c r="D26" s="78">
         <v>5.2</v>
       </c>
-      <c r="E26" s="122">
+      <c r="E26" s="110">
         <f t="shared" si="0"/>
         <v>3.1923383878691139E-3</v>
       </c>
       <c r="F26" s="78">
         <v>0</v>
       </c>
-      <c r="G26" s="122">
+      <c r="G26" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H26" s="78">
         <v>0.3</v>
       </c>
-      <c r="I26" s="123">
+      <c r="I26" s="111">
         <f t="shared" si="2"/>
         <v>5.8582308142940832E-4</v>
       </c>
       <c r="K26" t="s">
         <v>211</v>
       </c>
-      <c r="L26" s="109">
+      <c r="L26" s="97">
         <f>(D26)*($O26/100)</f>
         <v>3.9520000000000004</v>
       </c>
-      <c r="M26" s="111">
+      <c r="M26" s="99">
         <f>(F26)*($O26/100)</f>
         <v>0</v>
       </c>
-      <c r="N26" s="146">
+      <c r="N26" s="134">
         <f>(H26)*($O26/100)</f>
         <v>0.22799999999999998</v>
       </c>
-      <c r="O26" s="152">
+      <c r="O26" s="140">
         <v>76</v>
       </c>
-      <c r="Q26" s="148">
-        <f>L26/L$44*100</f>
+      <c r="Q26" s="136">
+        <f t="shared" si="3"/>
         <v>0.35458982068809092</v>
       </c>
-      <c r="R26" s="110">
-        <f>M26/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S26" s="110">
-        <f>N26/N$44*100</f>
+      <c r="R26" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="98">
+        <f t="shared" si="5"/>
         <v>7.1350224768854983E-2</v>
       </c>
-      <c r="T26" s="114">
-        <f t="shared" si="3"/>
+      <c r="T26" s="102">
+        <f t="shared" si="6"/>
         <v>7.1350224768854983E-2</v>
       </c>
-      <c r="U26" s="110"/>
+      <c r="U26" s="98"/>
       <c r="V26" t="s">
         <v>234</v>
       </c>
@@ -10719,193 +10727,193 @@
       <c r="B27" t="s">
         <v>212</v>
       </c>
-      <c r="C27" s="121" t="s">
+      <c r="C27" s="109" t="s">
         <v>178</v>
       </c>
       <c r="D27" s="78">
         <v>8.6999999999999993</v>
       </c>
-      <c r="E27" s="122">
+      <c r="E27" s="110">
         <f t="shared" si="0"/>
         <v>5.3410276873964019E-3</v>
       </c>
       <c r="F27" s="78">
         <v>0</v>
       </c>
-      <c r="G27" s="122">
+      <c r="G27" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H27" s="78">
         <v>0</v>
       </c>
-      <c r="I27" s="123">
+      <c r="I27" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K27" t="s">
         <v>212</v>
       </c>
-      <c r="L27" s="109">
+      <c r="L27" s="97">
         <f>(D27)*($O27/100)</f>
         <v>7.7429999999999994</v>
       </c>
-      <c r="M27" s="111">
+      <c r="M27" s="99">
         <f>(F27)*($O27/100)</f>
         <v>0</v>
       </c>
-      <c r="N27" s="146">
+      <c r="N27" s="134">
         <f>(H27)*($O27/100)</f>
         <v>0</v>
       </c>
-      <c r="O27" s="152">
+      <c r="O27" s="140">
         <v>89</v>
       </c>
-      <c r="Q27" s="148">
-        <f>L27/L$44*100</f>
+      <c r="Q27" s="136">
+        <f t="shared" si="3"/>
         <v>0.69473405404551813</v>
       </c>
-      <c r="R27" s="110">
-        <f>M27/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S27" s="110">
-        <f>N27/N$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="T27" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U27" s="110"/>
+      <c r="R27" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="98"/>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="121" t="s">
+      <c r="C28" s="109" t="s">
         <v>200</v>
       </c>
       <c r="D28" s="78">
         <v>188.4</v>
       </c>
-      <c r="E28" s="122">
+      <c r="E28" s="110">
         <f t="shared" si="0"/>
         <v>0.11566087543741174</v>
       </c>
       <c r="F28" s="78">
         <v>9.6</v>
       </c>
-      <c r="G28" s="122">
+      <c r="G28" s="110">
         <f t="shared" si="1"/>
         <v>0.17454545454545453</v>
       </c>
       <c r="H28" s="78">
         <v>0</v>
       </c>
-      <c r="I28" s="123">
+      <c r="I28" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K28" t="s">
         <v>227</v>
       </c>
-      <c r="L28" s="109">
+      <c r="L28" s="97">
         <f>(D28+D38)*($O28/100)</f>
         <v>11.869200000000001</v>
       </c>
-      <c r="M28" s="111">
+      <c r="M28" s="99">
         <f>(F28+F38)*($O28/100)</f>
         <v>0.6048</v>
       </c>
-      <c r="N28" s="146">
+      <c r="N28" s="134">
         <f>(H28+H38)*($O28/100)</f>
         <v>7.8434999999999997</v>
       </c>
-      <c r="O28" s="152">
+      <c r="O28" s="140">
         <v>6.3</v>
       </c>
-      <c r="Q28" s="148">
-        <f>L28/L$44*100</f>
+      <c r="Q28" s="136">
+        <f t="shared" si="3"/>
         <v>1.0649538207770974</v>
       </c>
-      <c r="R28" s="110">
-        <f>M28/M$44*100</f>
+      <c r="R28" s="98">
+        <f t="shared" si="4"/>
         <v>1.7626075400433656</v>
       </c>
-      <c r="S28" s="110">
-        <f>N28/N$44*100</f>
+      <c r="S28" s="98">
+        <f t="shared" si="5"/>
         <v>2.4545416139233072</v>
       </c>
-      <c r="T28" s="114">
-        <f t="shared" si="3"/>
+      <c r="T28" s="102">
+        <f t="shared" si="6"/>
         <v>2.4545416139233072</v>
       </c>
-      <c r="U28" s="110"/>
+      <c r="U28" s="98"/>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="121" t="s">
+      <c r="C29" s="109" t="s">
         <v>193</v>
       </c>
       <c r="D29" s="78">
         <v>0</v>
       </c>
-      <c r="E29" s="122">
+      <c r="E29" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F29" s="78">
         <v>0.1</v>
       </c>
-      <c r="G29" s="122">
+      <c r="G29" s="110">
         <f t="shared" si="1"/>
         <v>1.8181818181818182E-3</v>
       </c>
       <c r="H29" s="78">
         <v>0</v>
       </c>
-      <c r="I29" s="123">
+      <c r="I29" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K29" t="s">
         <v>241</v>
       </c>
-      <c r="L29" s="109">
+      <c r="L29" s="97">
         <f>(D29)*($O29/100)</f>
         <v>0</v>
       </c>
-      <c r="M29" s="111">
+      <c r="M29" s="99">
         <f>(F29)*($O29/100)</f>
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="N29" s="146">
+      <c r="N29" s="134">
         <f>(H29)*($O29/100)</f>
         <v>0</v>
       </c>
-      <c r="O29" s="152">
+      <c r="O29" s="140">
         <v>97</v>
       </c>
-      <c r="Q29" s="148">
-        <f>L29/L$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="R29" s="110">
-        <f>M29/M$44*100</f>
+      <c r="Q29" s="136">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="98">
+        <f t="shared" si="4"/>
         <v>0.2826933389289128</v>
       </c>
-      <c r="S29" s="110">
-        <f>N29/N$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="T29" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="110"/>
+      <c r="S29" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U29" s="98"/>
       <c r="V29" t="s">
         <v>236</v>
       </c>
@@ -10914,129 +10922,129 @@
       <c r="B30" t="s">
         <v>223</v>
       </c>
-      <c r="C30" s="121" t="s">
+      <c r="C30" s="109" t="s">
         <v>195</v>
       </c>
       <c r="D30" s="78">
         <v>0</v>
       </c>
-      <c r="E30" s="122">
+      <c r="E30" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F30" s="78">
         <v>0.5</v>
       </c>
-      <c r="G30" s="122">
+      <c r="G30" s="110">
         <f t="shared" si="1"/>
         <v>9.0909090909090905E-3</v>
       </c>
       <c r="H30" s="78">
         <v>0</v>
       </c>
-      <c r="I30" s="123">
+      <c r="I30" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K30" t="s">
         <v>223</v>
       </c>
-      <c r="L30" s="109">
+      <c r="L30" s="97">
         <f>(D30)*($O30/100)</f>
         <v>0</v>
       </c>
-      <c r="M30" s="111">
+      <c r="M30" s="99">
         <f>(F30)*($O30/100)</f>
         <v>0.46</v>
       </c>
-      <c r="N30" s="146">
+      <c r="N30" s="134">
         <f>(H30)*($O30/100)</f>
         <v>0</v>
       </c>
-      <c r="O30" s="152">
+      <c r="O30" s="140">
         <v>92</v>
       </c>
-      <c r="Q30" s="148">
-        <f>L30/L$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="R30" s="110">
-        <f>M30/M$44*100</f>
+      <c r="Q30" s="136">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="98">
+        <f t="shared" si="4"/>
         <v>1.3406075866731948</v>
       </c>
-      <c r="S30" s="110">
-        <f>N30/N$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="T30" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U30" s="110"/>
+      <c r="S30" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U30" s="98"/>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>224</v>
       </c>
-      <c r="C31" s="121" t="s">
+      <c r="C31" s="109" t="s">
         <v>196</v>
       </c>
       <c r="D31" s="78">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E31" s="122">
+      <c r="E31" s="110">
         <f t="shared" si="0"/>
         <v>1.3506047025600098E-3</v>
       </c>
       <c r="F31" s="78">
         <v>1.2</v>
       </c>
-      <c r="G31" s="122">
+      <c r="G31" s="110">
         <f t="shared" si="1"/>
         <v>2.1818181818181816E-2</v>
       </c>
       <c r="H31" s="78">
         <v>0</v>
       </c>
-      <c r="I31" s="123">
+      <c r="I31" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K31" t="s">
         <v>224</v>
       </c>
-      <c r="L31" s="109">
+      <c r="L31" s="97">
         <f>(D31)*($O31/100)</f>
         <v>2.0240000000000005</v>
       </c>
-      <c r="M31" s="111">
+      <c r="M31" s="99">
         <f>(F31)*($O31/100)</f>
         <v>1.1040000000000001</v>
       </c>
-      <c r="N31" s="146">
+      <c r="N31" s="134">
         <f>(H31)*($O31/100)</f>
         <v>0</v>
       </c>
-      <c r="O31" s="152">
+      <c r="O31" s="140">
         <v>92</v>
       </c>
-      <c r="Q31" s="148">
-        <f>L31/L$44*100</f>
+      <c r="Q31" s="136">
+        <f t="shared" si="3"/>
         <v>0.18160166929977128</v>
       </c>
-      <c r="R31" s="110">
-        <f>M31/M$44*100</f>
+      <c r="R31" s="98">
+        <f t="shared" si="4"/>
         <v>3.2174582080156675</v>
       </c>
-      <c r="S31" s="110">
-        <f>N31/N$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="T31" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="110"/>
+      <c r="S31" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U31" s="98"/>
       <c r="V31" t="s">
         <v>237</v>
       </c>
@@ -11045,65 +11053,65 @@
       <c r="B32" t="s">
         <v>246</v>
       </c>
-      <c r="C32" s="121" t="s">
+      <c r="C32" s="109" t="s">
         <v>197</v>
       </c>
       <c r="D32" s="78">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E32" s="122">
+      <c r="E32" s="110">
         <f t="shared" si="0"/>
         <v>1.4119958254036463E-3</v>
       </c>
       <c r="F32" s="78">
         <v>0.5</v>
       </c>
-      <c r="G32" s="122">
+      <c r="G32" s="110">
         <f t="shared" si="1"/>
         <v>9.0909090909090905E-3</v>
       </c>
       <c r="H32" s="78">
         <v>0</v>
       </c>
-      <c r="I32" s="123">
+      <c r="I32" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K32" t="s">
         <v>246</v>
       </c>
-      <c r="L32" s="109">
+      <c r="L32" s="97">
         <f>(D32)*($O32/100)</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="M32" s="111">
+      <c r="M32" s="99">
         <f>(F32)*($O32/100)</f>
         <v>0.5</v>
       </c>
-      <c r="N32" s="146">
+      <c r="N32" s="134">
         <f>(H32)*($O32/100)</f>
         <v>0</v>
       </c>
-      <c r="O32" s="152">
+      <c r="O32" s="140">
         <v>100</v>
       </c>
-      <c r="Q32" s="148">
-        <f>L32/L$44*100</f>
+      <c r="Q32" s="136">
+        <f t="shared" si="3"/>
         <v>0.20636553329519458</v>
       </c>
-      <c r="R32" s="110">
-        <f>M32/M$44*100</f>
+      <c r="R32" s="98">
+        <f t="shared" si="4"/>
         <v>1.4571821594273857</v>
       </c>
-      <c r="S32" s="110">
-        <f>N32/N$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="T32" s="114">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U32" s="110"/>
+      <c r="S32" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="102">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U32" s="98"/>
       <c r="V32" t="s">
         <v>238</v>
       </c>
@@ -11115,34 +11123,34 @@
       <c r="B33" s="87" t="s">
         <v>253</v>
       </c>
-      <c r="C33" s="113" t="s">
+      <c r="C33" s="101" t="s">
         <v>172</v>
       </c>
       <c r="D33" s="78">
         <v>62.6</v>
       </c>
-      <c r="E33" s="122">
+      <c r="E33" s="110">
         <f t="shared" si="0"/>
         <v>3.8430842900116641E-2</v>
       </c>
       <c r="F33" s="78">
         <v>1.8</v>
       </c>
-      <c r="G33" s="122">
+      <c r="G33" s="110">
         <f t="shared" si="1"/>
         <v>3.272727272727273E-2</v>
       </c>
       <c r="H33" s="78">
         <v>11</v>
       </c>
-      <c r="I33" s="123">
+      <c r="I33" s="111">
         <f t="shared" si="2"/>
         <v>2.1480179652411637E-2</v>
       </c>
       <c r="K33" t="s">
         <v>229</v>
       </c>
-      <c r="L33" s="113">
+      <c r="L33" s="101">
         <f>D41</f>
         <v>0</v>
       </c>
@@ -11150,143 +11158,143 @@
         <f>F41</f>
         <v>0</v>
       </c>
-      <c r="N33" s="112">
+      <c r="N33" s="100">
         <f>H41</f>
         <v>8.8000000000000007</v>
       </c>
-      <c r="O33" s="152">
+      <c r="O33" s="140">
         <v>91</v>
       </c>
-      <c r="Q33" s="148">
-        <f>L33/L$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="R33" s="110">
-        <f>M33/M$44*100</f>
-        <v>0</v>
-      </c>
-      <c r="S33" s="110">
-        <f>N33/N$44*100</f>
+      <c r="Q33" s="136">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R33" s="98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="98">
+        <f t="shared" si="5"/>
         <v>2.7538683244119473</v>
       </c>
-      <c r="T33" s="114">
-        <f t="shared" si="3"/>
+      <c r="T33" s="102">
+        <f t="shared" si="6"/>
         <v>2.7538683244119473</v>
       </c>
-      <c r="U33" s="110"/>
+      <c r="U33" s="98"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B34" s="87" t="s">
         <v>253</v>
       </c>
-      <c r="C34" s="113" t="s">
+      <c r="C34" s="101" t="s">
         <v>186</v>
       </c>
       <c r="D34" s="78">
         <v>5.8</v>
       </c>
-      <c r="E34" s="122">
+      <c r="E34" s="110">
         <f t="shared" si="0"/>
         <v>3.5606851249309346E-3</v>
       </c>
       <c r="F34" s="78">
         <v>0.2</v>
       </c>
-      <c r="G34" s="122">
+      <c r="G34" s="110">
         <f t="shared" si="1"/>
         <v>3.6363636363636364E-3</v>
       </c>
       <c r="H34" s="78">
         <v>1.4</v>
       </c>
-      <c r="I34" s="123">
+      <c r="I34" s="111">
         <f t="shared" si="2"/>
         <v>2.7338410466705718E-3</v>
       </c>
-      <c r="L34" s="113"/>
+      <c r="L34" s="101"/>
       <c r="M34" s="78"/>
-      <c r="N34" s="112"/>
-      <c r="O34" s="152"/>
-      <c r="Q34" s="113"/>
+      <c r="N34" s="100"/>
+      <c r="O34" s="140"/>
+      <c r="Q34" s="101"/>
       <c r="R34" s="78"/>
       <c r="S34" s="78"/>
-      <c r="T34" s="112"/>
+      <c r="T34" s="100"/>
       <c r="U34" s="78"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B35" s="87" t="s">
         <v>253</v>
       </c>
-      <c r="C35" s="113" t="s">
+      <c r="C35" s="101" t="s">
         <v>201</v>
       </c>
       <c r="D35" s="78">
         <v>43.3</v>
       </c>
-      <c r="E35" s="122">
+      <c r="E35" s="110">
         <f t="shared" si="0"/>
         <v>2.6582356191294735E-2</v>
       </c>
       <c r="F35" s="78">
         <v>4.5</v>
       </c>
-      <c r="G35" s="122">
+      <c r="G35" s="110">
         <f t="shared" si="1"/>
         <v>8.1818181818181818E-2</v>
       </c>
       <c r="H35" s="78">
         <v>0</v>
       </c>
-      <c r="I35" s="123">
+      <c r="I35" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="113"/>
+      <c r="L35" s="101"/>
       <c r="M35" s="78"/>
-      <c r="N35" s="112"/>
-      <c r="O35" s="152"/>
-      <c r="Q35" s="113"/>
+      <c r="N35" s="100"/>
+      <c r="O35" s="140"/>
+      <c r="Q35" s="101"/>
       <c r="R35" s="78"/>
       <c r="S35" s="78"/>
-      <c r="T35" s="112"/>
+      <c r="T35" s="100"/>
       <c r="U35" s="78"/>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>161</v>
       </c>
-      <c r="C36" s="121" t="s">
+      <c r="C36" s="109" t="s">
         <v>185</v>
       </c>
       <c r="D36" s="78">
         <v>0</v>
       </c>
-      <c r="E36" s="122">
+      <c r="E36" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F36" s="78">
         <v>0.2</v>
       </c>
-      <c r="G36" s="122">
+      <c r="G36" s="110">
         <f t="shared" si="1"/>
         <v>3.6363636363636364E-3</v>
       </c>
       <c r="H36" s="78">
         <v>0</v>
       </c>
-      <c r="I36" s="123">
+      <c r="I36" s="111">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L36" s="113"/>
+      <c r="L36" s="101"/>
       <c r="M36" s="78"/>
-      <c r="N36" s="112"/>
-      <c r="O36" s="152"/>
-      <c r="Q36" s="113"/>
+      <c r="N36" s="100"/>
+      <c r="O36" s="140"/>
+      <c r="Q36" s="101"/>
       <c r="R36" s="78"/>
       <c r="S36" s="78"/>
-      <c r="T36" s="112"/>
+      <c r="T36" s="100"/>
       <c r="U36" s="78"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -11294,232 +11302,232 @@
       <c r="B37" t="s">
         <v>226</v>
       </c>
-      <c r="C37" s="130" t="s">
+      <c r="C37" s="118" t="s">
         <v>202</v>
       </c>
-      <c r="D37" s="131">
-        <v>0</v>
-      </c>
-      <c r="E37" s="132">
+      <c r="D37" s="119">
+        <v>0</v>
+      </c>
+      <c r="E37" s="120">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F37" s="131">
-        <v>0</v>
-      </c>
-      <c r="G37" s="132">
+      <c r="F37" s="119">
+        <v>0</v>
+      </c>
+      <c r="G37" s="120">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H37" s="131">
+      <c r="H37" s="119">
         <v>120.2</v>
       </c>
-      <c r="I37" s="133">
+      <c r="I37" s="121">
         <f t="shared" si="2"/>
         <v>0.23471978129271626</v>
       </c>
-      <c r="L37" s="113"/>
+      <c r="L37" s="101"/>
       <c r="M37" s="78"/>
-      <c r="N37" s="112"/>
-      <c r="O37" s="152"/>
-      <c r="Q37" s="113"/>
+      <c r="N37" s="100"/>
+      <c r="O37" s="140"/>
+      <c r="Q37" s="101"/>
       <c r="R37" s="78"/>
       <c r="S37" s="78"/>
-      <c r="T37" s="112"/>
+      <c r="T37" s="100"/>
       <c r="U37" s="78"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>227</v>
       </c>
-      <c r="C38" s="121" t="s">
+      <c r="C38" s="109" t="s">
         <v>203</v>
       </c>
       <c r="D38" s="78">
         <v>0</v>
       </c>
-      <c r="E38" s="122">
+      <c r="E38" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F38" s="78">
         <v>0</v>
       </c>
-      <c r="G38" s="122">
+      <c r="G38" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H38" s="78">
         <v>124.5</v>
       </c>
-      <c r="I38" s="123">
+      <c r="I38" s="111">
         <f t="shared" si="2"/>
         <v>0.24311657879320445</v>
       </c>
-      <c r="L38" s="113"/>
+      <c r="L38" s="101"/>
       <c r="M38" s="78"/>
-      <c r="N38" s="112"/>
-      <c r="O38" s="152"/>
-      <c r="Q38" s="113"/>
+      <c r="N38" s="100"/>
+      <c r="O38" s="140"/>
+      <c r="Q38" s="101"/>
       <c r="R38" s="78"/>
       <c r="S38" s="78"/>
-      <c r="T38" s="112"/>
+      <c r="T38" s="100"/>
       <c r="U38" s="78"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
         <v>214</v>
       </c>
-      <c r="C39" s="121" t="s">
+      <c r="C39" s="109" t="s">
         <v>204</v>
       </c>
       <c r="D39" s="78">
         <v>0</v>
       </c>
-      <c r="E39" s="122">
+      <c r="E39" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F39" s="78">
         <v>0</v>
       </c>
-      <c r="G39" s="122">
+      <c r="G39" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H39" s="78">
         <v>17.899999999999999</v>
       </c>
-      <c r="I39" s="123">
+      <c r="I39" s="111">
         <f t="shared" si="2"/>
         <v>3.4954110525288025E-2</v>
       </c>
-      <c r="L39" s="113"/>
+      <c r="L39" s="101"/>
       <c r="M39" s="78"/>
-      <c r="N39" s="112"/>
-      <c r="O39" s="152"/>
-      <c r="Q39" s="113"/>
+      <c r="N39" s="100"/>
+      <c r="O39" s="140"/>
+      <c r="Q39" s="101"/>
       <c r="R39" s="78"/>
       <c r="S39" s="78"/>
-      <c r="T39" s="112"/>
+      <c r="T39" s="100"/>
       <c r="U39" s="78"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B40" s="87" t="s">
         <v>253</v>
       </c>
-      <c r="C40" s="124" t="s">
+      <c r="C40" s="112" t="s">
         <v>205</v>
       </c>
       <c r="D40" s="78">
         <v>0</v>
       </c>
-      <c r="E40" s="122">
+      <c r="E40" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F40" s="78">
         <v>0</v>
       </c>
-      <c r="G40" s="122">
+      <c r="G40" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H40" s="78">
         <v>15.7</v>
       </c>
-      <c r="I40" s="123">
+      <c r="I40" s="111">
         <f t="shared" si="2"/>
         <v>3.0658074594805698E-2</v>
       </c>
-      <c r="L40" s="113"/>
+      <c r="L40" s="101"/>
       <c r="M40" s="78"/>
-      <c r="N40" s="112"/>
-      <c r="O40" s="152"/>
-      <c r="Q40" s="113"/>
+      <c r="N40" s="100"/>
+      <c r="O40" s="140"/>
+      <c r="Q40" s="101"/>
       <c r="R40" s="78"/>
       <c r="S40" s="78"/>
-      <c r="T40" s="112"/>
+      <c r="T40" s="100"/>
       <c r="U40" s="78"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>229</v>
       </c>
-      <c r="C41" s="121" t="s">
+      <c r="C41" s="109" t="s">
         <v>206</v>
       </c>
       <c r="D41" s="78">
         <v>0</v>
       </c>
-      <c r="E41" s="122">
+      <c r="E41" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F41" s="78">
         <v>0</v>
       </c>
-      <c r="G41" s="122">
+      <c r="G41" s="110">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H41" s="78">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I41" s="123">
+      <c r="I41" s="111">
         <f t="shared" si="2"/>
         <v>1.718414372192931E-2</v>
       </c>
-      <c r="L41" s="113"/>
+      <c r="L41" s="101"/>
       <c r="M41" s="78"/>
-      <c r="N41" s="112"/>
-      <c r="O41" s="152"/>
-      <c r="Q41" s="113"/>
+      <c r="N41" s="100"/>
+      <c r="O41" s="140"/>
+      <c r="Q41" s="101"/>
       <c r="R41" s="78"/>
       <c r="S41" s="78"/>
-      <c r="T41" s="112"/>
+      <c r="T41" s="100"/>
       <c r="U41" s="78"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B42" s="87" t="s">
         <v>253</v>
       </c>
-      <c r="C42" s="134" t="s">
+      <c r="C42" s="122" t="s">
         <v>207</v>
       </c>
       <c r="D42" s="76">
         <v>0</v>
       </c>
-      <c r="E42" s="135">
+      <c r="E42" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F42" s="76">
         <v>0</v>
       </c>
-      <c r="G42" s="135">
+      <c r="G42" s="123">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H42" s="76">
         <v>4.7</v>
       </c>
-      <c r="I42" s="136">
+      <c r="I42" s="124">
         <f t="shared" si="2"/>
         <v>9.1778949423940628E-3</v>
       </c>
-      <c r="L42" s="113"/>
+      <c r="L42" s="101"/>
       <c r="M42" s="78"/>
-      <c r="N42" s="112"/>
-      <c r="O42" s="152"/>
-      <c r="Q42" s="113"/>
+      <c r="N42" s="100"/>
+      <c r="O42" s="140"/>
+      <c r="Q42" s="101"/>
       <c r="R42" s="78"/>
       <c r="S42" s="78"/>
-      <c r="T42" s="112"/>
+      <c r="T42" s="100"/>
       <c r="U42" s="78"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C43" s="137" t="s">
+      <c r="C43" s="125" t="s">
         <v>198</v>
       </c>
       <c r="D43" s="77">
@@ -11533,107 +11541,107 @@
       <c r="H43" s="77">
         <v>330.2</v>
       </c>
-      <c r="I43" s="138"/>
-      <c r="L43" s="113"/>
+      <c r="I43" s="126"/>
+      <c r="L43" s="101"/>
       <c r="M43" s="78"/>
-      <c r="N43" s="112"/>
-      <c r="O43" s="152"/>
-      <c r="Q43" s="113"/>
+      <c r="N43" s="100"/>
+      <c r="O43" s="140"/>
+      <c r="Q43" s="101"/>
       <c r="R43" s="78"/>
       <c r="S43" s="78"/>
-      <c r="T43" s="112"/>
+      <c r="T43" s="100"/>
       <c r="U43" s="78"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C44" s="119" t="s">
+      <c r="C44" s="107" t="s">
         <v>208</v>
       </c>
-      <c r="D44" s="125">
+      <c r="D44" s="113">
         <v>4375.1000000000004</v>
       </c>
-      <c r="E44" s="125"/>
-      <c r="F44" s="125">
+      <c r="E44" s="113"/>
+      <c r="F44" s="113">
         <v>134.9</v>
       </c>
-      <c r="G44" s="125"/>
-      <c r="H44" s="125">
+      <c r="G44" s="113"/>
+      <c r="H44" s="113">
         <v>842.3</v>
       </c>
-      <c r="I44" s="126"/>
+      <c r="I44" s="114"/>
       <c r="K44" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="L44" s="139">
+      <c r="L44" s="127">
         <f>SUM(L8:L43)</f>
         <v>1114.5272</v>
       </c>
-      <c r="M44" s="149">
+      <c r="M44" s="137">
         <f>SUM(M8:M43)</f>
         <v>34.312800000000003</v>
       </c>
-      <c r="N44" s="140">
+      <c r="N44" s="128">
         <f>SUM(N8:N43)</f>
         <v>319.55050000000006</v>
       </c>
-      <c r="O44" s="152"/>
-      <c r="Q44" s="139">
+      <c r="O44" s="140"/>
+      <c r="Q44" s="127">
         <f>SUM(Q8:Q43)</f>
         <v>100</v>
       </c>
-      <c r="R44" s="149">
-        <f t="shared" ref="R44:T44" si="4">SUM(R8:R43)</f>
+      <c r="R44" s="137">
+        <f t="shared" ref="R44:T44" si="10">SUM(R8:R43)</f>
         <v>100</v>
       </c>
-      <c r="S44" s="149">
-        <f t="shared" si="4"/>
+      <c r="S44" s="137">
+        <f t="shared" si="10"/>
         <v>99.999999999999986</v>
       </c>
-      <c r="T44" s="140">
-        <f t="shared" si="4"/>
+      <c r="T44" s="128">
+        <f t="shared" si="10"/>
         <v>99.999999999999986</v>
       </c>
-      <c r="U44" s="145"/>
+      <c r="U44" s="133"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C45" s="127" t="s">
+      <c r="C45" s="115" t="s">
         <v>228</v>
       </c>
-      <c r="D45" s="128">
+      <c r="D45" s="116">
         <f>SUM(D8:D42)</f>
         <v>1628.9</v>
       </c>
-      <c r="E45" s="128"/>
-      <c r="F45" s="128">
+      <c r="E45" s="116"/>
+      <c r="F45" s="116">
         <f>SUM(F8:F42)</f>
         <v>55</v>
       </c>
-      <c r="G45" s="128"/>
-      <c r="H45" s="128">
+      <c r="G45" s="116"/>
+      <c r="H45" s="116">
         <f>SUM(H8:H42)</f>
         <v>512.1</v>
       </c>
-      <c r="I45" s="129"/>
+      <c r="I45" s="117"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="K46" s="115"/>
+      <c r="K46" s="103"/>
       <c r="L46" s="87"/>
       <c r="M46" s="87"/>
       <c r="N46" s="87"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C47" s="153" t="s">
+      <c r="C47" s="141" t="s">
         <v>251</v>
       </c>
-      <c r="K47" s="115"/>
+      <c r="K47" s="103"/>
       <c r="L47" s="87"/>
       <c r="M47" s="87"/>
       <c r="N47" s="87"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C48" s="153" t="s">
+      <c r="C48" s="141" t="s">
         <v>252</v>
       </c>
-      <c r="K48" s="115"/>
+      <c r="K48" s="103"/>
       <c r="L48" s="87"/>
       <c r="M48" s="87"/>
       <c r="N48" s="87"/>
@@ -11645,7 +11653,7 @@
       <c r="N49" s="87"/>
     </row>
     <row r="50" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K50" s="115"/>
+      <c r="K50" s="103"/>
       <c r="L50" s="87"/>
       <c r="M50" s="87"/>
       <c r="N50" s="87"/>
@@ -13907,19 +13915,19 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="40"/>
-      <c r="C23" s="103" t="s">
+      <c r="C23" s="148" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="105" t="s">
+      <c r="D23" s="150" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="98" t="s">
+      <c r="E23" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="100" t="s">
+      <c r="F23" s="145" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="102"/>
+      <c r="G23" s="147"/>
       <c r="H23" s="31"/>
       <c r="O23">
         <v>11</v>
@@ -13941,11 +13949,11 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="41"/>
-      <c r="C24" s="104"/>
-      <c r="D24" s="106"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="102"/>
+      <c r="C24" s="149"/>
+      <c r="D24" s="151"/>
+      <c r="E24" s="144"/>
+      <c r="F24" s="146"/>
+      <c r="G24" s="147"/>
       <c r="H24" s="18"/>
       <c r="O24">
         <v>13</v>
@@ -13966,13 +13974,13 @@
       </c>
     </row>
     <row r="25" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="108" t="s">
+      <c r="B25" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="108"/>
-      <c r="D25" s="108"/>
-      <c r="E25" s="108"/>
-      <c r="F25" s="108"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
       <c r="G25" s="42"/>
       <c r="H25" s="18"/>
       <c r="O25">
@@ -13994,13 +14002,13 @@
       </c>
     </row>
     <row r="26" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="97" t="s">
+      <c r="B26" s="142" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
+      <c r="C26" s="142"/>
+      <c r="D26" s="142"/>
+      <c r="E26" s="142"/>
+      <c r="F26" s="142"/>
       <c r="G26" s="42"/>
       <c r="H26" s="18"/>
       <c r="O26">
@@ -14192,25 +14200,25 @@
       <c r="R33" s="3"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="107" t="s">
+      <c r="B34" s="152" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="107"/>
-      <c r="D34" s="107"/>
-      <c r="E34" s="107"/>
-      <c r="F34" s="107"/>
+      <c r="C34" s="152"/>
+      <c r="D34" s="152"/>
+      <c r="E34" s="152"/>
+      <c r="F34" s="152"/>
       <c r="G34" s="42"/>
       <c r="H34" s="18"/>
       <c r="R34" s="13"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="142" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="97"/>
-      <c r="D35" s="97"/>
-      <c r="E35" s="97"/>
-      <c r="F35" s="97"/>
+      <c r="C35" s="142"/>
+      <c r="D35" s="142"/>
+      <c r="E35" s="142"/>
+      <c r="F35" s="142"/>
       <c r="G35" s="42"/>
       <c r="H35" s="18"/>
     </row>

--- a/data/prod_parameters/PigHerd.xlsx
+++ b/data/prod_parameters/PigHerd.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="9000"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="9000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="246">
   <si>
     <t>parameter</t>
   </si>
@@ -728,36 +728,6 @@
     <t>barley brewers grain</t>
   </si>
   <si>
-    <t>Sojamjöl, 45% Rp i vara</t>
-  </si>
-  <si>
-    <t>Sojaprotein-Hamlet 310</t>
-  </si>
-  <si>
-    <t>http://www2.freefarm.se/fodertabell/fodtab.pl?djur=gris</t>
-  </si>
-  <si>
-    <t>Palmkärnkaka</t>
-  </si>
-  <si>
-    <t>Agrodrank10</t>
-  </si>
-  <si>
-    <t>Agrodrank90</t>
-  </si>
-  <si>
-    <t>Betfiber, omelasserad</t>
-  </si>
-  <si>
-    <t>Vasslepulver, söt vassle</t>
-  </si>
-  <si>
-    <t>Potatisproteinkoncentrat</t>
-  </si>
-  <si>
-    <t>Potato protein concentrate is a byproduct of potato starch production</t>
-  </si>
-  <si>
     <t>sows, gilts</t>
   </si>
   <si>
@@ -798,6 +768,54 @@
   </si>
   <si>
     <t>excluded</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Etanolindustri: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Ts-halten varierar mellan 8–27% på de produkter vi har räknat med, fyra olika drank: St1, Agroetanol, Drank Skåne och Drank Lidköping. Baserat på svaren från foderoptimerarna räknade vi ut en medel-ts på 8,7% och volymen 306 447 ton. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mejerindustri:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ts-halten varierar mellan 5–16 % på de produkter vi har räknat med. Det är fodermjölk, permeat och vassle från cirka 10 mejerier. Medel-ts blev 7,8 % och mängden 317 407 ton. </t>
+    </r>
+  </si>
+  <si>
+    <t>E-mail from Birgit Landquist (RISE) 2023-10-16</t>
   </si>
 </sst>
 </file>
@@ -810,7 +828,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -950,6 +968,21 @@
       <b/>
       <i/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1284,7 +1317,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1529,7 +1562,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1539,9 +1571,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1609,6 +1638,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -8050,7 +8102,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
       <c r="G54" s="8" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H54" s="8" t="s">
         <v>159</v>
@@ -8121,7 +8173,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="93" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="B60" s="93"/>
       <c r="C60" s="93"/>
@@ -8139,7 +8191,7 @@
         <v>71</v>
       </c>
       <c r="E61" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C61,'feed rations'!$K$8:$K$43,0),MATCH(B61,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C61,'feed rations'!$L$8:$L$43,0),MATCH(B61,'feed rations'!$Q$7:$T$7,0))</f>
         <v>39.939446969082496</v>
       </c>
       <c r="F61" t="s">
@@ -8154,7 +8206,7 @@
         <v>71</v>
       </c>
       <c r="E62" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C62,'feed rations'!$K$8:$K$43,0),MATCH(B62,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C62,'feed rations'!$L$8:$L$43,0),MATCH(B62,'feed rations'!$Q$7:$T$7,0))</f>
         <v>33.588951440574981</v>
       </c>
       <c r="F62" t="s">
@@ -8169,7 +8221,7 @@
         <v>71</v>
       </c>
       <c r="E63" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C63,'feed rations'!$K$8:$K$43,0),MATCH(B63,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C63,'feed rations'!$L$8:$L$43,0),MATCH(B63,'feed rations'!$Q$7:$T$7,0))</f>
         <v>4.876686724200181</v>
       </c>
       <c r="F63" t="s">
@@ -8184,7 +8236,7 @@
         <v>71</v>
       </c>
       <c r="E64" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C64,'feed rations'!$K$8:$K$43,0),MATCH(B64,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C64,'feed rations'!$L$8:$L$43,0),MATCH(B64,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.44754403481583932</v>
       </c>
       <c r="F64" t="s">
@@ -8199,7 +8251,7 @@
         <v>71</v>
       </c>
       <c r="E65" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C65,'feed rations'!$K$8:$K$43,0),MATCH(B65,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C65,'feed rations'!$L$8:$L$43,0),MATCH(B65,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.22377201740791966</v>
       </c>
       <c r="F65" t="s">
@@ -8214,7 +8266,7 @@
         <v>71</v>
       </c>
       <c r="E66" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C66,'feed rations'!$K$8:$K$43,0),MATCH(B66,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C66,'feed rations'!$L$8:$L$43,0),MATCH(B66,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.78553488869540378</v>
       </c>
       <c r="F66" t="s">
@@ -8229,7 +8281,7 @@
         <v>71</v>
       </c>
       <c r="E67" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C67,'feed rations'!$K$8:$K$43,0),MATCH(B67,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C67,'feed rations'!$L$8:$L$43,0),MATCH(B67,'feed rations'!$Q$7:$T$7,0))</f>
         <v>9.9145180126604351E-2</v>
       </c>
       <c r="F67" t="s">
@@ -8244,7 +8296,7 @@
         <v>71</v>
       </c>
       <c r="E68" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C68,'feed rations'!$K$8:$K$43,0),MATCH(B68,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C68,'feed rations'!$L$8:$L$43,0),MATCH(B68,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.35109057903656365</v>
       </c>
       <c r="F68" t="s">
@@ -8259,7 +8311,7 @@
         <v>71</v>
       </c>
       <c r="E69" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C69,'feed rations'!$K$8:$K$43,0),MATCH(B69,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C69,'feed rations'!$L$8:$L$43,0),MATCH(B69,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.13063835499034929</v>
       </c>
       <c r="F69" t="s">
@@ -8268,13 +8320,13 @@
     </row>
     <row r="70" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="D70" t="s">
         <v>71</v>
       </c>
       <c r="E70" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C70,'feed rations'!$K$8:$K$43,0),MATCH(B70,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C70,'feed rations'!$L$8:$L$43,0),MATCH(B70,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.20636553329519458</v>
       </c>
       <c r="F70" t="s">
@@ -8289,7 +8341,7 @@
         <v>71</v>
       </c>
       <c r="E71" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C71,'feed rations'!$K$8:$K$43,0),MATCH(B71,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C71,'feed rations'!$L$8:$L$43,0),MATCH(B71,'feed rations'!$Q$7:$T$7,0))</f>
         <v>6.9956121304172738</v>
       </c>
       <c r="F71" t="s">
@@ -8304,7 +8356,7 @@
         <v>71</v>
       </c>
       <c r="E72" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C72,'feed rations'!$K$8:$K$43,0),MATCH(B72,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C72,'feed rations'!$L$8:$L$43,0),MATCH(B72,'feed rations'!$Q$7:$T$7,0))</f>
         <v>3.2865954280882512</v>
       </c>
       <c r="F72" t="s">
@@ -8319,7 +8371,7 @@
         <v>71</v>
       </c>
       <c r="E73" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C73,'feed rations'!$K$8:$K$43,0),MATCH(B73,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C73,'feed rations'!$L$8:$L$43,0),MATCH(B73,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.44906934527932563</v>
       </c>
       <c r="F73" t="s">
@@ -8334,7 +8386,7 @@
         <v>71</v>
       </c>
       <c r="E74" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C74,'feed rations'!$K$8:$K$43,0),MATCH(B74,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C74,'feed rations'!$L$8:$L$43,0),MATCH(B74,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.13063835499034929</v>
       </c>
       <c r="F74" t="s">
@@ -8349,7 +8401,7 @@
         <v>71</v>
       </c>
       <c r="E75" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C75,'feed rations'!$K$8:$K$43,0),MATCH(B75,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C75,'feed rations'!$L$8:$L$43,0),MATCH(B75,'feed rations'!$Q$7:$T$7,0))</f>
         <v>3.1145942422939523</v>
       </c>
       <c r="F75" t="s">
@@ -8364,7 +8416,7 @@
         <v>71</v>
       </c>
       <c r="E76" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C76,'feed rations'!$K$8:$K$43,0),MATCH(B76,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C76,'feed rations'!$L$8:$L$43,0),MATCH(B76,'feed rations'!$Q$7:$T$7,0))</f>
         <v>2.3450302513926982</v>
       </c>
       <c r="F76" t="s">
@@ -8379,7 +8431,7 @@
         <v>71</v>
       </c>
       <c r="E77" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C77,'feed rations'!$K$8:$K$43,0),MATCH(B77,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C77,'feed rations'!$L$8:$L$43,0),MATCH(B77,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.13727794171375987</v>
       </c>
       <c r="F77" t="s">
@@ -8394,7 +8446,7 @@
         <v>71</v>
       </c>
       <c r="E78" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C78,'feed rations'!$K$8:$K$43,0),MATCH(B78,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C78,'feed rations'!$L$8:$L$43,0),MATCH(B78,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.59612721878837949</v>
       </c>
       <c r="F78" t="s">
@@ -8409,7 +8461,7 @@
         <v>71</v>
       </c>
       <c r="E79" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C79,'feed rations'!$K$8:$K$43,0),MATCH(B79,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C79,'feed rations'!$L$8:$L$43,0),MATCH(B79,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.35458982068809092</v>
       </c>
       <c r="F79" t="s">
@@ -8424,7 +8476,7 @@
         <v>71</v>
       </c>
       <c r="E80" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C80,'feed rations'!$K$8:$K$43,0),MATCH(B80,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C80,'feed rations'!$L$8:$L$43,0),MATCH(B80,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.69473405404551813</v>
       </c>
       <c r="F80" t="s">
@@ -8439,7 +8491,7 @@
         <v>71</v>
       </c>
       <c r="E81" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C81,'feed rations'!$K$8:$K$43,0),MATCH(B81,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C81,'feed rations'!$L$8:$L$43,0),MATCH(B81,'feed rations'!$Q$7:$T$7,0))</f>
         <v>1.0649538207770974</v>
       </c>
       <c r="F81" t="s">
@@ -8454,7 +8506,7 @@
         <v>71</v>
       </c>
       <c r="E82" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C82,'feed rations'!$K$8:$K$43,0),MATCH(B82,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C82,'feed rations'!$L$8:$L$43,0),MATCH(B82,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.18160166929977128</v>
       </c>
       <c r="F82" t="s">
@@ -8463,7 +8515,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="93" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B83" s="93"/>
       <c r="C83" s="93"/>
@@ -8484,7 +8536,7 @@
         <v>71</v>
       </c>
       <c r="E84" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C84,'feed rations'!$K$8:$K$43,0),MATCH(B84,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C84,'feed rations'!$L$8:$L$43,0),MATCH(B84,'feed rations'!$Q$7:$T$7,0))</f>
         <v>37.344664381805039</v>
       </c>
       <c r="F84" t="s">
@@ -8502,7 +8554,7 @@
         <v>71</v>
       </c>
       <c r="E85" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C85,'feed rations'!$K$8:$K$43,0),MATCH(B85,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C85,'feed rations'!$L$8:$L$43,0),MATCH(B85,'feed rations'!$Q$7:$T$7,0))</f>
         <v>33.835769741903896</v>
       </c>
       <c r="F85" t="s">
@@ -8520,7 +8572,7 @@
         <v>71</v>
       </c>
       <c r="E86" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C86,'feed rations'!$K$8:$K$43,0),MATCH(B86,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C86,'feed rations'!$L$8:$L$43,0),MATCH(B86,'feed rations'!$Q$7:$T$7,0))</f>
         <v>7.2684246112238</v>
       </c>
       <c r="F86" t="s">
@@ -8538,7 +8590,7 @@
         <v>71</v>
       </c>
       <c r="E87" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C87,'feed rations'!$K$8:$K$43,0),MATCH(B87,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C87,'feed rations'!$L$8:$L$43,0),MATCH(B87,'feed rations'!$Q$7:$T$7,0))</f>
         <v>1.7544473199505721</v>
       </c>
       <c r="F87" t="s">
@@ -8556,7 +8608,7 @@
         <v>71</v>
       </c>
       <c r="E88" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C88,'feed rations'!$K$8:$K$43,0),MATCH(B88,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C88,'feed rations'!$L$8:$L$43,0),MATCH(B88,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.24772096710265556</v>
       </c>
       <c r="F88" t="s">
@@ -8574,7 +8626,7 @@
         <v>71</v>
       </c>
       <c r="E89" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C89,'feed rations'!$K$8:$K$43,0),MATCH(B89,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C89,'feed rations'!$L$8:$L$43,0),MATCH(B89,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.74316290130796658</v>
       </c>
       <c r="F89" t="s">
@@ -8586,13 +8638,13 @@
         <v>15</v>
       </c>
       <c r="C90" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="D90" t="s">
         <v>71</v>
       </c>
       <c r="E90" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C90,'feed rations'!$K$8:$K$43,0),MATCH(B90,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C90,'feed rations'!$L$8:$L$43,0),MATCH(B90,'feed rations'!$Q$7:$T$7,0))</f>
         <v>1.4571821594273857</v>
       </c>
       <c r="F90" t="s">
@@ -8610,7 +8662,7 @@
         <v>71</v>
       </c>
       <c r="E91" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C91,'feed rations'!$K$8:$K$43,0),MATCH(B91,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C91,'feed rations'!$L$8:$L$43,0),MATCH(B91,'feed rations'!$Q$7:$T$7,0))</f>
         <v>7.1809936816581557</v>
       </c>
       <c r="F91" t="s">
@@ -8628,7 +8680,7 @@
         <v>71</v>
       </c>
       <c r="E92" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C92,'feed rations'!$K$8:$K$43,0),MATCH(B92,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C92,'feed rations'!$L$8:$L$43,0),MATCH(B92,'feed rations'!$Q$7:$T$7,0))</f>
         <v>2.2819472616632859</v>
       </c>
       <c r="F92" t="s">
@@ -8646,7 +8698,7 @@
         <v>71</v>
       </c>
       <c r="E93" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C93,'feed rations'!$K$8:$K$43,0),MATCH(B93,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C93,'feed rations'!$L$8:$L$43,0),MATCH(B93,'feed rations'!$Q$7:$T$7,0))</f>
         <v>1.2823203002960992</v>
       </c>
       <c r="F93" t="s">
@@ -8664,7 +8716,7 @@
         <v>71</v>
       </c>
       <c r="E94" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C94,'feed rations'!$K$8:$K$43,0),MATCH(B94,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C94,'feed rations'!$L$8:$L$43,0),MATCH(B94,'feed rations'!$Q$7:$T$7,0))</f>
         <v>1.7626075400433656</v>
       </c>
       <c r="F94" t="s">
@@ -8676,13 +8728,13 @@
         <v>15</v>
       </c>
       <c r="C95" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D95" t="s">
         <v>71</v>
       </c>
       <c r="E95" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C95,'feed rations'!$K$8:$K$43,0),MATCH(B95,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C95,'feed rations'!$L$8:$L$43,0),MATCH(B95,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0.2826933389289128</v>
       </c>
       <c r="F95" t="s">
@@ -8700,7 +8752,7 @@
         <v>71</v>
       </c>
       <c r="E96" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C96,'feed rations'!$K$8:$K$43,0),MATCH(B96,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C96,'feed rations'!$L$8:$L$43,0),MATCH(B96,'feed rations'!$Q$7:$T$7,0))</f>
         <v>1.3406075866731948</v>
       </c>
       <c r="F96" t="s">
@@ -8718,7 +8770,7 @@
         <v>71</v>
       </c>
       <c r="E97" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C97,'feed rations'!$K$8:$K$43,0),MATCH(B97,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C97,'feed rations'!$L$8:$L$43,0),MATCH(B97,'feed rations'!$Q$7:$T$7,0))</f>
         <v>3.2174582080156675</v>
       </c>
       <c r="F97" t="s">
@@ -8727,7 +8779,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="93" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B98" s="93"/>
       <c r="C98" s="93"/>
@@ -8748,8 +8800,8 @@
         <v>71</v>
       </c>
       <c r="E99" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C99,'feed rations'!$K$8:$K$43,0),MATCH(B99,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>21.826284108458598</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C99,'feed rations'!$L$8:$L$43,0),MATCH(B99,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>31.302145183860713</v>
       </c>
       <c r="F99" t="s">
         <v>23</v>
@@ -8766,8 +8818,8 @@
         <v>71</v>
       </c>
       <c r="E100" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C100,'feed rations'!$K$8:$K$43,0),MATCH(B100,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>16.76667694151628</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C100,'feed rations'!$L$8:$L$43,0),MATCH(B100,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>24.045914241116183</v>
       </c>
       <c r="F100" t="s">
         <v>23</v>
@@ -8784,8 +8836,8 @@
         <v>71</v>
       </c>
       <c r="E101" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C101,'feed rations'!$K$8:$K$43,0),MATCH(B101,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>2.8258444283454405</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C101,'feed rations'!$L$8:$L$43,0),MATCH(B101,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>4.0526821754690197</v>
       </c>
       <c r="F101" t="s">
         <v>23</v>
@@ -8802,8 +8854,8 @@
         <v>71</v>
       </c>
       <c r="E102" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C102,'feed rations'!$K$8:$K$43,0),MATCH(B102,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>2.6374547997890785</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C102,'feed rations'!$L$8:$L$43,0),MATCH(B102,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>3.7825033637710859</v>
       </c>
       <c r="F102" t="s">
         <v>23</v>
@@ -8820,8 +8872,8 @@
         <v>71</v>
       </c>
       <c r="E103" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C103,'feed rations'!$K$8:$K$43,0),MATCH(B103,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>5.3825608158960786E-2</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C103,'feed rations'!$L$8:$L$43,0),MATCH(B103,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>7.7193946199409905E-2</v>
       </c>
       <c r="F103" t="s">
         <v>23</v>
@@ -8838,8 +8890,8 @@
         <v>71</v>
       </c>
       <c r="E104" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C104,'feed rations'!$K$8:$K$43,0),MATCH(B104,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>0.31919837396593026</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C104,'feed rations'!$L$8:$L$43,0),MATCH(B104,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.45777805304301217</v>
       </c>
       <c r="F104" t="s">
         <v>23</v>
@@ -8856,8 +8908,8 @@
         <v>71</v>
       </c>
       <c r="E105" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C105,'feed rations'!$K$8:$K$43,0),MATCH(B105,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>5.3997724929236526</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C105,'feed rations'!$L$8:$L$43,0),MATCH(B105,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>7.74407873064429</v>
       </c>
       <c r="F105" t="s">
         <v>23</v>
@@ -8874,8 +8926,8 @@
         <v>71</v>
       </c>
       <c r="E106" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C106,'feed rations'!$K$8:$K$43,0),MATCH(B106,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>1.9827851935766017</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C106,'feed rations'!$L$8:$L$43,0),MATCH(B106,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.8436095530201233</v>
       </c>
       <c r="F106" t="s">
         <v>23</v>
@@ -8892,8 +8944,8 @@
         <v>71</v>
       </c>
       <c r="E107" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C107,'feed rations'!$K$8:$K$43,0),MATCH(B107,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>2.4503169295619931</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C107,'feed rations'!$L$8:$L$43,0),MATCH(B107,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>3.5141197601242991</v>
       </c>
       <c r="F107" t="s">
         <v>23</v>
@@ -8910,8 +8962,8 @@
         <v>71</v>
       </c>
       <c r="E108" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C108,'feed rations'!$K$8:$K$43,0),MATCH(B108,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>0.11391000796431236</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C108,'feed rations'!$L$8:$L$43,0),MATCH(B108,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.16336393265456514</v>
       </c>
       <c r="F108" t="s">
         <v>23</v>
@@ -8928,8 +8980,8 @@
         <v>71</v>
       </c>
       <c r="E109" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C109,'feed rations'!$K$8:$K$43,0),MATCH(B109,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>5.7718576563015853</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C109,'feed rations'!$L$8:$L$43,0),MATCH(B109,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>8.277704323848349</v>
       </c>
       <c r="F109" t="s">
         <v>23</v>
@@ -8946,8 +8998,8 @@
         <v>71</v>
       </c>
       <c r="E110" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C110,'feed rations'!$K$8:$K$43,0),MATCH(B110,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>0.60585103137062835</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C110,'feed rations'!$L$8:$L$43,0),MATCH(B110,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.86888069675614876</v>
       </c>
       <c r="F110" t="s">
         <v>23</v>
@@ -8964,8 +9016,8 @@
         <v>71</v>
       </c>
       <c r="E111" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C111,'feed rations'!$K$8:$K$43,0),MATCH(B111,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>33.966462264962807</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C111,'feed rations'!$L$8:$L$43,0),MATCH(B111,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.16156872460341609</v>
       </c>
       <c r="F111" t="s">
         <v>23</v>
@@ -8982,8 +9034,8 @@
         <v>71</v>
       </c>
       <c r="E112" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C112,'feed rations'!$K$8:$K$43,0),MATCH(B112,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>0</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C112,'feed rations'!$L$8:$L$43,0),MATCH(B112,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>4.6933021685215648</v>
       </c>
       <c r="F112" t="s">
         <v>23</v>
@@ -9000,8 +9052,8 @@
         <v>71</v>
       </c>
       <c r="E113" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C113,'feed rations'!$K$8:$K$43,0),MATCH(B113,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>2.7538683244119473</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C113,'feed rations'!$L$8:$L$43,0),MATCH(B113,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>3.554511941275154</v>
       </c>
       <c r="F113" t="s">
         <v>23</v>
@@ -9018,8 +9070,8 @@
         <v>71</v>
       </c>
       <c r="E114" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C114,'feed rations'!$K$8:$K$43,0),MATCH(B114,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>7.1350224768854983E-2</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C114,'feed rations'!$L$8:$L$43,0),MATCH(B114,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.10232685891549684</v>
       </c>
       <c r="F114" t="s">
         <v>23</v>
@@ -9036,8 +9088,8 @@
         <v>71</v>
       </c>
       <c r="E115" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C115,'feed rations'!$K$8:$K$43,0),MATCH(B115,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>2.4545416139233072</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C115,'feed rations'!$L$8:$L$43,0),MATCH(B115,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>4.3583163461771495</v>
       </c>
       <c r="F115" t="s">
         <v>23</v>
@@ -9054,7 +9106,7 @@
         <v>71</v>
       </c>
       <c r="E116" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C116,'feed rations'!$K$8:$K$43,0),MATCH(B116,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C116,'feed rations'!$L$8:$L$43,0),MATCH(B116,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0</v>
       </c>
       <c r="F116" t="s">
@@ -9072,8 +9124,8 @@
         <v>71</v>
       </c>
       <c r="E117" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C117,'feed rations'!$K$8:$K$43,0),MATCH(B117,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>21.826284108458598</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C117,'feed rations'!$L$8:$L$43,0),MATCH(B117,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>31.302145183860713</v>
       </c>
       <c r="F117" t="s">
         <v>23</v>
@@ -9090,8 +9142,8 @@
         <v>71</v>
       </c>
       <c r="E118" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C118,'feed rations'!$K$8:$K$43,0),MATCH(B118,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>16.76667694151628</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C118,'feed rations'!$L$8:$L$43,0),MATCH(B118,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>24.045914241116183</v>
       </c>
       <c r="F118" t="s">
         <v>23</v>
@@ -9108,8 +9160,8 @@
         <v>71</v>
       </c>
       <c r="E119" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C119,'feed rations'!$K$8:$K$43,0),MATCH(B119,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>2.8258444283454405</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C119,'feed rations'!$L$8:$L$43,0),MATCH(B119,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>4.0526821754690197</v>
       </c>
       <c r="F119" t="s">
         <v>23</v>
@@ -9126,8 +9178,8 @@
         <v>71</v>
       </c>
       <c r="E120" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C120,'feed rations'!$K$8:$K$43,0),MATCH(B120,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>2.6374547997890785</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C120,'feed rations'!$L$8:$L$43,0),MATCH(B120,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>3.7825033637710859</v>
       </c>
       <c r="F120" t="s">
         <v>23</v>
@@ -9144,8 +9196,8 @@
         <v>71</v>
       </c>
       <c r="E121" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C121,'feed rations'!$K$8:$K$43,0),MATCH(B121,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>5.3825608158960786E-2</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C121,'feed rations'!$L$8:$L$43,0),MATCH(B121,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>7.7193946199409905E-2</v>
       </c>
       <c r="F121" t="s">
         <v>23</v>
@@ -9162,8 +9214,8 @@
         <v>71</v>
       </c>
       <c r="E122" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C122,'feed rations'!$K$8:$K$43,0),MATCH(B122,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>0.31919837396593026</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C122,'feed rations'!$L$8:$L$43,0),MATCH(B122,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.45777805304301217</v>
       </c>
       <c r="F122" t="s">
         <v>23</v>
@@ -9180,8 +9232,8 @@
         <v>71</v>
       </c>
       <c r="E123" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C123,'feed rations'!$K$8:$K$43,0),MATCH(B123,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>5.3997724929236526</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C123,'feed rations'!$L$8:$L$43,0),MATCH(B123,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>7.74407873064429</v>
       </c>
       <c r="F123" t="s">
         <v>23</v>
@@ -9198,8 +9250,8 @@
         <v>71</v>
       </c>
       <c r="E124" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C124,'feed rations'!$K$8:$K$43,0),MATCH(B124,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>1.9827851935766017</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C124,'feed rations'!$L$8:$L$43,0),MATCH(B124,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>2.8436095530201233</v>
       </c>
       <c r="F124" t="s">
         <v>23</v>
@@ -9216,8 +9268,8 @@
         <v>71</v>
       </c>
       <c r="E125" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C125,'feed rations'!$K$8:$K$43,0),MATCH(B125,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>2.4503169295619931</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C125,'feed rations'!$L$8:$L$43,0),MATCH(B125,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>3.5141197601242991</v>
       </c>
       <c r="F125" t="s">
         <v>23</v>
@@ -9234,8 +9286,8 @@
         <v>71</v>
       </c>
       <c r="E126" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C126,'feed rations'!$K$8:$K$43,0),MATCH(B126,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>0.11391000796431236</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C126,'feed rations'!$L$8:$L$43,0),MATCH(B126,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.16336393265456514</v>
       </c>
       <c r="F126" t="s">
         <v>23</v>
@@ -9252,8 +9304,8 @@
         <v>71</v>
       </c>
       <c r="E127" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C127,'feed rations'!$K$8:$K$43,0),MATCH(B127,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>5.7718576563015853</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C127,'feed rations'!$L$8:$L$43,0),MATCH(B127,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>8.277704323848349</v>
       </c>
       <c r="F127" t="s">
         <v>23</v>
@@ -9270,8 +9322,8 @@
         <v>71</v>
       </c>
       <c r="E128" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C128,'feed rations'!$K$8:$K$43,0),MATCH(B128,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>0.60585103137062835</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C128,'feed rations'!$L$8:$L$43,0),MATCH(B128,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.86888069675614876</v>
       </c>
       <c r="F128" t="s">
         <v>23</v>
@@ -9288,8 +9340,8 @@
         <v>71</v>
       </c>
       <c r="E129" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C129,'feed rations'!$K$8:$K$43,0),MATCH(B129,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>33.966462264962807</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C129,'feed rations'!$L$8:$L$43,0),MATCH(B129,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.16156872460341609</v>
       </c>
       <c r="F129" t="s">
         <v>23</v>
@@ -9306,8 +9358,8 @@
         <v>71</v>
       </c>
       <c r="E130" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C130,'feed rations'!$K$8:$K$43,0),MATCH(B130,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>0</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C130,'feed rations'!$L$8:$L$43,0),MATCH(B130,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>4.6933021685215648</v>
       </c>
       <c r="F130" t="s">
         <v>23</v>
@@ -9324,8 +9376,8 @@
         <v>71</v>
       </c>
       <c r="E131" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C131,'feed rations'!$K$8:$K$43,0),MATCH(B131,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>2.7538683244119473</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C131,'feed rations'!$L$8:$L$43,0),MATCH(B131,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>3.554511941275154</v>
       </c>
       <c r="F131" t="s">
         <v>23</v>
@@ -9342,8 +9394,8 @@
         <v>71</v>
       </c>
       <c r="E132" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C132,'feed rations'!$K$8:$K$43,0),MATCH(B132,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>7.1350224768854983E-2</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C132,'feed rations'!$L$8:$L$43,0),MATCH(B132,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>0.10232685891549684</v>
       </c>
       <c r="F132" t="s">
         <v>23</v>
@@ -9360,8 +9412,8 @@
         <v>71</v>
       </c>
       <c r="E133" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C133,'feed rations'!$K$8:$K$43,0),MATCH(B133,'feed rations'!$Q$7:$T$7,0))</f>
-        <v>2.4545416139233072</v>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C133,'feed rations'!$L$8:$L$43,0),MATCH(B133,'feed rations'!$Q$7:$T$7,0))</f>
+        <v>4.3583163461771495</v>
       </c>
       <c r="F133" t="s">
         <v>23</v>
@@ -9378,7 +9430,7 @@
         <v>71</v>
       </c>
       <c r="E134" s="62">
-        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C134,'feed rations'!$K$8:$K$43,0),MATCH(B134,'feed rations'!$Q$7:$T$7,0))</f>
+        <f>INDEX('feed rations'!$Q$8:$T$43,MATCH(C134,'feed rations'!$L$8:$L$43,0),MATCH(B134,'feed rations'!$Q$7:$T$7,0))</f>
         <v>0</v>
       </c>
       <c r="F134" t="s">
@@ -9392,7 +9444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:Z50"/>
+  <dimension ref="A5:V52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -9403,8 +9455,9 @@
     <col min="7" max="7" width="4.85546875" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="5.42578125" customWidth="1"/>
-    <col min="11" max="11" width="27.7109375" customWidth="1"/>
-    <col min="12" max="14" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="12" max="12" width="27.7109375" customWidth="1"/>
+    <col min="13" max="15" width="13.28515625" customWidth="1"/>
     <col min="17" max="20" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9425,69 +9478,67 @@
       <c r="G6" s="105"/>
       <c r="H6" s="105"/>
       <c r="I6" s="106"/>
-      <c r="L6" s="90" t="s">
-        <v>248</v>
-      </c>
-      <c r="O6" s="78"/>
+      <c r="J6" s="112"/>
+      <c r="M6" s="90" t="s">
+        <v>238</v>
+      </c>
       <c r="Q6" s="90" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="2:22" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C7" s="115"/>
-      <c r="D7" s="131" t="s">
+      <c r="C7" s="114"/>
+      <c r="D7" s="127" t="s">
         <v>169</v>
       </c>
-      <c r="E7" s="131" t="s">
+      <c r="E7" s="127" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="131" t="s">
+      <c r="F7" s="127" t="s">
         <v>170</v>
       </c>
-      <c r="G7" s="131" t="s">
+      <c r="G7" s="127" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="131" t="s">
+      <c r="H7" s="127" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="132" t="s">
+      <c r="I7" s="128" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="91" t="s">
+      <c r="J7" s="135" t="s">
+        <v>209</v>
+      </c>
+      <c r="L7" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="L7" s="129" t="s">
+      <c r="M7" s="125" t="s">
+        <v>230</v>
+      </c>
+      <c r="N7" s="131" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="126" t="s">
         <v>240</v>
       </c>
-      <c r="M7" s="135" t="s">
+      <c r="P7" s="91"/>
+      <c r="Q7" s="125">
+        <v>0</v>
+      </c>
+      <c r="R7" s="131" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="130" t="s">
-        <v>250</v>
-      </c>
-      <c r="O7" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="129">
-        <v>0</v>
-      </c>
-      <c r="R7" s="135" t="s">
-        <v>15</v>
-      </c>
-      <c r="S7" s="135" t="s">
+      <c r="S7" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="T7" s="130" t="s">
+      <c r="T7" s="126" t="s">
         <v>25</v>
       </c>
       <c r="U7" s="108"/>
-      <c r="V7" s="92" t="s">
-        <v>232</v>
-      </c>
+      <c r="V7" s="92"/>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
@@ -9517,39 +9568,39 @@
         <f t="shared" ref="I8:I42" si="2">H8/H$45</f>
         <v>0.15836750634641669</v>
       </c>
-      <c r="K8" t="s">
+      <c r="J8" s="136">
+        <v>86</v>
+      </c>
+      <c r="L8" t="s">
         <v>70</v>
       </c>
-      <c r="L8" s="97">
-        <f>(D8)*($O8/100)</f>
+      <c r="M8" s="97">
+        <f>D8*($J8/100)</f>
         <v>445.13600000000002</v>
       </c>
-      <c r="M8" s="99">
-        <f>(F8)*($O8/100)</f>
+      <c r="N8" s="99">
+        <f>F8*($J8/100)</f>
         <v>12.814</v>
       </c>
-      <c r="N8" s="134">
-        <f>(H8)*($O8/100)</f>
+      <c r="O8" s="130">
+        <f>H8*($J8/100)</f>
         <v>69.745999999999995</v>
       </c>
-      <c r="O8" s="140">
-        <v>86</v>
-      </c>
-      <c r="Q8" s="136">
-        <f t="shared" ref="Q8:Q33" si="3">L8/L$44*100</f>
+      <c r="Q8" s="132">
+        <f>M8/M$44*100</f>
         <v>39.939446969082496</v>
       </c>
       <c r="R8" s="98">
-        <f t="shared" ref="R8:R33" si="4">M8/M$44*100</f>
+        <f>N8/N$44*100</f>
         <v>37.344664381805039</v>
       </c>
-      <c r="S8" s="138">
-        <f t="shared" ref="S8:S33" si="5">N8/N$44*100</f>
-        <v>21.826284108458598</v>
+      <c r="S8" s="134">
+        <f>O8/O$44*100</f>
+        <v>31.302145183860713</v>
       </c>
       <c r="T8" s="102">
-        <f>N8/N$44*100</f>
-        <v>21.826284108458598</v>
+        <f>O8/O$44*100</f>
+        <v>31.302145183860713</v>
       </c>
       <c r="U8" s="98"/>
     </row>
@@ -9581,39 +9632,39 @@
         <f t="shared" si="2"/>
         <v>0.12165592657684045</v>
       </c>
-      <c r="K9" t="s">
+      <c r="J9" s="136">
+        <v>86</v>
+      </c>
+      <c r="L9" t="s">
         <v>160</v>
       </c>
-      <c r="L9" s="97">
-        <f>(D9)*($O9/100)</f>
+      <c r="M9" s="97">
+        <f>D9*($J9/100)</f>
         <v>374.358</v>
       </c>
-      <c r="M9" s="99">
-        <f>(F9)*($O9/100)</f>
+      <c r="N9" s="99">
+        <f>F9*($J9/100)</f>
         <v>11.61</v>
       </c>
-      <c r="N9" s="134">
-        <f>(H9)*($O9/100)</f>
+      <c r="O9" s="130">
+        <f>H9*($J9/100)</f>
         <v>53.577999999999996</v>
       </c>
-      <c r="O9" s="140">
-        <v>86</v>
-      </c>
-      <c r="Q9" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q9" s="132">
+        <f>M9/M$44*100</f>
         <v>33.588951440574981</v>
       </c>
       <c r="R9" s="98">
-        <f t="shared" si="4"/>
+        <f>N9/N$44*100</f>
         <v>33.835769741903896</v>
       </c>
       <c r="S9" s="98">
-        <f t="shared" si="5"/>
-        <v>16.76667694151628</v>
+        <f>O9/O$44*100</f>
+        <v>24.045914241116183</v>
       </c>
       <c r="T9" s="102">
-        <f t="shared" ref="T9:T33" si="6">N9/N$44*100</f>
-        <v>16.76667694151628</v>
+        <f>O9/O$44*100</f>
+        <v>24.045914241116183</v>
       </c>
       <c r="U9" s="98"/>
     </row>
@@ -9645,39 +9696,39 @@
         <f t="shared" si="2"/>
         <v>2.0503807850029289E-2</v>
       </c>
-      <c r="K10" t="s">
+      <c r="J10" s="136">
+        <v>86</v>
+      </c>
+      <c r="L10" t="s">
         <v>161</v>
       </c>
-      <c r="L10" s="97">
-        <f>(D10+D36)*($O10/100)</f>
+      <c r="M10" s="97">
+        <f>D10*($J10/100)+D36*($J36/100)</f>
         <v>54.352000000000004</v>
       </c>
-      <c r="M10" s="99">
-        <f>(F10+F36)*($O10/100)</f>
+      <c r="N10" s="99">
+        <f>F10*($J10/100)+F36*($J36/100)</f>
         <v>2.4940000000000002</v>
       </c>
-      <c r="N10" s="134">
-        <f>(H10+H36)*($O10/100)</f>
+      <c r="O10" s="130">
+        <f>H10*($J10/100)+H36*($J36/100)</f>
         <v>9.0299999999999994</v>
       </c>
-      <c r="O10" s="140">
-        <v>86</v>
-      </c>
-      <c r="Q10" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q10" s="132">
+        <f>M10/M$44*100</f>
         <v>4.876686724200181</v>
       </c>
       <c r="R10" s="98">
-        <f t="shared" si="4"/>
+        <f>N10/N$44*100</f>
         <v>7.2684246112238</v>
       </c>
       <c r="S10" s="98">
-        <f t="shared" si="5"/>
-        <v>2.8258444283454405</v>
+        <f>O10/O$44*100</f>
+        <v>4.0526821754690197</v>
       </c>
       <c r="T10" s="102">
-        <f t="shared" si="6"/>
-        <v>2.8258444283454405</v>
+        <f>O10/O$44*100</f>
+        <v>4.0526821754690197</v>
       </c>
       <c r="U10" s="98"/>
     </row>
@@ -9709,39 +9760,39 @@
         <f t="shared" si="2"/>
         <v>1.9136887326694007E-2</v>
       </c>
-      <c r="K11" t="s">
+      <c r="J11" s="136">
+        <v>86</v>
+      </c>
+      <c r="L11" t="s">
         <v>162</v>
       </c>
-      <c r="L11" s="97">
-        <f t="shared" ref="L11:L21" si="7">(D11)*($O11/100)</f>
+      <c r="M11" s="97">
+        <f>D11*($J11/100)</f>
         <v>4.9879999999999995</v>
       </c>
-      <c r="M11" s="99">
-        <f t="shared" ref="M11:M21" si="8">(F11)*($O11/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="134">
-        <f t="shared" ref="N11:N21" si="9">(H11)*($O11/100)</f>
+      <c r="N11" s="99">
+        <f>F11*($J11/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="130">
+        <f>H11*($J11/100)</f>
         <v>8.4280000000000008</v>
       </c>
-      <c r="O11" s="140">
-        <v>86</v>
-      </c>
-      <c r="Q11" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q11" s="132">
+        <f>M11/M$44*100</f>
         <v>0.44754403481583932</v>
       </c>
       <c r="R11" s="98">
-        <f t="shared" si="4"/>
+        <f>N11/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S11" s="98">
-        <f t="shared" si="5"/>
-        <v>2.6374547997890785</v>
+        <f>O11/O$44*100</f>
+        <v>3.7825033637710859</v>
       </c>
       <c r="T11" s="102">
-        <f t="shared" si="6"/>
-        <v>2.6374547997890785</v>
+        <f>O11/O$44*100</f>
+        <v>3.7825033637710859</v>
       </c>
       <c r="U11" s="98"/>
     </row>
@@ -9773,39 +9824,39 @@
         <f t="shared" si="2"/>
         <v>3.905487209529389E-4</v>
       </c>
-      <c r="K12" t="s">
+      <c r="J12" s="136">
+        <v>86</v>
+      </c>
+      <c r="L12" t="s">
         <v>165</v>
       </c>
-      <c r="L12" s="97">
-        <f t="shared" si="7"/>
+      <c r="M12" s="97">
+        <f>D12*($J12/100)</f>
         <v>2.4939999999999998</v>
       </c>
-      <c r="M12" s="99">
-        <f t="shared" si="8"/>
+      <c r="N12" s="99">
+        <f>F12*($J12/100)</f>
         <v>0.60199999999999998</v>
       </c>
-      <c r="N12" s="134">
-        <f t="shared" si="9"/>
+      <c r="O12" s="130">
+        <f>H12*($J12/100)</f>
         <v>0.17200000000000001</v>
       </c>
-      <c r="O12" s="140">
-        <v>86</v>
-      </c>
-      <c r="Q12" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q12" s="132">
+        <f>M12/M$44*100</f>
         <v>0.22377201740791966</v>
       </c>
       <c r="R12" s="98">
-        <f t="shared" si="4"/>
+        <f>N12/N$44*100</f>
         <v>1.7544473199505721</v>
       </c>
       <c r="S12" s="98">
-        <f t="shared" si="5"/>
-        <v>5.3825608158960786E-2</v>
+        <f>O12/O$44*100</f>
+        <v>7.7193946199409905E-2</v>
       </c>
       <c r="T12" s="102">
-        <f t="shared" si="6"/>
-        <v>5.3825608158960786E-2</v>
+        <f>O12/O$44*100</f>
+        <v>7.7193946199409905E-2</v>
       </c>
       <c r="U12" s="98"/>
     </row>
@@ -9837,39 +9888,39 @@
         <f t="shared" si="2"/>
         <v>2.3432923257176333E-3</v>
       </c>
-      <c r="K13" t="s">
+      <c r="J13" s="136">
+        <v>85</v>
+      </c>
+      <c r="L13" t="s">
         <v>218</v>
       </c>
-      <c r="L13" s="97">
-        <f t="shared" si="7"/>
+      <c r="M13" s="97">
+        <f>D13*($J13/100)</f>
         <v>8.7550000000000008</v>
       </c>
-      <c r="M13" s="99">
-        <f t="shared" si="8"/>
+      <c r="N13" s="99">
+        <f>F13*($J13/100)</f>
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="N13" s="134">
-        <f t="shared" si="9"/>
+      <c r="O13" s="130">
+        <f>H13*($J13/100)</f>
         <v>1.02</v>
       </c>
-      <c r="O13" s="140">
-        <v>85</v>
-      </c>
-      <c r="Q13" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q13" s="132">
+        <f>M13/M$44*100</f>
         <v>0.78553488869540378</v>
       </c>
       <c r="R13" s="98">
-        <f t="shared" si="4"/>
+        <f>N13/N$44*100</f>
         <v>0.24772096710265556</v>
       </c>
       <c r="S13" s="98">
-        <f t="shared" si="5"/>
-        <v>0.31919837396593026</v>
+        <f>O13/O$44*100</f>
+        <v>0.45777805304301217</v>
       </c>
       <c r="T13" s="102">
-        <f t="shared" si="6"/>
-        <v>0.31919837396593026</v>
+        <f>O13/O$44*100</f>
+        <v>0.45777805304301217</v>
       </c>
       <c r="U13" s="98"/>
     </row>
@@ -9901,39 +9952,39 @@
         <f t="shared" si="2"/>
         <v>3.9640695176723299E-2</v>
       </c>
-      <c r="K14" t="s">
+      <c r="J14" s="136">
+        <v>85</v>
+      </c>
+      <c r="L14" t="s">
         <v>219</v>
       </c>
-      <c r="L14" s="97">
-        <f t="shared" si="7"/>
+      <c r="M14" s="97">
+        <f>D14*($J14/100)</f>
         <v>1.105</v>
       </c>
-      <c r="M14" s="99">
-        <f t="shared" si="8"/>
+      <c r="N14" s="99">
+        <f>F14*($J14/100)</f>
         <v>0.255</v>
       </c>
-      <c r="N14" s="134">
-        <f t="shared" si="9"/>
+      <c r="O14" s="130">
+        <f>H14*($J14/100)</f>
         <v>17.254999999999999</v>
       </c>
-      <c r="O14" s="140">
-        <v>85</v>
-      </c>
-      <c r="Q14" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q14" s="132">
+        <f>M14/M$44*100</f>
         <v>9.9145180126604351E-2</v>
       </c>
       <c r="R14" s="98">
-        <f t="shared" si="4"/>
+        <f>N14/N$44*100</f>
         <v>0.74316290130796658</v>
       </c>
       <c r="S14" s="98">
-        <f t="shared" si="5"/>
-        <v>5.3997724929236526</v>
+        <f>O14/O$44*100</f>
+        <v>7.74407873064429</v>
       </c>
       <c r="T14" s="102">
-        <f t="shared" si="6"/>
-        <v>5.3997724929236526</v>
+        <f>O14/O$44*100</f>
+        <v>7.74407873064429</v>
       </c>
       <c r="U14" s="98"/>
     </row>
@@ -9965,38 +10016,38 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K15" t="s">
+      <c r="J15" s="136">
+        <v>91</v>
+      </c>
+      <c r="L15" t="s">
         <v>163</v>
       </c>
-      <c r="L15" s="97">
-        <f t="shared" si="7"/>
+      <c r="M15" s="97">
+        <f>D15*($J15/100)</f>
         <v>3.9129999999999998</v>
       </c>
-      <c r="M15" s="99">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="134">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="140">
-        <v>91</v>
-      </c>
-      <c r="Q15" s="136">
-        <f t="shared" si="3"/>
+      <c r="N15" s="99">
+        <f>F15*($J15/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="130">
+        <f>H15*($J15/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="132">
+        <f>M15/M$44*100</f>
         <v>0.35109057903656365</v>
       </c>
       <c r="R15" s="98">
-        <f t="shared" si="4"/>
+        <f>N15/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S15" s="98">
-        <f t="shared" si="5"/>
+        <f>O15/O$44*100</f>
         <v>0</v>
       </c>
       <c r="T15" s="102">
-        <f t="shared" si="6"/>
+        <f>O15/O$44*100</f>
         <v>0</v>
       </c>
       <c r="U15" s="98"/>
@@ -10029,43 +10080,43 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K16" t="s">
+      <c r="J16" s="136">
+        <v>91</v>
+      </c>
+      <c r="L16" t="s">
         <v>164</v>
       </c>
-      <c r="L16" s="97">
-        <f t="shared" si="7"/>
+      <c r="M16" s="97">
+        <f>D16*($J16/100)</f>
         <v>1.4560000000000002</v>
       </c>
-      <c r="M16" s="99">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="134">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="140">
-        <v>91</v>
-      </c>
-      <c r="Q16" s="136">
-        <f t="shared" si="3"/>
+      <c r="N16" s="99">
+        <f>F16*($J16/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O16" s="130">
+        <f>H16*($J16/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="132">
+        <f>M16/M$44*100</f>
         <v>0.13063835499034929</v>
       </c>
       <c r="R16" s="98">
-        <f t="shared" si="4"/>
+        <f>N16/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S16" s="98">
-        <f t="shared" si="5"/>
+        <f>O16/O$44*100</f>
         <v>0</v>
       </c>
       <c r="T16" s="102">
-        <f t="shared" si="6"/>
+        <f>O16/O$44*100</f>
         <v>0</v>
       </c>
       <c r="U16" s="98"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>220</v>
       </c>
@@ -10093,43 +10144,43 @@
         <f t="shared" si="2"/>
         <v>1.4059753954305799E-2</v>
       </c>
-      <c r="K17" t="s">
+      <c r="J17" s="136">
+        <v>88</v>
+      </c>
+      <c r="L17" t="s">
         <v>220</v>
       </c>
-      <c r="L17" s="97">
-        <f t="shared" si="7"/>
+      <c r="M17" s="97">
+        <f>D17*($J17/100)</f>
         <v>77.967999999999989</v>
       </c>
-      <c r="M17" s="99">
-        <f t="shared" si="8"/>
+      <c r="N17" s="99">
+        <f>F17*($J17/100)</f>
         <v>2.464</v>
       </c>
-      <c r="N17" s="134">
-        <f t="shared" si="9"/>
+      <c r="O17" s="130">
+        <f>H17*($J17/100)</f>
         <v>6.3360000000000003</v>
       </c>
-      <c r="O17" s="140">
-        <v>88</v>
-      </c>
-      <c r="Q17" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q17" s="132">
+        <f>M17/M$44*100</f>
         <v>6.9956121304172738</v>
       </c>
       <c r="R17" s="98">
-        <f t="shared" si="4"/>
+        <f>N17/N$44*100</f>
         <v>7.1809936816581557</v>
       </c>
       <c r="S17" s="98">
-        <f t="shared" si="5"/>
-        <v>1.9827851935766017</v>
+        <f>O17/O$44*100</f>
+        <v>2.8436095530201233</v>
       </c>
       <c r="T17" s="102">
-        <f t="shared" si="6"/>
-        <v>1.9827851935766017</v>
+        <f>O17/O$44*100</f>
+        <v>2.8436095530201233</v>
       </c>
       <c r="U17" s="98"/>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>222</v>
       </c>
@@ -10157,46 +10208,43 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K18" t="s">
+      <c r="J18" s="136">
+        <v>87</v>
+      </c>
+      <c r="L18" t="s">
         <v>222</v>
       </c>
-      <c r="L18" s="97">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="99">
-        <f t="shared" si="8"/>
+      <c r="M18" s="97">
+        <f>D18*($J18/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="99">
+        <f>F18*($J18/100)</f>
         <v>0.78300000000000003</v>
       </c>
-      <c r="N18" s="134">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="140">
-        <v>87</v>
-      </c>
-      <c r="Q18" s="136">
-        <f t="shared" si="3"/>
+      <c r="O18" s="130">
+        <f>H18*($J18/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="132">
+        <f>M18/M$44*100</f>
         <v>0</v>
       </c>
       <c r="R18" s="98">
-        <f t="shared" si="4"/>
+        <f>N18/N$44*100</f>
         <v>2.2819472616632859</v>
       </c>
       <c r="S18" s="98">
-        <f t="shared" si="5"/>
+        <f>O18/O$44*100</f>
         <v>0</v>
       </c>
       <c r="T18" s="102">
-        <f t="shared" si="6"/>
+        <f>O18/O$44*100</f>
         <v>0</v>
       </c>
       <c r="U18" s="98"/>
-      <c r="V18" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>221</v>
       </c>
@@ -10224,46 +10272,43 @@
         <f t="shared" si="2"/>
         <v>1.698886936145284E-2</v>
       </c>
-      <c r="K19" t="s">
+      <c r="J19" s="136">
+        <v>90</v>
+      </c>
+      <c r="L19" t="s">
         <v>221</v>
       </c>
-      <c r="L19" s="97">
-        <f t="shared" si="7"/>
+      <c r="M19" s="97">
+        <f>D19*($J19/100)</f>
         <v>36.630000000000003</v>
       </c>
-      <c r="M19" s="99">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="134">
-        <f t="shared" si="9"/>
+      <c r="N19" s="99">
+        <f>F19*($J19/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O19" s="130">
+        <f>H19*($J19/100)</f>
         <v>7.8299999999999992</v>
       </c>
-      <c r="O19" s="140">
-        <v>90</v>
-      </c>
-      <c r="Q19" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q19" s="132">
+        <f>M19/M$44*100</f>
         <v>3.2865954280882512</v>
       </c>
       <c r="R19" s="98">
-        <f t="shared" si="4"/>
+        <f>N19/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S19" s="98">
-        <f t="shared" si="5"/>
-        <v>2.4503169295619931</v>
+        <f>O19/O$44*100</f>
+        <v>3.5141197601242991</v>
       </c>
       <c r="T19" s="102">
-        <f t="shared" si="6"/>
-        <v>2.4503169295619931</v>
+        <f>O19/O$44*100</f>
+        <v>3.5141197601242991</v>
       </c>
       <c r="U19" s="98"/>
-      <c r="V19" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>217</v>
       </c>
@@ -10291,43 +10336,43 @@
         <f t="shared" si="2"/>
         <v>7.810974419058778E-4</v>
       </c>
-      <c r="K20" t="s">
+      <c r="J20" s="136">
+        <v>91</v>
+      </c>
+      <c r="L20" t="s">
         <v>217</v>
       </c>
-      <c r="L20" s="97">
-        <f t="shared" si="7"/>
+      <c r="M20" s="97">
+        <f>D20*($J20/100)</f>
         <v>5.0049999999999999</v>
       </c>
-      <c r="M20" s="99">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="134">
-        <f t="shared" si="9"/>
+      <c r="N20" s="99">
+        <f>F20*($J20/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O20" s="130">
+        <f>H20*($J20/100)</f>
         <v>0.36400000000000005</v>
       </c>
-      <c r="O20" s="140">
-        <v>91</v>
-      </c>
-      <c r="Q20" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q20" s="132">
+        <f>M20/M$44*100</f>
         <v>0.44906934527932563</v>
       </c>
       <c r="R20" s="98">
-        <f t="shared" si="4"/>
+        <f>N20/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S20" s="98">
-        <f t="shared" si="5"/>
-        <v>0.11391000796431236</v>
+        <f>O20/O$44*100</f>
+        <v>0.16336393265456514</v>
       </c>
       <c r="T20" s="102">
-        <f t="shared" si="6"/>
-        <v>0.11391000796431236</v>
+        <f>O20/O$44*100</f>
+        <v>0.16336393265456514</v>
       </c>
       <c r="U20" s="98"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>213</v>
       </c>
@@ -10355,46 +10400,43 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K21" t="s">
+      <c r="J21" s="136">
+        <v>91</v>
+      </c>
+      <c r="L21" t="s">
         <v>213</v>
       </c>
-      <c r="L21" s="97">
-        <f t="shared" si="7"/>
+      <c r="M21" s="97">
+        <f>D21*($J21/100)</f>
         <v>1.4560000000000002</v>
       </c>
-      <c r="M21" s="99">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="134">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="140">
-        <v>91</v>
-      </c>
-      <c r="Q21" s="136">
-        <f t="shared" si="3"/>
+      <c r="N21" s="99">
+        <f>F21*($J21/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="130">
+        <f>H21*($J21/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="132">
+        <f>M21/M$44*100</f>
         <v>0.13063835499034929</v>
       </c>
       <c r="R21" s="98">
-        <f t="shared" si="4"/>
+        <f>N21/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S21" s="98">
-        <f t="shared" si="5"/>
+        <f>O21/O$44*100</f>
         <v>0</v>
       </c>
       <c r="T21" s="102">
-        <f t="shared" si="6"/>
+        <f>O21/O$44*100</f>
         <v>0</v>
       </c>
       <c r="U21" s="98"/>
-      <c r="V21" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>214</v>
       </c>
@@ -10422,43 +10464,43 @@
         <f t="shared" si="2"/>
         <v>6.444053895723491E-3</v>
       </c>
-      <c r="K22" t="s">
+      <c r="J22" s="136">
+        <v>87</v>
+      </c>
+      <c r="L22" t="s">
         <v>214</v>
       </c>
-      <c r="L22" s="97">
-        <f>(D22+D39)*($O22/100)</f>
+      <c r="M22" s="97">
+        <f>D22*($J22/100)+D39*($J39/100)</f>
         <v>34.713000000000001</v>
       </c>
-      <c r="M22" s="99">
-        <f>(F22+F39)*($O22/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="134">
-        <f>(H22+H39)*($O22/100)</f>
+      <c r="N22" s="99">
+        <f>F22*($J22/100)+F39*($J39/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="130">
+        <f>H22*($J22/100)+H39*($J39/100)</f>
         <v>18.443999999999999</v>
       </c>
-      <c r="O22" s="140">
-        <v>87</v>
-      </c>
-      <c r="Q22" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q22" s="132">
+        <f>M22/M$44*100</f>
         <v>3.1145942422939523</v>
       </c>
       <c r="R22" s="98">
-        <f t="shared" si="4"/>
+        <f>N22/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S22" s="98">
-        <f t="shared" si="5"/>
-        <v>5.7718576563015853</v>
+        <f>O22/O$44*100</f>
+        <v>8.277704323848349</v>
       </c>
       <c r="T22" s="102">
-        <f t="shared" si="6"/>
-        <v>5.7718576563015853</v>
+        <f>O22/O$44*100</f>
+        <v>8.277704323848349</v>
       </c>
       <c r="U22" s="98"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="87" t="s">
         <v>215</v>
       </c>
@@ -10489,43 +10531,43 @@
         <f t="shared" si="2"/>
         <v>4.2960359304823276E-3</v>
       </c>
-      <c r="K23" t="s">
+      <c r="J23" s="136">
+        <v>88</v>
+      </c>
+      <c r="L23" t="s">
         <v>216</v>
       </c>
-      <c r="L23" s="97">
-        <f>(D23)*($O23/100)</f>
+      <c r="M23" s="97">
+        <f>D23*($J23/100)</f>
         <v>26.135999999999999</v>
       </c>
-      <c r="M23" s="99">
-        <f>(F23)*($O23/100)</f>
+      <c r="N23" s="99">
+        <f>F23*($J23/100)</f>
         <v>0.44</v>
       </c>
-      <c r="N23" s="134">
-        <f>(H23)*($O23/100)</f>
+      <c r="O23" s="130">
+        <f>H23*($J23/100)</f>
         <v>1.9360000000000002</v>
       </c>
-      <c r="O23" s="140">
-        <v>88</v>
-      </c>
-      <c r="Q23" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q23" s="132">
+        <f>M23/M$44*100</f>
         <v>2.3450302513926982</v>
       </c>
       <c r="R23" s="98">
-        <f t="shared" si="4"/>
+        <f>N23/N$44*100</f>
         <v>1.2823203002960992</v>
       </c>
       <c r="S23" s="98">
-        <f t="shared" si="5"/>
-        <v>0.60585103137062835</v>
+        <f>O23/O$44*100</f>
+        <v>0.86888069675614876</v>
       </c>
       <c r="T23" s="102">
-        <f t="shared" si="6"/>
-        <v>0.60585103137062835</v>
+        <f>O23/O$44*100</f>
+        <v>0.86888069675614876</v>
       </c>
       <c r="U23" s="98"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>225</v>
       </c>
@@ -10553,43 +10595,43 @@
         <f t="shared" si="2"/>
         <v>7.810974419058778E-4</v>
       </c>
-      <c r="K24" t="s">
+      <c r="J24" s="136">
+        <v>90</v>
+      </c>
+      <c r="L24" t="s">
         <v>225</v>
       </c>
-      <c r="L24" s="97">
-        <f>(D24+D37)*($O24/100)</f>
+      <c r="M24" s="97">
+        <f>D24*($J24/100)</f>
         <v>1.53</v>
       </c>
-      <c r="M24" s="99">
-        <f>(F24+F37)*($O24/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="134">
-        <f>(H24+H37)*($O24/100)</f>
-        <v>108.54</v>
-      </c>
-      <c r="O24" s="140">
-        <v>90</v>
-      </c>
-      <c r="Q24" s="136">
-        <f t="shared" si="3"/>
+      <c r="N24" s="99">
+        <f>F24*($J24/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="130">
+        <f>H24*($J24/100)</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="Q24" s="132">
+        <f>M24/M$44*100</f>
         <v>0.13727794171375987</v>
       </c>
       <c r="R24" s="98">
-        <f t="shared" si="4"/>
+        <f>N24/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S24" s="98">
-        <f t="shared" si="5"/>
-        <v>33.966462264962807</v>
+        <f>O24/O$44*100</f>
+        <v>0.16156872460341609</v>
       </c>
       <c r="T24" s="102">
-        <f t="shared" si="6"/>
-        <v>33.966462264962807</v>
+        <f>O24/O$44*100</f>
+        <v>0.16156872460341609</v>
       </c>
       <c r="U24" s="98"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>226</v>
       </c>
@@ -10617,46 +10659,43 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K25" t="s">
+      <c r="J25" s="136">
+        <v>11</v>
+      </c>
+      <c r="L25" t="s">
         <v>226</v>
       </c>
-      <c r="L25" s="97">
-        <f>(D25)*($O25/100)</f>
+      <c r="M25" s="97">
+        <f>D25*($J25/100)+D37*($J37/100)</f>
         <v>6.6440000000000001</v>
       </c>
-      <c r="M25" s="99">
-        <f>(F25)*($O25/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N25" s="134">
-        <f>(H25)*($O25/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O25" s="140">
-        <v>11</v>
-      </c>
-      <c r="Q25" s="136">
-        <f t="shared" si="3"/>
+      <c r="N25" s="99">
+        <f>F25*($J25/100)+F37*($J37/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O25" s="130">
+        <f>H25*($J25/100)+H37*($J37/100)</f>
+        <v>10.4574</v>
+      </c>
+      <c r="Q25" s="132">
+        <f>M25/M$44*100</f>
         <v>0.59612721878837949</v>
       </c>
       <c r="R25" s="98">
-        <f t="shared" si="4"/>
+        <f>N25/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S25" s="98">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f>O25/O$44*100</f>
+        <v>4.6933021685215648</v>
       </c>
       <c r="T25" s="102">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f>O25/O$44*100</f>
+        <v>4.6933021685215648</v>
       </c>
       <c r="U25" s="98"/>
-      <c r="V25" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>211</v>
       </c>
@@ -10684,46 +10723,43 @@
         <f t="shared" si="2"/>
         <v>5.8582308142940832E-4</v>
       </c>
-      <c r="K26" t="s">
+      <c r="J26" s="136">
+        <v>76</v>
+      </c>
+      <c r="L26" t="s">
         <v>211</v>
       </c>
-      <c r="L26" s="97">
-        <f>(D26)*($O26/100)</f>
+      <c r="M26" s="97">
+        <f>D26*($J26/100)</f>
         <v>3.9520000000000004</v>
       </c>
-      <c r="M26" s="99">
-        <f>(F26)*($O26/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="134">
-        <f>(H26)*($O26/100)</f>
+      <c r="N26" s="99">
+        <f>F26*($J26/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O26" s="130">
+        <f>H26*($J26/100)</f>
         <v>0.22799999999999998</v>
       </c>
-      <c r="O26" s="140">
-        <v>76</v>
-      </c>
-      <c r="Q26" s="136">
-        <f t="shared" si="3"/>
+      <c r="Q26" s="132">
+        <f>M26/M$44*100</f>
         <v>0.35458982068809092</v>
       </c>
       <c r="R26" s="98">
-        <f t="shared" si="4"/>
+        <f>N26/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S26" s="98">
-        <f t="shared" si="5"/>
-        <v>7.1350224768854983E-2</v>
+        <f>O26/O$44*100</f>
+        <v>0.10232685891549684</v>
       </c>
       <c r="T26" s="102">
-        <f t="shared" si="6"/>
-        <v>7.1350224768854983E-2</v>
+        <f>O26/O$44*100</f>
+        <v>0.10232685891549684</v>
       </c>
       <c r="U26" s="98"/>
-      <c r="V26" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>212</v>
       </c>
@@ -10751,43 +10787,43 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K27" t="s">
+      <c r="J27" s="136">
+        <v>89</v>
+      </c>
+      <c r="L27" t="s">
         <v>212</v>
       </c>
-      <c r="L27" s="97">
-        <f>(D27)*($O27/100)</f>
+      <c r="M27" s="97">
+        <f>D27*($J27/100)</f>
         <v>7.7429999999999994</v>
       </c>
-      <c r="M27" s="99">
-        <f>(F27)*($O27/100)</f>
-        <v>0</v>
-      </c>
-      <c r="N27" s="134">
-        <f>(H27)*($O27/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O27" s="140">
-        <v>89</v>
-      </c>
-      <c r="Q27" s="136">
-        <f t="shared" si="3"/>
+      <c r="N27" s="99">
+        <f>F27*($J27/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="130">
+        <f>H27*($J27/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="132">
+        <f>M27/M$44*100</f>
         <v>0.69473405404551813</v>
       </c>
       <c r="R27" s="98">
-        <f t="shared" si="4"/>
+        <f>N27/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S27" s="98">
-        <f t="shared" si="5"/>
+        <f>O27/O$44*100</f>
         <v>0</v>
       </c>
       <c r="T27" s="102">
-        <f t="shared" si="6"/>
+        <f>O27/O$44*100</f>
         <v>0</v>
       </c>
       <c r="U27" s="98"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>227</v>
       </c>
@@ -10815,45 +10851,45 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K28" t="s">
+      <c r="J28" s="136">
+        <v>6.3</v>
+      </c>
+      <c r="L28" t="s">
         <v>227</v>
       </c>
-      <c r="L28" s="97">
-        <f>(D28+D38)*($O28/100)</f>
+      <c r="M28" s="97">
+        <f>D28*($J28/100)+D38*($J38/100)</f>
         <v>11.869200000000001</v>
       </c>
-      <c r="M28" s="99">
-        <f>(F28+F38)*($O28/100)</f>
+      <c r="N28" s="99">
+        <f>F28*($J28/100)+F38*($J38/100)</f>
         <v>0.6048</v>
       </c>
-      <c r="N28" s="134">
-        <f>(H28+H38)*($O28/100)</f>
-        <v>7.8434999999999997</v>
-      </c>
-      <c r="O28" s="140">
-        <v>6.3</v>
-      </c>
-      <c r="Q28" s="136">
-        <f t="shared" si="3"/>
+      <c r="O28" s="130">
+        <f>H28*($J28/100)+H38*($J38/100)</f>
+        <v>9.7110000000000003</v>
+      </c>
+      <c r="Q28" s="132">
+        <f>M28/M$44*100</f>
         <v>1.0649538207770974</v>
       </c>
       <c r="R28" s="98">
-        <f t="shared" si="4"/>
+        <f>N28/N$44*100</f>
         <v>1.7626075400433656</v>
       </c>
       <c r="S28" s="98">
-        <f t="shared" si="5"/>
-        <v>2.4545416139233072</v>
+        <f>O28/O$44*100</f>
+        <v>4.3583163461771495</v>
       </c>
       <c r="T28" s="102">
-        <f t="shared" si="6"/>
-        <v>2.4545416139233072</v>
+        <f>O28/O$44*100</f>
+        <v>4.3583163461771495</v>
       </c>
       <c r="U28" s="98"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C29" s="109" t="s">
         <v>193</v>
@@ -10879,46 +10915,43 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K29" t="s">
-        <v>241</v>
-      </c>
-      <c r="L29" s="97">
-        <f>(D29)*($O29/100)</f>
-        <v>0</v>
-      </c>
-      <c r="M29" s="99">
-        <f>(F29)*($O29/100)</f>
+      <c r="J29" s="136">
+        <v>97</v>
+      </c>
+      <c r="L29" t="s">
+        <v>231</v>
+      </c>
+      <c r="M29" s="97">
+        <f>D29*($J29/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="99">
+        <f>F29*($J29/100)</f>
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="N29" s="134">
-        <f>(H29)*($O29/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O29" s="140">
-        <v>97</v>
-      </c>
-      <c r="Q29" s="136">
-        <f t="shared" si="3"/>
+      <c r="O29" s="130">
+        <f>H29*($J29/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="132">
+        <f>M29/M$44*100</f>
         <v>0</v>
       </c>
       <c r="R29" s="98">
-        <f t="shared" si="4"/>
+        <f>N29/N$44*100</f>
         <v>0.2826933389289128</v>
       </c>
       <c r="S29" s="98">
-        <f t="shared" si="5"/>
+        <f>O29/O$44*100</f>
         <v>0</v>
       </c>
       <c r="T29" s="102">
-        <f t="shared" si="6"/>
+        <f>O29/O$44*100</f>
         <v>0</v>
       </c>
       <c r="U29" s="98"/>
-      <c r="V29" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>223</v>
       </c>
@@ -10946,43 +10979,43 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K30" t="s">
+      <c r="J30" s="136">
+        <v>92</v>
+      </c>
+      <c r="L30" t="s">
         <v>223</v>
       </c>
-      <c r="L30" s="97">
-        <f>(D30)*($O30/100)</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="99">
-        <f>(F30)*($O30/100)</f>
+      <c r="M30" s="97">
+        <f>D30*($J30/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="99">
+        <f>F30*($J30/100)</f>
         <v>0.46</v>
       </c>
-      <c r="N30" s="134">
-        <f>(H30)*($O30/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O30" s="140">
-        <v>92</v>
-      </c>
-      <c r="Q30" s="136">
-        <f t="shared" si="3"/>
+      <c r="O30" s="130">
+        <f>H30*($J30/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="132">
+        <f>M30/M$44*100</f>
         <v>0</v>
       </c>
       <c r="R30" s="98">
-        <f t="shared" si="4"/>
+        <f>N30/N$44*100</f>
         <v>1.3406075866731948</v>
       </c>
       <c r="S30" s="98">
-        <f t="shared" si="5"/>
+        <f>O30/O$44*100</f>
         <v>0</v>
       </c>
       <c r="T30" s="102">
-        <f t="shared" si="6"/>
+        <f>O30/O$44*100</f>
         <v>0</v>
       </c>
       <c r="U30" s="98"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>224</v>
       </c>
@@ -11010,48 +11043,45 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K31" t="s">
+      <c r="J31" s="136">
+        <v>92</v>
+      </c>
+      <c r="L31" t="s">
         <v>224</v>
       </c>
-      <c r="L31" s="97">
-        <f>(D31)*($O31/100)</f>
+      <c r="M31" s="97">
+        <f>D31*($J31/100)</f>
         <v>2.0240000000000005</v>
       </c>
-      <c r="M31" s="99">
-        <f>(F31)*($O31/100)</f>
+      <c r="N31" s="99">
+        <f>F31*($J31/100)</f>
         <v>1.1040000000000001</v>
       </c>
-      <c r="N31" s="134">
-        <f>(H31)*($O31/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O31" s="140">
-        <v>92</v>
-      </c>
-      <c r="Q31" s="136">
-        <f t="shared" si="3"/>
+      <c r="O31" s="130">
+        <f>H31*($J31/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="132">
+        <f>M31/M$44*100</f>
         <v>0.18160166929977128</v>
       </c>
       <c r="R31" s="98">
-        <f t="shared" si="4"/>
+        <f>N31/N$44*100</f>
         <v>3.2174582080156675</v>
       </c>
       <c r="S31" s="98">
-        <f t="shared" si="5"/>
+        <f>O31/O$44*100</f>
         <v>0</v>
       </c>
       <c r="T31" s="102">
-        <f t="shared" si="6"/>
+        <f>O31/O$44*100</f>
         <v>0</v>
       </c>
       <c r="U31" s="98"/>
-      <c r="V31" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C32" s="109" t="s">
         <v>197</v>
@@ -11077,144 +11107,136 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K32" t="s">
-        <v>246</v>
-      </c>
-      <c r="L32" s="97">
-        <f>(D32)*($O32/100)</f>
+      <c r="J32" s="136">
+        <v>100</v>
+      </c>
+      <c r="L32" t="s">
+        <v>236</v>
+      </c>
+      <c r="M32" s="97">
+        <f>D32*($J32/100)</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="M32" s="99">
-        <f>(F32)*($O32/100)</f>
+      <c r="N32" s="99">
+        <f>F32*($J32/100)</f>
         <v>0.5</v>
       </c>
-      <c r="N32" s="134">
-        <f>(H32)*($O32/100)</f>
-        <v>0</v>
-      </c>
-      <c r="O32" s="140">
-        <v>100</v>
-      </c>
-      <c r="Q32" s="136">
-        <f t="shared" si="3"/>
+      <c r="O32" s="130">
+        <f>H32*($J32/100)</f>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="132">
+        <f>M32/M$44*100</f>
         <v>0.20636553329519458</v>
       </c>
       <c r="R32" s="98">
-        <f t="shared" si="4"/>
+        <f>N32/N$44*100</f>
         <v>1.4571821594273857</v>
       </c>
       <c r="S32" s="98">
-        <f t="shared" si="5"/>
+        <f>O32/O$44*100</f>
         <v>0</v>
       </c>
       <c r="T32" s="102">
-        <f t="shared" si="6"/>
+        <f>O32/O$44*100</f>
         <v>0</v>
       </c>
       <c r="U32" s="98"/>
-      <c r="V32" t="s">
-        <v>238</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>239</v>
-      </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B33" s="87" t="s">
-        <v>253</v>
-      </c>
-      <c r="C33" s="101" t="s">
+        <v>243</v>
+      </c>
+      <c r="C33" s="156" t="s">
         <v>172</v>
       </c>
-      <c r="D33" s="78">
+      <c r="D33" s="157">
         <v>62.6</v>
       </c>
-      <c r="E33" s="110">
+      <c r="E33" s="158">
         <f t="shared" si="0"/>
         <v>3.8430842900116641E-2</v>
       </c>
-      <c r="F33" s="78">
+      <c r="F33" s="157">
         <v>1.8</v>
       </c>
-      <c r="G33" s="110">
+      <c r="G33" s="158">
         <f t="shared" si="1"/>
         <v>3.272727272727273E-2</v>
       </c>
-      <c r="H33" s="78">
+      <c r="H33" s="157">
         <v>11</v>
       </c>
-      <c r="I33" s="111">
+      <c r="I33" s="159">
         <f t="shared" si="2"/>
         <v>2.1480179652411637E-2</v>
       </c>
-      <c r="K33" t="s">
+      <c r="J33" s="136"/>
+      <c r="L33" t="s">
         <v>229</v>
       </c>
-      <c r="L33" s="101">
-        <f>D41</f>
-        <v>0</v>
-      </c>
-      <c r="M33" s="78">
-        <f>F41</f>
-        <v>0</v>
-      </c>
-      <c r="N33" s="100">
-        <f>H41</f>
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="O33" s="140">
-        <v>91</v>
-      </c>
-      <c r="Q33" s="136">
-        <f t="shared" si="3"/>
+      <c r="M33" s="101">
+        <f>D41*($J41/100)</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="78">
+        <f>F41*($J41/100)</f>
+        <v>0</v>
+      </c>
+      <c r="O33" s="100">
+        <f>H41*($J41/100)</f>
+        <v>7.9200000000000008</v>
+      </c>
+      <c r="Q33" s="132">
+        <f>M33/M$44*100</f>
         <v>0</v>
       </c>
       <c r="R33" s="98">
-        <f t="shared" si="4"/>
+        <f>N33/N$44*100</f>
         <v>0</v>
       </c>
       <c r="S33" s="98">
-        <f t="shared" si="5"/>
-        <v>2.7538683244119473</v>
+        <f>O33/O$44*100</f>
+        <v>3.554511941275154</v>
       </c>
       <c r="T33" s="102">
-        <f t="shared" si="6"/>
-        <v>2.7538683244119473</v>
+        <f>O33/O$44*100</f>
+        <v>3.554511941275154</v>
       </c>
       <c r="U33" s="98"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B34" s="87" t="s">
-        <v>253</v>
-      </c>
-      <c r="C34" s="101" t="s">
+        <v>243</v>
+      </c>
+      <c r="C34" s="156" t="s">
         <v>186</v>
       </c>
-      <c r="D34" s="78">
+      <c r="D34" s="157">
         <v>5.8</v>
       </c>
-      <c r="E34" s="110">
+      <c r="E34" s="158">
         <f t="shared" si="0"/>
         <v>3.5606851249309346E-3</v>
       </c>
-      <c r="F34" s="78">
+      <c r="F34" s="157">
         <v>0.2</v>
       </c>
-      <c r="G34" s="110">
+      <c r="G34" s="158">
         <f t="shared" si="1"/>
         <v>3.6363636363636364E-3</v>
       </c>
-      <c r="H34" s="78">
+      <c r="H34" s="157">
         <v>1.4</v>
       </c>
-      <c r="I34" s="111">
+      <c r="I34" s="159">
         <f t="shared" si="2"/>
         <v>2.7338410466705718E-3</v>
       </c>
-      <c r="L34" s="101"/>
-      <c r="M34" s="78"/>
-      <c r="N34" s="100"/>
-      <c r="O34" s="140"/>
+      <c r="J34" s="136"/>
+      <c r="M34" s="101"/>
+      <c r="N34" s="78"/>
+      <c r="O34" s="100"/>
       <c r="Q34" s="101"/>
       <c r="R34" s="78"/>
       <c r="S34" s="78"/>
@@ -11223,36 +11245,36 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B35" s="87" t="s">
-        <v>253</v>
-      </c>
-      <c r="C35" s="101" t="s">
+        <v>243</v>
+      </c>
+      <c r="C35" s="156" t="s">
         <v>201</v>
       </c>
-      <c r="D35" s="78">
+      <c r="D35" s="157">
         <v>43.3</v>
       </c>
-      <c r="E35" s="110">
+      <c r="E35" s="158">
         <f t="shared" si="0"/>
         <v>2.6582356191294735E-2</v>
       </c>
-      <c r="F35" s="78">
+      <c r="F35" s="157">
         <v>4.5</v>
       </c>
-      <c r="G35" s="110">
+      <c r="G35" s="158">
         <f t="shared" si="1"/>
         <v>8.1818181818181818E-2</v>
       </c>
-      <c r="H35" s="78">
-        <v>0</v>
-      </c>
-      <c r="I35" s="111">
+      <c r="H35" s="157">
+        <v>0</v>
+      </c>
+      <c r="I35" s="159">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L35" s="101"/>
-      <c r="M35" s="78"/>
-      <c r="N35" s="100"/>
-      <c r="O35" s="140"/>
+      <c r="J35" s="136"/>
+      <c r="M35" s="101"/>
+      <c r="N35" s="78"/>
+      <c r="O35" s="100"/>
       <c r="Q35" s="101"/>
       <c r="R35" s="78"/>
       <c r="S35" s="78"/>
@@ -11287,10 +11309,12 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L36" s="101"/>
-      <c r="M36" s="78"/>
-      <c r="N36" s="100"/>
-      <c r="O36" s="140"/>
+      <c r="J36" s="136">
+        <v>86</v>
+      </c>
+      <c r="M36" s="101"/>
+      <c r="N36" s="78"/>
+      <c r="O36" s="100"/>
       <c r="Q36" s="101"/>
       <c r="R36" s="78"/>
       <c r="S36" s="78"/>
@@ -11302,34 +11326,36 @@
       <c r="B37" t="s">
         <v>226</v>
       </c>
-      <c r="C37" s="118" t="s">
+      <c r="C37" s="117" t="s">
         <v>202</v>
       </c>
-      <c r="D37" s="119">
-        <v>0</v>
-      </c>
-      <c r="E37" s="120">
+      <c r="D37" s="118">
+        <v>0</v>
+      </c>
+      <c r="E37" s="119">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F37" s="119">
-        <v>0</v>
-      </c>
-      <c r="G37" s="120">
+      <c r="F37" s="118">
+        <v>0</v>
+      </c>
+      <c r="G37" s="119">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H37" s="119">
+      <c r="H37" s="118">
         <v>120.2</v>
       </c>
-      <c r="I37" s="121">
+      <c r="I37" s="120">
         <f t="shared" si="2"/>
         <v>0.23471978129271626</v>
       </c>
-      <c r="L37" s="101"/>
-      <c r="M37" s="78"/>
-      <c r="N37" s="100"/>
-      <c r="O37" s="140"/>
+      <c r="J37" s="136">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="M37" s="101"/>
+      <c r="N37" s="78"/>
+      <c r="O37" s="100"/>
       <c r="Q37" s="101"/>
       <c r="R37" s="78"/>
       <c r="S37" s="78"/>
@@ -11364,10 +11390,12 @@
         <f t="shared" si="2"/>
         <v>0.24311657879320445</v>
       </c>
-      <c r="L38" s="101"/>
-      <c r="M38" s="78"/>
-      <c r="N38" s="100"/>
-      <c r="O38" s="140"/>
+      <c r="J38" s="136">
+        <v>7.8</v>
+      </c>
+      <c r="M38" s="101"/>
+      <c r="N38" s="78"/>
+      <c r="O38" s="100"/>
       <c r="Q38" s="101"/>
       <c r="R38" s="78"/>
       <c r="S38" s="78"/>
@@ -11402,10 +11430,12 @@
         <f t="shared" si="2"/>
         <v>3.4954110525288025E-2</v>
       </c>
-      <c r="L39" s="101"/>
-      <c r="M39" s="78"/>
-      <c r="N39" s="100"/>
-      <c r="O39" s="140"/>
+      <c r="J39" s="136">
+        <v>87</v>
+      </c>
+      <c r="M39" s="101"/>
+      <c r="N39" s="78"/>
+      <c r="O39" s="100"/>
       <c r="Q39" s="101"/>
       <c r="R39" s="78"/>
       <c r="S39" s="78"/>
@@ -11414,36 +11444,38 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B40" s="87" t="s">
-        <v>253</v>
-      </c>
-      <c r="C40" s="112" t="s">
+        <v>243</v>
+      </c>
+      <c r="C40" s="160" t="s">
         <v>205</v>
       </c>
-      <c r="D40" s="78">
-        <v>0</v>
-      </c>
-      <c r="E40" s="110">
+      <c r="D40" s="157">
+        <v>0</v>
+      </c>
+      <c r="E40" s="158">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F40" s="78">
-        <v>0</v>
-      </c>
-      <c r="G40" s="110">
+      <c r="F40" s="157">
+        <v>0</v>
+      </c>
+      <c r="G40" s="158">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H40" s="78">
+      <c r="H40" s="157">
         <v>15.7</v>
       </c>
-      <c r="I40" s="111">
+      <c r="I40" s="159">
         <f t="shared" si="2"/>
         <v>3.0658074594805698E-2</v>
       </c>
-      <c r="L40" s="101"/>
-      <c r="M40" s="78"/>
-      <c r="N40" s="100"/>
-      <c r="O40" s="140"/>
+      <c r="J40" s="136">
+        <v>91</v>
+      </c>
+      <c r="M40" s="101"/>
+      <c r="N40" s="78"/>
+      <c r="O40" s="100"/>
       <c r="Q40" s="101"/>
       <c r="R40" s="78"/>
       <c r="S40" s="78"/>
@@ -11478,10 +11510,12 @@
         <f t="shared" si="2"/>
         <v>1.718414372192931E-2</v>
       </c>
-      <c r="L41" s="101"/>
-      <c r="M41" s="78"/>
-      <c r="N41" s="100"/>
-      <c r="O41" s="140"/>
+      <c r="J41" s="136">
+        <v>90</v>
+      </c>
+      <c r="M41" s="101"/>
+      <c r="N41" s="78"/>
+      <c r="O41" s="100"/>
       <c r="Q41" s="101"/>
       <c r="R41" s="78"/>
       <c r="S41" s="78"/>
@@ -11490,36 +11524,36 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B42" s="87" t="s">
-        <v>253</v>
-      </c>
-      <c r="C42" s="122" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="161" t="s">
         <v>207</v>
       </c>
-      <c r="D42" s="76">
-        <v>0</v>
-      </c>
-      <c r="E42" s="123">
+      <c r="D42" s="162">
+        <v>0</v>
+      </c>
+      <c r="E42" s="163">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F42" s="76">
-        <v>0</v>
-      </c>
-      <c r="G42" s="123">
+      <c r="F42" s="162">
+        <v>0</v>
+      </c>
+      <c r="G42" s="163">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H42" s="76">
+      <c r="H42" s="162">
         <v>4.7</v>
       </c>
-      <c r="I42" s="124">
+      <c r="I42" s="164">
         <f t="shared" si="2"/>
         <v>9.1778949423940628E-3</v>
       </c>
-      <c r="L42" s="101"/>
-      <c r="M42" s="78"/>
-      <c r="N42" s="100"/>
-      <c r="O42" s="140"/>
+      <c r="J42" s="136"/>
+      <c r="M42" s="101"/>
+      <c r="N42" s="78"/>
+      <c r="O42" s="100"/>
       <c r="Q42" s="101"/>
       <c r="R42" s="78"/>
       <c r="S42" s="78"/>
@@ -11527,7 +11561,7 @@
       <c r="U42" s="78"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C43" s="125" t="s">
+      <c r="C43" s="121" t="s">
         <v>198</v>
       </c>
       <c r="D43" s="77">
@@ -11541,11 +11575,11 @@
       <c r="H43" s="77">
         <v>330.2</v>
       </c>
-      <c r="I43" s="126"/>
-      <c r="L43" s="101"/>
-      <c r="M43" s="78"/>
-      <c r="N43" s="100"/>
-      <c r="O43" s="140"/>
+      <c r="I43" s="122"/>
+      <c r="J43" s="136"/>
+      <c r="M43" s="101"/>
+      <c r="N43" s="78"/>
+      <c r="O43" s="100"/>
       <c r="Q43" s="101"/>
       <c r="R43" s="78"/>
       <c r="S43" s="78"/>
@@ -11556,114 +11590,139 @@
       <c r="C44" s="107" t="s">
         <v>208</v>
       </c>
-      <c r="D44" s="113">
+      <c r="D44" s="112">
         <v>4375.1000000000004</v>
       </c>
-      <c r="E44" s="113"/>
-      <c r="F44" s="113">
+      <c r="E44" s="112"/>
+      <c r="F44" s="112">
         <v>134.9</v>
       </c>
-      <c r="G44" s="113"/>
-      <c r="H44" s="113">
+      <c r="G44" s="112"/>
+      <c r="H44" s="112">
         <v>842.3</v>
       </c>
-      <c r="I44" s="114"/>
-      <c r="K44" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="L44" s="127">
-        <f>SUM(L8:L43)</f>
+      <c r="I44" s="113"/>
+      <c r="J44" s="136"/>
+      <c r="L44" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="M44" s="123">
+        <f>SUM(M8:M43)</f>
         <v>1114.5272</v>
       </c>
-      <c r="M44" s="137">
-        <f>SUM(M8:M43)</f>
+      <c r="N44" s="133">
+        <f>SUM(N8:N43)</f>
         <v>34.312800000000003</v>
       </c>
-      <c r="N44" s="128">
-        <f>SUM(N8:N43)</f>
-        <v>319.55050000000006</v>
-      </c>
-      <c r="O44" s="140"/>
-      <c r="Q44" s="127">
+      <c r="O44" s="124">
+        <f>SUM(O8:O43)</f>
+        <v>222.81540000000004</v>
+      </c>
+      <c r="Q44" s="123">
         <f>SUM(Q8:Q43)</f>
         <v>100</v>
       </c>
-      <c r="R44" s="137">
-        <f t="shared" ref="R44:T44" si="10">SUM(R8:R43)</f>
+      <c r="R44" s="133">
+        <f t="shared" ref="R44:T44" si="3">SUM(R8:R43)</f>
         <v>100</v>
       </c>
-      <c r="S44" s="137">
-        <f t="shared" si="10"/>
-        <v>99.999999999999986</v>
-      </c>
-      <c r="T44" s="128">
-        <f t="shared" si="10"/>
-        <v>99.999999999999986</v>
-      </c>
-      <c r="U44" s="133"/>
+      <c r="S44" s="133">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="T44" s="124">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="U44" s="129"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C45" s="115" t="s">
+      <c r="C45" s="114" t="s">
         <v>228</v>
       </c>
-      <c r="D45" s="116">
+      <c r="D45" s="115">
         <f>SUM(D8:D42)</f>
         <v>1628.9</v>
       </c>
-      <c r="E45" s="116"/>
-      <c r="F45" s="116">
+      <c r="E45" s="115"/>
+      <c r="F45" s="115">
         <f>SUM(F8:F42)</f>
         <v>55</v>
       </c>
-      <c r="G45" s="116"/>
-      <c r="H45" s="116">
+      <c r="G45" s="115"/>
+      <c r="H45" s="115">
         <f>SUM(H8:H42)</f>
         <v>512.1</v>
       </c>
-      <c r="I45" s="117"/>
+      <c r="I45" s="116"/>
+      <c r="J45" s="136"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="K46" s="103"/>
-      <c r="L46" s="87"/>
+      <c r="L46" s="103"/>
       <c r="M46" s="87"/>
       <c r="N46" s="87"/>
+      <c r="O46" s="87"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C47" s="141" t="s">
-        <v>251</v>
-      </c>
-      <c r="K47" s="103"/>
-      <c r="L47" s="87"/>
+      <c r="C47" s="137" t="s">
+        <v>241</v>
+      </c>
+      <c r="L47" s="103"/>
       <c r="M47" s="87"/>
       <c r="N47" s="87"/>
+      <c r="O47" s="87"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C48" s="141" t="s">
-        <v>252</v>
-      </c>
-      <c r="K48" s="103"/>
-      <c r="L48" s="87"/>
+      <c r="C48" s="137" t="s">
+        <v>242</v>
+      </c>
+      <c r="L48" s="103"/>
       <c r="M48" s="87"/>
       <c r="N48" s="87"/>
-    </row>
-    <row r="49" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K49" s="87"/>
+      <c r="O48" s="87"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.25">
       <c r="L49" s="87"/>
       <c r="M49" s="87"/>
       <c r="N49" s="87"/>
-    </row>
-    <row r="50" spans="11:14" x14ac:dyDescent="0.25">
-      <c r="K50" s="103"/>
-      <c r="L50" s="87"/>
+      <c r="O49" s="87"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="L50" s="103"/>
       <c r="M50" s="87"/>
       <c r="N50" s="87"/>
+      <c r="O50" s="87"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C51" s="150" t="s">
+        <v>245</v>
+      </c>
+      <c r="D51" s="118"/>
+      <c r="E51" s="118"/>
+      <c r="F51" s="118"/>
+      <c r="G51" s="118"/>
+      <c r="H51" s="118"/>
+      <c r="I51" s="151"/>
+      <c r="J51" s="78"/>
+    </row>
+    <row r="52" spans="3:15" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C52" s="152" t="s">
+        <v>244</v>
+      </c>
+      <c r="D52" s="153"/>
+      <c r="E52" s="153"/>
+      <c r="F52" s="153"/>
+      <c r="G52" s="153"/>
+      <c r="H52" s="153"/>
+      <c r="I52" s="154"/>
+      <c r="J52" s="155"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="V7" r:id="rId1"/>
-  </hyperlinks>
+  <mergeCells count="1">
+    <mergeCell ref="C52:I52"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13915,19 +13974,19 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B23" s="40"/>
-      <c r="C23" s="148" t="s">
+      <c r="C23" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="150" t="s">
+      <c r="D23" s="146" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="143" t="s">
+      <c r="E23" s="139" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="145" t="s">
+      <c r="F23" s="141" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="147"/>
+      <c r="G23" s="143"/>
       <c r="H23" s="31"/>
       <c r="O23">
         <v>11</v>
@@ -13949,11 +14008,11 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B24" s="41"/>
-      <c r="C24" s="149"/>
-      <c r="D24" s="151"/>
-      <c r="E24" s="144"/>
-      <c r="F24" s="146"/>
-      <c r="G24" s="147"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="142"/>
+      <c r="G24" s="143"/>
       <c r="H24" s="18"/>
       <c r="O24">
         <v>13</v>
@@ -13974,13 +14033,13 @@
       </c>
     </row>
     <row r="25" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="153" t="s">
+      <c r="B25" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="153"/>
+      <c r="C25" s="149"/>
+      <c r="D25" s="149"/>
+      <c r="E25" s="149"/>
+      <c r="F25" s="149"/>
       <c r="G25" s="42"/>
       <c r="H25" s="18"/>
       <c r="O25">
@@ -14002,13 +14061,13 @@
       </c>
     </row>
     <row r="26" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="142" t="s">
+      <c r="B26" s="138" t="s">
         <v>93</v>
       </c>
-      <c r="C26" s="142"/>
-      <c r="D26" s="142"/>
-      <c r="E26" s="142"/>
-      <c r="F26" s="142"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
       <c r="G26" s="42"/>
       <c r="H26" s="18"/>
       <c r="O26">
@@ -14200,25 +14259,25 @@
       <c r="R33" s="3"/>
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="152" t="s">
+      <c r="B34" s="148" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="152"/>
-      <c r="D34" s="152"/>
-      <c r="E34" s="152"/>
-      <c r="F34" s="152"/>
+      <c r="C34" s="148"/>
+      <c r="D34" s="148"/>
+      <c r="E34" s="148"/>
+      <c r="F34" s="148"/>
       <c r="G34" s="42"/>
       <c r="H34" s="18"/>
       <c r="R34" s="13"/>
     </row>
     <row r="35" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="142" t="s">
+      <c r="B35" s="138" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="142"/>
-      <c r="D35" s="142"/>
-      <c r="E35" s="142"/>
-      <c r="F35" s="142"/>
+      <c r="C35" s="138"/>
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="138"/>
       <c r="G35" s="42"/>
       <c r="H35" s="18"/>
     </row>
